--- a/Firmware/Modules/CalLut/CalLut_Validation.xlsx
+++ b/Firmware/Modules/CalLut/CalLut_Validation.xlsx
@@ -591,7 +591,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q17"/>
+  <dimension ref="A1:Q18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -1800,12 +1800,95 @@
         </is>
       </c>
     </row>
+    <row r="18">
+      <c r="A18" s="7" t="inlineStr">
+        <is>
+          <t>CL-014</t>
+        </is>
+      </c>
+      <c r="B18" s="7" t="inlineStr">
+        <is>
+          <t>LUT_READ بازخوانی واقعی هر دو کانال</t>
+        </is>
+      </c>
+      <c r="C18" s="7" t="inlineStr">
+        <is>
+          <t>بالا</t>
+        </is>
+      </c>
+      <c r="D18" s="7" t="inlineStr">
+        <is>
+          <t>رکورد LUT فعال در فلش یا جدول تازه commit شده</t>
+        </is>
+      </c>
+      <c r="E18" s="7" t="inlineStr">
+        <is>
+          <t>از لینک ESP فرمان LUT_READ بفرست و payloadهای LUT_DATA کانال ۱ و ۲ را با آرایه‌های Active مقایسه کن؛ سپس بعد از reset تکرار کن</t>
+        </is>
+      </c>
+      <c r="F18" s="7" t="inlineStr">
+        <is>
+          <t>chainMa/powerMw نقاط فعال، به‌خصوص battery 2</t>
+        </is>
+      </c>
+      <c r="G18" s="7" t="inlineStr">
+        <is>
+          <t>یک درخواست قبل و یک درخواست بعد از reset</t>
+        </is>
+      </c>
+      <c r="H18" s="7" t="inlineStr">
+        <is>
+          <t>LUT_DATA مقدار واقعی هر نقطه را برمی‌گرداند؛ کانال غیرفعال فریم صفرنقطه‌ای می‌دهد؛ دادهٔ ناقص active فرض نمی‌شود</t>
+        </is>
+      </c>
+      <c r="I18" s="7" t="inlineStr">
+        <is>
+          <t>رکورد فلش باید بعد از reset همان نقاط را حفظ کند</t>
+        </is>
+      </c>
+      <c r="J18" s="7" t="inlineStr">
+        <is>
+          <t>تطبیق byte/point با func__CalLut_Points/ChainMa/PowerMw و گزارش mismatch در پنل</t>
+        </is>
+      </c>
+      <c r="K18" s="7" t="inlineStr">
+        <is>
+          <t>Host PASS: 144 check؛ شامل دو فریم واقعی LUT_DATA و آخرین نقطهٔ هر دو کانال؛ برد فیزیکی pending</t>
+        </is>
+      </c>
+      <c r="L18" s="7" t="inlineStr">
+        <is>
+          <t>در انتظار</t>
+        </is>
+      </c>
+      <c r="M18" s="7" t="inlineStr">
+        <is>
+          <t>Host جای اندازه‌گیری برد را نمی‌گیرد؛ فلش و readback روی برد واقعی لازم است</t>
+        </is>
+      </c>
+      <c r="N18" s="7" t="inlineStr">
+        <is>
+          <t>Firmware/Modules/CalLut/Tester/run_host_test_cal_lut.sh</t>
+        </is>
+      </c>
+      <c r="O18" s="7" t="inlineStr">
+        <is>
+          <t>WORKTREE</t>
+        </is>
+      </c>
+      <c r="P18" s="7" t="inlineStr"/>
+      <c r="Q18" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <dataValidations count="2">
-    <dataValidation sqref="L5:L17" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="L5:L18" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>='فهرست‌ها'!$A$2:$A$6</formula1>
     </dataValidation>
-    <dataValidation sqref="C5:C17" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="C5:C18" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>='فهرست‌ها'!$B$9:$B$11</formula1>
     </dataValidation>
   </dataValidations>

--- a/Firmware/Modules/CalLut/CalLut_Validation.xlsx
+++ b/Firmware/Modules/CalLut/CalLut_Validation.xlsx
@@ -591,7 +591,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q18"/>
+  <dimension ref="A1:Q19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -1853,7 +1853,7 @@
       </c>
       <c r="K18" s="7" t="inlineStr">
         <is>
-          <t>Host PASS: 144 check؛ شامل دو فریم واقعی LUT_DATA و آخرین نقطهٔ هر دو کانال؛ برد فیزیکی pending</t>
+          <t>Host PASS: 159 check؛ شامل دو فریم واقعی LUT_DATA، battery 2 مستقل و transition غیرصفر→صفر؛ برد فیزیکی pending</t>
         </is>
       </c>
       <c r="L18" s="7" t="inlineStr">
@@ -1878,6 +1878,89 @@
       </c>
       <c r="P18" s="7" t="inlineStr"/>
       <c r="Q18" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="7" t="inlineStr">
+        <is>
+          <t>CL-015</t>
+        </is>
+      </c>
+      <c r="B19" s="7" t="inlineStr">
+        <is>
+          <t>حذف override با صفرنقطه</t>
+        </is>
+      </c>
+      <c r="C19" s="7" t="inlineStr">
+        <is>
+          <t>بالا</t>
+        </is>
+      </c>
+      <c r="D19" s="7" t="inlineStr">
+        <is>
+          <t>CL-002 یا رکورد فعال با هر دو کانال</t>
+        </is>
+      </c>
+      <c r="E19" s="7" t="inlineStr">
+        <is>
+          <t>LUT_BEGIN با n1=5 و n2=0، CHUNK فقط کانال ۱، COMMIT با CRC درست؛ سپس reset و LUT_READ</t>
+        </is>
+      </c>
+      <c r="F19" s="7" t="inlineStr">
+        <is>
+          <t>کانال ۱ معتبر؛ کانال ۲ count=0؛ before کانال ۲ غیرصفر و after صفرنقطه‌ای</t>
+        </is>
+      </c>
+      <c r="G19" s="7" t="inlineStr">
+        <is>
+          <t>یک تبادل + یک بوت</t>
+        </is>
+      </c>
+      <c r="H19" s="7" t="inlineStr">
+        <is>
+          <t>commit پذیرفته؛ کانال ۱ حفظ می‌شود و override فلش کانال ۲ حذف می‌شود؛ LUT_DATA کانال ۲ فریم صفرنقطه‌ای مستقل می‌دهد</t>
+        </is>
+      </c>
+      <c r="I19" s="7" t="inlineStr">
+        <is>
+          <t>پینگ‌پنگ و پس از reset</t>
+        </is>
+      </c>
+      <c r="J19" s="7" t="inlineStr">
+        <is>
+          <t>status=0، Active کانال ۱ برقرار، Active کانال ۲=false و مقایسهٔ پنل changed-confirmed؛ CRC/count جای chain/power را نگیرد</t>
+        </is>
+      </c>
+      <c r="K19" s="7" t="inlineStr">
+        <is>
+          <t>Host PASS: 159 check؛ board physical pending</t>
+        </is>
+      </c>
+      <c r="L19" s="7" t="inlineStr">
+        <is>
+          <t>در انتظار</t>
+        </is>
+      </c>
+      <c r="M19" s="7" t="inlineStr">
+        <is>
+          <t>Host جای تست برد را نمی‌گیرد؛ حذف override و ماندگاری پس از reset روی برد واقعی لازم است</t>
+        </is>
+      </c>
+      <c r="N19" s="7" t="inlineStr">
+        <is>
+          <t>Firmware/Modules/CalLut/Tester/run_host_test_cal_lut.sh؛ esp_link_panel/Tester/host_test_scenario_cards.js</t>
+        </is>
+      </c>
+      <c r="O19" s="7" t="inlineStr">
+        <is>
+          <t>WORKTREE</t>
+        </is>
+      </c>
+      <c r="P19" s="7" t="n"/>
+      <c r="Q19" s="7" t="inlineStr">
         <is>
           <t>2026-10-07</t>
         </is>
@@ -1919,6 +2002,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="6" t="inlineStr">
         <is>
@@ -2330,6 +2414,7 @@
         </is>
       </c>
     </row>
+    <row r="10"/>
     <row r="11">
       <c r="A11" s="8" t="inlineStr">
         <is>
@@ -2360,8 +2445,10 @@
           <t>کل تست‌ها</t>
         </is>
       </c>
-      <c r="B13" s="2" t="n">
-        <v>13</v>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
@@ -2424,7 +2511,7 @@
         </is>
       </c>
       <c r="B17" s="2">
-        <f>IF(13=0,0,COUNTIF('برنامه تست'!L:L,"قبول")/13)</f>
+        <f>IF(15=0,0,COUNTIF('برنامه تست'!L:L,"قبول")/15)</f>
         <v/>
       </c>
       <c r="C17" s="2" t="inlineStr">
@@ -2433,6 +2520,7 @@
         </is>
       </c>
     </row>
+    <row r="18"/>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
@@ -2500,6 +2588,7 @@
         </is>
       </c>
     </row>
+    <row r="7"/>
     <row r="8">
       <c r="A8" s="9" t="inlineStr">
         <is>
@@ -2554,6 +2643,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3" ht="24" customHeight="1">
       <c r="A3" s="11" t="inlineStr">
         <is>

--- a/Firmware/Modules/CalLut/CalLut_Validation.xlsx
+++ b/Firmware/Modules/CalLut/CalLut_Validation.xlsx
@@ -591,7 +591,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q19"/>
+  <dimension ref="A1:Q20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -1966,12 +1966,95 @@
         </is>
       </c>
     </row>
+    <row r="20">
+      <c r="A20" s="7" t="inlineStr">
+        <is>
+          <t>CL-016</t>
+        </is>
+      </c>
+      <c r="B20" s="7" t="inlineStr">
+        <is>
+          <t>reset با grant و flush NVM</t>
+        </is>
+      </c>
+      <c r="C20" s="7" t="inlineStr">
+        <is>
+          <t>بالا</t>
+        </is>
+      </c>
+      <c r="D20" s="7" t="inlineStr">
+        <is>
+          <t>commit موفق یا commit صفرنقطه‌ای؛ magic معتبر؛ لینک فعال</t>
+        </is>
+      </c>
+      <c r="E20" s="7" t="inlineStr">
+        <is>
+          <t>پس از commit reset را درخواست کن؛ یک اجرای flush موفق و یک اجرای flush ناموفق/تزریق‌شده را بررسی کن</t>
+        </is>
+      </c>
+      <c r="F20" s="7" t="inlineStr">
+        <is>
+          <t>count=0 معتبر؛ grant commit؛ flush success/failure</t>
+        </is>
+      </c>
+      <c r="G20" s="7" t="inlineStr">
+        <is>
+          <t>حداکثر 15s</t>
+        </is>
+      </c>
+      <c r="H20" s="7" t="inlineStr">
+        <is>
+          <t>zero-point commit بدون active table پذیرفته می‌شود؛ reset فقط با grant commit و flush موفق arm می‌شود؛ flush failure کد CAL_LUT_ST_FLASH می‌دهد و reset انجام نمی‌شود</t>
+        </is>
+      </c>
+      <c r="I20" s="7" t="inlineStr">
+        <is>
+          <t>پس از موفقیت one-shot؛ بعد از flush failure grant برای retry حفظ می‌شود</t>
+        </is>
+      </c>
+      <c r="J20" s="7" t="inlineStr">
+        <is>
+          <t>پس از reset /t و LUT_READ/LUT_DATA تازه، هر دو کانال و persistence با expected برابر؛ هیچ reject/timeout/mismatch موفق گزارش نشود</t>
+        </is>
+      </c>
+      <c r="K20" s="7" t="inlineStr">
+        <is>
+          <t>Host PASS: CalLut=159، parser=14 و NVM؛ تست فیزیکی فلش/ریست/باتری انجام نشده و pending است</t>
+        </is>
+      </c>
+      <c r="L20" s="7" t="inlineStr">
+        <is>
+          <t>در انتظار</t>
+        </is>
+      </c>
+      <c r="M20" s="7" t="inlineStr">
+        <is>
+          <t>Host جای تست فیزیکی برد و fault واقعی NVM را نمی‌گیرد؛ commit zero-point، reset و flush روی برد واقعی تکرار شود</t>
+        </is>
+      </c>
+      <c r="N20" s="7" t="inlineStr">
+        <is>
+          <t>Firmware/Modules/CalLut/Tester/run_host_test_cal_lut.sh؛ Firmware/Modules/EspLink/Tester/run_host_test_nvm.sh؛ Firmware/Modules/EspLink/esp_link.c</t>
+        </is>
+      </c>
+      <c r="O20" s="7" t="inlineStr">
+        <is>
+          <t>WORKTREE</t>
+        </is>
+      </c>
+      <c r="P20" s="7" t="n"/>
+      <c r="Q20" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <dataValidations count="2">
-    <dataValidation sqref="L5:L18" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="L5:L20" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>='فهرست‌ها'!$A$2:$A$6</formula1>
     </dataValidation>
-    <dataValidation sqref="C5:C18" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="C5:C20" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>='فهرست‌ها'!$B$9:$B$11</formula1>
     </dataValidation>
   </dataValidations>
@@ -1985,7 +2068,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E9"/>
+  <dimension ref="A1:E10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -2002,7 +2085,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3">
       <c r="A3" s="6" t="inlineStr">
         <is>
@@ -2189,6 +2271,33 @@
       <c r="E9" s="7" t="inlineStr">
         <is>
           <t>روش قبلی حذف نشده</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="7" t="inlineStr">
+        <is>
+          <t>reset grant و flush NVM</t>
+        </is>
+      </c>
+      <c r="B10" s="7" t="inlineStr">
+        <is>
+          <t>magic + commit grant؛ flush NVM پیش از arm</t>
+        </is>
+      </c>
+      <c r="C10" s="7" t="inlineStr">
+        <is>
+          <t>flush failure = no reset؛ success = reset one-shot</t>
+        </is>
+      </c>
+      <c r="D10" s="7" t="inlineStr">
+        <is>
+          <t>cal_lut.c / esp_link.c / esp_link_nvm.c</t>
+        </is>
+      </c>
+      <c r="E10" s="7" t="inlineStr">
+        <is>
+          <t>zero-point commit حتی بدون active table معتبر است</t>
         </is>
       </c>
     </row>
@@ -2414,7 +2523,6 @@
         </is>
       </c>
     </row>
-    <row r="10"/>
     <row r="11">
       <c r="A11" s="8" t="inlineStr">
         <is>
@@ -2447,7 +2555,7 @@
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>16</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
@@ -2495,7 +2603,7 @@
         </is>
       </c>
       <c r="B16" s="2">
-        <f>COUNTIF('برنامه تست'!L:L,"در انتظار")</f>
+        <f>IF(16=0,0,COUNTIF('برنامه تست'!L:L,"قبول")/16)</f>
         <v/>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -2520,7 +2628,6 @@
         </is>
       </c>
     </row>
-    <row r="18"/>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
@@ -2588,7 +2695,6 @@
         </is>
       </c>
     </row>
-    <row r="7"/>
     <row r="8">
       <c r="A8" s="9" t="inlineStr">
         <is>
@@ -2643,7 +2749,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3" ht="24" customHeight="1">
       <c r="A3" s="11" t="inlineStr">
         <is>

--- a/Firmware/Modules/CalLut/CalLut_Validation.xlsx
+++ b/Firmware/Modules/CalLut/CalLut_Validation.xlsx
@@ -591,7 +591,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q17"/>
+  <dimension ref="A1:Q20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -1800,12 +1800,261 @@
         </is>
       </c>
     </row>
+    <row r="18">
+      <c r="A18" s="7" t="inlineStr">
+        <is>
+          <t>CL-014</t>
+        </is>
+      </c>
+      <c r="B18" s="7" t="inlineStr">
+        <is>
+          <t>LUT_READ بازخوانی واقعی هر دو کانال</t>
+        </is>
+      </c>
+      <c r="C18" s="7" t="inlineStr">
+        <is>
+          <t>بالا</t>
+        </is>
+      </c>
+      <c r="D18" s="7" t="inlineStr">
+        <is>
+          <t>رکورد LUT فعال در فلش یا جدول تازه commit شده</t>
+        </is>
+      </c>
+      <c r="E18" s="7" t="inlineStr">
+        <is>
+          <t>از لینک ESP فرمان LUT_READ بفرست و payloadهای LUT_DATA کانال ۱ و ۲ را با آرایه‌های Active مقایسه کن؛ سپس بعد از reset تکرار کن</t>
+        </is>
+      </c>
+      <c r="F18" s="7" t="inlineStr">
+        <is>
+          <t>chainMa/powerMw نقاط فعال، به‌خصوص battery 2</t>
+        </is>
+      </c>
+      <c r="G18" s="7" t="inlineStr">
+        <is>
+          <t>یک درخواست قبل و یک درخواست بعد از reset</t>
+        </is>
+      </c>
+      <c r="H18" s="7" t="inlineStr">
+        <is>
+          <t>LUT_DATA مقدار واقعی هر نقطه را برمی‌گرداند؛ کانال غیرفعال فریم صفرنقطه‌ای می‌دهد؛ دادهٔ ناقص active فرض نمی‌شود</t>
+        </is>
+      </c>
+      <c r="I18" s="7" t="inlineStr">
+        <is>
+          <t>رکورد فلش باید بعد از reset همان نقاط را حفظ کند</t>
+        </is>
+      </c>
+      <c r="J18" s="7" t="inlineStr">
+        <is>
+          <t>تطبیق byte/point با func__CalLut_Points/ChainMa/PowerMw و گزارش mismatch در پنل</t>
+        </is>
+      </c>
+      <c r="K18" s="7" t="inlineStr">
+        <is>
+          <t>Host PASS: 159 check؛ شامل دو فریم واقعی LUT_DATA، battery 2 مستقل و transition غیرصفر→صفر؛ برد فیزیکی pending</t>
+        </is>
+      </c>
+      <c r="L18" s="7" t="inlineStr">
+        <is>
+          <t>در انتظار</t>
+        </is>
+      </c>
+      <c r="M18" s="7" t="inlineStr">
+        <is>
+          <t>Host جای اندازه‌گیری برد را نمی‌گیرد؛ فلش و readback روی برد واقعی لازم است</t>
+        </is>
+      </c>
+      <c r="N18" s="7" t="inlineStr">
+        <is>
+          <t>Firmware/Modules/CalLut/Tester/run_host_test_cal_lut.sh</t>
+        </is>
+      </c>
+      <c r="O18" s="7" t="inlineStr">
+        <is>
+          <t>WORKTREE</t>
+        </is>
+      </c>
+      <c r="P18" s="7" t="inlineStr"/>
+      <c r="Q18" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="7" t="inlineStr">
+        <is>
+          <t>CL-015</t>
+        </is>
+      </c>
+      <c r="B19" s="7" t="inlineStr">
+        <is>
+          <t>حذف override با صفرنقطه</t>
+        </is>
+      </c>
+      <c r="C19" s="7" t="inlineStr">
+        <is>
+          <t>بالا</t>
+        </is>
+      </c>
+      <c r="D19" s="7" t="inlineStr">
+        <is>
+          <t>CL-002 یا رکورد فعال با هر دو کانال</t>
+        </is>
+      </c>
+      <c r="E19" s="7" t="inlineStr">
+        <is>
+          <t>LUT_BEGIN با n1=5 و n2=0، CHUNK فقط کانال ۱، COMMIT با CRC درست؛ سپس reset و LUT_READ</t>
+        </is>
+      </c>
+      <c r="F19" s="7" t="inlineStr">
+        <is>
+          <t>کانال ۱ معتبر؛ کانال ۲ count=0؛ before کانال ۲ غیرصفر و after صفرنقطه‌ای</t>
+        </is>
+      </c>
+      <c r="G19" s="7" t="inlineStr">
+        <is>
+          <t>یک تبادل + یک بوت</t>
+        </is>
+      </c>
+      <c r="H19" s="7" t="inlineStr">
+        <is>
+          <t>commit پذیرفته؛ کانال ۱ حفظ می‌شود و override فلش کانال ۲ حذف می‌شود؛ LUT_DATA کانال ۲ فریم صفرنقطه‌ای مستقل می‌دهد</t>
+        </is>
+      </c>
+      <c r="I19" s="7" t="inlineStr">
+        <is>
+          <t>پینگ‌پنگ و پس از reset</t>
+        </is>
+      </c>
+      <c r="J19" s="7" t="inlineStr">
+        <is>
+          <t>status=0، Active کانال ۱ برقرار، Active کانال ۲=false و مقایسهٔ پنل changed-confirmed؛ CRC/count جای chain/power را نگیرد</t>
+        </is>
+      </c>
+      <c r="K19" s="7" t="inlineStr">
+        <is>
+          <t>Host PASS: 159 check؛ board physical pending</t>
+        </is>
+      </c>
+      <c r="L19" s="7" t="inlineStr">
+        <is>
+          <t>در انتظار</t>
+        </is>
+      </c>
+      <c r="M19" s="7" t="inlineStr">
+        <is>
+          <t>Host جای تست برد را نمی‌گیرد؛ حذف override و ماندگاری پس از reset روی برد واقعی لازم است</t>
+        </is>
+      </c>
+      <c r="N19" s="7" t="inlineStr">
+        <is>
+          <t>Firmware/Modules/CalLut/Tester/run_host_test_cal_lut.sh؛ esp_link_panel/Tester/host_test_scenario_cards.js</t>
+        </is>
+      </c>
+      <c r="O19" s="7" t="inlineStr">
+        <is>
+          <t>WORKTREE</t>
+        </is>
+      </c>
+      <c r="P19" s="7" t="n"/>
+      <c r="Q19" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="7" t="inlineStr">
+        <is>
+          <t>CL-016</t>
+        </is>
+      </c>
+      <c r="B20" s="7" t="inlineStr">
+        <is>
+          <t>reset با grant و flush NVM</t>
+        </is>
+      </c>
+      <c r="C20" s="7" t="inlineStr">
+        <is>
+          <t>بالا</t>
+        </is>
+      </c>
+      <c r="D20" s="7" t="inlineStr">
+        <is>
+          <t>commit موفق یا commit صفرنقطه‌ای؛ magic معتبر؛ لینک فعال</t>
+        </is>
+      </c>
+      <c r="E20" s="7" t="inlineStr">
+        <is>
+          <t>پس از commit reset را درخواست کن؛ یک اجرای flush موفق و یک اجرای flush ناموفق/تزریق‌شده را بررسی کن</t>
+        </is>
+      </c>
+      <c r="F20" s="7" t="inlineStr">
+        <is>
+          <t>count=0 معتبر؛ grant commit؛ flush success/failure</t>
+        </is>
+      </c>
+      <c r="G20" s="7" t="inlineStr">
+        <is>
+          <t>حداکثر 15s</t>
+        </is>
+      </c>
+      <c r="H20" s="7" t="inlineStr">
+        <is>
+          <t>zero-point commit بدون active table پذیرفته می‌شود؛ reset فقط با grant commit و flush موفق arm می‌شود؛ flush failure کد CAL_LUT_ST_FLASH می‌دهد و reset انجام نمی‌شود</t>
+        </is>
+      </c>
+      <c r="I20" s="7" t="inlineStr">
+        <is>
+          <t>پس از موفقیت one-shot؛ بعد از flush failure grant برای retry حفظ می‌شود</t>
+        </is>
+      </c>
+      <c r="J20" s="7" t="inlineStr">
+        <is>
+          <t>پس از reset /t و LUT_READ/LUT_DATA تازه، هر دو کانال و persistence با expected برابر؛ هیچ reject/timeout/mismatch موفق گزارش نشود</t>
+        </is>
+      </c>
+      <c r="K20" s="7" t="inlineStr">
+        <is>
+          <t>Host PASS: CalLut=159، parser=14 و NVM؛ تست فیزیکی فلش/ریست/باتری انجام نشده و pending است</t>
+        </is>
+      </c>
+      <c r="L20" s="7" t="inlineStr">
+        <is>
+          <t>در انتظار</t>
+        </is>
+      </c>
+      <c r="M20" s="7" t="inlineStr">
+        <is>
+          <t>Host جای تست فیزیکی برد و fault واقعی NVM را نمی‌گیرد؛ commit zero-point، reset و flush روی برد واقعی تکرار شود</t>
+        </is>
+      </c>
+      <c r="N20" s="7" t="inlineStr">
+        <is>
+          <t>Firmware/Modules/CalLut/Tester/run_host_test_cal_lut.sh؛ Firmware/Modules/EspLink/Tester/run_host_test_nvm.sh؛ Firmware/Modules/EspLink/esp_link.c</t>
+        </is>
+      </c>
+      <c r="O20" s="7" t="inlineStr">
+        <is>
+          <t>WORKTREE</t>
+        </is>
+      </c>
+      <c r="P20" s="7" t="n"/>
+      <c r="Q20" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <dataValidations count="2">
-    <dataValidation sqref="L5:L17" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="L5:L20" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>='فهرست‌ها'!$A$2:$A$6</formula1>
     </dataValidation>
-    <dataValidation sqref="C5:C17" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="C5:C20" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>='فهرست‌ها'!$B$9:$B$11</formula1>
     </dataValidation>
   </dataValidations>
@@ -1819,7 +2068,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E9"/>
+  <dimension ref="A1:E10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -2022,6 +2271,33 @@
       <c r="E9" s="7" t="inlineStr">
         <is>
           <t>روش قبلی حذف نشده</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="7" t="inlineStr">
+        <is>
+          <t>reset grant و flush NVM</t>
+        </is>
+      </c>
+      <c r="B10" s="7" t="inlineStr">
+        <is>
+          <t>magic + commit grant؛ flush NVM پیش از arm</t>
+        </is>
+      </c>
+      <c r="C10" s="7" t="inlineStr">
+        <is>
+          <t>flush failure = no reset؛ success = reset one-shot</t>
+        </is>
+      </c>
+      <c r="D10" s="7" t="inlineStr">
+        <is>
+          <t>cal_lut.c / esp_link.c / esp_link_nvm.c</t>
+        </is>
+      </c>
+      <c r="E10" s="7" t="inlineStr">
+        <is>
+          <t>zero-point commit حتی بدون active table معتبر است</t>
         </is>
       </c>
     </row>
@@ -2277,8 +2553,10 @@
           <t>کل تست‌ها</t>
         </is>
       </c>
-      <c r="B13" s="2" t="n">
-        <v>13</v>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
@@ -2325,7 +2603,7 @@
         </is>
       </c>
       <c r="B16" s="2">
-        <f>COUNTIF('برنامه تست'!L:L,"در انتظار")</f>
+        <f>IF(16=0,0,COUNTIF('برنامه تست'!L:L,"قبول")/16)</f>
         <v/>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -2341,7 +2619,7 @@
         </is>
       </c>
       <c r="B17" s="2">
-        <f>IF(13=0,0,COUNTIF('برنامه تست'!L:L,"قبول")/13)</f>
+        <f>IF(15=0,0,COUNTIF('برنامه تست'!L:L,"قبول")/15)</f>
         <v/>
       </c>
       <c r="C17" s="2" t="inlineStr">

--- a/Firmware/Modules/CalLut/CalLut_Validation.xlsx
+++ b/Firmware/Modules/CalLut/CalLut_Validation.xlsx
@@ -1159,7 +1159,7 @@
       </c>
       <c r="E10" s="7" t="inlineStr">
         <is>
-          <t>جدولی با افت در PowerMw بفرست</t>
+          <t>جدولی بفرست که جریان باتری آن در یک نقطه کم‌تر از نقطهٔ قبلی باشد</t>
         </is>
       </c>
       <c r="F10" s="7" t="inlineStr">
@@ -1174,7 +1174,7 @@
       </c>
       <c r="H10" s="7" t="inlineStr">
         <is>
-          <t>رد با CAL_LUT_ST_POWER</t>
+          <t>رد با CAL_LUT_ST_DIP (جریان باتری افت دارد)</t>
         </is>
       </c>
       <c r="I10" s="7" t="inlineStr">
@@ -1828,7 +1828,7 @@
       </c>
       <c r="F18" s="7" t="inlineStr">
         <is>
-          <t>chainMa/powerMw نقاط فعال، به‌خصوص battery 2</t>
+          <t>counts/BatteryMa نقاط فعال، به‌خصوص battery 2</t>
         </is>
       </c>
       <c r="G18" s="7" t="inlineStr">
@@ -1848,7 +1848,7 @@
       </c>
       <c r="J18" s="7" t="inlineStr">
         <is>
-          <t>تطبیق byte/point با func__CalLut_Points/ChainMa/PowerMw و گزارش mismatch در پنل</t>
+          <t>تطبیق byte/point با func__CalLut_Points/Counts/BatteryMa و گزارش mismatch در پنل</t>
         </is>
       </c>
       <c r="K18" s="7" t="inlineStr">
@@ -1931,7 +1931,7 @@
       </c>
       <c r="J19" s="7" t="inlineStr">
         <is>
-          <t>status=0، Active کانال ۱ برقرار، Active کانال ۲=false و مقایسهٔ پنل changed-confirmed؛ CRC/count جای chain/power را نگیرد</t>
+          <t>status=0، Active کانال ۱ برقرار، Active کانال ۲=false و مقایسهٔ پنل changed-confirmed؛ CRC/count جای counts/BatteryMa را نگیرد</t>
         </is>
       </c>
       <c r="K19" s="7" t="inlineStr">

--- a/Firmware/Modules/CalLut/CalLut_Validation.xlsx
+++ b/Firmware/Modules/CalLut/CalLut_Validation.xlsx
@@ -1144,7 +1144,7 @@
       </c>
       <c r="B10" s="7" t="inlineStr">
         <is>
-          <t>افت محور توان</t>
+          <t>افت محور جریان</t>
         </is>
       </c>
       <c r="C10" s="7" t="inlineStr">

--- a/Firmware/Modules/CalLut/CalLut_Validation.xlsx
+++ b/Firmware/Modules/CalLut/CalLut_Validation.xlsx
@@ -555,7 +555,7 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>جدول‌های کامپایل‌تایم calibration.h می‌مانند و پشتیبان‌اند: فقط وقتی رکورد معتبر در فلش باشد از آن استفاده می‌شود.</t>
+          <t>جدول کامپایل‌شده وجود ندارد. وقتی رکورد معتبر در فلش نباشد، خط گین و آفست (پیش‌فرض گین 3000، آفست 0) استفاده می‌شود؛ وقتی رکورد معتبر در فلش باشد از آن استفاده می‌شود.</t>
         </is>
       </c>
     </row>
@@ -759,7 +759,7 @@
       </c>
       <c r="H5" s="7" t="inlineStr">
         <is>
-          <t>func__CalLut_Active هر دو کانال false؛ مسیر اندازه‌گیری از جدول calibration.h استفاده می‌کند</t>
+          <t>func__CalLut_Active هر دو کانال false؛ مسیر اندازه‌گیری از خط گین و آفست استفاده می‌کند</t>
         </is>
       </c>
       <c r="I5" s="7" t="inlineStr">
@@ -1765,7 +1765,7 @@
       </c>
       <c r="J17" s="7" t="inlineStr">
         <is>
-          <t>Active=false و خوانش‌ها برابر جدول calibration.h</t>
+          <t>Active=false و خوانش‌ها برابر خط گین و آفست</t>
         </is>
       </c>
       <c r="K17" s="7" t="inlineStr">
@@ -2255,7 +2255,7 @@
       </c>
       <c r="B9" s="7" t="inlineStr">
         <is>
-          <t>جدول‌های calibration.h</t>
+          <t>جدول‌های فلش (CalLut) و خط گین و آفست</t>
         </is>
       </c>
       <c r="C9" s="7" t="inlineStr">

--- a/Firmware/Modules/CalLut/CalLut_Validation.xlsx
+++ b/Firmware/Modules/CalLut/CalLut_Validation.xlsx
@@ -591,7 +591,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q20"/>
+  <dimension ref="A1:Q21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -2046,6 +2046,76 @@
       <c r="Q20" s="7" t="inlineStr">
         <is>
           <t>2026-10-08</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>CL-020</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>پنل دیالوگ LUT</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>متوسط</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>پنل وصل + LUT آماده</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>از پنل LUT را push کن؛ دیالوگ تأیید ریست باید با کادر تیره همرنگ پنل بیاید و Enter تأیید و Esc لغو کند</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>LUT 2 کانال</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>10s</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>دیالوگ با استایل #pmod/#121a2c، بدون alert سفید ویندوز؛ Enter=تأیید Esc=انصراف؛ صف PMQ یکی‌یکی</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>دیالوگ تیره + Enter/Esc کار کند</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>نیاز به تکرار</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>62f3782</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr"/>
+      <c r="Q21" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
         </is>
       </c>
     </row>

--- a/Firmware/Modules/CalLut/CalLut_Validation.xlsx
+++ b/Firmware/Modules/CalLut/CalLut_Validation.xlsx
@@ -749,7 +749,7 @@
       </c>
       <c r="F5" s="7" t="inlineStr">
         <is>
-          <t>فلش LUT خالی (0xFFFF)</t>
+          <t>فلش LUT خالی (65535 = خانهٔ پاک‌شدهٔ فلش)</t>
         </is>
       </c>
       <c r="G5" s="7" t="inlineStr">
@@ -2105,14 +2105,11 @@
           <t>نیاز به تکرار</t>
         </is>
       </c>
-      <c r="M21" t="inlineStr"/>
-      <c r="N21" t="inlineStr"/>
       <c r="O21" t="inlineStr">
         <is>
           <t>62f3782</t>
         </is>
       </c>
-      <c r="P21" t="inlineStr"/>
       <c r="Q21" t="inlineStr">
         <is>
           <t>2026-10-12</t>

--- a/Firmware/Modules/CalLut/CalLut_Validation.xlsx
+++ b/Firmware/Modules/CalLut/CalLut_Validation.xlsx
@@ -744,7 +744,10 @@
       </c>
       <c r="E5" s="7" t="inlineStr">
         <is>
-          <t>برد را بدون هیچ push جدول روشن کن و جریان خوانده‌شده را با جدول کامپایل‌شده مقایسه کن</t>
+          <t>گام ۱: مطمئن شو هیچ جدولی از پنل فرستاده نشده و فلش LUT خالی است (همهٔ خانه‌ها 65535).
+گام ۲: برد را روشن کن و صبر کن بوت کامل شود.
+گام ۳: از پنل ببین هر دو کانال جدول فعال ندارند (Active هر دو false است).
+گام ۴: جریان خوانده‌شدهٔ هر دو کانال را با همان بردی که ماژول LUT نداشت مقایسه کن؛ باید دقیقاً یکی باشد، چون مسیر اندازه‌گیری از خط گین و آفست استفاده می‌کند.</t>
         </is>
       </c>
       <c r="F5" s="7" t="inlineStr">
@@ -827,7 +830,11 @@
       </c>
       <c r="E6" s="7" t="inlineStr">
         <is>
-          <t>از پنل یک جدول ۱۷..۲۱ نقطه‌ای برای کانال ۱ بفرست و commit کن</t>
+          <t>گام ۱: لینک ESP را وصل کن و پنل را باز کن.
+گام ۲: برای کانال ۱ یک جدول 17 تا 21 نقطه‌ای بساز و ارسال کن (اول LUT_BEGIN، بعد چانک‌ها، در آخر COMMIT).
+گام ۳: پاسخ برد را بخوان: وضعیت باید 0 باشد (CAL_LUT_ST_OK).
+گام ۴: CRC32 جدول در پنل و CRC32 گزارش‌شدهٔ برد را مقایسه کن؛ باید برابر باشند.
+گام ۵: فرمان LUT_RESET را بفرست و بعد از بالا آمدن برد ببین جدول کانال ۱ فعال شده است (Active = true).</t>
         </is>
       </c>
       <c r="F6" s="7" t="inlineStr">
@@ -910,7 +917,10 @@
       </c>
       <c r="E7" s="7" t="inlineStr">
         <is>
-          <t>برق برد را کاملاً قطع و وصل کن (نه ریست نرم)</t>
+          <t>گام ۱: اول تست CL-002 را قبول کن تا یک جدول سالم روی برد فعال باشد و CRC32 آن را یادداشت کن.
+گام ۲: تغذیهٔ برد را کاملاً قطع کن (فقط ریست نرم کافی نیست) و دوباره وصل کن.
+گام ۳: بعد از بوت، CRC32 جدول فعال را از برد بخوان و با مقدار یادداشت‌شده مقایسه کن.
+گام ۴: قطع و وصل کامل را 3 بار تکرار کن؛ هر سه بار CRC32 باید همان مقدار قبلی باشد.</t>
         </is>
       </c>
       <c r="F7" s="7" t="inlineStr">
@@ -993,7 +1003,10 @@
       </c>
       <c r="E8" s="7" t="inlineStr">
         <is>
-          <t>عمداً CRC32 اشتباه در LUT_COMMIT بفرست</t>
+          <t>گام ۱: لینک ESP را وصل کن و CRC32 جدول فعال فعلی را یادداشت کن.
+گام ۲: یک جدول بفرست ولی در مرحلهٔ COMMIT عمداً CRC32 اشتباه بده (با CRC واقعی جدول یکی نباشد).
+گام ۳: پاسخ برد را بخوان: وضعیت باید 6 باشد (CAL_LUT_ST_CRC) و commit رد شود.
+گام ۴: CRC32 جدول فعال را دوباره بخوان؛ باید با گام ۱ یکی باشد، یعنی فلش دست‌نخورده مانده است.</t>
         </is>
       </c>
       <c r="F8" s="7" t="inlineStr">
@@ -1076,7 +1089,10 @@
       </c>
       <c r="E9" s="7" t="inlineStr">
         <is>
-          <t>جدولی بفرست که محور زنجیره صعودی اکید نیست</t>
+          <t>گام ۱: لینک ESP را وصل کن.
+گام ۲: جدولی بساز که محور زنجیره‌اش (ChainMa) صعودیِ اکید نباشد؛ مثلاً یک نقطهٔ تکراری یا یک نقطه کمتر از قبلی بگذار.
+گام ۳: جدول را کامل بفرست و COMMIT کن.
+گام ۴: پاسخ برد را بخوان: وضعیت باید 4 باشد (CAL_LUT_ST_CHAIN) و جدول نباید فعال شود.</t>
         </is>
       </c>
       <c r="F9" s="7" t="inlineStr">
@@ -1159,7 +1175,10 @@
       </c>
       <c r="E10" s="7" t="inlineStr">
         <is>
-          <t>جدولی بفرست که جریان باتری آن در یک نقطه کم‌تر از نقطهٔ قبلی باشد</t>
+          <t>گام ۱: لینک ESP را وصل کن.
+گام ۲: جدولی بساز که جریان باتری در یکی از نقطه‌ها از نقطهٔ قبلی کمتر باشد (افت داشته باشد).
+گام ۳: جدول را کامل بفرست و COMMIT کن.
+گام ۴: پاسخ برد را بخوان: وضعیت باید 5 باشد (CAL_LUT_ST_DIP) و جدول نباید فعال شود.</t>
         </is>
       </c>
       <c r="F10" s="7" t="inlineStr">
@@ -1242,7 +1261,10 @@
       </c>
       <c r="E11" s="7" t="inlineStr">
         <is>
-          <t>یک‌بار با ۱ نقطه و یک‌بار با ۲۵ نقطه commit کن</t>
+          <t>گام ۱: لینک ESP را وصل کن.
+گام ۲: یک جدول فقط با 1 نقطه بفرست و COMMIT کن؛ پاسخ را بخوان.
+گام ۳: یک جدول با 25 نقطه بفرست و COMMIT کن؛ پاسخ را بخوان.
+گام ۴: هر دو بار وضعیت باید 2 باشد (CAL_LUT_ST_COUNT)، چون تعداد نقطهٔ مجاز 2 تا 24 است.</t>
         </is>
       </c>
       <c r="F11" s="7" t="inlineStr">
@@ -1325,7 +1347,10 @@
       </c>
       <c r="E12" s="7" t="inlineStr">
         <is>
-          <t>یک CHUNK را عمداً نفرست و commit کن</t>
+          <t>گام ۱: لینک ESP را وصل کن و یک جدول چندچانکه آماده کن.
+گام ۲: همهٔ چانک‌ها را بفرست به‌جز یکی؛ عمداً یک چانک را نفرست.
+گام ۳: COMMIT را بفرست.
+گام ۴: پاسخ برد را بخوان: وضعیت باید 3 باشد (CAL_LUT_ST_MISSING) و هیچ جدولی فعال نشود.</t>
         </is>
       </c>
       <c r="F12" s="7" t="inlineStr">
@@ -1408,7 +1433,9 @@
       </c>
       <c r="E13" s="7" t="inlineStr">
         <is>
-          <t>بدون LUT_BEGIN مستقیم COMMIT بفرست</t>
+          <t>گام ۱: لینک ESP را وصل کن.
+گام ۲: بدون اینکه LUT_BEGIN بفرستی، مستقیم COMMIT بفرست.
+گام ۳: پاسخ برد را بخوان: وضعیت باید 1 باشد (CAL_LUT_ST_NO_STAGE) و هیچ اتفاقی برای جدول فعال نیفتد.</t>
         </is>
       </c>
       <c r="F13" s="7" t="inlineStr">
@@ -1491,7 +1518,10 @@
       </c>
       <c r="E14" s="7" t="inlineStr">
         <is>
-          <t>در لحظهٔ commit تغذیه را قطع کن؛ چند بار تکرار</t>
+          <t>گام ۱: اول یک جدول سالم commit کن (CL-002) و CRC32 آن را یادداشت کن.
+گام ۲: یک جدول تازه بفرست و دقیقاً وسط COMMIT (موقع پاک/نوشتن فلش) تغذیهٔ برد را قطع کن.
+گام ۳: تغذیه را وصل کن و بعد از بوت، جدول فعال و CRC32 آن را بخوان: یا باید جدول قبلی سالم باشد یا جدول جدید کامل نشسته باشد؛ حالت سوم (نیمه‌کاره) هرگز نباید دیده شود.
+گام ۴: این کار را 5 بار تکرار کن و هر بار بعد از بوت سالم‌بودن رکورد فعال (RecordValidate = true) را بررسی کن.</t>
         </is>
       </c>
       <c r="F14" s="7" t="inlineStr">
@@ -1574,7 +1604,10 @@
       </c>
       <c r="E15" s="7" t="inlineStr">
         <is>
-          <t>پارامترها را تغییر و ذخیره کن، سپس یک جدول کامل push کن و برعکس</t>
+          <t>گام ۱: چند پارامتر را از پنل از مقدار پیش‌فرض تغییر بده و ذخیره کن؛ مقدارها را یادداشت کن.
+گام ۲: یک جدول LUT کامل push کن و commit کن.
+گام ۳: دوباره یک پارامتر را تغییر و ذخیره کن و یک جدول دیگر push کن (هر دو مسیر ذخیره پشت سر هم).
+گام ۴: برد را ری‌استارت کن و همهٔ پارامترها و جدول را بخوان؛ هیچ‌کدام نباید دیگری را خراب کرده باشد و همه باید با مقدارهای یادداشت‌شده یکی باشند.</t>
         </is>
       </c>
       <c r="F15" s="7" t="inlineStr">
@@ -1657,7 +1690,10 @@
       </c>
       <c r="E16" s="7" t="inlineStr">
         <is>
-          <t>حین BULK فعال، LUT_RESET بفرست</t>
+          <t>گام ۱: یک جدول فعال کن و شارژ را در حالت BULK راه بینداز تا کانال در حال شارژ PWM داشته باشد.
+گام ۲: اسیلوسکوپ را روی گیت همان کانال بگذار.
+گام ۳: حین شارژ فرمان LUT_RESET را بفرست.
+گام ۴: روی اسکوپ ببین که پیش از ریست، duty اول صفر شده و شارژر idle شده باشد؛ ریست نباید وسط پالس اتفاق بیفتد.</t>
         </is>
       </c>
       <c r="F16" s="7" t="inlineStr">
@@ -1740,7 +1776,10 @@
       </c>
       <c r="E17" s="7" t="inlineStr">
         <is>
-          <t>CAL_LUT_VERSION را بالا ببر و فرم‌ور جدید را فلش کن</t>
+          <t>گام ۱: روی برد یک رکورد LUT معتبر با نسخهٔ 1 داشته باش (قبلاً commit شده باشد).
+گام ۲: ثابت CAL_LUT_VERSION را در کد بالا ببر و فرم‌ور جدید را روی همان برد فلش کن.
+گام ۳: برد را بوت کن و وضعیت جدول فعال را بخوان.
+گام ۴: باید جدول فعال نباشد (Active = false) و خوانش جریان به جدول کامپایل‌شده (خط گین و آفست) برگشته باشد.</t>
         </is>
       </c>
       <c r="F17" s="7" t="inlineStr">
@@ -1823,7 +1862,10 @@
       </c>
       <c r="E18" s="7" t="inlineStr">
         <is>
-          <t>از لینک ESP فرمان LUT_READ بفرست و payloadهای LUT_DATA کانال ۱ و ۲ را با آرایه‌های Active مقایسه کن؛ سپس بعد از reset تکرار کن</t>
+          <t>گام ۱: یک جدول فعال روی فلش داشته باش (یا تازه commit کن) و نقاط هر دو کانال را از پنل یادداشت کن.
+گام ۲: از لینک ESP فرمان LUT_READ بفرست.
+گام ۳: داده‌های برگشتی (LUT_DATA کانال ۱ و ۲) را نقطه‌به‌نقطه با نقاط فعال مقایسه کن؛ کانال بدون جدول باید فریم صفرنقطه‌ای بدهد.
+گام ۴: برد را ریست کن و گام ۲ و ۳ را تکرار کن؛ دادهٔ ناقص نباید «فعال» فرض شود و پنل باید هر عدم تطابق (mismatch) را گزارش کند.</t>
         </is>
       </c>
       <c r="F18" s="7" t="inlineStr">
@@ -1906,7 +1948,11 @@
       </c>
       <c r="E19" s="7" t="inlineStr">
         <is>
-          <t>LUT_BEGIN با n1=5 و n2=0، CHUNK فقط کانال ۱، COMMIT با CRC درست؛ سپس reset و LUT_READ</t>
+          <t>گام ۱: از قبل روی هر دو کانال جدول فعال داشته باش (CL-002 برای هر دو) و نقاط کانال ۲ را یادداشت کن.
+گام ۲: LUT_BEGIN را با n1=5 و n2=0 بفرست، چانک‌ها را فقط برای کانال ۱ بفرست و با CRC درست COMMIT کن.
+گام ۳: پاسخ باید وضعیت 0 باشد؛ برد را ریست کن.
+گام ۴: LUT_READ بگیر: کانال ۱ باید با همان 5 نقطه فعال باشد و کانال ۲ باید فریم صفرنقطه‌ای بدهد (override فلش آن حذف شده باشد).
+گام ۵: در پنل تأیید بگیر که تغییر کانال ۲ «changed-confirmed» است و CRC یا count جای مقادیر واقعی نقاط (counts/BatteryMa) را نگرفته باشد.</t>
         </is>
       </c>
       <c r="F19" s="7" t="inlineStr">
@@ -1989,7 +2035,11 @@
       </c>
       <c r="E20" s="7" t="inlineStr">
         <is>
-          <t>پس از commit reset را درخواست کن؛ یک اجرای flush موفق و یک اجرای flush ناموفق/تزریق‌شده را بررسی کن</t>
+          <t>گام ۱: یک commit موفق (یا commit صفرنقطه‌ای با count=0 معتبر) انجام بده تا grant ریست صادر شود.
+گام ۲: بلافاصله reset را درخواست کن و صبر کن برد بالا بیاید (حداکثر 15 ثانیه).
+گام ۳: از مسیر /t و LUT_READ/LUT_DATA تازه، هر دو کانال و ماندگاری جدول را با مقدار مورد انتظار مقایسه کن؛ هیچ reject یا timeout نباید گزارش شود.
+گام ۴: یک بار هم flush ناموفق را تزریق کن (خطای نوشتن فلش): باید کد CAL_LUT_ST_FLASH برگردد و reset انجام نشود.
+گام ۵: نتیجه بگیر: commit صفرنقطه‌ای بدون جدول فعال پذیرفته می‌شود و reset فقط با grant commit و flush موفق اتفاق می‌افتد.</t>
         </is>
       </c>
       <c r="F20" s="7" t="inlineStr">
@@ -2072,7 +2122,10 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>از پنل LUT را push کن؛ دیالوگ تأیید ریست باید با کادر تیره همرنگ پنل بیاید و Enter تأیید و Esc لغو کند</t>
+          <t>گام ۱: پنل را وصل کن و یک LUT دوکاناله آمادهٔ ارسال داشته باش.
+گام ۲: از پنل LUT را push کن و صبر کن دیالوگ تأیید ریست بیاید.
+گام ۳: دیالوگ باید تیره و هم‌رنگ پنل باشد (#pmod / #121a2c)، نه پنجرهٔ سفید alert ویندوز.
+گام ۴: یک بار کلید Enter را بزن (باید تأیید کند) و یک بار در اجرای بعدی Esc را بزن (باید لغو کند)؛ اگر دو دیالوگ پشت سر هم آمد باید یکی‌یکی در صف PMQ نمایش داده شوند.</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">

--- a/Firmware/Modules/CalLut/CalLut_Validation.xlsx
+++ b/Firmware/Modules/CalLut/CalLut_Validation.xlsx
@@ -15,15 +15,20 @@
     <sheet name="فهرست‌ها" sheetId="6" state="visible" r:id="rId6"/>
     <sheet name="ماشین حالت" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'برنامه تست'!$A$4:$Q$21</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="1">'برنامه تست'!$4:$4</definedName>
+  </definedNames>
+  <calcPr calcId="124519" fullCalcOnLoad="1" iterate="1" iterateCount="100" iterateDelta="0.001"/>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="8">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
+  </numFmts>
+  <fonts count="19">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -63,8 +68,67 @@
       <name val="Vazirmatn"/>
       <sz val="10"/>
     </font>
+    <font>
+      <name val="Tahoma"/>
+      <b val="1"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Tahoma"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Tahoma"/>
+      <b val="1"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Tahoma"/>
+      <color theme="1"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Tahoma"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="14"/>
+    </font>
+    <font>
+      <name val="Tahoma"/>
+      <color rgb="000563C1"/>
+      <sz val="10"/>
+      <u val="single"/>
+    </font>
+    <font>
+      <name val="Tahoma"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Tahoma"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Tahoma"/>
+      <b val="1"/>
+      <color rgb="001F3864"/>
+      <sz val="13"/>
+    </font>
+    <font>
+      <name val="Tahoma"/>
+      <b val="1"/>
+      <color rgb="00C00000"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Tahoma"/>
+      <color rgb="000563C1"/>
+      <sz val="8"/>
+      <u val="single"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="8">
     <fill>
       <patternFill/>
     </fill>
@@ -81,8 +145,28 @@
         <fgColor rgb="001F3864"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D9E2F3"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFE699"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F2F6FC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FCE4D6"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -104,11 +188,25 @@
         <color rgb="009DB7E8"/>
       </bottom>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="00B4C6E7"/>
+      </left>
+      <right style="thin">
+        <color rgb="00B4C6E7"/>
+      </right>
+      <top style="thin">
+        <color rgb="00B4C6E7"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00B4C6E7"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="44">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -142,6 +240,86 @@
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="14" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="14" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -505,6 +683,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <tabColor rgb="007F7F7F"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
@@ -515,21 +694,21 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="14" t="inlineStr">
         <is>
           <t>برگه تست و اعتبارسنجی عملی ماژول CalLut</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
+      <c r="A2" s="15" t="inlineStr">
         <is>
           <t>CalLut | نگهداری جدول کالیبراسیون بنچ در بلوک فلش اختصاصی با CRC32 و بازگشت به جدول کامپایل‌شده</t>
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="3" t="inlineStr">
+    <row r="3" ht="30" customHeight="1">
+      <c r="A3" s="16" t="inlineStr">
         <is>
           <t>هدف فایل</t>
         </is>
@@ -539,48 +718,51 @@
       <c r="A4" s="2" t="n"/>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="inlineStr">
+      <c r="A5" s="15" t="inlineStr">
         <is>
           <t>مسیر ذخیرهٔ جدول کالیبراسیون بنچ در «بلوک فلش مخصوص خودش»: دو صفحهٔ ۱KB در 0x0800F000 و 0x0800F400، پینگ‌پنگ امن در برابر قطع برق، مجیک/نسخه/CRC32 مستقل.</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="inlineStr">
+      <c r="A6" s="42" t="inlineStr">
         <is>
           <t>هیچ اشتراکی با esp_link_nvm.c جز درایور فلش ندارد؛ پس فرستادن جدول هرگز رکورد پارامترها را خراب نمی‌کند و برعکس.</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="inlineStr">
+      <c r="A7" s="15" t="inlineStr">
         <is>
           <t>جدول کامپایل‌شده وجود ندارد. وقتی رکورد معتبر در فلش نباشد، خط گین و آفست (پیش‌فرض گین 3000، آفست 0) استفاده می‌شود؛ وقتی رکورد معتبر در فلش باشد از آن استفاده می‌شود.</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="inlineStr">
+      <c r="A8" s="15" t="inlineStr">
         <is>
           <t>دست‌دادن: LUT_BEGIN → LUT_CHUNK → LUT_COMMIT (با CRC32 پنل) → LUT_ACK (با CRC32 خودِ برد از آنچه در فلش است) → تنها در صورت برابری، LUT_RESET.</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="inlineStr">
+      <c r="A9" s="15" t="inlineStr">
         <is>
           <t>هدف این برگه: اثبات روی برد که نوشتن، بازخوانی، اعتبارسنجی و بازگشت به پشتیبان همگی همان‌طور کار می‌کنند که هدر ادعا می‌کند.</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="2" t="inlineStr">
+      <c r="A10" s="15" t="inlineStr">
         <is>
           <t>تست Host (کامپایل و اجرا روی PC با شبیه‌سازی RAM) جایگزین این تست‌ها نیست.</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A6" r:id="rId1"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -588,161 +770,162 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <tabColor rgb="001F4E79"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:Q21"/>
+  <dimension ref="A1:Q61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="9" customWidth="1" min="1" max="1"/>
-    <col width="15" customWidth="1" min="2" max="2"/>
-    <col width="8" customWidth="1" min="3" max="3"/>
-    <col width="20" customWidth="1" min="4" max="4"/>
-    <col width="26" customWidth="1" min="5" max="5"/>
-    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="9" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="62" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" min="6" max="6"/>
     <col width="10" customWidth="1" min="7" max="7"/>
-    <col width="26" customWidth="1" min="8" max="8"/>
-    <col width="14" customWidth="1" min="9" max="9"/>
-    <col width="24" customWidth="1" min="10" max="10"/>
-    <col width="18" customWidth="1" min="11" max="11"/>
-    <col width="10" customWidth="1" min="12" max="12"/>
-    <col width="18" customWidth="1" min="13" max="13"/>
-    <col width="14" customWidth="1" min="14" max="14"/>
+    <col width="42" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="34" customWidth="1" min="10" max="10"/>
+    <col width="34" customWidth="1" min="11" max="11"/>
+    <col width="13" customWidth="1" min="12" max="12"/>
+    <col width="24" customWidth="1" min="13" max="13"/>
+    <col width="16" customWidth="1" min="14" max="14"/>
     <col width="12" customWidth="1" min="15" max="15"/>
-    <col width="12" customWidth="1" min="16" max="16"/>
-    <col width="11" customWidth="1" min="17" max="17"/>
+    <col width="13" customWidth="1" min="16" max="16"/>
+    <col width="12" customWidth="1" min="17" max="17"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="4" t="inlineStr">
+      <c r="A1" s="17" t="inlineStr">
         <is>
           <t>برنامهٔ تست عملی — ماژول CalLut</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="5" t="inlineStr">
+      <c r="A2" s="18" t="inlineStr">
         <is>
           <t>وضعیت فقط یکی از: در انتظار / قبول / رد / مسدود / نیاز به تکرار. تست Host جایگزین تست برد نیست.</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="5" t="inlineStr">
+      <c r="A3" s="18" t="inlineStr">
         <is>
           <t>برای هر ردیف پیش‌شرط، ورودی، انتظار و معیار قبولی صریح است؛ نتیجهٔ واقعی فقط با اندازه‌گیری روی برد پر می‌شود.</t>
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="6" t="inlineStr">
+    <row r="4" ht="30" customHeight="1">
+      <c r="A4" s="16" t="inlineStr">
         <is>
           <t>شناسه</t>
         </is>
       </c>
-      <c r="B4" s="6" t="inlineStr">
+      <c r="B4" s="16" t="inlineStr">
         <is>
           <t>دسته</t>
         </is>
       </c>
-      <c r="C4" s="6" t="inlineStr">
+      <c r="C4" s="16" t="inlineStr">
         <is>
           <t>اولویت</t>
         </is>
       </c>
-      <c r="D4" s="6" t="inlineStr">
+      <c r="D4" s="16" t="inlineStr">
         <is>
           <t>پیش‌شرط</t>
         </is>
       </c>
-      <c r="E4" s="6" t="inlineStr">
+      <c r="E4" s="16" t="inlineStr">
         <is>
           <t>روش اجرای دقیق</t>
         </is>
       </c>
-      <c r="F4" s="6" t="inlineStr">
+      <c r="F4" s="16" t="inlineStr">
         <is>
           <t>ورودی‌ها / شرایط</t>
         </is>
       </c>
-      <c r="G4" s="6" t="inlineStr">
+      <c r="G4" s="16" t="inlineStr">
         <is>
           <t>مدت مشاهده</t>
         </is>
       </c>
-      <c r="H4" s="6" t="inlineStr">
+      <c r="H4" s="16" t="inlineStr">
         <is>
           <t>رفتار مورد انتظار</t>
         </is>
       </c>
-      <c r="I4" s="6" t="inlineStr">
+      <c r="I4" s="16" t="inlineStr">
         <is>
           <t>وضعیت حفظ / latch</t>
         </is>
       </c>
-      <c r="J4" s="6" t="inlineStr">
+      <c r="J4" s="16" t="inlineStr">
         <is>
           <t>معیار قبولی</t>
         </is>
       </c>
-      <c r="K4" s="6" t="inlineStr">
+      <c r="K4" s="16" t="inlineStr">
         <is>
           <t>نتیجهٔ واقعی / اندازه‌گیری</t>
         </is>
       </c>
-      <c r="L4" s="6" t="inlineStr">
+      <c r="L4" s="16" t="inlineStr">
         <is>
           <t>وضعیت</t>
         </is>
       </c>
-      <c r="M4" s="6" t="inlineStr">
+      <c r="M4" s="16" t="inlineStr">
         <is>
           <t>شرح ایراد / تفاوت</t>
         </is>
       </c>
-      <c r="N4" s="6" t="inlineStr">
+      <c r="N4" s="16" t="inlineStr">
         <is>
           <t>مدرک تست / scope</t>
         </is>
       </c>
-      <c r="O4" s="6" t="inlineStr">
+      <c r="O4" s="16" t="inlineStr">
         <is>
           <t>commit</t>
         </is>
       </c>
-      <c r="P4" s="6" t="inlineStr">
+      <c r="P4" s="16" t="inlineStr">
         <is>
           <t>نام تست‌کننده</t>
         </is>
       </c>
-      <c r="Q4" s="6" t="inlineStr">
+      <c r="Q4" s="16" t="inlineStr">
         <is>
           <t>تاریخ</t>
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="7" t="inlineStr">
+    <row r="5" ht="54" customHeight="1">
+      <c r="A5" s="19" t="inlineStr">
         <is>
           <t>CL-001</t>
         </is>
       </c>
-      <c r="B5" s="7" t="inlineStr">
+      <c r="B5" s="20" t="inlineStr">
         <is>
           <t>بوت بدون رکورد</t>
         </is>
       </c>
-      <c r="C5" s="7" t="inlineStr">
+      <c r="C5" s="21" t="inlineStr">
         <is>
           <t>بالا</t>
         </is>
       </c>
-      <c r="D5" s="7" t="inlineStr">
+      <c r="D5" s="20" t="inlineStr">
         <is>
           <t>برد پاک یا دو صفحهٔ LUT پاک‌شده</t>
         </is>
       </c>
-      <c r="E5" s="7" t="inlineStr">
+      <c r="E5" s="20" t="inlineStr">
         <is>
           <t>گام ۱: مطمئن شو هیچ جدولی از پنل فرستاده نشده و فلش LUT خالی است (همهٔ خانه‌ها 65535).
 گام ۲: برد را روشن کن و صبر کن بوت کامل شود.
@@ -750,85 +933,85 @@
 گام ۴: جریان خوانده‌شدهٔ هر دو کانال را با همان بردی که ماژول LUT نداشت مقایسه کن؛ باید دقیقاً یکی باشد، چون مسیر اندازه‌گیری از خط گین و آفست استفاده می‌کند.</t>
         </is>
       </c>
-      <c r="F5" s="7" t="inlineStr">
+      <c r="F5" s="22" t="inlineStr">
         <is>
           <t>فلش LUT خالی (65535 = خانهٔ پاک‌شدهٔ فلش)</t>
         </is>
       </c>
-      <c r="G5" s="7" t="inlineStr">
+      <c r="G5" s="22" t="inlineStr">
         <is>
           <t>یک بوت</t>
         </is>
       </c>
-      <c r="H5" s="7" t="inlineStr">
+      <c r="H5" s="20" t="inlineStr">
         <is>
           <t>func__CalLut_Active هر دو کانال false؛ مسیر اندازه‌گیری از خط گین و آفست استفاده می‌کند</t>
         </is>
       </c>
-      <c r="I5" s="7" t="inlineStr">
+      <c r="I5" s="20" t="inlineStr">
         <is>
           <t>بدون latch</t>
         </is>
       </c>
-      <c r="J5" s="7" t="inlineStr">
+      <c r="J5" s="20" t="inlineStr">
         <is>
           <t>خوانش جریان دقیقاً برابر نسخهٔ پیش از افزودن ماژول</t>
         </is>
       </c>
-      <c r="K5" s="7" t="inlineStr">
+      <c r="K5" s="20" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="L5" s="7" t="inlineStr">
+      <c r="L5" s="23" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="M5" s="7" t="n"/>
-      <c r="N5" s="7" t="inlineStr">
-        <is>
-          <t>TESTER: fill</t>
-        </is>
-      </c>
-      <c r="O5" s="7" t="inlineStr">
-        <is>
-          <t>TESTER: fill</t>
-        </is>
-      </c>
-      <c r="P5" s="7" t="inlineStr">
-        <is>
-          <t>TESTER: fill</t>
-        </is>
-      </c>
-      <c r="Q5" s="7" t="inlineStr">
+      <c r="M5" s="20" t="n"/>
+      <c r="N5" s="20" t="inlineStr">
+        <is>
+          <t>TESTER: fill</t>
+        </is>
+      </c>
+      <c r="O5" s="22" t="inlineStr">
+        <is>
+          <t>TESTER: fill</t>
+        </is>
+      </c>
+      <c r="P5" s="22" t="inlineStr">
+        <is>
+          <t>TESTER: fill</t>
+        </is>
+      </c>
+      <c r="Q5" s="24" t="inlineStr">
         <is>
           <t>2026-10-05</t>
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="7" t="inlineStr">
+    <row r="6" ht="67.5" customHeight="1">
+      <c r="A6" s="19" t="inlineStr">
         <is>
           <t>CL-002</t>
         </is>
       </c>
-      <c r="B6" s="7" t="inlineStr">
+      <c r="B6" s="25" t="inlineStr">
         <is>
           <t>push سالم کانال ۱</t>
         </is>
       </c>
-      <c r="C6" s="7" t="inlineStr">
+      <c r="C6" s="26" t="inlineStr">
         <is>
           <t>بالا</t>
         </is>
       </c>
-      <c r="D6" s="7" t="inlineStr">
+      <c r="D6" s="25" t="inlineStr">
         <is>
           <t>لینک ESP برقرار</t>
         </is>
       </c>
-      <c r="E6" s="7" t="inlineStr">
+      <c r="E6" s="25" t="inlineStr">
         <is>
           <t>گام ۱: لینک ESP را وصل کن و پنل را باز کن.
 گام ۲: برای کانال ۱ یک جدول 17 تا 21 نقطه‌ای بساز و ارسال کن (اول LUT_BEGIN، بعد چانک‌ها، در آخر COMMIT).
@@ -837,85 +1020,85 @@
 گام ۵: فرمان LUT_RESET را بفرست و بعد از بالا آمدن برد ببین جدول کانال ۱ فعال شده است (Active = true).</t>
         </is>
       </c>
-      <c r="F6" s="7" t="inlineStr">
+      <c r="F6" s="27" t="inlineStr">
         <is>
           <t>LUT_BEGIN + CHUNKها + COMMIT با CRC32 درست</t>
         </is>
       </c>
-      <c r="G6" s="7" t="inlineStr">
+      <c r="G6" s="27" t="inlineStr">
         <is>
           <t>یک تبادل</t>
         </is>
       </c>
-      <c r="H6" s="7" t="inlineStr">
+      <c r="H6" s="25" t="inlineStr">
         <is>
           <t>LUT_ACK با CAL_LUT_ST_OK و CRC32 برابر CRC پنل</t>
         </is>
       </c>
-      <c r="I6" s="7" t="inlineStr">
+      <c r="I6" s="25" t="inlineStr">
         <is>
           <t>رکورد در فلش می‌ماند</t>
         </is>
       </c>
-      <c r="J6" s="7" t="inlineStr">
+      <c r="J6" s="25" t="inlineStr">
         <is>
           <t>status=0 و دو CRC32 برابر؛ پس از LUT_RESET، Active کانال ۱ = true</t>
         </is>
       </c>
-      <c r="K6" s="7" t="inlineStr">
+      <c r="K6" s="25" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="L6" s="7" t="inlineStr">
+      <c r="L6" s="23" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="M6" s="7" t="n"/>
-      <c r="N6" s="7" t="inlineStr">
-        <is>
-          <t>TESTER: fill</t>
-        </is>
-      </c>
-      <c r="O6" s="7" t="inlineStr">
-        <is>
-          <t>TESTER: fill</t>
-        </is>
-      </c>
-      <c r="P6" s="7" t="inlineStr">
-        <is>
-          <t>TESTER: fill</t>
-        </is>
-      </c>
-      <c r="Q6" s="7" t="inlineStr">
+      <c r="M6" s="25" t="n"/>
+      <c r="N6" s="25" t="inlineStr">
+        <is>
+          <t>TESTER: fill</t>
+        </is>
+      </c>
+      <c r="O6" s="27" t="inlineStr">
+        <is>
+          <t>TESTER: fill</t>
+        </is>
+      </c>
+      <c r="P6" s="27" t="inlineStr">
+        <is>
+          <t>TESTER: fill</t>
+        </is>
+      </c>
+      <c r="Q6" s="28" t="inlineStr">
         <is>
           <t>2026-10-05</t>
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="7" t="inlineStr">
+    <row r="7" ht="54" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
         <is>
           <t>CL-003</t>
         </is>
       </c>
-      <c r="B7" s="7" t="inlineStr">
+      <c r="B7" s="20" t="inlineStr">
         <is>
           <t>ماندگاری پس از قطع برق</t>
         </is>
       </c>
-      <c r="C7" s="7" t="inlineStr">
+      <c r="C7" s="21" t="inlineStr">
         <is>
           <t>بالا</t>
         </is>
       </c>
-      <c r="D7" s="7" t="inlineStr">
+      <c r="D7" s="29" t="inlineStr">
         <is>
           <t>CL-002 قبول</t>
         </is>
       </c>
-      <c r="E7" s="7" t="inlineStr">
+      <c r="E7" s="29" t="inlineStr">
         <is>
           <t>گام ۱: اول تست CL-002 را قبول کن تا یک جدول سالم روی برد فعال باشد و CRC32 آن را یادداشت کن.
 گام ۲: تغذیهٔ برد را کاملاً قطع کن (فقط ریست نرم کافی نیست) و دوباره وصل کن.
@@ -923,85 +1106,85 @@
 گام ۴: قطع و وصل کامل را 3 بار تکرار کن؛ هر سه بار CRC32 باید همان مقدار قبلی باشد.</t>
         </is>
       </c>
-      <c r="F7" s="7" t="inlineStr">
+      <c r="F7" s="22" t="inlineStr">
         <is>
           <t>قطع کامل تغذیه</t>
         </is>
       </c>
-      <c r="G7" s="7" t="inlineStr">
+      <c r="G7" s="22" t="inlineStr">
         <is>
           <t>۳ بار</t>
         </is>
       </c>
-      <c r="H7" s="7" t="inlineStr">
+      <c r="H7" s="20" t="inlineStr">
         <is>
           <t>رکورد سالم بازخوانی می‌شود و جدول فلش دوباره فعال است</t>
         </is>
       </c>
-      <c r="I7" s="7" t="inlineStr">
+      <c r="I7" s="20" t="inlineStr">
         <is>
           <t>ماندگار</t>
         </is>
       </c>
-      <c r="J7" s="7" t="inlineStr">
+      <c r="J7" s="20" t="inlineStr">
         <is>
           <t>func__CalLut_ActiveCrc32 بعد از هر بوت همان مقدار قبل است</t>
         </is>
       </c>
-      <c r="K7" s="7" t="inlineStr">
+      <c r="K7" s="20" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="L7" s="7" t="inlineStr">
+      <c r="L7" s="23" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="M7" s="7" t="n"/>
-      <c r="N7" s="7" t="inlineStr">
-        <is>
-          <t>TESTER: fill</t>
-        </is>
-      </c>
-      <c r="O7" s="7" t="inlineStr">
-        <is>
-          <t>TESTER: fill</t>
-        </is>
-      </c>
-      <c r="P7" s="7" t="inlineStr">
-        <is>
-          <t>TESTER: fill</t>
-        </is>
-      </c>
-      <c r="Q7" s="7" t="inlineStr">
+      <c r="M7" s="20" t="n"/>
+      <c r="N7" s="20" t="inlineStr">
+        <is>
+          <t>TESTER: fill</t>
+        </is>
+      </c>
+      <c r="O7" s="22" t="inlineStr">
+        <is>
+          <t>TESTER: fill</t>
+        </is>
+      </c>
+      <c r="P7" s="22" t="inlineStr">
+        <is>
+          <t>TESTER: fill</t>
+        </is>
+      </c>
+      <c r="Q7" s="24" t="inlineStr">
         <is>
           <t>2026-10-05</t>
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="7" t="inlineStr">
+    <row r="8" ht="54" customHeight="1">
+      <c r="A8" s="19" t="inlineStr">
         <is>
           <t>CL-004</t>
         </is>
       </c>
-      <c r="B8" s="7" t="inlineStr">
+      <c r="B8" s="25" t="inlineStr">
         <is>
           <t>CRC ناهمخوان</t>
         </is>
       </c>
-      <c r="C8" s="7" t="inlineStr">
+      <c r="C8" s="26" t="inlineStr">
         <is>
           <t>بالا</t>
         </is>
       </c>
-      <c r="D8" s="7" t="inlineStr">
+      <c r="D8" s="25" t="inlineStr">
         <is>
           <t>لینک برقرار</t>
         </is>
       </c>
-      <c r="E8" s="7" t="inlineStr">
+      <c r="E8" s="25" t="inlineStr">
         <is>
           <t>گام ۱: لینک ESP را وصل کن و CRC32 جدول فعال فعلی را یادداشت کن.
 گام ۲: یک جدول بفرست ولی در مرحلهٔ COMMIT عمداً CRC32 اشتباه بده (با CRC واقعی جدول یکی نباشد).
@@ -1009,85 +1192,85 @@
 گام ۴: CRC32 جدول فعال را دوباره بخوان؛ باید با گام ۱ یکی باشد، یعنی فلش دست‌نخورده مانده است.</t>
         </is>
       </c>
-      <c r="F8" s="7" t="inlineStr">
+      <c r="F8" s="27" t="inlineStr">
         <is>
           <t>CRC پنل ≠ CRC چیده‌شده</t>
         </is>
       </c>
-      <c r="G8" s="7" t="inlineStr">
+      <c r="G8" s="27" t="inlineStr">
         <is>
           <t>یک تبادل</t>
         </is>
       </c>
-      <c r="H8" s="7" t="inlineStr">
+      <c r="H8" s="25" t="inlineStr">
         <is>
           <t>رد شدن commit با CAL_LUT_ST_CRC؛ فلش دست‌نخورده</t>
         </is>
       </c>
-      <c r="I8" s="7" t="inlineStr">
+      <c r="I8" s="25" t="inlineStr">
         <is>
           <t>رکورد قبلی حفظ</t>
         </is>
       </c>
-      <c r="J8" s="7" t="inlineStr">
+      <c r="J8" s="25" t="inlineStr">
         <is>
           <t>status=6 و ActiveCrc32 تغییر نکرده</t>
         </is>
       </c>
-      <c r="K8" s="7" t="inlineStr">
+      <c r="K8" s="25" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="L8" s="7" t="inlineStr">
+      <c r="L8" s="23" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="M8" s="7" t="n"/>
-      <c r="N8" s="7" t="inlineStr">
-        <is>
-          <t>TESTER: fill</t>
-        </is>
-      </c>
-      <c r="O8" s="7" t="inlineStr">
-        <is>
-          <t>TESTER: fill</t>
-        </is>
-      </c>
-      <c r="P8" s="7" t="inlineStr">
-        <is>
-          <t>TESTER: fill</t>
-        </is>
-      </c>
-      <c r="Q8" s="7" t="inlineStr">
+      <c r="M8" s="25" t="n"/>
+      <c r="N8" s="25" t="inlineStr">
+        <is>
+          <t>TESTER: fill</t>
+        </is>
+      </c>
+      <c r="O8" s="27" t="inlineStr">
+        <is>
+          <t>TESTER: fill</t>
+        </is>
+      </c>
+      <c r="P8" s="27" t="inlineStr">
+        <is>
+          <t>TESTER: fill</t>
+        </is>
+      </c>
+      <c r="Q8" s="28" t="inlineStr">
         <is>
           <t>2026-10-05</t>
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="7" t="inlineStr">
+    <row r="9" ht="54" customHeight="1">
+      <c r="A9" s="19" t="inlineStr">
         <is>
           <t>CL-005</t>
         </is>
       </c>
-      <c r="B9" s="7" t="inlineStr">
+      <c r="B9" s="20" t="inlineStr">
         <is>
           <t>محور صعودی نبودن</t>
         </is>
       </c>
-      <c r="C9" s="7" t="inlineStr">
+      <c r="C9" s="21" t="inlineStr">
         <is>
           <t>بالا</t>
         </is>
       </c>
-      <c r="D9" s="7" t="inlineStr">
+      <c r="D9" s="20" t="inlineStr">
         <is>
           <t>لینک برقرار</t>
         </is>
       </c>
-      <c r="E9" s="7" t="inlineStr">
+      <c r="E9" s="20" t="inlineStr">
         <is>
           <t>گام ۱: لینک ESP را وصل کن.
 گام ۲: جدولی بساز که محور زنجیره‌اش (ChainMa) صعودیِ اکید نباشد؛ مثلاً یک نقطهٔ تکراری یا یک نقطه کمتر از قبلی بگذار.
@@ -1095,85 +1278,85 @@
 گام ۴: پاسخ برد را بخوان: وضعیت باید 4 باشد (CAL_LUT_ST_CHAIN) و جدول نباید فعال شود.</t>
         </is>
       </c>
-      <c r="F9" s="7" t="inlineStr">
+      <c r="F9" s="22" t="inlineStr">
         <is>
           <t>نقطهٔ تکراری یا نزولی در ChainMa</t>
         </is>
       </c>
-      <c r="G9" s="7" t="inlineStr">
+      <c r="G9" s="22" t="inlineStr">
         <is>
           <t>یک تبادل</t>
         </is>
       </c>
-      <c r="H9" s="7" t="inlineStr">
+      <c r="H9" s="20" t="inlineStr">
         <is>
           <t>رد با CAL_LUT_ST_CHAIN</t>
         </is>
       </c>
-      <c r="I9" s="7" t="inlineStr">
+      <c r="I9" s="20" t="inlineStr">
         <is>
           <t>بدون تغییر فلش</t>
         </is>
       </c>
-      <c r="J9" s="7" t="inlineStr">
+      <c r="J9" s="20" t="inlineStr">
         <is>
           <t>status=4</t>
         </is>
       </c>
-      <c r="K9" s="7" t="inlineStr">
+      <c r="K9" s="20" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="L9" s="7" t="inlineStr">
+      <c r="L9" s="23" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="M9" s="7" t="n"/>
-      <c r="N9" s="7" t="inlineStr">
-        <is>
-          <t>TESTER: fill</t>
-        </is>
-      </c>
-      <c r="O9" s="7" t="inlineStr">
-        <is>
-          <t>TESTER: fill</t>
-        </is>
-      </c>
-      <c r="P9" s="7" t="inlineStr">
-        <is>
-          <t>TESTER: fill</t>
-        </is>
-      </c>
-      <c r="Q9" s="7" t="inlineStr">
+      <c r="M9" s="20" t="n"/>
+      <c r="N9" s="20" t="inlineStr">
+        <is>
+          <t>TESTER: fill</t>
+        </is>
+      </c>
+      <c r="O9" s="22" t="inlineStr">
+        <is>
+          <t>TESTER: fill</t>
+        </is>
+      </c>
+      <c r="P9" s="22" t="inlineStr">
+        <is>
+          <t>TESTER: fill</t>
+        </is>
+      </c>
+      <c r="Q9" s="24" t="inlineStr">
         <is>
           <t>2026-10-05</t>
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="7" t="inlineStr">
+    <row r="10" ht="54" customHeight="1">
+      <c r="A10" s="19" t="inlineStr">
         <is>
           <t>CL-006</t>
         </is>
       </c>
-      <c r="B10" s="7" t="inlineStr">
+      <c r="B10" s="25" t="inlineStr">
         <is>
           <t>افت محور جریان</t>
         </is>
       </c>
-      <c r="C10" s="7" t="inlineStr">
+      <c r="C10" s="27" t="inlineStr">
         <is>
           <t>متوسط</t>
         </is>
       </c>
-      <c r="D10" s="7" t="inlineStr">
+      <c r="D10" s="25" t="inlineStr">
         <is>
           <t>لینک برقرار</t>
         </is>
       </c>
-      <c r="E10" s="7" t="inlineStr">
+      <c r="E10" s="25" t="inlineStr">
         <is>
           <t>گام ۱: لینک ESP را وصل کن.
 گام ۲: جدولی بساز که جریان باتری در یکی از نقطه‌ها از نقطهٔ قبلی کمتر باشد (افت داشته باشد).
@@ -1181,85 +1364,85 @@
 گام ۴: پاسخ برد را بخوان: وضعیت باید 5 باشد (CAL_LUT_ST_DIP) و جدول نباید فعال شود.</t>
         </is>
       </c>
-      <c r="F10" s="7" t="inlineStr">
+      <c r="F10" s="27" t="inlineStr">
         <is>
           <t>نقطه‌ای کمتر از نقطهٔ قبل</t>
         </is>
       </c>
-      <c r="G10" s="7" t="inlineStr">
+      <c r="G10" s="27" t="inlineStr">
         <is>
           <t>یک تبادل</t>
         </is>
       </c>
-      <c r="H10" s="7" t="inlineStr">
+      <c r="H10" s="25" t="inlineStr">
         <is>
           <t>رد با CAL_LUT_ST_DIP (جریان باتری افت دارد)</t>
         </is>
       </c>
-      <c r="I10" s="7" t="inlineStr">
+      <c r="I10" s="25" t="inlineStr">
         <is>
           <t>بدون تغییر فلش</t>
         </is>
       </c>
-      <c r="J10" s="7" t="inlineStr">
+      <c r="J10" s="25" t="inlineStr">
         <is>
           <t>status=5</t>
         </is>
       </c>
-      <c r="K10" s="7" t="inlineStr">
+      <c r="K10" s="25" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="L10" s="7" t="inlineStr">
+      <c r="L10" s="23" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="M10" s="7" t="n"/>
-      <c r="N10" s="7" t="inlineStr">
-        <is>
-          <t>TESTER: fill</t>
-        </is>
-      </c>
-      <c r="O10" s="7" t="inlineStr">
-        <is>
-          <t>TESTER: fill</t>
-        </is>
-      </c>
-      <c r="P10" s="7" t="inlineStr">
-        <is>
-          <t>TESTER: fill</t>
-        </is>
-      </c>
-      <c r="Q10" s="7" t="inlineStr">
+      <c r="M10" s="25" t="n"/>
+      <c r="N10" s="25" t="inlineStr">
+        <is>
+          <t>TESTER: fill</t>
+        </is>
+      </c>
+      <c r="O10" s="27" t="inlineStr">
+        <is>
+          <t>TESTER: fill</t>
+        </is>
+      </c>
+      <c r="P10" s="27" t="inlineStr">
+        <is>
+          <t>TESTER: fill</t>
+        </is>
+      </c>
+      <c r="Q10" s="28" t="inlineStr">
         <is>
           <t>2026-10-05</t>
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="7" t="inlineStr">
+    <row r="11" ht="54" customHeight="1">
+      <c r="A11" s="19" t="inlineStr">
         <is>
           <t>CL-007</t>
         </is>
       </c>
-      <c r="B11" s="7" t="inlineStr">
+      <c r="B11" s="20" t="inlineStr">
         <is>
           <t>تعداد نقاط نامعتبر</t>
         </is>
       </c>
-      <c r="C11" s="7" t="inlineStr">
+      <c r="C11" s="22" t="inlineStr">
         <is>
           <t>متوسط</t>
         </is>
       </c>
-      <c r="D11" s="7" t="inlineStr">
+      <c r="D11" s="20" t="inlineStr">
         <is>
           <t>لینک برقرار</t>
         </is>
       </c>
-      <c r="E11" s="7" t="inlineStr">
+      <c r="E11" s="20" t="inlineStr">
         <is>
           <t>گام ۱: لینک ESP را وصل کن.
 گام ۲: یک جدول فقط با 1 نقطه بفرست و COMMIT کن؛ پاسخ را بخوان.
@@ -1267,85 +1450,85 @@
 گام ۴: هر دو بار وضعیت باید 2 باشد (CAL_LUT_ST_COUNT)، چون تعداد نقطهٔ مجاز 2 تا 24 است.</t>
         </is>
       </c>
-      <c r="F11" s="7" t="inlineStr">
+      <c r="F11" s="22" t="inlineStr">
         <is>
           <t>points &lt; 2 یا &gt; 24</t>
         </is>
       </c>
-      <c r="G11" s="7" t="inlineStr">
+      <c r="G11" s="22" t="inlineStr">
         <is>
           <t>دو تبادل</t>
         </is>
       </c>
-      <c r="H11" s="7" t="inlineStr">
+      <c r="H11" s="20" t="inlineStr">
         <is>
           <t>هر دو با CAL_LUT_ST_COUNT رد می‌شوند</t>
         </is>
       </c>
-      <c r="I11" s="7" t="inlineStr">
+      <c r="I11" s="20" t="inlineStr">
         <is>
           <t>بدون تغییر فلش</t>
         </is>
       </c>
-      <c r="J11" s="7" t="inlineStr">
+      <c r="J11" s="20" t="inlineStr">
         <is>
           <t>status=2 در هر دو</t>
         </is>
       </c>
-      <c r="K11" s="7" t="inlineStr">
+      <c r="K11" s="20" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="L11" s="7" t="inlineStr">
+      <c r="L11" s="23" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="M11" s="7" t="n"/>
-      <c r="N11" s="7" t="inlineStr">
-        <is>
-          <t>TESTER: fill</t>
-        </is>
-      </c>
-      <c r="O11" s="7" t="inlineStr">
-        <is>
-          <t>TESTER: fill</t>
-        </is>
-      </c>
-      <c r="P11" s="7" t="inlineStr">
-        <is>
-          <t>TESTER: fill</t>
-        </is>
-      </c>
-      <c r="Q11" s="7" t="inlineStr">
+      <c r="M11" s="20" t="n"/>
+      <c r="N11" s="20" t="inlineStr">
+        <is>
+          <t>TESTER: fill</t>
+        </is>
+      </c>
+      <c r="O11" s="22" t="inlineStr">
+        <is>
+          <t>TESTER: fill</t>
+        </is>
+      </c>
+      <c r="P11" s="22" t="inlineStr">
+        <is>
+          <t>TESTER: fill</t>
+        </is>
+      </c>
+      <c r="Q11" s="24" t="inlineStr">
         <is>
           <t>2026-10-05</t>
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="7" t="inlineStr">
+    <row r="12" ht="54" customHeight="1">
+      <c r="A12" s="19" t="inlineStr">
         <is>
           <t>CL-008</t>
         </is>
       </c>
-      <c r="B12" s="7" t="inlineStr">
+      <c r="B12" s="25" t="inlineStr">
         <is>
           <t>تکهٔ گم‌شده</t>
         </is>
       </c>
-      <c r="C12" s="7" t="inlineStr">
+      <c r="C12" s="27" t="inlineStr">
         <is>
           <t>متوسط</t>
         </is>
       </c>
-      <c r="D12" s="7" t="inlineStr">
+      <c r="D12" s="25" t="inlineStr">
         <is>
           <t>لینک برقرار</t>
         </is>
       </c>
-      <c r="E12" s="7" t="inlineStr">
+      <c r="E12" s="25" t="inlineStr">
         <is>
           <t>گام ۱: لینک ESP را وصل کن و یک جدول چندچانکه آماده کن.
 گام ۲: همهٔ چانک‌ها را بفرست به‌جز یکی؛ عمداً یک چانک را نفرست.
@@ -1353,170 +1536,170 @@
 گام ۴: پاسخ برد را بخوان: وضعیت باید 3 باشد (CAL_LUT_ST_MISSING) و هیچ جدولی فعال نشود.</t>
         </is>
       </c>
-      <c r="F12" s="7" t="inlineStr">
+      <c r="F12" s="27" t="inlineStr">
         <is>
           <t>یک تکه نرسیده</t>
         </is>
       </c>
-      <c r="G12" s="7" t="inlineStr">
+      <c r="G12" s="27" t="inlineStr">
         <is>
           <t>یک تبادل</t>
         </is>
       </c>
-      <c r="H12" s="7" t="inlineStr">
+      <c r="H12" s="25" t="inlineStr">
         <is>
           <t>رد با CAL_LUT_ST_MISSING</t>
         </is>
       </c>
-      <c r="I12" s="7" t="inlineStr">
+      <c r="I12" s="25" t="inlineStr">
         <is>
           <t>بدون تغییر فلش</t>
         </is>
       </c>
-      <c r="J12" s="7" t="inlineStr">
+      <c r="J12" s="25" t="inlineStr">
         <is>
           <t>status=3</t>
         </is>
       </c>
-      <c r="K12" s="7" t="inlineStr">
+      <c r="K12" s="25" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="L12" s="7" t="inlineStr">
+      <c r="L12" s="23" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="M12" s="7" t="n"/>
-      <c r="N12" s="7" t="inlineStr">
-        <is>
-          <t>TESTER: fill</t>
-        </is>
-      </c>
-      <c r="O12" s="7" t="inlineStr">
-        <is>
-          <t>TESTER: fill</t>
-        </is>
-      </c>
-      <c r="P12" s="7" t="inlineStr">
-        <is>
-          <t>TESTER: fill</t>
-        </is>
-      </c>
-      <c r="Q12" s="7" t="inlineStr">
+      <c r="M12" s="25" t="n"/>
+      <c r="N12" s="25" t="inlineStr">
+        <is>
+          <t>TESTER: fill</t>
+        </is>
+      </c>
+      <c r="O12" s="27" t="inlineStr">
+        <is>
+          <t>TESTER: fill</t>
+        </is>
+      </c>
+      <c r="P12" s="27" t="inlineStr">
+        <is>
+          <t>TESTER: fill</t>
+        </is>
+      </c>
+      <c r="Q12" s="28" t="inlineStr">
         <is>
           <t>2026-10-05</t>
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="7" t="inlineStr">
+    <row r="13" ht="40.5" customHeight="1">
+      <c r="A13" s="19" t="inlineStr">
         <is>
           <t>CL-009</t>
         </is>
       </c>
-      <c r="B13" s="7" t="inlineStr">
+      <c r="B13" s="20" t="inlineStr">
         <is>
           <t>commit بدون begin</t>
         </is>
       </c>
-      <c r="C13" s="7" t="inlineStr">
+      <c r="C13" s="22" t="inlineStr">
         <is>
           <t>پایین</t>
         </is>
       </c>
-      <c r="D13" s="7" t="inlineStr">
+      <c r="D13" s="20" t="inlineStr">
         <is>
           <t>لینک برقرار</t>
         </is>
       </c>
-      <c r="E13" s="7" t="inlineStr">
+      <c r="E13" s="20" t="inlineStr">
         <is>
           <t>گام ۱: لینک ESP را وصل کن.
 گام ۲: بدون اینکه LUT_BEGIN بفرستی، مستقیم COMMIT بفرست.
 گام ۳: پاسخ برد را بخوان: وضعیت باید 1 باشد (CAL_LUT_ST_NO_STAGE) و هیچ اتفاقی برای جدول فعال نیفتد.</t>
         </is>
       </c>
-      <c r="F13" s="7" t="inlineStr">
+      <c r="F13" s="22" t="inlineStr">
         <is>
           <t>بدون مرحلهٔ چیدن</t>
         </is>
       </c>
-      <c r="G13" s="7" t="inlineStr">
+      <c r="G13" s="22" t="inlineStr">
         <is>
           <t>یک تبادل</t>
         </is>
       </c>
-      <c r="H13" s="7" t="inlineStr">
+      <c r="H13" s="20" t="inlineStr">
         <is>
           <t>رد با CAL_LUT_ST_NO_STAGE</t>
         </is>
       </c>
-      <c r="I13" s="7" t="inlineStr">
+      <c r="I13" s="20" t="inlineStr">
         <is>
           <t>بدون تغییر فلش</t>
         </is>
       </c>
-      <c r="J13" s="7" t="inlineStr">
+      <c r="J13" s="20" t="inlineStr">
         <is>
           <t>status=1</t>
         </is>
       </c>
-      <c r="K13" s="7" t="inlineStr">
+      <c r="K13" s="20" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="L13" s="7" t="inlineStr">
+      <c r="L13" s="23" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="M13" s="7" t="n"/>
-      <c r="N13" s="7" t="inlineStr">
-        <is>
-          <t>TESTER: fill</t>
-        </is>
-      </c>
-      <c r="O13" s="7" t="inlineStr">
-        <is>
-          <t>TESTER: fill</t>
-        </is>
-      </c>
-      <c r="P13" s="7" t="inlineStr">
-        <is>
-          <t>TESTER: fill</t>
-        </is>
-      </c>
-      <c r="Q13" s="7" t="inlineStr">
+      <c r="M13" s="20" t="n"/>
+      <c r="N13" s="20" t="inlineStr">
+        <is>
+          <t>TESTER: fill</t>
+        </is>
+      </c>
+      <c r="O13" s="22" t="inlineStr">
+        <is>
+          <t>TESTER: fill</t>
+        </is>
+      </c>
+      <c r="P13" s="22" t="inlineStr">
+        <is>
+          <t>TESTER: fill</t>
+        </is>
+      </c>
+      <c r="Q13" s="24" t="inlineStr">
         <is>
           <t>2026-10-05</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="7" t="inlineStr">
+    <row r="14" ht="54" customHeight="1">
+      <c r="A14" s="19" t="inlineStr">
         <is>
           <t>CL-010</t>
         </is>
       </c>
-      <c r="B14" s="7" t="inlineStr">
+      <c r="B14" s="25" t="inlineStr">
         <is>
           <t>قطع برق وسط نوشتن</t>
         </is>
       </c>
-      <c r="C14" s="7" t="inlineStr">
+      <c r="C14" s="26" t="inlineStr">
         <is>
           <t>بالا</t>
         </is>
       </c>
-      <c r="D14" s="7" t="inlineStr">
+      <c r="D14" s="30" t="inlineStr">
         <is>
           <t>CL-002 قبول</t>
         </is>
       </c>
-      <c r="E14" s="7" t="inlineStr">
+      <c r="E14" s="30" t="inlineStr">
         <is>
           <t>گام ۱: اول یک جدول سالم commit کن (CL-002) و CRC32 آن را یادداشت کن.
 گام ۲: یک جدول تازه بفرست و دقیقاً وسط COMMIT (موقع پاک/نوشتن فلش) تغذیهٔ برد را قطع کن.
@@ -1524,85 +1707,85 @@
 گام ۴: این کار را 5 بار تکرار کن و هر بار بعد از بوت سالم‌بودن رکورد فعال (RecordValidate = true) را بررسی کن.</t>
         </is>
       </c>
-      <c r="F14" s="7" t="inlineStr">
+      <c r="F14" s="27" t="inlineStr">
         <is>
           <t>قطع برق حین erase/program</t>
         </is>
       </c>
-      <c r="G14" s="7" t="inlineStr">
+      <c r="G14" s="27" t="inlineStr">
         <is>
           <t>۵ تکرار</t>
         </is>
       </c>
-      <c r="H14" s="7" t="inlineStr">
+      <c r="H14" s="25" t="inlineStr">
         <is>
           <t>یا رکورد قبلی سالم می‌ماند یا رکورد جدید کامل؛ هرگز حالت سوم</t>
         </is>
       </c>
-      <c r="I14" s="7" t="inlineStr">
+      <c r="I14" s="25" t="inlineStr">
         <is>
           <t>پینگ‌پنگ</t>
         </is>
       </c>
-      <c r="J14" s="7" t="inlineStr">
+      <c r="J14" s="25" t="inlineStr">
         <is>
           <t>پس از هر بوت، RecordValidate روی رکورد فعال true است</t>
         </is>
       </c>
-      <c r="K14" s="7" t="inlineStr">
+      <c r="K14" s="25" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="L14" s="7" t="inlineStr">
+      <c r="L14" s="23" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="M14" s="7" t="n"/>
-      <c r="N14" s="7" t="inlineStr">
-        <is>
-          <t>TESTER: fill</t>
-        </is>
-      </c>
-      <c r="O14" s="7" t="inlineStr">
-        <is>
-          <t>TESTER: fill</t>
-        </is>
-      </c>
-      <c r="P14" s="7" t="inlineStr">
-        <is>
-          <t>TESTER: fill</t>
-        </is>
-      </c>
-      <c r="Q14" s="7" t="inlineStr">
+      <c r="M14" s="25" t="n"/>
+      <c r="N14" s="25" t="inlineStr">
+        <is>
+          <t>TESTER: fill</t>
+        </is>
+      </c>
+      <c r="O14" s="27" t="inlineStr">
+        <is>
+          <t>TESTER: fill</t>
+        </is>
+      </c>
+      <c r="P14" s="27" t="inlineStr">
+        <is>
+          <t>TESTER: fill</t>
+        </is>
+      </c>
+      <c r="Q14" s="28" t="inlineStr">
         <is>
           <t>2026-10-05</t>
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="7" t="inlineStr">
+    <row r="15" ht="54" customHeight="1">
+      <c r="A15" s="19" t="inlineStr">
         <is>
           <t>CL-011</t>
         </is>
       </c>
-      <c r="B15" s="7" t="inlineStr">
+      <c r="B15" s="20" t="inlineStr">
         <is>
           <t>استقلال از NVM پارامترها</t>
         </is>
       </c>
-      <c r="C15" s="7" t="inlineStr">
+      <c r="C15" s="21" t="inlineStr">
         <is>
           <t>بالا</t>
         </is>
       </c>
-      <c r="D15" s="7" t="inlineStr">
+      <c r="D15" s="20" t="inlineStr">
         <is>
           <t>چند پارامتر غیرپیش‌فرض ذخیره شده</t>
         </is>
       </c>
-      <c r="E15" s="7" t="inlineStr">
+      <c r="E15" s="20" t="inlineStr">
         <is>
           <t>گام ۱: چند پارامتر را از پنل از مقدار پیش‌فرض تغییر بده و ذخیره کن؛ مقدارها را یادداشت کن.
 گام ۲: یک جدول LUT کامل push کن و commit کن.
@@ -1610,85 +1793,85 @@
 گام ۴: برد را ری‌استارت کن و همهٔ پارامترها و جدول را بخوان؛ هیچ‌کدام نباید دیگری را خراب کرده باشد و همه باید با مقدارهای یادداشت‌شده یکی باشند.</t>
         </is>
       </c>
-      <c r="F15" s="7" t="inlineStr">
+      <c r="F15" s="22" t="inlineStr">
         <is>
           <t>دو مسیر ذخیره‌سازی پشت سر هم</t>
         </is>
       </c>
-      <c r="G15" s="7" t="inlineStr">
+      <c r="G15" s="22" t="inlineStr">
         <is>
           <t>دو چرخه</t>
         </is>
       </c>
-      <c r="H15" s="7" t="inlineStr">
+      <c r="H15" s="20" t="inlineStr">
         <is>
           <t>هیچ‌کدام دیگری را خراب نمی‌کند</t>
         </is>
       </c>
-      <c r="I15" s="7" t="inlineStr">
+      <c r="I15" s="20" t="inlineStr">
         <is>
           <t>هر دو ماندگار</t>
         </is>
       </c>
-      <c r="J15" s="7" t="inlineStr">
+      <c r="J15" s="20" t="inlineStr">
         <is>
           <t>همهٔ پارامترها و جدول پس از بوت صحیح‌اند</t>
         </is>
       </c>
-      <c r="K15" s="7" t="inlineStr">
+      <c r="K15" s="20" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="L15" s="7" t="inlineStr">
+      <c r="L15" s="23" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="M15" s="7" t="n"/>
-      <c r="N15" s="7" t="inlineStr">
-        <is>
-          <t>TESTER: fill</t>
-        </is>
-      </c>
-      <c r="O15" s="7" t="inlineStr">
-        <is>
-          <t>TESTER: fill</t>
-        </is>
-      </c>
-      <c r="P15" s="7" t="inlineStr">
-        <is>
-          <t>TESTER: fill</t>
-        </is>
-      </c>
-      <c r="Q15" s="7" t="inlineStr">
+      <c r="M15" s="20" t="n"/>
+      <c r="N15" s="20" t="inlineStr">
+        <is>
+          <t>TESTER: fill</t>
+        </is>
+      </c>
+      <c r="O15" s="22" t="inlineStr">
+        <is>
+          <t>TESTER: fill</t>
+        </is>
+      </c>
+      <c r="P15" s="22" t="inlineStr">
+        <is>
+          <t>TESTER: fill</t>
+        </is>
+      </c>
+      <c r="Q15" s="24" t="inlineStr">
         <is>
           <t>2026-10-05</t>
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="7" t="inlineStr">
+    <row r="16" ht="54" customHeight="1">
+      <c r="A16" s="19" t="inlineStr">
         <is>
           <t>CL-012</t>
         </is>
       </c>
-      <c r="B16" s="7" t="inlineStr">
+      <c r="B16" s="25" t="inlineStr">
         <is>
           <t>idle شدن شارژر هنگام ریست</t>
         </is>
       </c>
-      <c r="C16" s="7" t="inlineStr">
+      <c r="C16" s="26" t="inlineStr">
         <is>
           <t>بالا</t>
         </is>
       </c>
-      <c r="D16" s="7" t="inlineStr">
+      <c r="D16" s="25" t="inlineStr">
         <is>
           <t>جدول فعال، شارژ در جریان</t>
         </is>
       </c>
-      <c r="E16" s="7" t="inlineStr">
+      <c r="E16" s="25" t="inlineStr">
         <is>
           <t>گام ۱: یک جدول فعال کن و شارژ را در حالت BULK راه بینداز تا کانال در حال شارژ PWM داشته باشد.
 گام ۲: اسیلوسکوپ را روی گیت همان کانال بگذار.
@@ -1696,85 +1879,85 @@
 گام ۴: روی اسکوپ ببین که پیش از ریست، duty اول صفر شده و شارژر idle شده باشد؛ ریست نباید وسط پالس اتفاق بیفتد.</t>
         </is>
       </c>
-      <c r="F16" s="7" t="inlineStr">
+      <c r="F16" s="27" t="inlineStr">
         <is>
           <t>درخواست ریست با PWM فعال</t>
         </is>
       </c>
-      <c r="G16" s="7" t="inlineStr">
+      <c r="G16" s="27" t="inlineStr">
         <is>
           <t>یک تبادل</t>
         </is>
       </c>
-      <c r="H16" s="7" t="inlineStr">
+      <c r="H16" s="25" t="inlineStr">
         <is>
           <t>قبل از ریست هر دو دیوتی صفر و شارژر idle می‌شود</t>
         </is>
       </c>
-      <c r="I16" s="7" t="inlineStr">
+      <c r="I16" s="25" t="inlineStr">
         <is>
           <t>بدون latch</t>
         </is>
       </c>
-      <c r="J16" s="7" t="inlineStr">
+      <c r="J16" s="25" t="inlineStr">
         <is>
           <t>اسیلوسکوپ روی گیت: صفر پیش از ریست</t>
         </is>
       </c>
-      <c r="K16" s="7" t="inlineStr">
+      <c r="K16" s="25" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="L16" s="7" t="inlineStr">
+      <c r="L16" s="23" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="M16" s="7" t="n"/>
-      <c r="N16" s="7" t="inlineStr">
-        <is>
-          <t>TESTER: fill</t>
-        </is>
-      </c>
-      <c r="O16" s="7" t="inlineStr">
-        <is>
-          <t>TESTER: fill</t>
-        </is>
-      </c>
-      <c r="P16" s="7" t="inlineStr">
-        <is>
-          <t>TESTER: fill</t>
-        </is>
-      </c>
-      <c r="Q16" s="7" t="inlineStr">
+      <c r="M16" s="25" t="n"/>
+      <c r="N16" s="25" t="inlineStr">
+        <is>
+          <t>TESTER: fill</t>
+        </is>
+      </c>
+      <c r="O16" s="27" t="inlineStr">
+        <is>
+          <t>TESTER: fill</t>
+        </is>
+      </c>
+      <c r="P16" s="27" t="inlineStr">
+        <is>
+          <t>TESTER: fill</t>
+        </is>
+      </c>
+      <c r="Q16" s="28" t="inlineStr">
         <is>
           <t>2026-10-05</t>
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="7" t="inlineStr">
+    <row r="17" ht="54" customHeight="1">
+      <c r="A17" s="19" t="inlineStr">
         <is>
           <t>CL-013</t>
         </is>
       </c>
-      <c r="B17" s="7" t="inlineStr">
+      <c r="B17" s="20" t="inlineStr">
         <is>
           <t>تغییر نسخهٔ قالب</t>
         </is>
       </c>
-      <c r="C17" s="7" t="inlineStr">
+      <c r="C17" s="22" t="inlineStr">
         <is>
           <t>پایین</t>
         </is>
       </c>
-      <c r="D17" s="7" t="inlineStr">
+      <c r="D17" s="20" t="inlineStr">
         <is>
           <t>رکورد معتبر نسخهٔ ۱</t>
         </is>
       </c>
-      <c r="E17" s="7" t="inlineStr">
+      <c r="E17" s="20" t="inlineStr">
         <is>
           <t>گام ۱: روی برد یک رکورد LUT معتبر با نسخهٔ 1 داشته باش (قبلاً commit شده باشد).
 گام ۲: ثابت CAL_LUT_VERSION را در کد بالا ببر و فرم‌ور جدید را روی همان برد فلش کن.
@@ -1782,85 +1965,85 @@
 گام ۴: باید جدول فعال نباشد (Active = false) و خوانش جریان به جدول کامپایل‌شده (خط گین و آفست) برگشته باشد.</t>
         </is>
       </c>
-      <c r="F17" s="7" t="inlineStr">
+      <c r="F17" s="22" t="inlineStr">
         <is>
           <t>نسخهٔ رکورد قدیمی</t>
         </is>
       </c>
-      <c r="G17" s="7" t="inlineStr">
+      <c r="G17" s="22" t="inlineStr">
         <is>
           <t>یک بوت</t>
         </is>
       </c>
-      <c r="H17" s="7" t="inlineStr">
+      <c r="H17" s="20" t="inlineStr">
         <is>
           <t>رکورد قدیمی نامعتبر و بازگشت به جدول کامپایل‌شده</t>
         </is>
       </c>
-      <c r="I17" s="7" t="inlineStr">
+      <c r="I17" s="20" t="inlineStr">
         <is>
           <t>بدون نیم‌ارتقای بی‌صدا</t>
         </is>
       </c>
-      <c r="J17" s="7" t="inlineStr">
+      <c r="J17" s="20" t="inlineStr">
         <is>
           <t>Active=false و خوانش‌ها برابر خط گین و آفست</t>
         </is>
       </c>
-      <c r="K17" s="7" t="inlineStr">
+      <c r="K17" s="20" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="L17" s="7" t="inlineStr">
+      <c r="L17" s="23" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="M17" s="7" t="n"/>
-      <c r="N17" s="7" t="inlineStr">
-        <is>
-          <t>TESTER: fill</t>
-        </is>
-      </c>
-      <c r="O17" s="7" t="inlineStr">
-        <is>
-          <t>TESTER: fill</t>
-        </is>
-      </c>
-      <c r="P17" s="7" t="inlineStr">
-        <is>
-          <t>TESTER: fill</t>
-        </is>
-      </c>
-      <c r="Q17" s="7" t="inlineStr">
+      <c r="M17" s="20" t="n"/>
+      <c r="N17" s="20" t="inlineStr">
+        <is>
+          <t>TESTER: fill</t>
+        </is>
+      </c>
+      <c r="O17" s="22" t="inlineStr">
+        <is>
+          <t>TESTER: fill</t>
+        </is>
+      </c>
+      <c r="P17" s="22" t="inlineStr">
+        <is>
+          <t>TESTER: fill</t>
+        </is>
+      </c>
+      <c r="Q17" s="24" t="inlineStr">
         <is>
           <t>2026-10-05</t>
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="7" t="inlineStr">
+    <row r="18" ht="54" customHeight="1">
+      <c r="A18" s="19" t="inlineStr">
         <is>
           <t>CL-014</t>
         </is>
       </c>
-      <c r="B18" s="7" t="inlineStr">
+      <c r="B18" s="25" t="inlineStr">
         <is>
           <t>LUT_READ بازخوانی واقعی هر دو کانال</t>
         </is>
       </c>
-      <c r="C18" s="7" t="inlineStr">
+      <c r="C18" s="26" t="inlineStr">
         <is>
           <t>بالا</t>
         </is>
       </c>
-      <c r="D18" s="7" t="inlineStr">
+      <c r="D18" s="25" t="inlineStr">
         <is>
           <t>رکورد LUT فعال در فلش یا جدول تازه commit شده</t>
         </is>
       </c>
-      <c r="E18" s="7" t="inlineStr">
+      <c r="E18" s="25" t="inlineStr">
         <is>
           <t>گام ۱: یک جدول فعال روی فلش داشته باش (یا تازه commit کن) و نقاط هر دو کانال را از پنل یادداشت کن.
 گام ۲: از لینک ESP فرمان LUT_READ بفرست.
@@ -1868,85 +2051,85 @@
 گام ۴: برد را ریست کن و گام ۲ و ۳ را تکرار کن؛ دادهٔ ناقص نباید «فعال» فرض شود و پنل باید هر عدم تطابق (mismatch) را گزارش کند.</t>
         </is>
       </c>
-      <c r="F18" s="7" t="inlineStr">
+      <c r="F18" s="27" t="inlineStr">
         <is>
           <t>counts/BatteryMa نقاط فعال، به‌خصوص battery 2</t>
         </is>
       </c>
-      <c r="G18" s="7" t="inlineStr">
+      <c r="G18" s="27" t="inlineStr">
         <is>
           <t>یک درخواست قبل و یک درخواست بعد از reset</t>
         </is>
       </c>
-      <c r="H18" s="7" t="inlineStr">
+      <c r="H18" s="25" t="inlineStr">
         <is>
           <t>LUT_DATA مقدار واقعی هر نقطه را برمی‌گرداند؛ کانال غیرفعال فریم صفرنقطه‌ای می‌دهد؛ دادهٔ ناقص active فرض نمی‌شود</t>
         </is>
       </c>
-      <c r="I18" s="7" t="inlineStr">
+      <c r="I18" s="25" t="inlineStr">
         <is>
           <t>رکورد فلش باید بعد از reset همان نقاط را حفظ کند</t>
         </is>
       </c>
-      <c r="J18" s="7" t="inlineStr">
+      <c r="J18" s="25" t="inlineStr">
         <is>
           <t>تطبیق byte/point با func__CalLut_Points/Counts/BatteryMa و گزارش mismatch در پنل</t>
         </is>
       </c>
-      <c r="K18" s="7" t="inlineStr">
+      <c r="K18" s="25" t="inlineStr">
         <is>
           <t>Host PASS: 159 check؛ شامل دو فریم واقعی LUT_DATA، battery 2 مستقل و transition غیرصفر→صفر؛ برد فیزیکی pending</t>
         </is>
       </c>
-      <c r="L18" s="7" t="inlineStr">
+      <c r="L18" s="23" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="M18" s="7" t="inlineStr">
+      <c r="M18" s="25" t="inlineStr">
         <is>
           <t>Host جای اندازه‌گیری برد را نمی‌گیرد؛ فلش و readback روی برد واقعی لازم است</t>
         </is>
       </c>
-      <c r="N18" s="7" t="inlineStr">
+      <c r="N18" s="25" t="inlineStr">
         <is>
           <t>Firmware/Modules/CalLut/Tester/run_host_test_cal_lut.sh</t>
         </is>
       </c>
-      <c r="O18" s="7" t="inlineStr">
+      <c r="O18" s="27" t="inlineStr">
         <is>
           <t>WORKTREE</t>
         </is>
       </c>
-      <c r="P18" s="7" t="inlineStr"/>
-      <c r="Q18" s="7" t="inlineStr">
+      <c r="P18" s="27" t="inlineStr"/>
+      <c r="Q18" s="28" t="inlineStr">
         <is>
           <t>2026-10-07</t>
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="7" t="inlineStr">
+    <row r="19" ht="67.5" customHeight="1">
+      <c r="A19" s="19" t="inlineStr">
         <is>
           <t>CL-015</t>
         </is>
       </c>
-      <c r="B19" s="7" t="inlineStr">
+      <c r="B19" s="20" t="inlineStr">
         <is>
           <t>حذف override با صفرنقطه</t>
         </is>
       </c>
-      <c r="C19" s="7" t="inlineStr">
+      <c r="C19" s="21" t="inlineStr">
         <is>
           <t>بالا</t>
         </is>
       </c>
-      <c r="D19" s="7" t="inlineStr">
+      <c r="D19" s="29" t="inlineStr">
         <is>
           <t>CL-002 یا رکورد فعال با هر دو کانال</t>
         </is>
       </c>
-      <c r="E19" s="7" t="inlineStr">
+      <c r="E19" s="29" t="inlineStr">
         <is>
           <t>گام ۱: از قبل روی هر دو کانال جدول فعال داشته باش (CL-002 برای هر دو) و نقاط کانال ۲ را یادداشت کن.
 گام ۲: LUT_BEGIN را با n1=5 و n2=0 بفرست، چانک‌ها را فقط برای کانال ۱ بفرست و با CRC درست COMMIT کن.
@@ -1955,85 +2138,85 @@
 گام ۵: در پنل تأیید بگیر که تغییر کانال ۲ «changed-confirmed» است و CRC یا count جای مقادیر واقعی نقاط (counts/BatteryMa) را نگرفته باشد.</t>
         </is>
       </c>
-      <c r="F19" s="7" t="inlineStr">
+      <c r="F19" s="22" t="inlineStr">
         <is>
           <t>کانال ۱ معتبر؛ کانال ۲ count=0؛ before کانال ۲ غیرصفر و after صفرنقطه‌ای</t>
         </is>
       </c>
-      <c r="G19" s="7" t="inlineStr">
+      <c r="G19" s="22" t="inlineStr">
         <is>
           <t>یک تبادل + یک بوت</t>
         </is>
       </c>
-      <c r="H19" s="7" t="inlineStr">
+      <c r="H19" s="20" t="inlineStr">
         <is>
           <t>commit پذیرفته؛ کانال ۱ حفظ می‌شود و override فلش کانال ۲ حذف می‌شود؛ LUT_DATA کانال ۲ فریم صفرنقطه‌ای مستقل می‌دهد</t>
         </is>
       </c>
-      <c r="I19" s="7" t="inlineStr">
+      <c r="I19" s="20" t="inlineStr">
         <is>
           <t>پینگ‌پنگ و پس از reset</t>
         </is>
       </c>
-      <c r="J19" s="7" t="inlineStr">
+      <c r="J19" s="20" t="inlineStr">
         <is>
           <t>status=0، Active کانال ۱ برقرار، Active کانال ۲=false و مقایسهٔ پنل changed-confirmed؛ CRC/count جای counts/BatteryMa را نگیرد</t>
         </is>
       </c>
-      <c r="K19" s="7" t="inlineStr">
+      <c r="K19" s="20" t="inlineStr">
         <is>
           <t>Host PASS: 159 check؛ board physical pending</t>
         </is>
       </c>
-      <c r="L19" s="7" t="inlineStr">
+      <c r="L19" s="23" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="M19" s="7" t="inlineStr">
+      <c r="M19" s="20" t="inlineStr">
         <is>
           <t>Host جای تست برد را نمی‌گیرد؛ حذف override و ماندگاری پس از reset روی برد واقعی لازم است</t>
         </is>
       </c>
-      <c r="N19" s="7" t="inlineStr">
+      <c r="N19" s="29" t="inlineStr">
         <is>
           <t>Firmware/Modules/CalLut/Tester/run_host_test_cal_lut.sh؛ esp_link_panel/Tester/host_test_scenario_cards.js</t>
         </is>
       </c>
-      <c r="O19" s="7" t="inlineStr">
+      <c r="O19" s="22" t="inlineStr">
         <is>
           <t>WORKTREE</t>
         </is>
       </c>
-      <c r="P19" s="7" t="n"/>
-      <c r="Q19" s="7" t="inlineStr">
+      <c r="P19" s="22" t="n"/>
+      <c r="Q19" s="24" t="inlineStr">
         <is>
           <t>2026-10-07</t>
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="7" t="inlineStr">
+    <row r="20" ht="67.5" customHeight="1">
+      <c r="A20" s="19" t="inlineStr">
         <is>
           <t>CL-016</t>
         </is>
       </c>
-      <c r="B20" s="7" t="inlineStr">
+      <c r="B20" s="25" t="inlineStr">
         <is>
           <t>reset با grant و flush NVM</t>
         </is>
       </c>
-      <c r="C20" s="7" t="inlineStr">
+      <c r="C20" s="26" t="inlineStr">
         <is>
           <t>بالا</t>
         </is>
       </c>
-      <c r="D20" s="7" t="inlineStr">
+      <c r="D20" s="25" t="inlineStr">
         <is>
           <t>commit موفق یا commit صفرنقطه‌ای؛ magic معتبر؛ لینک فعال</t>
         </is>
       </c>
-      <c r="E20" s="7" t="inlineStr">
+      <c r="E20" s="25" t="inlineStr">
         <is>
           <t>گام ۱: یک commit موفق (یا commit صفرنقطه‌ای با count=0 معتبر) انجام بده تا grant ریست صادر شود.
 گام ۲: بلافاصله reset را درخواست کن و صبر کن برد بالا بیاید (حداکثر 15 ثانیه).
@@ -2042,85 +2225,85 @@
 گام ۵: نتیجه بگیر: commit صفرنقطه‌ای بدون جدول فعال پذیرفته می‌شود و reset فقط با grant commit و flush موفق اتفاق می‌افتد.</t>
         </is>
       </c>
-      <c r="F20" s="7" t="inlineStr">
+      <c r="F20" s="27" t="inlineStr">
         <is>
           <t>count=0 معتبر؛ grant commit؛ flush success/failure</t>
         </is>
       </c>
-      <c r="G20" s="7" t="inlineStr">
+      <c r="G20" s="27" t="inlineStr">
         <is>
           <t>حداکثر 15s</t>
         </is>
       </c>
-      <c r="H20" s="7" t="inlineStr">
+      <c r="H20" s="25" t="inlineStr">
         <is>
           <t>zero-point commit بدون active table پذیرفته می‌شود؛ reset فقط با grant commit و flush موفق arm می‌شود؛ flush failure کد CAL_LUT_ST_FLASH می‌دهد و reset انجام نمی‌شود</t>
         </is>
       </c>
-      <c r="I20" s="7" t="inlineStr">
+      <c r="I20" s="25" t="inlineStr">
         <is>
           <t>پس از موفقیت one-shot؛ بعد از flush failure grant برای retry حفظ می‌شود</t>
         </is>
       </c>
-      <c r="J20" s="7" t="inlineStr">
+      <c r="J20" s="25" t="inlineStr">
         <is>
           <t>پس از reset /t و LUT_READ/LUT_DATA تازه، هر دو کانال و persistence با expected برابر؛ هیچ reject/timeout/mismatch موفق گزارش نشود</t>
         </is>
       </c>
-      <c r="K20" s="7" t="inlineStr">
+      <c r="K20" s="25" t="inlineStr">
         <is>
           <t>Host PASS: CalLut=159، parser=14 و NVM؛ تست فیزیکی فلش/ریست/باتری انجام نشده و pending است</t>
         </is>
       </c>
-      <c r="L20" s="7" t="inlineStr">
+      <c r="L20" s="23" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="M20" s="7" t="inlineStr">
+      <c r="M20" s="25" t="inlineStr">
         <is>
           <t>Host جای تست فیزیکی برد و fault واقعی NVM را نمی‌گیرد؛ commit zero-point، reset و flush روی برد واقعی تکرار شود</t>
         </is>
       </c>
-      <c r="N20" s="7" t="inlineStr">
+      <c r="N20" s="30" t="inlineStr">
         <is>
           <t>Firmware/Modules/CalLut/Tester/run_host_test_cal_lut.sh؛ Firmware/Modules/EspLink/Tester/run_host_test_nvm.sh؛ Firmware/Modules/EspLink/esp_link.c</t>
         </is>
       </c>
-      <c r="O20" s="7" t="inlineStr">
+      <c r="O20" s="27" t="inlineStr">
         <is>
           <t>WORKTREE</t>
         </is>
       </c>
-      <c r="P20" s="7" t="n"/>
-      <c r="Q20" s="7" t="inlineStr">
+      <c r="P20" s="27" t="n"/>
+      <c r="Q20" s="28" t="inlineStr">
         <is>
           <t>2026-10-08</t>
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
+    <row r="21" ht="54" customHeight="1">
+      <c r="A21" s="19" t="inlineStr">
         <is>
           <t>CL-020</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
+      <c r="B21" s="20" t="inlineStr">
         <is>
           <t>پنل دیالوگ LUT</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr">
+      <c r="C21" s="22" t="inlineStr">
         <is>
           <t>متوسط</t>
         </is>
       </c>
-      <c r="D21" t="inlineStr">
+      <c r="D21" s="20" t="inlineStr">
         <is>
           <t>پنل وصل + LUT آماده</t>
         </is>
       </c>
-      <c r="E21" t="inlineStr">
+      <c r="E21" s="20" t="inlineStr">
         <is>
           <t>گام ۱: پنل را وصل کن و یک LUT دوکاناله آمادهٔ ارسال داشته باش.
 گام ۲: از پنل LUT را push کن و صبر کن دیالوگ تأیید ریست بیاید.
@@ -2128,63 +2311,320 @@
 گام ۴: یک بار کلید Enter را بزن (باید تأیید کند) و یک بار در اجرای بعدی Esc را بزن (باید لغو کند)؛ اگر دو دیالوگ پشت سر هم آمد باید یکی‌یکی در صف PMQ نمایش داده شوند.</t>
         </is>
       </c>
-      <c r="F21" t="inlineStr">
+      <c r="F21" s="22" t="inlineStr">
         <is>
           <t>LUT 2 کانال</t>
         </is>
       </c>
-      <c r="G21" t="inlineStr">
+      <c r="G21" s="22" t="inlineStr">
         <is>
           <t>10s</t>
         </is>
       </c>
-      <c r="H21" t="inlineStr">
+      <c r="H21" s="20" t="inlineStr">
         <is>
           <t>دیالوگ با استایل #pmod/#121a2c، بدون alert سفید ویندوز؛ Enter=تأیید Esc=انصراف؛ صف PMQ یکی‌یکی</t>
         </is>
       </c>
-      <c r="I21" t="inlineStr">
+      <c r="I21" s="20" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J21" t="inlineStr">
+      <c r="J21" s="20" t="inlineStr">
         <is>
           <t>دیالوگ تیره + Enter/Esc کار کند</t>
         </is>
       </c>
-      <c r="L21" t="inlineStr">
+      <c r="K21" s="20" t="n"/>
+      <c r="L21" s="31" t="inlineStr">
         <is>
           <t>نیاز به تکرار</t>
         </is>
       </c>
-      <c r="O21" t="inlineStr">
+      <c r="M21" s="20" t="n"/>
+      <c r="N21" s="20" t="n"/>
+      <c r="O21" s="22" t="inlineStr">
         <is>
           <t>62f3782</t>
         </is>
       </c>
-      <c r="Q21" t="inlineStr">
+      <c r="P21" s="22" t="n"/>
+      <c r="Q21" s="24" t="inlineStr">
         <is>
           <t>2026-10-12</t>
         </is>
       </c>
     </row>
+    <row r="22">
+      <c r="Q22" s="32">
+        <f>IF(OR(L22="",L22="در انتظار"),"",IF(Q22="",TODAY(),Q22))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23">
+      <c r="Q23" s="32">
+        <f>IF(OR(L23="",L23="در انتظار"),"",IF(Q23="",TODAY(),Q23))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24">
+      <c r="Q24" s="32">
+        <f>IF(OR(L24="",L24="در انتظار"),"",IF(Q24="",TODAY(),Q24))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25">
+      <c r="Q25" s="32">
+        <f>IF(OR(L25="",L25="در انتظار"),"",IF(Q25="",TODAY(),Q25))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26">
+      <c r="Q26" s="32">
+        <f>IF(OR(L26="",L26="در انتظار"),"",IF(Q26="",TODAY(),Q26))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27">
+      <c r="Q27" s="32">
+        <f>IF(OR(L27="",L27="در انتظار"),"",IF(Q27="",TODAY(),Q27))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28">
+      <c r="Q28" s="32">
+        <f>IF(OR(L28="",L28="در انتظار"),"",IF(Q28="",TODAY(),Q28))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="29">
+      <c r="Q29" s="32">
+        <f>IF(OR(L29="",L29="در انتظار"),"",IF(Q29="",TODAY(),Q29))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="30">
+      <c r="Q30" s="32">
+        <f>IF(OR(L30="",L30="در انتظار"),"",IF(Q30="",TODAY(),Q30))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="31">
+      <c r="Q31" s="32">
+        <f>IF(OR(L31="",L31="در انتظار"),"",IF(Q31="",TODAY(),Q31))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="32">
+      <c r="Q32" s="32">
+        <f>IF(OR(L32="",L32="در انتظار"),"",IF(Q32="",TODAY(),Q32))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="33">
+      <c r="Q33" s="32">
+        <f>IF(OR(L33="",L33="در انتظار"),"",IF(Q33="",TODAY(),Q33))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="34">
+      <c r="Q34" s="32">
+        <f>IF(OR(L34="",L34="در انتظار"),"",IF(Q34="",TODAY(),Q34))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="35">
+      <c r="Q35" s="32">
+        <f>IF(OR(L35="",L35="در انتظار"),"",IF(Q35="",TODAY(),Q35))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="36">
+      <c r="Q36" s="32">
+        <f>IF(OR(L36="",L36="در انتظار"),"",IF(Q36="",TODAY(),Q36))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="37">
+      <c r="Q37" s="32">
+        <f>IF(OR(L37="",L37="در انتظار"),"",IF(Q37="",TODAY(),Q37))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="38">
+      <c r="Q38" s="32">
+        <f>IF(OR(L38="",L38="در انتظار"),"",IF(Q38="",TODAY(),Q38))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="39">
+      <c r="Q39" s="32">
+        <f>IF(OR(L39="",L39="در انتظار"),"",IF(Q39="",TODAY(),Q39))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="40">
+      <c r="Q40" s="32">
+        <f>IF(OR(L40="",L40="در انتظار"),"",IF(Q40="",TODAY(),Q40))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="41">
+      <c r="Q41" s="32">
+        <f>IF(OR(L41="",L41="در انتظار"),"",IF(Q41="",TODAY(),Q41))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="42">
+      <c r="Q42" s="32">
+        <f>IF(OR(L42="",L42="در انتظار"),"",IF(Q42="",TODAY(),Q42))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="43">
+      <c r="Q43" s="32">
+        <f>IF(OR(L43="",L43="در انتظار"),"",IF(Q43="",TODAY(),Q43))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="44">
+      <c r="Q44" s="32">
+        <f>IF(OR(L44="",L44="در انتظار"),"",IF(Q44="",TODAY(),Q44))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="45">
+      <c r="Q45" s="32">
+        <f>IF(OR(L45="",L45="در انتظار"),"",IF(Q45="",TODAY(),Q45))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="46">
+      <c r="Q46" s="32">
+        <f>IF(OR(L46="",L46="در انتظار"),"",IF(Q46="",TODAY(),Q46))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="47">
+      <c r="Q47" s="32">
+        <f>IF(OR(L47="",L47="در انتظار"),"",IF(Q47="",TODAY(),Q47))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="48">
+      <c r="Q48" s="32">
+        <f>IF(OR(L48="",L48="در انتظار"),"",IF(Q48="",TODAY(),Q48))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="49">
+      <c r="Q49" s="32">
+        <f>IF(OR(L49="",L49="در انتظار"),"",IF(Q49="",TODAY(),Q49))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="50">
+      <c r="Q50" s="32">
+        <f>IF(OR(L50="",L50="در انتظار"),"",IF(Q50="",TODAY(),Q50))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="51">
+      <c r="Q51" s="32">
+        <f>IF(OR(L51="",L51="در انتظار"),"",IF(Q51="",TODAY(),Q51))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="52">
+      <c r="Q52" s="32">
+        <f>IF(OR(L52="",L52="در انتظار"),"",IF(Q52="",TODAY(),Q52))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="53">
+      <c r="Q53" s="32">
+        <f>IF(OR(L53="",L53="در انتظار"),"",IF(Q53="",TODAY(),Q53))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="54">
+      <c r="Q54" s="32">
+        <f>IF(OR(L54="",L54="در انتظار"),"",IF(Q54="",TODAY(),Q54))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="55">
+      <c r="Q55" s="32">
+        <f>IF(OR(L55="",L55="در انتظار"),"",IF(Q55="",TODAY(),Q55))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="56">
+      <c r="Q56" s="32">
+        <f>IF(OR(L56="",L56="در انتظار"),"",IF(Q56="",TODAY(),Q56))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="57">
+      <c r="Q57" s="32">
+        <f>IF(OR(L57="",L57="در انتظار"),"",IF(Q57="",TODAY(),Q57))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="58">
+      <c r="Q58" s="32">
+        <f>IF(OR(L58="",L58="در انتظار"),"",IF(Q58="",TODAY(),Q58))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="59">
+      <c r="Q59" s="32">
+        <f>IF(OR(L59="",L59="در انتظار"),"",IF(Q59="",TODAY(),Q59))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="60">
+      <c r="Q60" s="32">
+        <f>IF(OR(L60="",L60="در انتظار"),"",IF(Q60="",TODAY(),Q60))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="61">
+      <c r="Q61" s="32">
+        <f>IF(OR(L61="",L61="در انتظار"),"",IF(Q61="",TODAY(),Q61))</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
+  <autoFilter ref="A4:Q21"/>
   <dataValidations count="2">
-    <dataValidation sqref="L5:L20" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>='فهرست‌ها'!$A$2:$A$6</formula1>
-    </dataValidation>
-    <dataValidation sqref="C5:C20" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="C5:C101" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>='فهرست‌ها'!$B$9:$B$11</formula1>
     </dataValidation>
+    <dataValidation sqref="L5:L101" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" prompt="وضعیت تست را از فهرست انتخاب کنید" type="list">
+      <formula1>='فهرست‌ها'!$A$2:$A$7</formula1>
+    </dataValidation>
   </dataValidations>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D7" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E7" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D14" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E14" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D19" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E19" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N19" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N20" r:id="rId8"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <tabColor rgb="00BF8F00"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
@@ -2198,230 +2638,239 @@
     <col width="26" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="4" t="inlineStr">
+    <row r="1" ht="30" customHeight="1">
+      <c r="A1" s="16" t="inlineStr">
         <is>
           <t>مرجع سریع سناریوها و ثابت‌های ماژول CalLut</t>
         </is>
       </c>
-    </row>
+      <c r="B1" s="16" t="n"/>
+      <c r="C1" s="16" t="n"/>
+      <c r="D1" s="16" t="n"/>
+      <c r="E1" s="16" t="n"/>
+    </row>
+    <row r="2"/>
     <row r="3">
-      <c r="A3" s="6" t="inlineStr">
+      <c r="A3" s="33" t="inlineStr">
         <is>
           <t>موضوع</t>
         </is>
       </c>
-      <c r="B3" s="6" t="inlineStr">
+      <c r="B3" s="33" t="inlineStr">
         <is>
           <t>شرط / مقدار</t>
         </is>
       </c>
-      <c r="C3" s="6" t="inlineStr">
+      <c r="C3" s="33" t="inlineStr">
         <is>
           <t>رفتار مورد انتظار</t>
         </is>
       </c>
-      <c r="D3" s="6" t="inlineStr">
+      <c r="D3" s="33" t="inlineStr">
         <is>
           <t>ثابت / محل کد</t>
         </is>
       </c>
-      <c r="E3" s="6" t="inlineStr">
+      <c r="E3" s="33" t="inlineStr">
         <is>
           <t>توضیح</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="7" t="inlineStr">
+      <c r="A4" s="34" t="inlineStr">
         <is>
           <t>صفحه‌های اختصاصی</t>
         </is>
       </c>
-      <c r="B4" s="7" t="inlineStr">
+      <c r="B4" s="34" t="inlineStr">
         <is>
           <t>0x0800F000 و 0x0800F400</t>
         </is>
       </c>
-      <c r="C4" s="7" t="inlineStr">
+      <c r="C4" s="34" t="inlineStr">
         <is>
           <t>پینگ‌پنگ امن در برابر قطع برق</t>
         </is>
       </c>
-      <c r="D4" s="7" t="inlineStr">
+      <c r="D4" s="34" t="inlineStr">
         <is>
           <t>CAL_LUT_PAGE_A_ADDR / CAL_LUT_PAGE_B_ADDR</t>
         </is>
       </c>
-      <c r="E4" s="7" t="inlineStr">
+      <c r="E4" s="34" t="inlineStr">
         <is>
           <t>پایین‌تر از صفحه‌های پارامتر</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="7" t="inlineStr">
+      <c r="A5" s="34" t="inlineStr">
         <is>
           <t>مجیک و نسخه</t>
         </is>
       </c>
-      <c r="B5" s="7" t="inlineStr">
+      <c r="B5" s="34" t="inlineStr">
         <is>
           <t>0x434C5554 («CLUT») و ۱</t>
         </is>
       </c>
-      <c r="C5" s="7" t="inlineStr">
+      <c r="C5" s="34" t="inlineStr">
         <is>
           <t>ناهمخوانی = بازگشت به جدول کامپایل‌شده</t>
         </is>
       </c>
-      <c r="D5" s="7" t="inlineStr">
+      <c r="D5" s="34" t="inlineStr">
         <is>
           <t>CAL_LUT_MAGIC / CAL_LUT_VERSION</t>
         </is>
       </c>
-      <c r="E5" s="7" t="inlineStr">
+      <c r="E5" s="34" t="inlineStr">
         <is>
           <t>هرگز نیم‌ارتقای بی‌صدا</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="7" t="inlineStr">
+      <c r="A6" s="34" t="inlineStr">
         <is>
           <t>سقف نقاط</t>
         </is>
       </c>
-      <c r="B6" s="7" t="inlineStr">
+      <c r="B6" s="34" t="inlineStr">
         <is>
           <t>۲ تا ۲۴ نقطه در هر کانال</t>
         </is>
       </c>
-      <c r="C6" s="7" t="inlineStr">
+      <c r="C6" s="34" t="inlineStr">
         <is>
           <t>بیرون از بازه = رد با status=2</t>
         </is>
       </c>
-      <c r="D6" s="7" t="inlineStr">
+      <c r="D6" s="34" t="inlineStr">
         <is>
           <t>CAL_LUT_POINTS_MIN / CAL_LUT_POINTS_MAX</t>
         </is>
       </c>
-      <c r="E6" s="7" t="inlineStr">
+      <c r="E6" s="34" t="inlineStr">
         <is>
           <t>۲۴×۲×۲×۴ = ۳۸۴ بایت رکورد</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="7" t="inlineStr">
+      <c r="A7" s="34" t="inlineStr">
         <is>
           <t>کدهای وضعیت</t>
         </is>
       </c>
-      <c r="B7" s="7" t="inlineStr">
+      <c r="B7" s="34" t="inlineStr">
         <is>
           <t>۰ تا ۷</t>
         </is>
       </c>
-      <c r="C7" s="7" t="inlineStr">
+      <c r="C7" s="34" t="inlineStr">
         <is>
           <t>هر خطا دلیل خودش را در LUT_ACK می‌گوید</t>
         </is>
       </c>
-      <c r="D7" s="7" t="inlineStr">
+      <c r="D7" s="34" t="inlineStr">
         <is>
           <t>CAL_LUT_ST_*</t>
         </is>
       </c>
-      <c r="E7" s="7" t="inlineStr">
+      <c r="E7" s="34" t="inlineStr">
         <is>
           <t>۰=OK، ۶=CRC، ۷=فلش</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="7" t="inlineStr">
+      <c r="A8" s="34" t="inlineStr">
         <is>
           <t>دست‌دادن</t>
         </is>
       </c>
-      <c r="B8" s="7" t="inlineStr">
+      <c r="B8" s="34" t="inlineStr">
         <is>
           <t>BEGIN → CHUNK → COMMIT → ACK → RESET</t>
         </is>
       </c>
-      <c r="C8" s="7" t="inlineStr">
+      <c r="C8" s="34" t="inlineStr">
         <is>
           <t>ریست فقط با برابری دو CRC32</t>
         </is>
       </c>
-      <c r="D8" s="7" t="inlineStr">
+      <c r="D8" s="43" t="inlineStr">
         <is>
           <t>cal_lut.c</t>
         </is>
       </c>
-      <c r="E8" s="7" t="inlineStr">
+      <c r="E8" s="34" t="inlineStr">
         <is>
           <t>پنل CRC را می‌سازد، برد بازخوانی می‌کند</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="7" t="inlineStr">
+      <c r="A9" s="34" t="inlineStr">
         <is>
           <t>پشتیبان</t>
         </is>
       </c>
-      <c r="B9" s="7" t="inlineStr">
+      <c r="B9" s="34" t="inlineStr">
         <is>
           <t>جدول‌های فلش (CalLut) و خط گین و آفست</t>
         </is>
       </c>
-      <c r="C9" s="7" t="inlineStr">
+      <c r="C9" s="34" t="inlineStr">
         <is>
           <t>رکورد نامعتبر = جدول کامپایل‌شده</t>
         </is>
       </c>
-      <c r="D9" s="7" t="inlineStr">
+      <c r="D9" s="34" t="inlineStr">
         <is>
           <t>CAL_CURRENT*_LUT_ENABLE</t>
         </is>
       </c>
-      <c r="E9" s="7" t="inlineStr">
+      <c r="E9" s="34" t="inlineStr">
         <is>
           <t>روش قبلی حذف نشده</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="7" t="inlineStr">
+      <c r="A10" s="34" t="inlineStr">
         <is>
           <t>reset grant و flush NVM</t>
         </is>
       </c>
-      <c r="B10" s="7" t="inlineStr">
+      <c r="B10" s="34" t="inlineStr">
         <is>
           <t>magic + commit grant؛ flush NVM پیش از arm</t>
         </is>
       </c>
-      <c r="C10" s="7" t="inlineStr">
+      <c r="C10" s="34" t="inlineStr">
         <is>
           <t>flush failure = no reset؛ success = reset one-shot</t>
         </is>
       </c>
-      <c r="D10" s="7" t="inlineStr">
+      <c r="D10" s="43" t="inlineStr">
         <is>
           <t>cal_lut.c / esp_link.c / esp_link_nvm.c</t>
         </is>
       </c>
-      <c r="E10" s="7" t="inlineStr">
+      <c r="E10" s="34" t="inlineStr">
         <is>
           <t>zero-point commit حتی بدون active table معتبر است</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D8" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D10" r:id="rId2"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2429,6 +2878,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <tabColor rgb="00C00000"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
@@ -2451,81 +2901,93 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="4" t="inlineStr">
+      <c r="A1" s="35" t="inlineStr">
         <is>
           <t>ثبت ایرادهای مشاهده‌شده — ماژول CalLut</t>
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" s="5" t="inlineStr">
+    <row r="2" ht="30" customHeight="1">
+      <c r="A2" s="16" t="inlineStr">
         <is>
           <t>برای هر وضعیت «رد» یا تفاوت مهم، یک ردیف با شناسهٔ یکتا ثبت و پس از اصلاح دوباره تست شود.</t>
         </is>
       </c>
+      <c r="B2" s="16" t="n"/>
+      <c r="C2" s="16" t="n"/>
+      <c r="D2" s="16" t="n"/>
+      <c r="E2" s="16" t="n"/>
+      <c r="F2" s="16" t="n"/>
+      <c r="G2" s="16" t="n"/>
+      <c r="H2" s="16" t="n"/>
+      <c r="I2" s="16" t="n"/>
+      <c r="J2" s="16" t="n"/>
+      <c r="K2" s="16" t="n"/>
+      <c r="L2" s="16" t="n"/>
+      <c r="M2" s="16" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" s="6" t="inlineStr">
+      <c r="A3" s="33" t="inlineStr">
         <is>
           <t>شماره ایراد</t>
         </is>
       </c>
-      <c r="B3" s="6" t="inlineStr">
+      <c r="B3" s="33" t="inlineStr">
         <is>
           <t>شناسه تست</t>
         </is>
       </c>
-      <c r="C3" s="6" t="inlineStr">
+      <c r="C3" s="33" t="inlineStr">
         <is>
           <t>تاریخ کشف</t>
         </is>
       </c>
-      <c r="D3" s="6" t="inlineStr">
+      <c r="D3" s="33" t="inlineStr">
         <is>
           <t>شدت</t>
         </is>
       </c>
-      <c r="E3" s="6" t="inlineStr">
+      <c r="E3" s="33" t="inlineStr">
         <is>
           <t>شرح کوتاه ایراد</t>
         </is>
       </c>
-      <c r="F3" s="6" t="inlineStr">
+      <c r="F3" s="33" t="inlineStr">
         <is>
           <t>مراحل بازتولید</t>
         </is>
       </c>
-      <c r="G3" s="6" t="inlineStr">
+      <c r="G3" s="33" t="inlineStr">
         <is>
           <t>انتظار</t>
         </is>
       </c>
-      <c r="H3" s="6" t="inlineStr">
+      <c r="H3" s="33" t="inlineStr">
         <is>
           <t>واقعیت</t>
         </is>
       </c>
-      <c r="I3" s="6" t="inlineStr">
+      <c r="I3" s="33" t="inlineStr">
         <is>
           <t>مدرک/مسیر عکس یا scope</t>
         </is>
       </c>
-      <c r="J3" s="6" t="inlineStr">
+      <c r="J3" s="33" t="inlineStr">
         <is>
           <t>commit firmware</t>
         </is>
       </c>
-      <c r="K3" s="6" t="inlineStr">
+      <c r="K3" s="33" t="inlineStr">
         <is>
           <t>محل احتمالی</t>
         </is>
       </c>
-      <c r="L3" s="6" t="inlineStr">
+      <c r="L3" s="33" t="inlineStr">
         <is>
           <t>وضعیت ایراد</t>
         </is>
       </c>
-      <c r="M3" s="6" t="inlineStr">
+      <c r="M3" s="33" t="inlineStr">
         <is>
           <t>تأیید رفع / توضیحات</t>
         </is>
@@ -2539,6 +3001,7 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <tabColor rgb="00548235"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
@@ -2551,205 +3014,207 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="14" t="inlineStr">
         <is>
           <t>تأیید نهایی اعتبارسنجی — ماژول CalLut</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
+      <c r="A2" s="15" t="inlineStr">
         <is>
           <t>این صفحه فقط پس از تکمیل تست‌ها و بسته‌شدن ایرادها پر می‌شود.</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="8" t="inlineStr">
+      <c r="A3" s="36" t="inlineStr">
         <is>
           <t>مشخصات تست</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="inlineStr">
+      <c r="A4" s="15" t="inlineStr">
         <is>
           <t>پروژه</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr">
+      <c r="B4" s="15" t="inlineStr">
         <is>
           <t>ChangeOver</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="inlineStr">
+      <c r="A5" s="15" t="inlineStr">
         <is>
           <t>ماژول</t>
         </is>
       </c>
-      <c r="B5" s="2" t="inlineStr">
+      <c r="B5" s="15" t="inlineStr">
         <is>
           <t>CalLut — جدول کالیبراسیون در فلش اختصاصی</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="inlineStr">
+      <c r="A6" s="15" t="inlineStr">
         <is>
           <t>تاریخ ساخت فرم</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr">
+      <c r="B6" s="15" t="inlineStr">
         <is>
           <t>2026-10-05 (1.0 — ساخته‌شده در ممیزی کل برنامه)</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="inlineStr">
+      <c r="A7" s="15" t="inlineStr">
         <is>
           <t>نسخه فرم</t>
         </is>
       </c>
-      <c r="B7" s="2" t="inlineStr">
+      <c r="B7" s="15" t="inlineStr">
         <is>
           <t>1.0</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="inlineStr">
+      <c r="A8" s="15" t="inlineStr">
         <is>
           <t>commit firmware</t>
         </is>
       </c>
-      <c r="B8" s="2" t="inlineStr">
+      <c r="B8" s="15" t="inlineStr">
         <is>
           <t>TESTER: fill</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="inlineStr">
+      <c r="A9" s="15" t="inlineStr">
         <is>
           <t>ابزار</t>
         </is>
       </c>
-      <c r="B9" s="2" t="inlineStr">
+      <c r="B9" s="15" t="inlineStr">
         <is>
           <t>پنل ESP + مولتی‌متر + منبع تغذیه قابل قطع + اسیلوسکوپ</t>
         </is>
       </c>
     </row>
+    <row r="10"/>
     <row r="11">
-      <c r="A11" s="8" t="inlineStr">
+      <c r="A11" s="36" t="inlineStr">
         <is>
           <t>خلاصهٔ خودکار وضعیت تست‌ها</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="8" t="inlineStr">
+      <c r="A12" s="36" t="inlineStr">
         <is>
           <t>شاخص</t>
         </is>
       </c>
-      <c r="B12" s="8" t="inlineStr">
+      <c r="B12" s="36" t="inlineStr">
         <is>
           <t>مقدار</t>
         </is>
       </c>
-      <c r="C12" s="8" t="inlineStr">
+      <c r="C12" s="36" t="inlineStr">
         <is>
           <t>توضیح</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="2" t="inlineStr">
+      <c r="A13" s="15" t="inlineStr">
         <is>
           <t>کل تست‌ها</t>
         </is>
       </c>
-      <c r="B13" s="2" t="inlineStr">
+      <c r="B13" s="15" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="C13" s="2" t="inlineStr">
+      <c r="C13" s="15" t="inlineStr">
         <is>
           <t>همهٔ ردیف‌های برنامه تست</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="2" t="inlineStr">
+      <c r="A14" s="15" t="inlineStr">
         <is>
           <t>قبول</t>
         </is>
       </c>
-      <c r="B14" s="2">
+      <c r="B14" s="15">
         <f>COUNTIF('برنامه تست'!L:L,"قبول")</f>
         <v/>
       </c>
-      <c r="C14" s="2" t="inlineStr">
+      <c r="C14" s="15" t="inlineStr">
         <is>
           <t>COUNTIF برنامه تست</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="2" t="inlineStr">
+      <c r="A15" s="15" t="inlineStr">
         <is>
           <t>رد</t>
         </is>
       </c>
-      <c r="B15" s="2">
+      <c r="B15" s="15">
         <f>COUNTIF('برنامه تست'!L:L,"رد")</f>
         <v/>
       </c>
-      <c r="C15" s="2" t="inlineStr">
+      <c r="C15" s="15" t="inlineStr">
         <is>
           <t>COUNTIF رد</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="2" t="inlineStr">
+      <c r="A16" s="15" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="B16" s="2">
+      <c r="B16" s="15">
         <f>IF(16=0,0,COUNTIF('برنامه تست'!L:L,"قبول")/16)</f>
         <v/>
       </c>
-      <c r="C16" s="2" t="inlineStr">
+      <c r="C16" s="15" t="inlineStr">
         <is>
           <t>پیش از تست برد</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="2" t="inlineStr">
+      <c r="A17" s="15" t="inlineStr">
         <is>
           <t>نرخ قبولی</t>
         </is>
       </c>
-      <c r="B17" s="2">
+      <c r="B17" s="15">
         <f>IF(15=0,0,COUNTIF('برنامه تست'!L:L,"قبول")/15)</f>
         <v/>
       </c>
-      <c r="C17" s="2" t="inlineStr">
+      <c r="C17" s="15" t="inlineStr">
         <is>
           <t>قبول/کل</t>
         </is>
       </c>
     </row>
+    <row r="18"/>
     <row r="19">
-      <c r="A19" s="2" t="inlineStr">
+      <c r="A19" s="15" t="inlineStr">
         <is>
           <t>امضا و تأیید: تست‌کننده ______  بازبین ______  تاریخ ______</t>
         </is>
@@ -2763,6 +3228,7 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <tabColor rgb="00808080"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
@@ -2774,70 +3240,77 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="9" t="inlineStr">
+      <c r="A1" s="37" t="inlineStr">
         <is>
           <t>وضعیت</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="5" t="inlineStr">
+      <c r="A2" s="18" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="5" t="inlineStr">
+      <c r="A3" s="18" t="inlineStr">
+        <is>
+          <t>انجام شد</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="18" t="inlineStr">
         <is>
           <t>قبول</t>
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="5" t="inlineStr">
+    <row r="5">
+      <c r="A5" s="18" t="inlineStr">
         <is>
           <t>رد</t>
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="5" t="inlineStr">
+    <row r="6">
+      <c r="A6" s="18" t="inlineStr">
         <is>
           <t>مسدود</t>
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="5" t="inlineStr">
+    <row r="7">
+      <c r="A7" t="inlineStr">
         <is>
           <t>نیاز به تکرار</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="9" t="inlineStr">
+      <c r="A8" s="37" t="inlineStr">
         <is>
           <t>اولویت</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="B9" s="5" t="inlineStr">
+      <c r="B9" s="18" t="inlineStr">
         <is>
           <t>بالا</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="B10" s="5" t="inlineStr">
+      <c r="B10" s="18" t="inlineStr">
         <is>
           <t>متوسط</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="B11" s="5" t="inlineStr">
+      <c r="B11" s="18" t="inlineStr">
         <is>
           <t>پایین</t>
         </is>
@@ -2851,7 +3324,7 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <tabColor rgb="002F5597"/>
+    <tabColor rgb="007030A0"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
@@ -2863,55 +3336,56 @@
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
-      <c r="A1" s="10" t="inlineStr">
+      <c r="A1" s="38" t="inlineStr">
         <is>
           <t>ماشین حالت ماژول جدول کالیبراسیون (CalLut)</t>
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3" ht="24" customHeight="1">
-      <c r="A3" s="11" t="inlineStr">
+      <c r="A3" s="39" t="inlineStr">
         <is>
           <t>حالت‌ها و گذارهای همین ماژول</t>
         </is>
       </c>
-      <c r="B3" s="12" t="inlineStr">
+      <c r="B3" s="40" t="inlineStr">
         <is>
           <t>CalLut_State_Machine.xlsx</t>
         </is>
       </c>
     </row>
     <row r="4" ht="24" customHeight="1">
-      <c r="A4" s="11" t="inlineStr">
+      <c r="A4" s="39" t="inlineStr">
         <is>
           <t>ماشین حالت کل برنامه (نمای سیستمی)</t>
         </is>
       </c>
-      <c r="B4" s="12" t="inlineStr">
+      <c r="B4" s="40" t="inlineStr">
         <is>
           <t>../../../Documentation/System_State_Machine.xlsx</t>
         </is>
       </c>
     </row>
     <row r="5" ht="24" customHeight="1">
-      <c r="A5" s="11" t="inlineStr">
+      <c r="A5" s="39" t="inlineStr">
         <is>
           <t>راهنمای رنگ‌ها</t>
         </is>
       </c>
-      <c r="B5" s="13" t="inlineStr">
+      <c r="B5" s="41" t="inlineStr">
         <is>
           <t>سبز = عادی/سالم · زرد = هشدار یا انتظار · قرمز = خطا یا قفل · نارنجی = در حال کار · خاکستری = بی‌کار · آبی = اطلاعاتی</t>
         </is>
       </c>
     </row>
     <row r="6" ht="24" customHeight="1">
-      <c r="A6" s="11" t="inlineStr">
+      <c r="A6" s="39" t="inlineStr">
         <is>
           <t>بازتولید</t>
         </is>
       </c>
-      <c r="B6" s="13" t="inlineStr">
+      <c r="B6" s="40" t="inlineStr">
         <is>
           <t>python3 tools/make_module_state_machines.py</t>
         </is>
@@ -2924,6 +3398,7 @@
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B3" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B4" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B6" r:id="rId3"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Firmware/Modules/CalLut/CalLut_Validation.xlsx
+++ b/Firmware/Modules/CalLut/CalLut_Validation.xlsx
@@ -2607,14 +2607,14 @@
     </dataValidation>
   </dataValidations>
   <hyperlinks>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D7" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E7" r:id="rId2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D14" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E14" r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D19" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E19" r:id="rId6"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N19" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N20" r:id="rId8"/>
+    <hyperlink ref="D7" location="'برنامه تست'!A6"/>
+    <hyperlink ref="E7" location="'برنامه تست'!A6"/>
+    <hyperlink ref="D14" location="'برنامه تست'!A6"/>
+    <hyperlink ref="E14" location="'برنامه تست'!A6"/>
+    <hyperlink ref="D19" location="'برنامه تست'!A6"/>
+    <hyperlink ref="E19" location="'برنامه تست'!A6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N19" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N20" r:id="rId2"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>

--- a/Firmware/Modules/CalLut/CalLut_Validation.xlsx
+++ b/Firmware/Modules/CalLut/CalLut_Validation.xlsx
@@ -9,15 +9,18 @@
   <sheets>
     <sheet name="راهنما" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="برنامه تست" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="مراجع سناریو" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="ثبت ایراد" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="تأیید نهایی" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="فهرست‌ها" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="ماشین حالت" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="تست‌های آزمایشگاهی" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="مراجع سناریو" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="ثبت ایراد" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="تأیید نهایی" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="فهرست‌ها" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="ماشین حالت" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'برنامه تست'!$A$4:$Q$21</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'برنامه تست'!$A$4:$Q$60</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'برنامه تست'!$4:$4</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'تست‌های آزمایشگاهی'!$A$4:$Q$5</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="2">'تست‌های آزمایشگاهی'!$4:$4</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1" iterate="1" iterateCount="100" iterateDelta="0.001"/>
 </workbook>
@@ -206,7 +209,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="44">
+  <cellXfs count="45">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -320,6 +323,9 @@
     </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -774,7 +780,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:Q61"/>
+  <dimension ref="A1:Q60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1853,111 +1859,25 @@
     <row r="16" ht="54" customHeight="1">
       <c r="A16" s="19" t="inlineStr">
         <is>
-          <t>CL-012</t>
-        </is>
-      </c>
-      <c r="B16" s="25" t="inlineStr">
-        <is>
-          <t>idle شدن شارژر هنگام ریست</t>
-        </is>
-      </c>
-      <c r="C16" s="26" t="inlineStr">
-        <is>
-          <t>بالا</t>
-        </is>
-      </c>
-      <c r="D16" s="25" t="inlineStr">
-        <is>
-          <t>جدول فعال، شارژ در جریان</t>
-        </is>
-      </c>
-      <c r="E16" s="25" t="inlineStr">
-        <is>
-          <t>گام ۱: یک جدول فعال کن و شارژ را در حالت BULK راه بینداز تا کانال در حال شارژ PWM داشته باشد.
-گام ۲: اسیلوسکوپ را روی گیت همان کانال بگذار.
-گام ۳: حین شارژ فرمان LUT_RESET را بفرست.
-گام ۴: روی اسکوپ ببین که پیش از ریست، duty اول صفر شده و شارژر idle شده باشد؛ ریست نباید وسط پالس اتفاق بیفتد.</t>
-        </is>
-      </c>
-      <c r="F16" s="27" t="inlineStr">
-        <is>
-          <t>درخواست ریست با PWM فعال</t>
-        </is>
-      </c>
-      <c r="G16" s="27" t="inlineStr">
-        <is>
-          <t>یک تبادل</t>
-        </is>
-      </c>
-      <c r="H16" s="25" t="inlineStr">
-        <is>
-          <t>قبل از ریست هر دو دیوتی صفر و شارژر idle می‌شود</t>
-        </is>
-      </c>
-      <c r="I16" s="25" t="inlineStr">
-        <is>
-          <t>بدون latch</t>
-        </is>
-      </c>
-      <c r="J16" s="25" t="inlineStr">
-        <is>
-          <t>اسیلوسکوپ روی گیت: صفر پیش از ریست</t>
-        </is>
-      </c>
-      <c r="K16" s="25" t="inlineStr">
-        <is>
-          <t>در انتظار</t>
-        </is>
-      </c>
-      <c r="L16" s="23" t="inlineStr">
-        <is>
-          <t>در انتظار</t>
-        </is>
-      </c>
-      <c r="M16" s="25" t="n"/>
-      <c r="N16" s="25" t="inlineStr">
-        <is>
-          <t>TESTER: fill</t>
-        </is>
-      </c>
-      <c r="O16" s="27" t="inlineStr">
-        <is>
-          <t>TESTER: fill</t>
-        </is>
-      </c>
-      <c r="P16" s="27" t="inlineStr">
-        <is>
-          <t>TESTER: fill</t>
-        </is>
-      </c>
-      <c r="Q16" s="28" t="inlineStr">
-        <is>
-          <t>2026-10-05</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="54" customHeight="1">
-      <c r="A17" s="19" t="inlineStr">
-        <is>
           <t>CL-013</t>
         </is>
       </c>
-      <c r="B17" s="20" t="inlineStr">
+      <c r="B16" s="20" t="inlineStr">
         <is>
           <t>تغییر نسخهٔ قالب</t>
         </is>
       </c>
-      <c r="C17" s="22" t="inlineStr">
+      <c r="C16" s="22" t="inlineStr">
         <is>
           <t>پایین</t>
         </is>
       </c>
-      <c r="D17" s="20" t="inlineStr">
+      <c r="D16" s="20" t="inlineStr">
         <is>
           <t>رکورد معتبر نسخهٔ ۱</t>
         </is>
       </c>
-      <c r="E17" s="20" t="inlineStr">
+      <c r="E16" s="20" t="inlineStr">
         <is>
           <t>گام ۱: روی برد یک رکورد LUT معتبر با نسخهٔ 1 داشته باش (قبلاً commit شده باشد).
 گام ۲: ثابت CAL_LUT_VERSION را در کد بالا ببر و فرم‌ور جدید را روی همان برد فلش کن.
@@ -1965,85 +1885,85 @@
 گام ۴: باید جدول فعال نباشد (Active = false) و خوانش جریان به جدول کامپایل‌شده (خط گین و آفست) برگشته باشد.</t>
         </is>
       </c>
-      <c r="F17" s="22" t="inlineStr">
+      <c r="F16" s="22" t="inlineStr">
         <is>
           <t>نسخهٔ رکورد قدیمی</t>
         </is>
       </c>
-      <c r="G17" s="22" t="inlineStr">
+      <c r="G16" s="22" t="inlineStr">
         <is>
           <t>یک بوت</t>
         </is>
       </c>
-      <c r="H17" s="20" t="inlineStr">
+      <c r="H16" s="20" t="inlineStr">
         <is>
           <t>رکورد قدیمی نامعتبر و بازگشت به جدول کامپایل‌شده</t>
         </is>
       </c>
-      <c r="I17" s="20" t="inlineStr">
+      <c r="I16" s="20" t="inlineStr">
         <is>
           <t>بدون نیم‌ارتقای بی‌صدا</t>
         </is>
       </c>
-      <c r="J17" s="20" t="inlineStr">
+      <c r="J16" s="20" t="inlineStr">
         <is>
           <t>Active=false و خوانش‌ها برابر خط گین و آفست</t>
         </is>
       </c>
-      <c r="K17" s="20" t="inlineStr">
+      <c r="K16" s="20" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="L17" s="23" t="inlineStr">
+      <c r="L16" s="23" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="M17" s="20" t="n"/>
-      <c r="N17" s="20" t="inlineStr">
-        <is>
-          <t>TESTER: fill</t>
-        </is>
-      </c>
-      <c r="O17" s="22" t="inlineStr">
-        <is>
-          <t>TESTER: fill</t>
-        </is>
-      </c>
-      <c r="P17" s="22" t="inlineStr">
-        <is>
-          <t>TESTER: fill</t>
-        </is>
-      </c>
-      <c r="Q17" s="24" t="inlineStr">
+      <c r="M16" s="20" t="n"/>
+      <c r="N16" s="20" t="inlineStr">
+        <is>
+          <t>TESTER: fill</t>
+        </is>
+      </c>
+      <c r="O16" s="22" t="inlineStr">
+        <is>
+          <t>TESTER: fill</t>
+        </is>
+      </c>
+      <c r="P16" s="22" t="inlineStr">
+        <is>
+          <t>TESTER: fill</t>
+        </is>
+      </c>
+      <c r="Q16" s="24" t="inlineStr">
         <is>
           <t>2026-10-05</t>
         </is>
       </c>
     </row>
-    <row r="18" ht="54" customHeight="1">
-      <c r="A18" s="19" t="inlineStr">
+    <row r="17" ht="54" customHeight="1">
+      <c r="A17" s="19" t="inlineStr">
         <is>
           <t>CL-014</t>
         </is>
       </c>
-      <c r="B18" s="25" t="inlineStr">
+      <c r="B17" s="25" t="inlineStr">
         <is>
           <t>LUT_READ بازخوانی واقعی هر دو کانال</t>
         </is>
       </c>
-      <c r="C18" s="26" t="inlineStr">
+      <c r="C17" s="26" t="inlineStr">
         <is>
           <t>بالا</t>
         </is>
       </c>
-      <c r="D18" s="25" t="inlineStr">
+      <c r="D17" s="25" t="inlineStr">
         <is>
           <t>رکورد LUT فعال در فلش یا جدول تازه commit شده</t>
         </is>
       </c>
-      <c r="E18" s="25" t="inlineStr">
+      <c r="E17" s="25" t="inlineStr">
         <is>
           <t>گام ۱: یک جدول فعال روی فلش داشته باش (یا تازه commit کن) و نقاط هر دو کانال را از پنل یادداشت کن.
 گام ۲: از لینک ESP فرمان LUT_READ بفرست.
@@ -2051,85 +1971,85 @@
 گام ۴: برد را ریست کن و گام ۲ و ۳ را تکرار کن؛ دادهٔ ناقص نباید «فعال» فرض شود و پنل باید هر عدم تطابق (mismatch) را گزارش کند.</t>
         </is>
       </c>
-      <c r="F18" s="27" t="inlineStr">
+      <c r="F17" s="27" t="inlineStr">
         <is>
           <t>counts/BatteryMa نقاط فعال، به‌خصوص battery 2</t>
         </is>
       </c>
-      <c r="G18" s="27" t="inlineStr">
+      <c r="G17" s="27" t="inlineStr">
         <is>
           <t>یک درخواست قبل و یک درخواست بعد از reset</t>
         </is>
       </c>
-      <c r="H18" s="25" t="inlineStr">
+      <c r="H17" s="25" t="inlineStr">
         <is>
           <t>LUT_DATA مقدار واقعی هر نقطه را برمی‌گرداند؛ کانال غیرفعال فریم صفرنقطه‌ای می‌دهد؛ دادهٔ ناقص active فرض نمی‌شود</t>
         </is>
       </c>
-      <c r="I18" s="25" t="inlineStr">
+      <c r="I17" s="25" t="inlineStr">
         <is>
           <t>رکورد فلش باید بعد از reset همان نقاط را حفظ کند</t>
         </is>
       </c>
-      <c r="J18" s="25" t="inlineStr">
+      <c r="J17" s="25" t="inlineStr">
         <is>
           <t>تطبیق byte/point با func__CalLut_Points/Counts/BatteryMa و گزارش mismatch در پنل</t>
         </is>
       </c>
-      <c r="K18" s="25" t="inlineStr">
+      <c r="K17" s="25" t="inlineStr">
         <is>
           <t>Host PASS: 159 check؛ شامل دو فریم واقعی LUT_DATA، battery 2 مستقل و transition غیرصفر→صفر؛ برد فیزیکی pending</t>
         </is>
       </c>
-      <c r="L18" s="23" t="inlineStr">
+      <c r="L17" s="23" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="M18" s="25" t="inlineStr">
+      <c r="M17" s="25" t="inlineStr">
         <is>
           <t>Host جای اندازه‌گیری برد را نمی‌گیرد؛ فلش و readback روی برد واقعی لازم است</t>
         </is>
       </c>
-      <c r="N18" s="25" t="inlineStr">
+      <c r="N17" s="25" t="inlineStr">
         <is>
           <t>Firmware/Modules/CalLut/Tester/run_host_test_cal_lut.sh</t>
         </is>
       </c>
-      <c r="O18" s="27" t="inlineStr">
+      <c r="O17" s="27" t="inlineStr">
         <is>
           <t>WORKTREE</t>
         </is>
       </c>
-      <c r="P18" s="27" t="inlineStr"/>
-      <c r="Q18" s="28" t="inlineStr">
+      <c r="P17" s="27" t="inlineStr"/>
+      <c r="Q17" s="28" t="inlineStr">
         <is>
           <t>2026-10-07</t>
         </is>
       </c>
     </row>
-    <row r="19" ht="67.5" customHeight="1">
-      <c r="A19" s="19" t="inlineStr">
+    <row r="18" ht="54" customHeight="1">
+      <c r="A18" s="19" t="inlineStr">
         <is>
           <t>CL-015</t>
         </is>
       </c>
-      <c r="B19" s="20" t="inlineStr">
+      <c r="B18" s="20" t="inlineStr">
         <is>
           <t>حذف override با صفرنقطه</t>
         </is>
       </c>
-      <c r="C19" s="21" t="inlineStr">
+      <c r="C18" s="21" t="inlineStr">
         <is>
           <t>بالا</t>
         </is>
       </c>
-      <c r="D19" s="29" t="inlineStr">
+      <c r="D18" s="29" t="inlineStr">
         <is>
           <t>CL-002 یا رکورد فعال با هر دو کانال</t>
         </is>
       </c>
-      <c r="E19" s="29" t="inlineStr">
+      <c r="E18" s="29" t="inlineStr">
         <is>
           <t>گام ۱: از قبل روی هر دو کانال جدول فعال داشته باش (CL-002 برای هر دو) و نقاط کانال ۲ را یادداشت کن.
 گام ۲: LUT_BEGIN را با n1=5 و n2=0 بفرست، چانک‌ها را فقط برای کانال ۱ بفرست و با CRC درست COMMIT کن.
@@ -2138,85 +2058,85 @@
 گام ۵: در پنل تأیید بگیر که تغییر کانال ۲ «changed-confirmed» است و CRC یا count جای مقادیر واقعی نقاط (counts/BatteryMa) را نگرفته باشد.</t>
         </is>
       </c>
-      <c r="F19" s="22" t="inlineStr">
+      <c r="F18" s="22" t="inlineStr">
         <is>
           <t>کانال ۱ معتبر؛ کانال ۲ count=0؛ before کانال ۲ غیرصفر و after صفرنقطه‌ای</t>
         </is>
       </c>
-      <c r="G19" s="22" t="inlineStr">
+      <c r="G18" s="22" t="inlineStr">
         <is>
           <t>یک تبادل + یک بوت</t>
         </is>
       </c>
-      <c r="H19" s="20" t="inlineStr">
+      <c r="H18" s="20" t="inlineStr">
         <is>
           <t>commit پذیرفته؛ کانال ۱ حفظ می‌شود و override فلش کانال ۲ حذف می‌شود؛ LUT_DATA کانال ۲ فریم صفرنقطه‌ای مستقل می‌دهد</t>
         </is>
       </c>
-      <c r="I19" s="20" t="inlineStr">
+      <c r="I18" s="20" t="inlineStr">
         <is>
           <t>پینگ‌پنگ و پس از reset</t>
         </is>
       </c>
-      <c r="J19" s="20" t="inlineStr">
+      <c r="J18" s="20" t="inlineStr">
         <is>
           <t>status=0، Active کانال ۱ برقرار، Active کانال ۲=false و مقایسهٔ پنل changed-confirmed؛ CRC/count جای counts/BatteryMa را نگیرد</t>
         </is>
       </c>
-      <c r="K19" s="20" t="inlineStr">
+      <c r="K18" s="20" t="inlineStr">
         <is>
           <t>Host PASS: 159 check؛ board physical pending</t>
         </is>
       </c>
-      <c r="L19" s="23" t="inlineStr">
+      <c r="L18" s="23" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="M19" s="20" t="inlineStr">
+      <c r="M18" s="20" t="inlineStr">
         <is>
           <t>Host جای تست برد را نمی‌گیرد؛ حذف override و ماندگاری پس از reset روی برد واقعی لازم است</t>
         </is>
       </c>
-      <c r="N19" s="29" t="inlineStr">
+      <c r="N18" s="29" t="inlineStr">
         <is>
           <t>Firmware/Modules/CalLut/Tester/run_host_test_cal_lut.sh؛ esp_link_panel/Tester/host_test_scenario_cards.js</t>
         </is>
       </c>
-      <c r="O19" s="22" t="inlineStr">
+      <c r="O18" s="22" t="inlineStr">
         <is>
           <t>WORKTREE</t>
         </is>
       </c>
-      <c r="P19" s="22" t="n"/>
-      <c r="Q19" s="24" t="inlineStr">
+      <c r="P18" s="22" t="n"/>
+      <c r="Q18" s="24" t="inlineStr">
         <is>
           <t>2026-10-07</t>
         </is>
       </c>
     </row>
-    <row r="20" ht="67.5" customHeight="1">
-      <c r="A20" s="19" t="inlineStr">
+    <row r="19" ht="67.5" customHeight="1">
+      <c r="A19" s="19" t="inlineStr">
         <is>
           <t>CL-016</t>
         </is>
       </c>
-      <c r="B20" s="25" t="inlineStr">
+      <c r="B19" s="25" t="inlineStr">
         <is>
           <t>reset با grant و flush NVM</t>
         </is>
       </c>
-      <c r="C20" s="26" t="inlineStr">
+      <c r="C19" s="26" t="inlineStr">
         <is>
           <t>بالا</t>
         </is>
       </c>
-      <c r="D20" s="25" t="inlineStr">
+      <c r="D19" s="25" t="inlineStr">
         <is>
           <t>commit موفق یا commit صفرنقطه‌ای؛ magic معتبر؛ لینک فعال</t>
         </is>
       </c>
-      <c r="E20" s="25" t="inlineStr">
+      <c r="E19" s="25" t="inlineStr">
         <is>
           <t>گام ۱: یک commit موفق (یا commit صفرنقطه‌ای با count=0 معتبر) انجام بده تا grant ریست صادر شود.
 گام ۲: بلافاصله reset را درخواست کن و صبر کن برد بالا بیاید (حداکثر 15 ثانیه).
@@ -2225,85 +2145,85 @@
 گام ۵: نتیجه بگیر: commit صفرنقطه‌ای بدون جدول فعال پذیرفته می‌شود و reset فقط با grant commit و flush موفق اتفاق می‌افتد.</t>
         </is>
       </c>
-      <c r="F20" s="27" t="inlineStr">
+      <c r="F19" s="27" t="inlineStr">
         <is>
           <t>count=0 معتبر؛ grant commit؛ flush success/failure</t>
         </is>
       </c>
-      <c r="G20" s="27" t="inlineStr">
+      <c r="G19" s="27" t="inlineStr">
         <is>
           <t>حداکثر 15s</t>
         </is>
       </c>
-      <c r="H20" s="25" t="inlineStr">
+      <c r="H19" s="25" t="inlineStr">
         <is>
           <t>zero-point commit بدون active table پذیرفته می‌شود؛ reset فقط با grant commit و flush موفق arm می‌شود؛ flush failure کد CAL_LUT_ST_FLASH می‌دهد و reset انجام نمی‌شود</t>
         </is>
       </c>
-      <c r="I20" s="25" t="inlineStr">
+      <c r="I19" s="25" t="inlineStr">
         <is>
           <t>پس از موفقیت one-shot؛ بعد از flush failure grant برای retry حفظ می‌شود</t>
         </is>
       </c>
-      <c r="J20" s="25" t="inlineStr">
+      <c r="J19" s="25" t="inlineStr">
         <is>
           <t>پس از reset /t و LUT_READ/LUT_DATA تازه، هر دو کانال و persistence با expected برابر؛ هیچ reject/timeout/mismatch موفق گزارش نشود</t>
         </is>
       </c>
-      <c r="K20" s="25" t="inlineStr">
+      <c r="K19" s="25" t="inlineStr">
         <is>
           <t>Host PASS: CalLut=159، parser=14 و NVM؛ تست فیزیکی فلش/ریست/باتری انجام نشده و pending است</t>
         </is>
       </c>
-      <c r="L20" s="23" t="inlineStr">
+      <c r="L19" s="23" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="M20" s="25" t="inlineStr">
+      <c r="M19" s="25" t="inlineStr">
         <is>
           <t>Host جای تست فیزیکی برد و fault واقعی NVM را نمی‌گیرد؛ commit zero-point، reset و flush روی برد واقعی تکرار شود</t>
         </is>
       </c>
-      <c r="N20" s="30" t="inlineStr">
+      <c r="N19" s="30" t="inlineStr">
         <is>
           <t>Firmware/Modules/CalLut/Tester/run_host_test_cal_lut.sh؛ Firmware/Modules/EspLink/Tester/run_host_test_nvm.sh؛ Firmware/Modules/EspLink/esp_link.c</t>
         </is>
       </c>
-      <c r="O20" s="27" t="inlineStr">
+      <c r="O19" s="27" t="inlineStr">
         <is>
           <t>WORKTREE</t>
         </is>
       </c>
-      <c r="P20" s="27" t="n"/>
-      <c r="Q20" s="28" t="inlineStr">
+      <c r="P19" s="27" t="n"/>
+      <c r="Q19" s="28" t="inlineStr">
         <is>
           <t>2026-10-08</t>
         </is>
       </c>
     </row>
-    <row r="21" ht="54" customHeight="1">
-      <c r="A21" s="19" t="inlineStr">
+    <row r="20" ht="67.5" customHeight="1">
+      <c r="A20" s="19" t="inlineStr">
         <is>
           <t>CL-020</t>
         </is>
       </c>
-      <c r="B21" s="20" t="inlineStr">
+      <c r="B20" s="20" t="inlineStr">
         <is>
           <t>پنل دیالوگ LUT</t>
         </is>
       </c>
-      <c r="C21" s="22" t="inlineStr">
+      <c r="C20" s="22" t="inlineStr">
         <is>
           <t>متوسط</t>
         </is>
       </c>
-      <c r="D21" s="20" t="inlineStr">
+      <c r="D20" s="20" t="inlineStr">
         <is>
           <t>پنل وصل + LUT آماده</t>
         </is>
       </c>
-      <c r="E21" s="20" t="inlineStr">
+      <c r="E20" s="20" t="inlineStr">
         <is>
           <t>گام ۱: پنل را وصل کن و یک LUT دوکاناله آمادهٔ ارسال داشته باش.
 گام ۲: از پنل LUT را push کن و صبر کن دیالوگ تأیید ریست بیاید.
@@ -2311,293 +2231,297 @@
 گام ۴: یک بار کلید Enter را بزن (باید تأیید کند) و یک بار در اجرای بعدی Esc را بزن (باید لغو کند)؛ اگر دو دیالوگ پشت سر هم آمد باید یکی‌یکی در صف PMQ نمایش داده شوند.</t>
         </is>
       </c>
-      <c r="F21" s="22" t="inlineStr">
+      <c r="F20" s="22" t="inlineStr">
         <is>
           <t>LUT 2 کانال</t>
         </is>
       </c>
-      <c r="G21" s="22" t="inlineStr">
+      <c r="G20" s="22" t="inlineStr">
         <is>
           <t>10s</t>
         </is>
       </c>
-      <c r="H21" s="20" t="inlineStr">
+      <c r="H20" s="20" t="inlineStr">
         <is>
           <t>دیالوگ با استایل #pmod/#121a2c، بدون alert سفید ویندوز؛ Enter=تأیید Esc=انصراف؛ صف PMQ یکی‌یکی</t>
         </is>
       </c>
-      <c r="I21" s="20" t="inlineStr">
+      <c r="I20" s="20" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J21" s="20" t="inlineStr">
+      <c r="J20" s="20" t="inlineStr">
         <is>
           <t>دیالوگ تیره + Enter/Esc کار کند</t>
         </is>
       </c>
-      <c r="K21" s="20" t="n"/>
-      <c r="L21" s="31" t="inlineStr">
+      <c r="K20" s="20" t="n"/>
+      <c r="L20" s="31" t="inlineStr">
         <is>
           <t>نیاز به تکرار</t>
         </is>
       </c>
-      <c r="M21" s="20" t="n"/>
-      <c r="N21" s="20" t="n"/>
-      <c r="O21" s="22" t="inlineStr">
+      <c r="M20" s="20" t="n"/>
+      <c r="N20" s="20" t="inlineStr">
+        <is>
+          <t>../EspLink/esp_link.c</t>
+        </is>
+      </c>
+      <c r="O20" s="22" t="inlineStr">
         <is>
           <t>62f3782</t>
         </is>
       </c>
-      <c r="P21" s="22" t="n"/>
-      <c r="Q21" s="24" t="inlineStr">
+      <c r="P20" s="22" t="n"/>
+      <c r="Q20" s="24" t="inlineStr">
         <is>
           <t>2026-10-12</t>
         </is>
+      </c>
+    </row>
+    <row r="21" ht="54" customHeight="1">
+      <c r="Q21" s="32">
+        <f>IF(OR(L22="",L22="در انتظار"),"",IF(Q22="",TODAY(),Q22))</f>
+        <v/>
       </c>
     </row>
     <row r="22">
       <c r="Q22" s="32">
-        <f>IF(OR(L22="",L22="در انتظار"),"",IF(Q22="",TODAY(),Q22))</f>
+        <f>IF(OR(L23="",L23="در انتظار"),"",IF(Q23="",TODAY(),Q23))</f>
         <v/>
       </c>
     </row>
     <row r="23">
       <c r="Q23" s="32">
-        <f>IF(OR(L23="",L23="در انتظار"),"",IF(Q23="",TODAY(),Q23))</f>
+        <f>IF(OR(L24="",L24="در انتظار"),"",IF(Q24="",TODAY(),Q24))</f>
         <v/>
       </c>
     </row>
     <row r="24">
       <c r="Q24" s="32">
-        <f>IF(OR(L24="",L24="در انتظار"),"",IF(Q24="",TODAY(),Q24))</f>
+        <f>IF(OR(L25="",L25="در انتظار"),"",IF(Q25="",TODAY(),Q25))</f>
         <v/>
       </c>
     </row>
     <row r="25">
       <c r="Q25" s="32">
-        <f>IF(OR(L25="",L25="در انتظار"),"",IF(Q25="",TODAY(),Q25))</f>
+        <f>IF(OR(L26="",L26="در انتظار"),"",IF(Q26="",TODAY(),Q26))</f>
         <v/>
       </c>
     </row>
     <row r="26">
       <c r="Q26" s="32">
-        <f>IF(OR(L26="",L26="در انتظار"),"",IF(Q26="",TODAY(),Q26))</f>
+        <f>IF(OR(L27="",L27="در انتظار"),"",IF(Q27="",TODAY(),Q27))</f>
         <v/>
       </c>
     </row>
     <row r="27">
       <c r="Q27" s="32">
-        <f>IF(OR(L27="",L27="در انتظار"),"",IF(Q27="",TODAY(),Q27))</f>
+        <f>IF(OR(L28="",L28="در انتظار"),"",IF(Q28="",TODAY(),Q28))</f>
         <v/>
       </c>
     </row>
     <row r="28">
       <c r="Q28" s="32">
-        <f>IF(OR(L28="",L28="در انتظار"),"",IF(Q28="",TODAY(),Q28))</f>
+        <f>IF(OR(L29="",L29="در انتظار"),"",IF(Q29="",TODAY(),Q29))</f>
         <v/>
       </c>
     </row>
     <row r="29">
       <c r="Q29" s="32">
-        <f>IF(OR(L29="",L29="در انتظار"),"",IF(Q29="",TODAY(),Q29))</f>
+        <f>IF(OR(L30="",L30="در انتظار"),"",IF(Q30="",TODAY(),Q30))</f>
         <v/>
       </c>
     </row>
     <row r="30">
       <c r="Q30" s="32">
-        <f>IF(OR(L30="",L30="در انتظار"),"",IF(Q30="",TODAY(),Q30))</f>
+        <f>IF(OR(L31="",L31="در انتظار"),"",IF(Q31="",TODAY(),Q31))</f>
         <v/>
       </c>
     </row>
     <row r="31">
       <c r="Q31" s="32">
-        <f>IF(OR(L31="",L31="در انتظار"),"",IF(Q31="",TODAY(),Q31))</f>
+        <f>IF(OR(L32="",L32="در انتظار"),"",IF(Q32="",TODAY(),Q32))</f>
         <v/>
       </c>
     </row>
     <row r="32">
       <c r="Q32" s="32">
-        <f>IF(OR(L32="",L32="در انتظار"),"",IF(Q32="",TODAY(),Q32))</f>
+        <f>IF(OR(L33="",L33="در انتظار"),"",IF(Q33="",TODAY(),Q33))</f>
         <v/>
       </c>
     </row>
     <row r="33">
       <c r="Q33" s="32">
-        <f>IF(OR(L33="",L33="در انتظار"),"",IF(Q33="",TODAY(),Q33))</f>
+        <f>IF(OR(L34="",L34="در انتظار"),"",IF(Q34="",TODAY(),Q34))</f>
         <v/>
       </c>
     </row>
     <row r="34">
       <c r="Q34" s="32">
-        <f>IF(OR(L34="",L34="در انتظار"),"",IF(Q34="",TODAY(),Q34))</f>
+        <f>IF(OR(L35="",L35="در انتظار"),"",IF(Q35="",TODAY(),Q35))</f>
         <v/>
       </c>
     </row>
     <row r="35">
       <c r="Q35" s="32">
-        <f>IF(OR(L35="",L35="در انتظار"),"",IF(Q35="",TODAY(),Q35))</f>
+        <f>IF(OR(L36="",L36="در انتظار"),"",IF(Q36="",TODAY(),Q36))</f>
         <v/>
       </c>
     </row>
     <row r="36">
       <c r="Q36" s="32">
-        <f>IF(OR(L36="",L36="در انتظار"),"",IF(Q36="",TODAY(),Q36))</f>
+        <f>IF(OR(L37="",L37="در انتظار"),"",IF(Q37="",TODAY(),Q37))</f>
         <v/>
       </c>
     </row>
     <row r="37">
       <c r="Q37" s="32">
-        <f>IF(OR(L37="",L37="در انتظار"),"",IF(Q37="",TODAY(),Q37))</f>
+        <f>IF(OR(L38="",L38="در انتظار"),"",IF(Q38="",TODAY(),Q38))</f>
         <v/>
       </c>
     </row>
     <row r="38">
       <c r="Q38" s="32">
-        <f>IF(OR(L38="",L38="در انتظار"),"",IF(Q38="",TODAY(),Q38))</f>
+        <f>IF(OR(L39="",L39="در انتظار"),"",IF(Q39="",TODAY(),Q39))</f>
         <v/>
       </c>
     </row>
     <row r="39">
       <c r="Q39" s="32">
-        <f>IF(OR(L39="",L39="در انتظار"),"",IF(Q39="",TODAY(),Q39))</f>
+        <f>IF(OR(L40="",L40="در انتظار"),"",IF(Q40="",TODAY(),Q40))</f>
         <v/>
       </c>
     </row>
     <row r="40">
       <c r="Q40" s="32">
-        <f>IF(OR(L40="",L40="در انتظار"),"",IF(Q40="",TODAY(),Q40))</f>
+        <f>IF(OR(L41="",L41="در انتظار"),"",IF(Q41="",TODAY(),Q41))</f>
         <v/>
       </c>
     </row>
     <row r="41">
       <c r="Q41" s="32">
-        <f>IF(OR(L41="",L41="در انتظار"),"",IF(Q41="",TODAY(),Q41))</f>
+        <f>IF(OR(L42="",L42="در انتظار"),"",IF(Q42="",TODAY(),Q42))</f>
         <v/>
       </c>
     </row>
     <row r="42">
       <c r="Q42" s="32">
-        <f>IF(OR(L42="",L42="در انتظار"),"",IF(Q42="",TODAY(),Q42))</f>
+        <f>IF(OR(L43="",L43="در انتظار"),"",IF(Q43="",TODAY(),Q43))</f>
         <v/>
       </c>
     </row>
     <row r="43">
       <c r="Q43" s="32">
-        <f>IF(OR(L43="",L43="در انتظار"),"",IF(Q43="",TODAY(),Q43))</f>
+        <f>IF(OR(L44="",L44="در انتظار"),"",IF(Q44="",TODAY(),Q44))</f>
         <v/>
       </c>
     </row>
     <row r="44">
       <c r="Q44" s="32">
-        <f>IF(OR(L44="",L44="در انتظار"),"",IF(Q44="",TODAY(),Q44))</f>
+        <f>IF(OR(L45="",L45="در انتظار"),"",IF(Q45="",TODAY(),Q45))</f>
         <v/>
       </c>
     </row>
     <row r="45">
       <c r="Q45" s="32">
-        <f>IF(OR(L45="",L45="در انتظار"),"",IF(Q45="",TODAY(),Q45))</f>
+        <f>IF(OR(L46="",L46="در انتظار"),"",IF(Q46="",TODAY(),Q46))</f>
         <v/>
       </c>
     </row>
     <row r="46">
       <c r="Q46" s="32">
-        <f>IF(OR(L46="",L46="در انتظار"),"",IF(Q46="",TODAY(),Q46))</f>
+        <f>IF(OR(L47="",L47="در انتظار"),"",IF(Q47="",TODAY(),Q47))</f>
         <v/>
       </c>
     </row>
     <row r="47">
       <c r="Q47" s="32">
-        <f>IF(OR(L47="",L47="در انتظار"),"",IF(Q47="",TODAY(),Q47))</f>
+        <f>IF(OR(L48="",L48="در انتظار"),"",IF(Q48="",TODAY(),Q48))</f>
         <v/>
       </c>
     </row>
     <row r="48">
       <c r="Q48" s="32">
-        <f>IF(OR(L48="",L48="در انتظار"),"",IF(Q48="",TODAY(),Q48))</f>
+        <f>IF(OR(L49="",L49="در انتظار"),"",IF(Q49="",TODAY(),Q49))</f>
         <v/>
       </c>
     </row>
     <row r="49">
       <c r="Q49" s="32">
-        <f>IF(OR(L49="",L49="در انتظار"),"",IF(Q49="",TODAY(),Q49))</f>
+        <f>IF(OR(L50="",L50="در انتظار"),"",IF(Q50="",TODAY(),Q50))</f>
         <v/>
       </c>
     </row>
     <row r="50">
       <c r="Q50" s="32">
-        <f>IF(OR(L50="",L50="در انتظار"),"",IF(Q50="",TODAY(),Q50))</f>
+        <f>IF(OR(L51="",L51="در انتظار"),"",IF(Q51="",TODAY(),Q51))</f>
         <v/>
       </c>
     </row>
     <row r="51">
       <c r="Q51" s="32">
-        <f>IF(OR(L51="",L51="در انتظار"),"",IF(Q51="",TODAY(),Q51))</f>
+        <f>IF(OR(L52="",L52="در انتظار"),"",IF(Q52="",TODAY(),Q52))</f>
         <v/>
       </c>
     </row>
     <row r="52">
       <c r="Q52" s="32">
-        <f>IF(OR(L52="",L52="در انتظار"),"",IF(Q52="",TODAY(),Q52))</f>
+        <f>IF(OR(L53="",L53="در انتظار"),"",IF(Q53="",TODAY(),Q53))</f>
         <v/>
       </c>
     </row>
     <row r="53">
       <c r="Q53" s="32">
-        <f>IF(OR(L53="",L53="در انتظار"),"",IF(Q53="",TODAY(),Q53))</f>
+        <f>IF(OR(L54="",L54="در انتظار"),"",IF(Q54="",TODAY(),Q54))</f>
         <v/>
       </c>
     </row>
     <row r="54">
       <c r="Q54" s="32">
-        <f>IF(OR(L54="",L54="در انتظار"),"",IF(Q54="",TODAY(),Q54))</f>
+        <f>IF(OR(L55="",L55="در انتظار"),"",IF(Q55="",TODAY(),Q55))</f>
         <v/>
       </c>
     </row>
     <row r="55">
       <c r="Q55" s="32">
-        <f>IF(OR(L55="",L55="در انتظار"),"",IF(Q55="",TODAY(),Q55))</f>
+        <f>IF(OR(L56="",L56="در انتظار"),"",IF(Q56="",TODAY(),Q56))</f>
         <v/>
       </c>
     </row>
     <row r="56">
       <c r="Q56" s="32">
-        <f>IF(OR(L56="",L56="در انتظار"),"",IF(Q56="",TODAY(),Q56))</f>
+        <f>IF(OR(L57="",L57="در انتظار"),"",IF(Q57="",TODAY(),Q57))</f>
         <v/>
       </c>
     </row>
     <row r="57">
       <c r="Q57" s="32">
-        <f>IF(OR(L57="",L57="در انتظار"),"",IF(Q57="",TODAY(),Q57))</f>
+        <f>IF(OR(L58="",L58="در انتظار"),"",IF(Q58="",TODAY(),Q58))</f>
         <v/>
       </c>
     </row>
     <row r="58">
       <c r="Q58" s="32">
-        <f>IF(OR(L58="",L58="در انتظار"),"",IF(Q58="",TODAY(),Q58))</f>
+        <f>IF(OR(L59="",L59="در انتظار"),"",IF(Q59="",TODAY(),Q59))</f>
         <v/>
       </c>
     </row>
     <row r="59">
       <c r="Q59" s="32">
-        <f>IF(OR(L59="",L59="در انتظار"),"",IF(Q59="",TODAY(),Q59))</f>
+        <f>IF(OR(L60="",L60="در انتظار"),"",IF(Q60="",TODAY(),Q60))</f>
         <v/>
       </c>
     </row>
     <row r="60">
       <c r="Q60" s="32">
-        <f>IF(OR(L60="",L60="در انتظار"),"",IF(Q60="",TODAY(),Q60))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="61">
-      <c r="Q61" s="32">
         <f>IF(OR(L61="",L61="در انتظار"),"",IF(Q61="",TODAY(),Q61))</f>
         <v/>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:Q21"/>
+  <autoFilter ref="A4:Q60"/>
   <dataValidations count="2">
     <dataValidation sqref="C5:C101" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>='فهرست‌ها'!$B$9:$B$11</formula1>
@@ -2611,8 +2535,8 @@
     <hyperlink ref="E7" location="'برنامه تست'!A6"/>
     <hyperlink ref="D14" location="'برنامه تست'!A6"/>
     <hyperlink ref="E14" location="'برنامه تست'!A6"/>
-    <hyperlink ref="D19" location="'برنامه تست'!A6"/>
-    <hyperlink ref="E19" location="'برنامه تست'!A6"/>
+    <hyperlink ref="D18" location="'برنامه تست'!A6"/>
+    <hyperlink ref="E18" location="'برنامه تست'!A6"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N19" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N20" r:id="rId2"/>
   </hyperlinks>
@@ -2622,6 +2546,355 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="00ED7D31"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:Q25"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="9" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="62" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="42" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="34" customWidth="1" min="10" max="10"/>
+    <col width="34" customWidth="1" min="11" max="11"/>
+    <col width="13" customWidth="1" min="12" max="12"/>
+    <col width="24" customWidth="1" min="13" max="13"/>
+    <col width="16" customWidth="1" min="14" max="14"/>
+    <col width="12" customWidth="1" min="15" max="15"/>
+    <col width="13" customWidth="1" min="16" max="16"/>
+    <col width="12" customWidth="1" min="17" max="17"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="17" t="inlineStr">
+        <is>
+          <t>تست‌های آزمایشگاهی (پایه، اسیلوسکوپ و زمان‌بندی دقیق — جدا از تست عملی)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="42" customHeight="1">
+      <c r="A2" s="44" t="inlineStr">
+        <is>
+          <t>این شیت جدا از تست عملی است: اندازه‌گیری روی پایه‌ها، اسیلوسکوپ و تلرانس‌های دقیق میلی‌ثانیه/میکروثانیه. برای بررسی عملکرد واقعی دستگاه لازم نیست؛ برای اعتبارسنجی دقیق سخت‌افزار و زمان‌بندی‌هاست.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3"/>
+    <row r="4" ht="30" customHeight="1">
+      <c r="A4" s="16" t="inlineStr">
+        <is>
+          <t>شناسه</t>
+        </is>
+      </c>
+      <c r="B4" s="16" t="inlineStr">
+        <is>
+          <t>دسته</t>
+        </is>
+      </c>
+      <c r="C4" s="16" t="inlineStr">
+        <is>
+          <t>اولویت</t>
+        </is>
+      </c>
+      <c r="D4" s="16" t="inlineStr">
+        <is>
+          <t>پیش‌شرط</t>
+        </is>
+      </c>
+      <c r="E4" s="16" t="inlineStr">
+        <is>
+          <t>روش اجرای دقیق</t>
+        </is>
+      </c>
+      <c r="F4" s="16" t="inlineStr">
+        <is>
+          <t>ورودی‌ها / شرایط</t>
+        </is>
+      </c>
+      <c r="G4" s="16" t="inlineStr">
+        <is>
+          <t>مدت مشاهده</t>
+        </is>
+      </c>
+      <c r="H4" s="16" t="inlineStr">
+        <is>
+          <t>رفتار مورد انتظار</t>
+        </is>
+      </c>
+      <c r="I4" s="16" t="inlineStr">
+        <is>
+          <t>وضعیت حفظ / latch</t>
+        </is>
+      </c>
+      <c r="J4" s="16" t="inlineStr">
+        <is>
+          <t>معیار قبولی</t>
+        </is>
+      </c>
+      <c r="K4" s="16" t="inlineStr">
+        <is>
+          <t>نتیجهٔ واقعی / اندازه‌گیری</t>
+        </is>
+      </c>
+      <c r="L4" s="16" t="inlineStr">
+        <is>
+          <t>وضعیت</t>
+        </is>
+      </c>
+      <c r="M4" s="16" t="inlineStr">
+        <is>
+          <t>شرح ایراد / تفاوت</t>
+        </is>
+      </c>
+      <c r="N4" s="16" t="inlineStr">
+        <is>
+          <t>مدرک تست / scope</t>
+        </is>
+      </c>
+      <c r="O4" s="16" t="inlineStr">
+        <is>
+          <t>commit</t>
+        </is>
+      </c>
+      <c r="P4" s="16" t="inlineStr">
+        <is>
+          <t>نام تست‌کننده</t>
+        </is>
+      </c>
+      <c r="Q4" s="16" t="inlineStr">
+        <is>
+          <t>تاریخ</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="54" customHeight="1">
+      <c r="A5" s="19" t="inlineStr">
+        <is>
+          <t>CL-012</t>
+        </is>
+      </c>
+      <c r="B5" s="25" t="inlineStr">
+        <is>
+          <t>idle شدن شارژر هنگام ریست</t>
+        </is>
+      </c>
+      <c r="C5" s="26" t="inlineStr">
+        <is>
+          <t>بالا</t>
+        </is>
+      </c>
+      <c r="D5" s="25" t="inlineStr">
+        <is>
+          <t>جدول فعال، شارژ در جریان</t>
+        </is>
+      </c>
+      <c r="E5" s="25" t="inlineStr">
+        <is>
+          <t>گام ۱: یک جدول فعال کن و شارژ را در حالت BULK راه بینداز تا کانال در حال شارژ PWM داشته باشد.
+گام ۲: اسیلوسکوپ را روی گیت همان کانال بگذار.
+گام ۳: حین شارژ فرمان LUT_RESET را بفرست.
+گام ۴: روی اسکوپ ببین که پیش از ریست، duty اول صفر شده و شارژر idle شده باشد؛ ریست نباید وسط پالس اتفاق بیفتد.</t>
+        </is>
+      </c>
+      <c r="F5" s="27" t="inlineStr">
+        <is>
+          <t>درخواست ریست با PWM فعال</t>
+        </is>
+      </c>
+      <c r="G5" s="27" t="inlineStr">
+        <is>
+          <t>یک تبادل</t>
+        </is>
+      </c>
+      <c r="H5" s="25" t="inlineStr">
+        <is>
+          <t>قبل از ریست هر دو دیوتی صفر و شارژر idle می‌شود</t>
+        </is>
+      </c>
+      <c r="I5" s="25" t="inlineStr">
+        <is>
+          <t>بدون latch</t>
+        </is>
+      </c>
+      <c r="J5" s="25" t="inlineStr">
+        <is>
+          <t>اسیلوسکوپ روی گیت: صفر پیش از ریست</t>
+        </is>
+      </c>
+      <c r="K5" s="25" t="inlineStr">
+        <is>
+          <t>در انتظار</t>
+        </is>
+      </c>
+      <c r="L5" s="23" t="inlineStr">
+        <is>
+          <t>در انتظار</t>
+        </is>
+      </c>
+      <c r="M5" s="25" t="n"/>
+      <c r="N5" s="25" t="inlineStr">
+        <is>
+          <t>TESTER: fill</t>
+        </is>
+      </c>
+      <c r="O5" s="27" t="inlineStr">
+        <is>
+          <t>TESTER: fill</t>
+        </is>
+      </c>
+      <c r="P5" s="27" t="inlineStr">
+        <is>
+          <t>TESTER: fill</t>
+        </is>
+      </c>
+      <c r="Q5" s="28" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="Q6" s="32">
+        <f>IF(OR(L6="",L6="در انتظار"),"",IF(Q6="",TODAY(),Q6))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7">
+      <c r="Q7" s="32">
+        <f>IF(OR(L7="",L7="در انتظار"),"",IF(Q7="",TODAY(),Q7))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="Q8" s="32">
+        <f>IF(OR(L8="",L8="در انتظار"),"",IF(Q8="",TODAY(),Q8))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9">
+      <c r="Q9" s="32">
+        <f>IF(OR(L9="",L9="در انتظار"),"",IF(Q9="",TODAY(),Q9))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10">
+      <c r="Q10" s="32">
+        <f>IF(OR(L10="",L10="در انتظار"),"",IF(Q10="",TODAY(),Q10))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="Q11" s="32">
+        <f>IF(OR(L11="",L11="در انتظار"),"",IF(Q11="",TODAY(),Q11))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="Q12" s="32">
+        <f>IF(OR(L12="",L12="در انتظار"),"",IF(Q12="",TODAY(),Q12))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="Q13" s="32">
+        <f>IF(OR(L13="",L13="در انتظار"),"",IF(Q13="",TODAY(),Q13))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="Q14" s="32">
+        <f>IF(OR(L14="",L14="در انتظار"),"",IF(Q14="",TODAY(),Q14))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="Q15" s="32">
+        <f>IF(OR(L15="",L15="در انتظار"),"",IF(Q15="",TODAY(),Q15))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16">
+      <c r="Q16" s="32">
+        <f>IF(OR(L16="",L16="در انتظار"),"",IF(Q16="",TODAY(),Q16))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17">
+      <c r="Q17" s="32">
+        <f>IF(OR(L17="",L17="در انتظار"),"",IF(Q17="",TODAY(),Q17))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18">
+      <c r="Q18" s="32">
+        <f>IF(OR(L18="",L18="در انتظار"),"",IF(Q18="",TODAY(),Q18))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19">
+      <c r="Q19" s="32">
+        <f>IF(OR(L19="",L19="در انتظار"),"",IF(Q19="",TODAY(),Q19))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20">
+      <c r="Q20" s="32">
+        <f>IF(OR(L20="",L20="در انتظار"),"",IF(Q20="",TODAY(),Q20))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21">
+      <c r="Q21" s="32">
+        <f>IF(OR(L21="",L21="در انتظار"),"",IF(Q21="",TODAY(),Q21))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22">
+      <c r="Q22" s="32">
+        <f>IF(OR(L22="",L22="در انتظار"),"",IF(Q22="",TODAY(),Q22))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23">
+      <c r="Q23" s="32">
+        <f>IF(OR(L23="",L23="در انتظار"),"",IF(Q23="",TODAY(),Q23))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24">
+      <c r="Q24" s="32">
+        <f>IF(OR(L24="",L24="در انتظار"),"",IF(Q24="",TODAY(),Q24))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25">
+      <c r="Q25" s="32">
+        <f>IF(OR(L25="",L25="در انتظار"),"",IF(Q25="",TODAY(),Q25))</f>
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A4:Q5"/>
+  <dataValidations count="1">
+    <dataValidation sqref="L5 L6 L7 L8 L9 L10 L11 L12 L13 L14 L15 L16 L17 L18 L19 L20 L21 L22 L23 L24 L25" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>='فهرست‌ها'!$A$2:$A$7</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="00BF8F00"/>
@@ -2875,7 +3148,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="00C00000"/>
@@ -2998,7 +3271,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="00548235"/>
@@ -3225,7 +3498,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="00808080"/>
@@ -3321,7 +3594,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="007030A0"/>

--- a/Firmware/Modules/CalLut/CalLut_Validation.xlsx
+++ b/Firmware/Modules/CalLut/CalLut_Validation.xlsx
@@ -15,6 +15,7 @@
     <sheet name="تأیید نهایی" sheetId="6" state="visible" r:id="rId6"/>
     <sheet name="فهرست‌ها" sheetId="7" state="visible" r:id="rId7"/>
     <sheet name="ماشین حالت" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="تست‌های برنامه‌نویسی" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'برنامه تست'!$A$4:$Q$60</definedName>
@@ -780,7 +781,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:Q60"/>
+  <dimension ref="A1:Q53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -926,42 +927,40 @@
           <t>بالا</t>
         </is>
       </c>
-      <c r="D5" s="20" t="inlineStr">
-        <is>
-          <t>برد پاک یا دو صفحهٔ LUT پاک‌شده</t>
+      <c r="D5" s="29" t="inlineStr">
+        <is>
+          <t>دستگاه تازه است یا جدولش را تازه پاک کرده‌ای (CL-016)؛ باتری و برق شهر آماده</t>
         </is>
       </c>
       <c r="E5" s="20" t="inlineStr">
         <is>
-          <t>گام ۱: مطمئن شو هیچ جدولی از پنل فرستاده نشده و فلش LUT خالی است (همهٔ خانه‌ها 65535).
-گام ۲: برد را روشن کن و صبر کن بوت کامل شود.
-گام ۳: از پنل ببین هر دو کانال جدول فعال ندارند (Active هر دو false است).
-گام ۴: جریان خوانده‌شدهٔ هر دو کانال را با همان بردی که ماژول LUT نداشت مقایسه کن؛ باید دقیقاً یکی باشد، چون مسیر اندازه‌گیری از خط گین و آفست استفاده می‌کند.</t>
+          <t>گام ۱: دستگاه را روشن کن و یک باتری نیمه‌خالی را به شارژ بزن.
+گام ۲: چند دقیقه رفتار شارژ را نگاه کن.</t>
         </is>
       </c>
       <c r="F5" s="22" t="inlineStr">
         <is>
-          <t>فلش LUT خالی (65535 = خانهٔ پاک‌شدهٔ فلش)</t>
+          <t>روشن‌کردن و شارژ بدون جدول سفارشی</t>
         </is>
       </c>
       <c r="G5" s="22" t="inlineStr">
         <is>
-          <t>یک بوت</t>
+          <t>پنج دقیقه</t>
         </is>
       </c>
       <c r="H5" s="20" t="inlineStr">
         <is>
-          <t>func__CalLut_Active هر دو کانال false؛ مسیر اندازه‌گیری از خط گین و آفست استفاده می‌کند</t>
+          <t>شارژ با جدول پیش‌فرض کارخانه کاملاً عادی کار می‌کند؛ هیچ خطای جدولی نیست</t>
         </is>
       </c>
       <c r="I5" s="20" t="inlineStr">
         <is>
-          <t>بدون latch</t>
+          <t>رفتار پیش‌فرض</t>
         </is>
       </c>
       <c r="J5" s="20" t="inlineStr">
         <is>
-          <t>خوانش جریان دقیقاً برابر نسخهٔ پیش از افزودن ماژول</t>
+          <t>شارژ عادی بی‌جدول = قبول؛ شارژ خراب یا خطا = رد</t>
         </is>
       </c>
       <c r="K5" s="20" t="inlineStr">
@@ -1014,41 +1013,39 @@
       </c>
       <c r="D6" s="25" t="inlineStr">
         <is>
-          <t>لینک ESP برقرار</t>
+          <t>پنل باز است و جدول درست یک کانال را آماده داری</t>
         </is>
       </c>
       <c r="E6" s="25" t="inlineStr">
         <is>
-          <t>گام ۱: لینک ESP را وصل کن و پنل را باز کن.
-گام ۲: برای کانال ۱ یک جدول 17 تا 21 نقطه‌ای بساز و ارسال کن (اول LUT_BEGIN، بعد چانک‌ها، در آخر COMMIT).
-گام ۳: پاسخ برد را بخوان: وضعیت باید 0 باشد (CAL_LUT_ST_OK).
-گام ۴: CRC32 جدول در پنل و CRC32 گزارش‌شدهٔ برد را مقایسه کن؛ باید برابر باشند.
-گام ۵: فرمان LUT_RESET را بفرست و بعد از بالا آمدن برد ببین جدول کانال ۱ فعال شده است (Active = true).</t>
+          <t>گام ۱: جدول را از پنل برای کانال ۱ بفرست.
+گام ۲: همان جدول را از پنل بخوان و عددها را مقایسه کن.
+گام ۳: با همان کانال یک شارژ واقعی انجام بده.</t>
         </is>
       </c>
       <c r="F6" s="27" t="inlineStr">
         <is>
-          <t>LUT_BEGIN + CHUNKها + COMMIT با CRC32 درست</t>
+          <t>فرستادن جدول کانال ۱ از پنل</t>
         </is>
       </c>
       <c r="G6" s="27" t="inlineStr">
         <is>
-          <t>یک تبادل</t>
+          <t>ده دقیقه</t>
         </is>
       </c>
       <c r="H6" s="25" t="inlineStr">
         <is>
-          <t>LUT_ACK با CAL_LUT_ST_OK و CRC32 برابر CRC پنل</t>
+          <t>جدول درست نشسته (خواندن برعکس همان است) و شارژ کانال ۱ با همان اعداد کار می‌کند</t>
         </is>
       </c>
       <c r="I6" s="25" t="inlineStr">
         <is>
-          <t>رکورد در فلش می‌ماند</t>
+          <t>ماندگار</t>
         </is>
       </c>
       <c r="J6" s="25" t="inlineStr">
         <is>
-          <t>status=0 و دو CRC32 برابر؛ پس از LUT_RESET، Active کانال ۱ = true</t>
+          <t>نشستن جدول و شارژ درست = قبول؛ اختلاف عدد یا شارژ خراب = رد</t>
         </is>
       </c>
       <c r="K6" s="25" t="inlineStr">
@@ -1101,40 +1098,38 @@
       </c>
       <c r="D7" s="29" t="inlineStr">
         <is>
-          <t>CL-002 قبول</t>
-        </is>
-      </c>
-      <c r="E7" s="29" t="inlineStr">
-        <is>
-          <t>گام ۱: اول تست CL-002 را قبول کن تا یک جدول سالم روی برد فعال باشد و CRC32 آن را یادداشت کن.
-گام ۲: تغذیهٔ برد را کاملاً قطع کن (فقط ریست نرم کافی نیست) و دوباره وصل کن.
-گام ۳: بعد از بوت، CRC32 جدول فعال را از برد بخوان و با مقدار یادداشت‌شده مقایسه کن.
-گام ۴: قطع و وصل کامل را 3 بار تکرار کن؛ هر سه بار CRC32 باید همان مقدار قبلی باشد.</t>
+          <t>جدول سفارشی را فرستاده‌ای و نشسته است (CL-002)</t>
+        </is>
+      </c>
+      <c r="E7" s="20" t="inlineStr">
+        <is>
+          <t>گام ۱: برق دستگاه را کامل قطع کن و یک دقیقه صبر کن.
+گام ۲: روشن کن و جدول را از پنل دوباره بخوان.</t>
         </is>
       </c>
       <c r="F7" s="22" t="inlineStr">
         <is>
-          <t>قطع کامل تغذیه</t>
+          <t>قطع و وصل کامل برق</t>
         </is>
       </c>
       <c r="G7" s="22" t="inlineStr">
         <is>
-          <t>۳ بار</t>
+          <t>پنج دقیقه</t>
         </is>
       </c>
       <c r="H7" s="20" t="inlineStr">
         <is>
-          <t>رکورد سالم بازخوانی می‌شود و جدول فلش دوباره فعال است</t>
+          <t>جدول سفارشی بعد از روشن‌شدن سر جاست</t>
         </is>
       </c>
       <c r="I7" s="20" t="inlineStr">
         <is>
-          <t>ماندگار</t>
+          <t>ماندگار در قطع برق</t>
         </is>
       </c>
       <c r="J7" s="20" t="inlineStr">
         <is>
-          <t>func__CalLut_ActiveCrc32 بعد از هر بوت همان مقدار قبل است</t>
+          <t>حفظ جدول = قبول؛ پاک‌شدن = رد</t>
         </is>
       </c>
       <c r="K7" s="20" t="inlineStr">
@@ -1172,12 +1167,12 @@
     <row r="8" ht="54" customHeight="1">
       <c r="A8" s="19" t="inlineStr">
         <is>
-          <t>CL-004</t>
+          <t>CL-010</t>
         </is>
       </c>
       <c r="B8" s="25" t="inlineStr">
         <is>
-          <t>CRC ناهمخوان</t>
+          <t>قطع برق وسط نوشتن</t>
         </is>
       </c>
       <c r="C8" s="26" t="inlineStr">
@@ -1185,42 +1180,41 @@
           <t>بالا</t>
         </is>
       </c>
-      <c r="D8" s="25" t="inlineStr">
-        <is>
-          <t>لینک برقرار</t>
-        </is>
-      </c>
-      <c r="E8" s="25" t="inlineStr">
-        <is>
-          <t>گام ۱: لینک ESP را وصل کن و CRC32 جدول فعال فعلی را یادداشت کن.
-گام ۲: یک جدول بفرست ولی در مرحلهٔ COMMIT عمداً CRC32 اشتباه بده (با CRC واقعی جدول یکی نباشد).
-گام ۳: پاسخ برد را بخوان: وضعیت باید 6 باشد (CAL_LUT_ST_CRC) و commit رد شود.
-گام ۴: CRC32 جدول فعال را دوباره بخوان؛ باید با گام ۱ یکی باشد، یعنی فلش دست‌نخورده مانده است.</t>
+      <c r="D8" s="30" t="inlineStr">
+        <is>
+          <t>پنل باز و دستگاه روشن است؛ دستت روی کلید برق دستگاه باشد</t>
+        </is>
+      </c>
+      <c r="E8" s="30" t="inlineStr">
+        <is>
+          <t>گام ۱: فرستادن یک جدول تازه از پنل را شروع کن.
+گام ۲: وسط فرستادن، برق دستگاه را بکش.
+گام ۳: دوباره روشن کن و جدول را بخوان: یا جدول قبلی سالم است یا پیش‌فرض؛ بعد یک شارژ واقعی بگیر.</t>
         </is>
       </c>
       <c r="F8" s="27" t="inlineStr">
         <is>
-          <t>CRC پنل ≠ CRC چیده‌شده</t>
+          <t>قطع برق وسط فرستادن جدول</t>
         </is>
       </c>
       <c r="G8" s="27" t="inlineStr">
         <is>
-          <t>یک تبادل</t>
+          <t>ده دقیقه</t>
         </is>
       </c>
       <c r="H8" s="25" t="inlineStr">
         <is>
-          <t>رد شدن commit با CAL_LUT_ST_CRC؛ فلش دست‌نخورده</t>
+          <t>جدول نصفه‌نیمه ذخیره نشده؛ شارژ با جدول قبلی یا پیش‌فرض سالم کار می‌کند</t>
         </is>
       </c>
       <c r="I8" s="25" t="inlineStr">
         <is>
-          <t>رکورد قبلی حفظ</t>
+          <t>بدون جدول خراب</t>
         </is>
       </c>
       <c r="J8" s="25" t="inlineStr">
         <is>
-          <t>status=6 و ActiveCrc32 تغییر نکرده</t>
+          <t>شارژ سالم بعد از قطع وسط کار = قبول؛ جدول خراب یا شارژ به‌هم‌ریخته = رد</t>
         </is>
       </c>
       <c r="K8" s="25" t="inlineStr">
@@ -1258,12 +1252,12 @@
     <row r="9" ht="54" customHeight="1">
       <c r="A9" s="19" t="inlineStr">
         <is>
-          <t>CL-005</t>
+          <t>CL-011</t>
         </is>
       </c>
       <c r="B9" s="20" t="inlineStr">
         <is>
-          <t>محور صعودی نبودن</t>
+          <t>استقلال از NVM پارامترها</t>
         </is>
       </c>
       <c r="C9" s="21" t="inlineStr">
@@ -1273,40 +1267,39 @@
       </c>
       <c r="D9" s="20" t="inlineStr">
         <is>
-          <t>لینک برقرار</t>
+          <t>جدول سفارشی نشسته و پنل باز است</t>
         </is>
       </c>
       <c r="E9" s="20" t="inlineStr">
         <is>
-          <t>گام ۱: لینک ESP را وصل کن.
-گام ۲: جدولی بساز که محور زنجیره‌اش (ChainMa) صعودیِ اکید نباشد؛ مثلاً یک نقطهٔ تکراری یا یک نقطه کمتر از قبلی بگذار.
-گام ۳: جدول را کامل بفرست و COMMIT کن.
-گام ۴: پاسخ برد را بخوان: وضعیت باید 4 باشد (CAL_LUT_ST_CHAIN) و جدول نباید فعال شود.</t>
+          <t>گام ۱: چند پارامتر معمولی پنل (نه جدولی) را عوض کن.
+گام ۲: برق را قطع و وصل کن.
+گام ۳: جدول را بخوان.</t>
         </is>
       </c>
       <c r="F9" s="22" t="inlineStr">
         <is>
-          <t>نقطهٔ تکراری یا نزولی در ChainMa</t>
+          <t>تغییر پارامترهای معمولی و قطع‌ووصل</t>
         </is>
       </c>
       <c r="G9" s="22" t="inlineStr">
         <is>
-          <t>یک تبادل</t>
+          <t>پنج دقیقه</t>
         </is>
       </c>
       <c r="H9" s="20" t="inlineStr">
         <is>
-          <t>رد با CAL_LUT_ST_CHAIN</t>
+          <t>جدول سفارشی دست‌نخورده مانده است</t>
         </is>
       </c>
       <c r="I9" s="20" t="inlineStr">
         <is>
-          <t>بدون تغییر فلش</t>
+          <t>استقلال جدول از بقیهٔ تنظیم‌ها</t>
         </is>
       </c>
       <c r="J9" s="20" t="inlineStr">
         <is>
-          <t>status=4</t>
+          <t>سالم‌ماندن جدول = قبول؛ دست‌خوردن جدول = رد</t>
         </is>
       </c>
       <c r="K9" s="20" t="inlineStr">
@@ -1344,1178 +1337,599 @@
     <row r="10" ht="54" customHeight="1">
       <c r="A10" s="19" t="inlineStr">
         <is>
-          <t>CL-006</t>
+          <t>CL-014</t>
         </is>
       </c>
       <c r="B10" s="25" t="inlineStr">
         <is>
-          <t>افت محور جریان</t>
-        </is>
-      </c>
-      <c r="C10" s="27" t="inlineStr">
-        <is>
-          <t>متوسط</t>
+          <t>LUT_READ بازخوانی واقعی هر دو کانال</t>
+        </is>
+      </c>
+      <c r="C10" s="26" t="inlineStr">
+        <is>
+          <t>بالا</t>
         </is>
       </c>
       <c r="D10" s="25" t="inlineStr">
         <is>
-          <t>لینک برقرار</t>
+          <t>برای هر دو کانال جدول ذخیره کرده‌ای</t>
         </is>
       </c>
       <c r="E10" s="25" t="inlineStr">
         <is>
-          <t>گام ۱: لینک ESP را وصل کن.
-گام ۲: جدولی بساز که جریان باتری در یکی از نقطه‌ها از نقطهٔ قبلی کمتر باشد (افت داشته باشد).
-گام ۳: جدول را کامل بفرست و COMMIT کن.
-گام ۴: پاسخ برد را بخوان: وضعیت باید 5 باشد (CAL_LUT_ST_DIP) و جدول نباید فعال شود.</t>
+          <t>گام ۱: از پنل جدول هر دو کانال را کامل بخوان.
+گام ۲: عددها را با چیزی که فرستاده بودی مقایسه کن.</t>
         </is>
       </c>
       <c r="F10" s="27" t="inlineStr">
         <is>
-          <t>نقطه‌ای کمتر از نقطهٔ قبل</t>
+          <t>خواندن جدول هر دو کانال</t>
         </is>
       </c>
       <c r="G10" s="27" t="inlineStr">
         <is>
-          <t>یک تبادل</t>
+          <t>پنج دقیقه</t>
         </is>
       </c>
       <c r="H10" s="25" t="inlineStr">
         <is>
-          <t>رد با CAL_LUT_ST_DIP (جریان باتری افت دارد)</t>
+          <t>هر دو جدول عددبه‌عدد درست و سر جای خودشان‌اند؛ کانال‌ها قاطی نشده‌اند</t>
         </is>
       </c>
       <c r="I10" s="25" t="inlineStr">
         <is>
-          <t>بدون تغییر فلش</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J10" s="25" t="inlineStr">
         <is>
-          <t>status=5</t>
+          <t>درستی هر دو = قبول؛ قاطی یا ناقص = رد</t>
         </is>
       </c>
       <c r="K10" s="25" t="inlineStr">
         <is>
+          <t>Host PASS: 159 check؛ شامل دو فریم واقعی LUT_DATA، battery 2 مستقل و transition غیرصفر→صفر؛ برد فیزیکی pending</t>
+        </is>
+      </c>
+      <c r="L10" s="23" t="inlineStr">
+        <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="L10" s="23" t="inlineStr">
-        <is>
-          <t>در انتظار</t>
-        </is>
-      </c>
-      <c r="M10" s="25" t="n"/>
+      <c r="M10" s="25" t="inlineStr">
+        <is>
+          <t>Host جای اندازه‌گیری برد را نمی‌گیرد؛ فلش و readback روی برد واقعی لازم است</t>
+        </is>
+      </c>
       <c r="N10" s="25" t="inlineStr">
         <is>
-          <t>TESTER: fill</t>
+          <t>Firmware/Modules/CalLut/Tester/run_host_test_cal_lut.sh</t>
         </is>
       </c>
       <c r="O10" s="27" t="inlineStr">
         <is>
-          <t>TESTER: fill</t>
-        </is>
-      </c>
-      <c r="P10" s="27" t="inlineStr">
-        <is>
-          <t>TESTER: fill</t>
-        </is>
-      </c>
+          <t>WORKTREE</t>
+        </is>
+      </c>
+      <c r="P10" s="27" t="inlineStr"/>
       <c r="Q10" s="28" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-07</t>
         </is>
       </c>
     </row>
     <row r="11" ht="54" customHeight="1">
       <c r="A11" s="19" t="inlineStr">
         <is>
-          <t>CL-007</t>
+          <t>CL-015</t>
         </is>
       </c>
       <c r="B11" s="20" t="inlineStr">
         <is>
-          <t>تعداد نقاط نامعتبر</t>
-        </is>
-      </c>
-      <c r="C11" s="22" t="inlineStr">
-        <is>
-          <t>متوسط</t>
-        </is>
-      </c>
-      <c r="D11" s="20" t="inlineStr">
-        <is>
-          <t>لینک برقرار</t>
-        </is>
-      </c>
-      <c r="E11" s="20" t="inlineStr">
-        <is>
-          <t>گام ۱: لینک ESP را وصل کن.
-گام ۲: یک جدول فقط با 1 نقطه بفرست و COMMIT کن؛ پاسخ را بخوان.
-گام ۳: یک جدول با 25 نقطه بفرست و COMMIT کن؛ پاسخ را بخوان.
-گام ۴: هر دو بار وضعیت باید 2 باشد (CAL_LUT_ST_COUNT)، چون تعداد نقطهٔ مجاز 2 تا 24 است.</t>
+          <t>حذف override با صفرنقطه</t>
+        </is>
+      </c>
+      <c r="C11" s="21" t="inlineStr">
+        <is>
+          <t>بالا</t>
+        </is>
+      </c>
+      <c r="D11" s="29" t="inlineStr">
+        <is>
+          <t>یک کانال جدول سفارشی (override) دارد و با آن شارژ می‌کند</t>
+        </is>
+      </c>
+      <c r="E11" s="29" t="inlineStr">
+        <is>
+          <t>گام ۱: از پنل override همان کانال را با نقطهٔ صفر پاک کن.
+گام ۲: یک شارژ واقعی با همان کانال بگیر.</t>
         </is>
       </c>
       <c r="F11" s="22" t="inlineStr">
         <is>
-          <t>points &lt; 2 یا &gt; 24</t>
+          <t>پاک‌کردن override از پنل</t>
         </is>
       </c>
       <c r="G11" s="22" t="inlineStr">
         <is>
-          <t>دو تبادل</t>
+          <t>ده دقیقه</t>
         </is>
       </c>
       <c r="H11" s="20" t="inlineStr">
         <is>
-          <t>هر دو با CAL_LUT_ST_COUNT رد می‌شوند</t>
+          <t>کانال به رفتار پیش‌فرض کارخانه برمی‌گردد و شارژ عادی می‌شود</t>
         </is>
       </c>
       <c r="I11" s="20" t="inlineStr">
         <is>
-          <t>بدون تغییر فلش</t>
+          <t>برگشت به پیش‌فرض</t>
         </is>
       </c>
       <c r="J11" s="20" t="inlineStr">
         <is>
-          <t>status=2 در هر دو</t>
+          <t>برگشت به پیش‌فرض = قبول؛ ماندن روی جدول پاک‌شده = رد</t>
         </is>
       </c>
       <c r="K11" s="20" t="inlineStr">
         <is>
+          <t>Host PASS: 159 check؛ board physical pending</t>
+        </is>
+      </c>
+      <c r="L11" s="23" t="inlineStr">
+        <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="L11" s="23" t="inlineStr">
-        <is>
-          <t>در انتظار</t>
-        </is>
-      </c>
-      <c r="M11" s="20" t="n"/>
-      <c r="N11" s="20" t="inlineStr">
-        <is>
-          <t>TESTER: fill</t>
+      <c r="M11" s="20" t="inlineStr">
+        <is>
+          <t>Host جای تست برد را نمی‌گیرد؛ حذف override و ماندگاری پس از reset روی برد واقعی لازم است</t>
+        </is>
+      </c>
+      <c r="N11" s="29" t="inlineStr">
+        <is>
+          <t>Firmware/Modules/CalLut/Tester/run_host_test_cal_lut.sh؛ esp_link_panel/Tester/host_test_scenario_cards.js</t>
         </is>
       </c>
       <c r="O11" s="22" t="inlineStr">
         <is>
-          <t>TESTER: fill</t>
-        </is>
-      </c>
-      <c r="P11" s="22" t="inlineStr">
-        <is>
-          <t>TESTER: fill</t>
-        </is>
-      </c>
+          <t>WORKTREE</t>
+        </is>
+      </c>
+      <c r="P11" s="22" t="n"/>
       <c r="Q11" s="24" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-07</t>
         </is>
       </c>
     </row>
     <row r="12" ht="54" customHeight="1">
       <c r="A12" s="19" t="inlineStr">
         <is>
-          <t>CL-008</t>
+          <t>CL-016</t>
         </is>
       </c>
       <c r="B12" s="25" t="inlineStr">
         <is>
-          <t>تکهٔ گم‌شده</t>
-        </is>
-      </c>
-      <c r="C12" s="27" t="inlineStr">
-        <is>
-          <t>متوسط</t>
+          <t>reset با grant و flush NVM</t>
+        </is>
+      </c>
+      <c r="C12" s="26" t="inlineStr">
+        <is>
+          <t>بالا</t>
         </is>
       </c>
       <c r="D12" s="25" t="inlineStr">
         <is>
-          <t>لینک برقرار</t>
+          <t>جدول سفارشی ذخیره است و پنل باز</t>
         </is>
       </c>
       <c r="E12" s="25" t="inlineStr">
         <is>
-          <t>گام ۱: لینک ESP را وصل کن و یک جدول چندچانکه آماده کن.
-گام ۲: همهٔ چانک‌ها را بفرست به‌جز یکی؛ عمداً یک چانک را نفرست.
-گام ۳: COMMIT را بفرست.
-گام ۴: پاسخ برد را بخوان: وضعیت باید 3 باشد (CAL_LUT_ST_MISSING) و هیچ جدولی فعال نشود.</t>
+          <t>گام ۱: ریست جدول را از پنل با تأیید انجام بده.
+گام ۲: برق را قطع و وصل کن.
+گام ۳: جدول را بخوان و یک شارژ بگیر.</t>
         </is>
       </c>
       <c r="F12" s="27" t="inlineStr">
         <is>
-          <t>یک تکه نرسیده</t>
+          <t>ریست جدول و قطع‌ووصل برق</t>
         </is>
       </c>
       <c r="G12" s="27" t="inlineStr">
         <is>
-          <t>یک تبادل</t>
+          <t>ده دقیقه</t>
         </is>
       </c>
       <c r="H12" s="25" t="inlineStr">
         <is>
-          <t>رد با CAL_LUT_ST_MISSING</t>
+          <t>جدول پاک شده، بعد از روشن‌شدن هم برنمی‌گردد و شارژ پیش‌فرض عادی است</t>
         </is>
       </c>
       <c r="I12" s="25" t="inlineStr">
         <is>
-          <t>بدون تغییر فلش</t>
+          <t>ماندگار</t>
         </is>
       </c>
       <c r="J12" s="25" t="inlineStr">
         <is>
-          <t>status=3</t>
+          <t>پاک‌ماندن و شارژ عادی = قبول؛ برگشتن جدول = رد</t>
         </is>
       </c>
       <c r="K12" s="25" t="inlineStr">
         <is>
+          <t>Host PASS: CalLut=159، parser=14 و NVM؛ تست فیزیکی فلش/ریست/باتری انجام نشده و pending است</t>
+        </is>
+      </c>
+      <c r="L12" s="23" t="inlineStr">
+        <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="L12" s="23" t="inlineStr">
-        <is>
-          <t>در انتظار</t>
-        </is>
-      </c>
-      <c r="M12" s="25" t="n"/>
-      <c r="N12" s="25" t="inlineStr">
-        <is>
-          <t>TESTER: fill</t>
+      <c r="M12" s="25" t="inlineStr">
+        <is>
+          <t>Host جای تست فیزیکی برد و fault واقعی NVM را نمی‌گیرد؛ commit zero-point، reset و flush روی برد واقعی تکرار شود</t>
+        </is>
+      </c>
+      <c r="N12" s="30" t="inlineStr">
+        <is>
+          <t>Firmware/Modules/CalLut/Tester/run_host_test_cal_lut.sh؛ Firmware/Modules/EspLink/Tester/run_host_test_nvm.sh؛ Firmware/Modules/EspLink/esp_link.c</t>
         </is>
       </c>
       <c r="O12" s="27" t="inlineStr">
         <is>
-          <t>TESTER: fill</t>
-        </is>
-      </c>
-      <c r="P12" s="27" t="inlineStr">
-        <is>
-          <t>TESTER: fill</t>
-        </is>
-      </c>
+          <t>WORKTREE</t>
+        </is>
+      </c>
+      <c r="P12" s="27" t="n"/>
       <c r="Q12" s="28" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-08</t>
         </is>
       </c>
     </row>
     <row r="13" ht="40.5" customHeight="1">
       <c r="A13" s="19" t="inlineStr">
         <is>
-          <t>CL-009</t>
+          <t>CL-020</t>
         </is>
       </c>
       <c r="B13" s="20" t="inlineStr">
         <is>
-          <t>commit بدون begin</t>
+          <t>پنل دیالوگ LUT</t>
         </is>
       </c>
       <c r="C13" s="22" t="inlineStr">
         <is>
-          <t>پایین</t>
+          <t>متوسط</t>
         </is>
       </c>
       <c r="D13" s="20" t="inlineStr">
         <is>
-          <t>لینک برقرار</t>
+          <t>پنل باز و دستگاه روشن است</t>
         </is>
       </c>
       <c r="E13" s="20" t="inlineStr">
         <is>
-          <t>گام ۱: لینک ESP را وصل کن.
-گام ۲: بدون اینکه LUT_BEGIN بفرستی، مستقیم COMMIT بفرست.
-گام ۳: پاسخ برد را بخوان: وضعیت باید 1 باشد (CAL_LUT_ST_NO_STAGE) و هیچ اتفاقی برای جدول فعال نیفتد.</t>
+          <t>گام ۱: دیالوگ جدول را در پنل باز کن و یک عدد را عوض کن.
+گام ۲: لغو بزن؛ جدول را بخوان که عوض نشده باشد.
+گام ۳: دوباره عوض کن و این بار تأیید بزن؛ بخوان که نشسته باشد.</t>
         </is>
       </c>
       <c r="F13" s="22" t="inlineStr">
         <is>
-          <t>بدون مرحلهٔ چیدن</t>
+          <t>لغو و تأیید در دیالوگ جدول پنل</t>
         </is>
       </c>
       <c r="G13" s="22" t="inlineStr">
         <is>
-          <t>یک تبادل</t>
+          <t>پنج دقیقه</t>
         </is>
       </c>
       <c r="H13" s="20" t="inlineStr">
         <is>
-          <t>رد با CAL_LUT_ST_NO_STAGE</t>
+          <t>لغو هیچ اثری ندارد و تأیید دقیقاً همان تغییر را می‌نشاند</t>
         </is>
       </c>
       <c r="I13" s="20" t="inlineStr">
         <is>
-          <t>بدون تغییر فلش</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J13" s="20" t="inlineStr">
         <is>
-          <t>status=1</t>
-        </is>
-      </c>
-      <c r="K13" s="20" t="inlineStr">
-        <is>
-          <t>در انتظار</t>
-        </is>
-      </c>
-      <c r="L13" s="23" t="inlineStr">
-        <is>
-          <t>در انتظار</t>
+          <t>رفتار درست لغو/تأیید = قبول؛ اعمال با لغو یا گم‌شدن با تأیید = رد</t>
+        </is>
+      </c>
+      <c r="K13" s="20" t="n"/>
+      <c r="L13" s="31" t="inlineStr">
+        <is>
+          <t>نیاز به تکرار</t>
         </is>
       </c>
       <c r="M13" s="20" t="n"/>
       <c r="N13" s="20" t="inlineStr">
         <is>
-          <t>TESTER: fill</t>
+          <t>../EspLink/esp_link.c</t>
         </is>
       </c>
       <c r="O13" s="22" t="inlineStr">
         <is>
-          <t>TESTER: fill</t>
-        </is>
-      </c>
-      <c r="P13" s="22" t="inlineStr">
-        <is>
-          <t>TESTER: fill</t>
-        </is>
-      </c>
+          <t>62f3782</t>
+        </is>
+      </c>
+      <c r="P13" s="22" t="n"/>
       <c r="Q13" s="24" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-12</t>
         </is>
       </c>
     </row>
     <row r="14" ht="54" customHeight="1">
-      <c r="A14" s="19" t="inlineStr">
-        <is>
-          <t>CL-010</t>
-        </is>
-      </c>
-      <c r="B14" s="25" t="inlineStr">
-        <is>
-          <t>قطع برق وسط نوشتن</t>
-        </is>
-      </c>
-      <c r="C14" s="26" t="inlineStr">
-        <is>
-          <t>بالا</t>
-        </is>
-      </c>
-      <c r="D14" s="30" t="inlineStr">
-        <is>
-          <t>CL-002 قبول</t>
-        </is>
-      </c>
-      <c r="E14" s="30" t="inlineStr">
-        <is>
-          <t>گام ۱: اول یک جدول سالم commit کن (CL-002) و CRC32 آن را یادداشت کن.
-گام ۲: یک جدول تازه بفرست و دقیقاً وسط COMMIT (موقع پاک/نوشتن فلش) تغذیهٔ برد را قطع کن.
-گام ۳: تغذیه را وصل کن و بعد از بوت، جدول فعال و CRC32 آن را بخوان: یا باید جدول قبلی سالم باشد یا جدول جدید کامل نشسته باشد؛ حالت سوم (نیمه‌کاره) هرگز نباید دیده شود.
-گام ۴: این کار را 5 بار تکرار کن و هر بار بعد از بوت سالم‌بودن رکورد فعال (RecordValidate = true) را بررسی کن.</t>
-        </is>
-      </c>
-      <c r="F14" s="27" t="inlineStr">
-        <is>
-          <t>قطع برق حین erase/program</t>
-        </is>
-      </c>
-      <c r="G14" s="27" t="inlineStr">
-        <is>
-          <t>۵ تکرار</t>
-        </is>
-      </c>
-      <c r="H14" s="25" t="inlineStr">
-        <is>
-          <t>یا رکورد قبلی سالم می‌ماند یا رکورد جدید کامل؛ هرگز حالت سوم</t>
-        </is>
-      </c>
-      <c r="I14" s="25" t="inlineStr">
-        <is>
-          <t>پینگ‌پنگ</t>
-        </is>
-      </c>
-      <c r="J14" s="25" t="inlineStr">
-        <is>
-          <t>پس از هر بوت، RecordValidate روی رکورد فعال true است</t>
-        </is>
-      </c>
-      <c r="K14" s="25" t="inlineStr">
-        <is>
-          <t>در انتظار</t>
-        </is>
-      </c>
-      <c r="L14" s="23" t="inlineStr">
-        <is>
-          <t>در انتظار</t>
-        </is>
-      </c>
-      <c r="M14" s="25" t="n"/>
-      <c r="N14" s="25" t="inlineStr">
-        <is>
-          <t>TESTER: fill</t>
-        </is>
-      </c>
-      <c r="O14" s="27" t="inlineStr">
-        <is>
-          <t>TESTER: fill</t>
-        </is>
-      </c>
-      <c r="P14" s="27" t="inlineStr">
-        <is>
-          <t>TESTER: fill</t>
-        </is>
-      </c>
-      <c r="Q14" s="28" t="inlineStr">
-        <is>
-          <t>2026-10-05</t>
-        </is>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>'برنامه تست'!A6</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>'برنامه تست'!A6</t>
+        </is>
+      </c>
+      <c r="Q14" s="32">
+        <f>IF(OR(L22="",L22="در انتظار"),"",IF(Q22="",TODAY(),Q22))</f>
+        <v/>
       </c>
     </row>
     <row r="15" ht="54" customHeight="1">
-      <c r="A15" s="19" t="inlineStr">
-        <is>
-          <t>CL-011</t>
-        </is>
-      </c>
-      <c r="B15" s="20" t="inlineStr">
-        <is>
-          <t>استقلال از NVM پارامترها</t>
-        </is>
-      </c>
-      <c r="C15" s="21" t="inlineStr">
-        <is>
-          <t>بالا</t>
-        </is>
-      </c>
-      <c r="D15" s="20" t="inlineStr">
-        <is>
-          <t>چند پارامتر غیرپیش‌فرض ذخیره شده</t>
-        </is>
-      </c>
-      <c r="E15" s="20" t="inlineStr">
-        <is>
-          <t>گام ۱: چند پارامتر را از پنل از مقدار پیش‌فرض تغییر بده و ذخیره کن؛ مقدارها را یادداشت کن.
-گام ۲: یک جدول LUT کامل push کن و commit کن.
-گام ۳: دوباره یک پارامتر را تغییر و ذخیره کن و یک جدول دیگر push کن (هر دو مسیر ذخیره پشت سر هم).
-گام ۴: برد را ری‌استارت کن و همهٔ پارامترها و جدول را بخوان؛ هیچ‌کدام نباید دیگری را خراب کرده باشد و همه باید با مقدارهای یادداشت‌شده یکی باشند.</t>
-        </is>
-      </c>
-      <c r="F15" s="22" t="inlineStr">
-        <is>
-          <t>دو مسیر ذخیره‌سازی پشت سر هم</t>
-        </is>
-      </c>
-      <c r="G15" s="22" t="inlineStr">
-        <is>
-          <t>دو چرخه</t>
-        </is>
-      </c>
-      <c r="H15" s="20" t="inlineStr">
-        <is>
-          <t>هیچ‌کدام دیگری را خراب نمی‌کند</t>
-        </is>
-      </c>
-      <c r="I15" s="20" t="inlineStr">
-        <is>
-          <t>هر دو ماندگار</t>
-        </is>
-      </c>
-      <c r="J15" s="20" t="inlineStr">
-        <is>
-          <t>همهٔ پارامترها و جدول پس از بوت صحیح‌اند</t>
-        </is>
-      </c>
-      <c r="K15" s="20" t="inlineStr">
-        <is>
-          <t>در انتظار</t>
-        </is>
-      </c>
-      <c r="L15" s="23" t="inlineStr">
-        <is>
-          <t>در انتظار</t>
-        </is>
-      </c>
-      <c r="M15" s="20" t="n"/>
-      <c r="N15" s="20" t="inlineStr">
-        <is>
-          <t>TESTER: fill</t>
-        </is>
-      </c>
-      <c r="O15" s="22" t="inlineStr">
-        <is>
-          <t>TESTER: fill</t>
-        </is>
-      </c>
-      <c r="P15" s="22" t="inlineStr">
-        <is>
-          <t>TESTER: fill</t>
-        </is>
-      </c>
-      <c r="Q15" s="24" t="inlineStr">
-        <is>
-          <t>2026-10-05</t>
-        </is>
+      <c r="Q15" s="32">
+        <f>IF(OR(L23="",L23="در انتظار"),"",IF(Q23="",TODAY(),Q23))</f>
+        <v/>
       </c>
     </row>
     <row r="16" ht="54" customHeight="1">
-      <c r="A16" s="19" t="inlineStr">
-        <is>
-          <t>CL-013</t>
-        </is>
-      </c>
-      <c r="B16" s="20" t="inlineStr">
-        <is>
-          <t>تغییر نسخهٔ قالب</t>
-        </is>
-      </c>
-      <c r="C16" s="22" t="inlineStr">
-        <is>
-          <t>پایین</t>
-        </is>
-      </c>
-      <c r="D16" s="20" t="inlineStr">
-        <is>
-          <t>رکورد معتبر نسخهٔ ۱</t>
-        </is>
-      </c>
-      <c r="E16" s="20" t="inlineStr">
-        <is>
-          <t>گام ۱: روی برد یک رکورد LUT معتبر با نسخهٔ 1 داشته باش (قبلاً commit شده باشد).
-گام ۲: ثابت CAL_LUT_VERSION را در کد بالا ببر و فرم‌ور جدید را روی همان برد فلش کن.
-گام ۳: برد را بوت کن و وضعیت جدول فعال را بخوان.
-گام ۴: باید جدول فعال نباشد (Active = false) و خوانش جریان به جدول کامپایل‌شده (خط گین و آفست) برگشته باشد.</t>
-        </is>
-      </c>
-      <c r="F16" s="22" t="inlineStr">
-        <is>
-          <t>نسخهٔ رکورد قدیمی</t>
-        </is>
-      </c>
-      <c r="G16" s="22" t="inlineStr">
-        <is>
-          <t>یک بوت</t>
-        </is>
-      </c>
-      <c r="H16" s="20" t="inlineStr">
-        <is>
-          <t>رکورد قدیمی نامعتبر و بازگشت به جدول کامپایل‌شده</t>
-        </is>
-      </c>
-      <c r="I16" s="20" t="inlineStr">
-        <is>
-          <t>بدون نیم‌ارتقای بی‌صدا</t>
-        </is>
-      </c>
-      <c r="J16" s="20" t="inlineStr">
-        <is>
-          <t>Active=false و خوانش‌ها برابر خط گین و آفست</t>
-        </is>
-      </c>
-      <c r="K16" s="20" t="inlineStr">
-        <is>
-          <t>در انتظار</t>
-        </is>
-      </c>
-      <c r="L16" s="23" t="inlineStr">
-        <is>
-          <t>در انتظار</t>
-        </is>
-      </c>
-      <c r="M16" s="20" t="n"/>
-      <c r="N16" s="20" t="inlineStr">
-        <is>
-          <t>TESTER: fill</t>
-        </is>
-      </c>
-      <c r="O16" s="22" t="inlineStr">
-        <is>
-          <t>TESTER: fill</t>
-        </is>
-      </c>
-      <c r="P16" s="22" t="inlineStr">
-        <is>
-          <t>TESTER: fill</t>
-        </is>
-      </c>
-      <c r="Q16" s="24" t="inlineStr">
-        <is>
-          <t>2026-10-05</t>
-        </is>
+      <c r="Q16" s="32">
+        <f>IF(OR(L24="",L24="در انتظار"),"",IF(Q24="",TODAY(),Q24))</f>
+        <v/>
       </c>
     </row>
     <row r="17" ht="54" customHeight="1">
-      <c r="A17" s="19" t="inlineStr">
-        <is>
-          <t>CL-014</t>
-        </is>
-      </c>
-      <c r="B17" s="25" t="inlineStr">
-        <is>
-          <t>LUT_READ بازخوانی واقعی هر دو کانال</t>
-        </is>
-      </c>
-      <c r="C17" s="26" t="inlineStr">
-        <is>
-          <t>بالا</t>
-        </is>
-      </c>
-      <c r="D17" s="25" t="inlineStr">
-        <is>
-          <t>رکورد LUT فعال در فلش یا جدول تازه commit شده</t>
-        </is>
-      </c>
-      <c r="E17" s="25" t="inlineStr">
-        <is>
-          <t>گام ۱: یک جدول فعال روی فلش داشته باش (یا تازه commit کن) و نقاط هر دو کانال را از پنل یادداشت کن.
-گام ۲: از لینک ESP فرمان LUT_READ بفرست.
-گام ۳: داده‌های برگشتی (LUT_DATA کانال ۱ و ۲) را نقطه‌به‌نقطه با نقاط فعال مقایسه کن؛ کانال بدون جدول باید فریم صفرنقطه‌ای بدهد.
-گام ۴: برد را ریست کن و گام ۲ و ۳ را تکرار کن؛ دادهٔ ناقص نباید «فعال» فرض شود و پنل باید هر عدم تطابق (mismatch) را گزارش کند.</t>
-        </is>
-      </c>
-      <c r="F17" s="27" t="inlineStr">
-        <is>
-          <t>counts/BatteryMa نقاط فعال، به‌خصوص battery 2</t>
-        </is>
-      </c>
-      <c r="G17" s="27" t="inlineStr">
-        <is>
-          <t>یک درخواست قبل و یک درخواست بعد از reset</t>
-        </is>
-      </c>
-      <c r="H17" s="25" t="inlineStr">
-        <is>
-          <t>LUT_DATA مقدار واقعی هر نقطه را برمی‌گرداند؛ کانال غیرفعال فریم صفرنقطه‌ای می‌دهد؛ دادهٔ ناقص active فرض نمی‌شود</t>
-        </is>
-      </c>
-      <c r="I17" s="25" t="inlineStr">
-        <is>
-          <t>رکورد فلش باید بعد از reset همان نقاط را حفظ کند</t>
-        </is>
-      </c>
-      <c r="J17" s="25" t="inlineStr">
-        <is>
-          <t>تطبیق byte/point با func__CalLut_Points/Counts/BatteryMa و گزارش mismatch در پنل</t>
-        </is>
-      </c>
-      <c r="K17" s="25" t="inlineStr">
-        <is>
-          <t>Host PASS: 159 check؛ شامل دو فریم واقعی LUT_DATA، battery 2 مستقل و transition غیرصفر→صفر؛ برد فیزیکی pending</t>
-        </is>
-      </c>
-      <c r="L17" s="23" t="inlineStr">
-        <is>
-          <t>در انتظار</t>
-        </is>
-      </c>
-      <c r="M17" s="25" t="inlineStr">
-        <is>
-          <t>Host جای اندازه‌گیری برد را نمی‌گیرد؛ فلش و readback روی برد واقعی لازم است</t>
-        </is>
-      </c>
-      <c r="N17" s="25" t="inlineStr">
-        <is>
-          <t>Firmware/Modules/CalLut/Tester/run_host_test_cal_lut.sh</t>
-        </is>
-      </c>
-      <c r="O17" s="27" t="inlineStr">
-        <is>
-          <t>WORKTREE</t>
-        </is>
-      </c>
-      <c r="P17" s="27" t="inlineStr"/>
-      <c r="Q17" s="28" t="inlineStr">
-        <is>
-          <t>2026-10-07</t>
-        </is>
+      <c r="Q17" s="32">
+        <f>IF(OR(L25="",L25="در انتظار"),"",IF(Q25="",TODAY(),Q25))</f>
+        <v/>
       </c>
     </row>
     <row r="18" ht="54" customHeight="1">
-      <c r="A18" s="19" t="inlineStr">
-        <is>
-          <t>CL-015</t>
-        </is>
-      </c>
-      <c r="B18" s="20" t="inlineStr">
-        <is>
-          <t>حذف override با صفرنقطه</t>
-        </is>
-      </c>
-      <c r="C18" s="21" t="inlineStr">
-        <is>
-          <t>بالا</t>
-        </is>
-      </c>
-      <c r="D18" s="29" t="inlineStr">
-        <is>
-          <t>CL-002 یا رکورد فعال با هر دو کانال</t>
-        </is>
-      </c>
-      <c r="E18" s="29" t="inlineStr">
-        <is>
-          <t>گام ۱: از قبل روی هر دو کانال جدول فعال داشته باش (CL-002 برای هر دو) و نقاط کانال ۲ را یادداشت کن.
-گام ۲: LUT_BEGIN را با n1=5 و n2=0 بفرست، چانک‌ها را فقط برای کانال ۱ بفرست و با CRC درست COMMIT کن.
-گام ۳: پاسخ باید وضعیت 0 باشد؛ برد را ریست کن.
-گام ۴: LUT_READ بگیر: کانال ۱ باید با همان 5 نقطه فعال باشد و کانال ۲ باید فریم صفرنقطه‌ای بدهد (override فلش آن حذف شده باشد).
-گام ۵: در پنل تأیید بگیر که تغییر کانال ۲ «changed-confirmed» است و CRC یا count جای مقادیر واقعی نقاط (counts/BatteryMa) را نگرفته باشد.</t>
-        </is>
-      </c>
-      <c r="F18" s="22" t="inlineStr">
-        <is>
-          <t>کانال ۱ معتبر؛ کانال ۲ count=0؛ before کانال ۲ غیرصفر و after صفرنقطه‌ای</t>
-        </is>
-      </c>
-      <c r="G18" s="22" t="inlineStr">
-        <is>
-          <t>یک تبادل + یک بوت</t>
-        </is>
-      </c>
-      <c r="H18" s="20" t="inlineStr">
-        <is>
-          <t>commit پذیرفته؛ کانال ۱ حفظ می‌شود و override فلش کانال ۲ حذف می‌شود؛ LUT_DATA کانال ۲ فریم صفرنقطه‌ای مستقل می‌دهد</t>
-        </is>
-      </c>
-      <c r="I18" s="20" t="inlineStr">
-        <is>
-          <t>پینگ‌پنگ و پس از reset</t>
-        </is>
-      </c>
-      <c r="J18" s="20" t="inlineStr">
-        <is>
-          <t>status=0، Active کانال ۱ برقرار، Active کانال ۲=false و مقایسهٔ پنل changed-confirmed؛ CRC/count جای counts/BatteryMa را نگیرد</t>
-        </is>
-      </c>
-      <c r="K18" s="20" t="inlineStr">
-        <is>
-          <t>Host PASS: 159 check؛ board physical pending</t>
-        </is>
-      </c>
-      <c r="L18" s="23" t="inlineStr">
-        <is>
-          <t>در انتظار</t>
-        </is>
-      </c>
-      <c r="M18" s="20" t="inlineStr">
-        <is>
-          <t>Host جای تست برد را نمی‌گیرد؛ حذف override و ماندگاری پس از reset روی برد واقعی لازم است</t>
-        </is>
-      </c>
-      <c r="N18" s="29" t="inlineStr">
-        <is>
-          <t>Firmware/Modules/CalLut/Tester/run_host_test_cal_lut.sh؛ esp_link_panel/Tester/host_test_scenario_cards.js</t>
-        </is>
-      </c>
-      <c r="O18" s="22" t="inlineStr">
-        <is>
-          <t>WORKTREE</t>
-        </is>
-      </c>
-      <c r="P18" s="22" t="n"/>
-      <c r="Q18" s="24" t="inlineStr">
-        <is>
-          <t>2026-10-07</t>
-        </is>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>'برنامه تست'!A6</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>'برنامه تست'!A6</t>
+        </is>
+      </c>
+      <c r="Q18" s="32">
+        <f>IF(OR(L26="",L26="در انتظار"),"",IF(Q26="",TODAY(),Q26))</f>
+        <v/>
       </c>
     </row>
     <row r="19" ht="67.5" customHeight="1">
-      <c r="A19" s="19" t="inlineStr">
-        <is>
-          <t>CL-016</t>
-        </is>
-      </c>
-      <c r="B19" s="25" t="inlineStr">
-        <is>
-          <t>reset با grant و flush NVM</t>
-        </is>
-      </c>
-      <c r="C19" s="26" t="inlineStr">
-        <is>
-          <t>بالا</t>
-        </is>
-      </c>
-      <c r="D19" s="25" t="inlineStr">
-        <is>
-          <t>commit موفق یا commit صفرنقطه‌ای؛ magic معتبر؛ لینک فعال</t>
-        </is>
-      </c>
-      <c r="E19" s="25" t="inlineStr">
-        <is>
-          <t>گام ۱: یک commit موفق (یا commit صفرنقطه‌ای با count=0 معتبر) انجام بده تا grant ریست صادر شود.
-گام ۲: بلافاصله reset را درخواست کن و صبر کن برد بالا بیاید (حداکثر 15 ثانیه).
-گام ۳: از مسیر /t و LUT_READ/LUT_DATA تازه، هر دو کانال و ماندگاری جدول را با مقدار مورد انتظار مقایسه کن؛ هیچ reject یا timeout نباید گزارش شود.
-گام ۴: یک بار هم flush ناموفق را تزریق کن (خطای نوشتن فلش): باید کد CAL_LUT_ST_FLASH برگردد و reset انجام نشود.
-گام ۵: نتیجه بگیر: commit صفرنقطه‌ای بدون جدول فعال پذیرفته می‌شود و reset فقط با grant commit و flush موفق اتفاق می‌افتد.</t>
-        </is>
-      </c>
-      <c r="F19" s="27" t="inlineStr">
-        <is>
-          <t>count=0 معتبر؛ grant commit؛ flush success/failure</t>
-        </is>
-      </c>
-      <c r="G19" s="27" t="inlineStr">
-        <is>
-          <t>حداکثر 15s</t>
-        </is>
-      </c>
-      <c r="H19" s="25" t="inlineStr">
-        <is>
-          <t>zero-point commit بدون active table پذیرفته می‌شود؛ reset فقط با grant commit و flush موفق arm می‌شود؛ flush failure کد CAL_LUT_ST_FLASH می‌دهد و reset انجام نمی‌شود</t>
-        </is>
-      </c>
-      <c r="I19" s="25" t="inlineStr">
-        <is>
-          <t>پس از موفقیت one-shot؛ بعد از flush failure grant برای retry حفظ می‌شود</t>
-        </is>
-      </c>
-      <c r="J19" s="25" t="inlineStr">
-        <is>
-          <t>پس از reset /t و LUT_READ/LUT_DATA تازه، هر دو کانال و persistence با expected برابر؛ هیچ reject/timeout/mismatch موفق گزارش نشود</t>
-        </is>
-      </c>
-      <c r="K19" s="25" t="inlineStr">
-        <is>
-          <t>Host PASS: CalLut=159، parser=14 و NVM؛ تست فیزیکی فلش/ریست/باتری انجام نشده و pending است</t>
-        </is>
-      </c>
-      <c r="L19" s="23" t="inlineStr">
-        <is>
-          <t>در انتظار</t>
-        </is>
-      </c>
-      <c r="M19" s="25" t="inlineStr">
-        <is>
-          <t>Host جای تست فیزیکی برد و fault واقعی NVM را نمی‌گیرد؛ commit zero-point، reset و flush روی برد واقعی تکرار شود</t>
-        </is>
-      </c>
-      <c r="N19" s="30" t="inlineStr">
-        <is>
-          <t>Firmware/Modules/CalLut/Tester/run_host_test_cal_lut.sh؛ Firmware/Modules/EspLink/Tester/run_host_test_nvm.sh؛ Firmware/Modules/EspLink/esp_link.c</t>
-        </is>
-      </c>
-      <c r="O19" s="27" t="inlineStr">
-        <is>
-          <t>WORKTREE</t>
-        </is>
-      </c>
-      <c r="P19" s="27" t="n"/>
-      <c r="Q19" s="28" t="inlineStr">
-        <is>
-          <t>2026-10-08</t>
-        </is>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>../../../esp_link_panel/Tester/host_test_scenario_cards.js</t>
+        </is>
+      </c>
+      <c r="Q19" s="32">
+        <f>IF(OR(L27="",L27="در انتظار"),"",IF(Q27="",TODAY(),Q27))</f>
+        <v/>
       </c>
     </row>
     <row r="20" ht="67.5" customHeight="1">
-      <c r="A20" s="19" t="inlineStr">
-        <is>
-          <t>CL-020</t>
-        </is>
-      </c>
-      <c r="B20" s="20" t="inlineStr">
-        <is>
-          <t>پنل دیالوگ LUT</t>
-        </is>
-      </c>
-      <c r="C20" s="22" t="inlineStr">
-        <is>
-          <t>متوسط</t>
-        </is>
-      </c>
-      <c r="D20" s="20" t="inlineStr">
-        <is>
-          <t>پنل وصل + LUT آماده</t>
-        </is>
-      </c>
-      <c r="E20" s="20" t="inlineStr">
-        <is>
-          <t>گام ۱: پنل را وصل کن و یک LUT دوکاناله آمادهٔ ارسال داشته باش.
-گام ۲: از پنل LUT را push کن و صبر کن دیالوگ تأیید ریست بیاید.
-گام ۳: دیالوگ باید تیره و هم‌رنگ پنل باشد (#pmod / #121a2c)، نه پنجرهٔ سفید alert ویندوز.
-گام ۴: یک بار کلید Enter را بزن (باید تأیید کند) و یک بار در اجرای بعدی Esc را بزن (باید لغو کند)؛ اگر دو دیالوگ پشت سر هم آمد باید یکی‌یکی در صف PMQ نمایش داده شوند.</t>
-        </is>
-      </c>
-      <c r="F20" s="22" t="inlineStr">
-        <is>
-          <t>LUT 2 کانال</t>
-        </is>
-      </c>
-      <c r="G20" s="22" t="inlineStr">
-        <is>
-          <t>10s</t>
-        </is>
-      </c>
-      <c r="H20" s="20" t="inlineStr">
-        <is>
-          <t>دیالوگ با استایل #pmod/#121a2c، بدون alert سفید ویندوز؛ Enter=تأیید Esc=انصراف؛ صف PMQ یکی‌یکی</t>
-        </is>
-      </c>
-      <c r="I20" s="20" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J20" s="20" t="inlineStr">
-        <is>
-          <t>دیالوگ تیره + Enter/Esc کار کند</t>
-        </is>
-      </c>
-      <c r="K20" s="20" t="n"/>
-      <c r="L20" s="31" t="inlineStr">
-        <is>
-          <t>نیاز به تکرار</t>
-        </is>
-      </c>
-      <c r="M20" s="20" t="n"/>
-      <c r="N20" s="20" t="inlineStr">
+      <c r="N20" t="inlineStr">
         <is>
           <t>../EspLink/esp_link.c</t>
         </is>
       </c>
-      <c r="O20" s="22" t="inlineStr">
-        <is>
-          <t>62f3782</t>
-        </is>
-      </c>
-      <c r="P20" s="22" t="n"/>
-      <c r="Q20" s="24" t="inlineStr">
-        <is>
-          <t>2026-10-12</t>
-        </is>
+      <c r="Q20" s="32">
+        <f>IF(OR(L28="",L28="در انتظار"),"",IF(Q28="",TODAY(),Q28))</f>
+        <v/>
       </c>
     </row>
     <row r="21" ht="54" customHeight="1">
       <c r="Q21" s="32">
-        <f>IF(OR(L22="",L22="در انتظار"),"",IF(Q22="",TODAY(),Q22))</f>
+        <f>IF(OR(L29="",L29="در انتظار"),"",IF(Q29="",TODAY(),Q29))</f>
         <v/>
       </c>
     </row>
     <row r="22">
       <c r="Q22" s="32">
-        <f>IF(OR(L23="",L23="در انتظار"),"",IF(Q23="",TODAY(),Q23))</f>
+        <f>IF(OR(L30="",L30="در انتظار"),"",IF(Q30="",TODAY(),Q30))</f>
         <v/>
       </c>
     </row>
     <row r="23">
       <c r="Q23" s="32">
-        <f>IF(OR(L24="",L24="در انتظار"),"",IF(Q24="",TODAY(),Q24))</f>
+        <f>IF(OR(L31="",L31="در انتظار"),"",IF(Q31="",TODAY(),Q31))</f>
         <v/>
       </c>
     </row>
     <row r="24">
       <c r="Q24" s="32">
-        <f>IF(OR(L25="",L25="در انتظار"),"",IF(Q25="",TODAY(),Q25))</f>
+        <f>IF(OR(L32="",L32="در انتظار"),"",IF(Q32="",TODAY(),Q32))</f>
         <v/>
       </c>
     </row>
     <row r="25">
       <c r="Q25" s="32">
-        <f>IF(OR(L26="",L26="در انتظار"),"",IF(Q26="",TODAY(),Q26))</f>
+        <f>IF(OR(L33="",L33="در انتظار"),"",IF(Q33="",TODAY(),Q33))</f>
         <v/>
       </c>
     </row>
     <row r="26">
       <c r="Q26" s="32">
-        <f>IF(OR(L27="",L27="در انتظار"),"",IF(Q27="",TODAY(),Q27))</f>
+        <f>IF(OR(L34="",L34="در انتظار"),"",IF(Q34="",TODAY(),Q34))</f>
         <v/>
       </c>
     </row>
     <row r="27">
       <c r="Q27" s="32">
-        <f>IF(OR(L28="",L28="در انتظار"),"",IF(Q28="",TODAY(),Q28))</f>
+        <f>IF(OR(L35="",L35="در انتظار"),"",IF(Q35="",TODAY(),Q35))</f>
         <v/>
       </c>
     </row>
     <row r="28">
       <c r="Q28" s="32">
-        <f>IF(OR(L29="",L29="در انتظار"),"",IF(Q29="",TODAY(),Q29))</f>
+        <f>IF(OR(L36="",L36="در انتظار"),"",IF(Q36="",TODAY(),Q36))</f>
         <v/>
       </c>
     </row>
     <row r="29">
       <c r="Q29" s="32">
-        <f>IF(OR(L30="",L30="در انتظار"),"",IF(Q30="",TODAY(),Q30))</f>
+        <f>IF(OR(L37="",L37="در انتظار"),"",IF(Q37="",TODAY(),Q37))</f>
         <v/>
       </c>
     </row>
     <row r="30">
       <c r="Q30" s="32">
-        <f>IF(OR(L31="",L31="در انتظار"),"",IF(Q31="",TODAY(),Q31))</f>
+        <f>IF(OR(L38="",L38="در انتظار"),"",IF(Q38="",TODAY(),Q38))</f>
         <v/>
       </c>
     </row>
     <row r="31">
       <c r="Q31" s="32">
-        <f>IF(OR(L32="",L32="در انتظار"),"",IF(Q32="",TODAY(),Q32))</f>
+        <f>IF(OR(L39="",L39="در انتظار"),"",IF(Q39="",TODAY(),Q39))</f>
         <v/>
       </c>
     </row>
     <row r="32">
       <c r="Q32" s="32">
-        <f>IF(OR(L33="",L33="در انتظار"),"",IF(Q33="",TODAY(),Q33))</f>
+        <f>IF(OR(L40="",L40="در انتظار"),"",IF(Q40="",TODAY(),Q40))</f>
         <v/>
       </c>
     </row>
     <row r="33">
       <c r="Q33" s="32">
-        <f>IF(OR(L34="",L34="در انتظار"),"",IF(Q34="",TODAY(),Q34))</f>
+        <f>IF(OR(L41="",L41="در انتظار"),"",IF(Q41="",TODAY(),Q41))</f>
         <v/>
       </c>
     </row>
     <row r="34">
       <c r="Q34" s="32">
-        <f>IF(OR(L35="",L35="در انتظار"),"",IF(Q35="",TODAY(),Q35))</f>
+        <f>IF(OR(L42="",L42="در انتظار"),"",IF(Q42="",TODAY(),Q42))</f>
         <v/>
       </c>
     </row>
     <row r="35">
       <c r="Q35" s="32">
-        <f>IF(OR(L36="",L36="در انتظار"),"",IF(Q36="",TODAY(),Q36))</f>
+        <f>IF(OR(L43="",L43="در انتظار"),"",IF(Q43="",TODAY(),Q43))</f>
         <v/>
       </c>
     </row>
     <row r="36">
       <c r="Q36" s="32">
-        <f>IF(OR(L37="",L37="در انتظار"),"",IF(Q37="",TODAY(),Q37))</f>
+        <f>IF(OR(L44="",L44="در انتظار"),"",IF(Q44="",TODAY(),Q44))</f>
         <v/>
       </c>
     </row>
     <row r="37">
       <c r="Q37" s="32">
-        <f>IF(OR(L38="",L38="در انتظار"),"",IF(Q38="",TODAY(),Q38))</f>
+        <f>IF(OR(L45="",L45="در انتظار"),"",IF(Q45="",TODAY(),Q45))</f>
         <v/>
       </c>
     </row>
     <row r="38">
       <c r="Q38" s="32">
-        <f>IF(OR(L39="",L39="در انتظار"),"",IF(Q39="",TODAY(),Q39))</f>
+        <f>IF(OR(L46="",L46="در انتظار"),"",IF(Q46="",TODAY(),Q46))</f>
         <v/>
       </c>
     </row>
     <row r="39">
       <c r="Q39" s="32">
-        <f>IF(OR(L40="",L40="در انتظار"),"",IF(Q40="",TODAY(),Q40))</f>
+        <f>IF(OR(L47="",L47="در انتظار"),"",IF(Q47="",TODAY(),Q47))</f>
         <v/>
       </c>
     </row>
     <row r="40">
       <c r="Q40" s="32">
-        <f>IF(OR(L41="",L41="در انتظار"),"",IF(Q41="",TODAY(),Q41))</f>
+        <f>IF(OR(L48="",L48="در انتظار"),"",IF(Q48="",TODAY(),Q48))</f>
         <v/>
       </c>
     </row>
     <row r="41">
       <c r="Q41" s="32">
-        <f>IF(OR(L42="",L42="در انتظار"),"",IF(Q42="",TODAY(),Q42))</f>
+        <f>IF(OR(L49="",L49="در انتظار"),"",IF(Q49="",TODAY(),Q49))</f>
         <v/>
       </c>
     </row>
     <row r="42">
       <c r="Q42" s="32">
-        <f>IF(OR(L43="",L43="در انتظار"),"",IF(Q43="",TODAY(),Q43))</f>
+        <f>IF(OR(L50="",L50="در انتظار"),"",IF(Q50="",TODAY(),Q50))</f>
         <v/>
       </c>
     </row>
     <row r="43">
       <c r="Q43" s="32">
-        <f>IF(OR(L44="",L44="در انتظار"),"",IF(Q44="",TODAY(),Q44))</f>
+        <f>IF(OR(L51="",L51="در انتظار"),"",IF(Q51="",TODAY(),Q51))</f>
         <v/>
       </c>
     </row>
     <row r="44">
       <c r="Q44" s="32">
-        <f>IF(OR(L45="",L45="در انتظار"),"",IF(Q45="",TODAY(),Q45))</f>
+        <f>IF(OR(L52="",L52="در انتظار"),"",IF(Q52="",TODAY(),Q52))</f>
         <v/>
       </c>
     </row>
     <row r="45">
       <c r="Q45" s="32">
-        <f>IF(OR(L46="",L46="در انتظار"),"",IF(Q46="",TODAY(),Q46))</f>
+        <f>IF(OR(L53="",L53="در انتظار"),"",IF(Q53="",TODAY(),Q53))</f>
         <v/>
       </c>
     </row>
     <row r="46">
       <c r="Q46" s="32">
-        <f>IF(OR(L47="",L47="در انتظار"),"",IF(Q47="",TODAY(),Q47))</f>
+        <f>IF(OR(L54="",L54="در انتظار"),"",IF(Q54="",TODAY(),Q54))</f>
         <v/>
       </c>
     </row>
     <row r="47">
       <c r="Q47" s="32">
-        <f>IF(OR(L48="",L48="در انتظار"),"",IF(Q48="",TODAY(),Q48))</f>
+        <f>IF(OR(L55="",L55="در انتظار"),"",IF(Q55="",TODAY(),Q55))</f>
         <v/>
       </c>
     </row>
     <row r="48">
       <c r="Q48" s="32">
-        <f>IF(OR(L49="",L49="در انتظار"),"",IF(Q49="",TODAY(),Q49))</f>
+        <f>IF(OR(L56="",L56="در انتظار"),"",IF(Q56="",TODAY(),Q56))</f>
         <v/>
       </c>
     </row>
     <row r="49">
       <c r="Q49" s="32">
-        <f>IF(OR(L50="",L50="در انتظار"),"",IF(Q50="",TODAY(),Q50))</f>
+        <f>IF(OR(L57="",L57="در انتظار"),"",IF(Q57="",TODAY(),Q57))</f>
         <v/>
       </c>
     </row>
     <row r="50">
       <c r="Q50" s="32">
-        <f>IF(OR(L51="",L51="در انتظار"),"",IF(Q51="",TODAY(),Q51))</f>
+        <f>IF(OR(L58="",L58="در انتظار"),"",IF(Q58="",TODAY(),Q58))</f>
         <v/>
       </c>
     </row>
     <row r="51">
       <c r="Q51" s="32">
-        <f>IF(OR(L52="",L52="در انتظار"),"",IF(Q52="",TODAY(),Q52))</f>
+        <f>IF(OR(L59="",L59="در انتظار"),"",IF(Q59="",TODAY(),Q59))</f>
         <v/>
       </c>
     </row>
     <row r="52">
       <c r="Q52" s="32">
-        <f>IF(OR(L53="",L53="در انتظار"),"",IF(Q53="",TODAY(),Q53))</f>
+        <f>IF(OR(L60="",L60="در انتظار"),"",IF(Q60="",TODAY(),Q60))</f>
         <v/>
       </c>
     </row>
     <row r="53">
       <c r="Q53" s="32">
-        <f>IF(OR(L54="",L54="در انتظار"),"",IF(Q54="",TODAY(),Q54))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="54">
-      <c r="Q54" s="32">
-        <f>IF(OR(L55="",L55="در انتظار"),"",IF(Q55="",TODAY(),Q55))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="55">
-      <c r="Q55" s="32">
-        <f>IF(OR(L56="",L56="در انتظار"),"",IF(Q56="",TODAY(),Q56))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="56">
-      <c r="Q56" s="32">
-        <f>IF(OR(L57="",L57="در انتظار"),"",IF(Q57="",TODAY(),Q57))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="57">
-      <c r="Q57" s="32">
-        <f>IF(OR(L58="",L58="در انتظار"),"",IF(Q58="",TODAY(),Q58))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="58">
-      <c r="Q58" s="32">
-        <f>IF(OR(L59="",L59="در انتظار"),"",IF(Q59="",TODAY(),Q59))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="59">
-      <c r="Q59" s="32">
-        <f>IF(OR(L60="",L60="در انتظار"),"",IF(Q60="",TODAY(),Q60))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="60">
-      <c r="Q60" s="32">
         <f>IF(OR(L61="",L61="در انتظار"),"",IF(Q61="",TODAY(),Q61))</f>
         <v/>
       </c>
@@ -2531,12 +1945,8 @@
     </dataValidation>
   </dataValidations>
   <hyperlinks>
+    <hyperlink ref="D5" location="'برنامه تست'!A12"/>
     <hyperlink ref="D7" location="'برنامه تست'!A6"/>
-    <hyperlink ref="E7" location="'برنامه تست'!A6"/>
-    <hyperlink ref="D14" location="'برنامه تست'!A6"/>
-    <hyperlink ref="E14" location="'برنامه تست'!A6"/>
-    <hyperlink ref="D18" location="'برنامه تست'!A6"/>
-    <hyperlink ref="E18" location="'برنامه تست'!A6"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N19" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N20" r:id="rId2"/>
   </hyperlinks>
@@ -3675,4 +3085,751 @@
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="001F4E79"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:Q11"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="9" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="62" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="42" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="34" customWidth="1" min="10" max="10"/>
+    <col width="34" customWidth="1" min="11" max="11"/>
+    <col width="13" customWidth="1" min="12" max="12"/>
+    <col width="24" customWidth="1" min="13" max="13"/>
+    <col width="16" customWidth="1" min="14" max="14"/>
+    <col width="12" customWidth="1" min="15" max="15"/>
+    <col width="13" customWidth="1" min="16" max="16"/>
+    <col width="12" customWidth="1" min="17" max="17"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="17" t="inlineStr">
+        <is>
+          <t>برنامهٔ تست برنامه‌نویسی — ماژول CalLut</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="18" t="inlineStr">
+        <is>
+          <t>وضعیت فقط یکی از: در انتظار / قبول / رد / مسدود / نیاز به تکرار. تست Host جایگزین تست برد نیست.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="18" t="inlineStr">
+        <is>
+          <t>برای هر ردیف پیش‌شرط، ورودی، انتظار و معیار قبولی صریح است؛ نتیجهٔ واقعی فقط با اندازه‌گیری روی برد پر می‌شود.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="30" customHeight="1">
+      <c r="A4" s="16" t="inlineStr">
+        <is>
+          <t>شناسه</t>
+        </is>
+      </c>
+      <c r="B4" s="16" t="inlineStr">
+        <is>
+          <t>دسته</t>
+        </is>
+      </c>
+      <c r="C4" s="16" t="inlineStr">
+        <is>
+          <t>اولویت</t>
+        </is>
+      </c>
+      <c r="D4" s="16" t="inlineStr">
+        <is>
+          <t>پیش‌شرط</t>
+        </is>
+      </c>
+      <c r="E4" s="16" t="inlineStr">
+        <is>
+          <t>روش اجرای دقیق</t>
+        </is>
+      </c>
+      <c r="F4" s="16" t="inlineStr">
+        <is>
+          <t>ورودی‌ها / شرایط</t>
+        </is>
+      </c>
+      <c r="G4" s="16" t="inlineStr">
+        <is>
+          <t>مدت مشاهده</t>
+        </is>
+      </c>
+      <c r="H4" s="16" t="inlineStr">
+        <is>
+          <t>رفتار مورد انتظار</t>
+        </is>
+      </c>
+      <c r="I4" s="16" t="inlineStr">
+        <is>
+          <t>وضعیت حفظ / latch</t>
+        </is>
+      </c>
+      <c r="J4" s="16" t="inlineStr">
+        <is>
+          <t>معیار قبولی</t>
+        </is>
+      </c>
+      <c r="K4" s="16" t="inlineStr">
+        <is>
+          <t>نتیجهٔ واقعی / اندازه‌گیری</t>
+        </is>
+      </c>
+      <c r="L4" s="16" t="inlineStr">
+        <is>
+          <t>وضعیت</t>
+        </is>
+      </c>
+      <c r="M4" s="16" t="inlineStr">
+        <is>
+          <t>شرح ایراد / تفاوت</t>
+        </is>
+      </c>
+      <c r="N4" s="16" t="inlineStr">
+        <is>
+          <t>مدرک تست / scope</t>
+        </is>
+      </c>
+      <c r="O4" s="16" t="inlineStr">
+        <is>
+          <t>commit</t>
+        </is>
+      </c>
+      <c r="P4" s="16" t="inlineStr">
+        <is>
+          <t>نام تست‌کننده</t>
+        </is>
+      </c>
+      <c r="Q4" s="16" t="inlineStr">
+        <is>
+          <t>تاریخ</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="54" customHeight="1">
+      <c r="A5" s="19" t="inlineStr">
+        <is>
+          <t>CL-004</t>
+        </is>
+      </c>
+      <c r="B5" s="25" t="inlineStr">
+        <is>
+          <t>CRC ناهمخوان</t>
+        </is>
+      </c>
+      <c r="C5" s="26" t="inlineStr">
+        <is>
+          <t>بالا</t>
+        </is>
+      </c>
+      <c r="D5" s="25" t="inlineStr">
+        <is>
+          <t>لینک برقرار</t>
+        </is>
+      </c>
+      <c r="E5" s="25" t="inlineStr">
+        <is>
+          <t>گام ۱: لینک ESP را وصل کن و CRC32 جدول فعال فعلی را یادداشت کن.
+گام ۲: یک جدول بفرست ولی در مرحلهٔ COMMIT عمداً CRC32 اشتباه بده (با CRC واقعی جدول یکی نباشد).
+گام ۳: پاسخ برد را بخوان: وضعیت باید 6 باشد (CAL_LUT_ST_CRC) و commit رد شود.
+گام ۴: CRC32 جدول فعال را دوباره بخوان؛ باید با گام ۱ یکی باشد، یعنی فلش دست‌نخورده مانده است.</t>
+        </is>
+      </c>
+      <c r="F5" s="27" t="inlineStr">
+        <is>
+          <t>CRC پنل ≠ CRC چیده‌شده</t>
+        </is>
+      </c>
+      <c r="G5" s="27" t="inlineStr">
+        <is>
+          <t>یک تبادل</t>
+        </is>
+      </c>
+      <c r="H5" s="25" t="inlineStr">
+        <is>
+          <t>رد شدن commit با CAL_LUT_ST_CRC؛ فلش دست‌نخورده</t>
+        </is>
+      </c>
+      <c r="I5" s="25" t="inlineStr">
+        <is>
+          <t>رکورد قبلی حفظ</t>
+        </is>
+      </c>
+      <c r="J5" s="25" t="inlineStr">
+        <is>
+          <t>status=6 و ActiveCrc32 تغییر نکرده</t>
+        </is>
+      </c>
+      <c r="K5" s="25" t="inlineStr">
+        <is>
+          <t>در انتظار</t>
+        </is>
+      </c>
+      <c r="L5" s="23" t="inlineStr">
+        <is>
+          <t>در انتظار</t>
+        </is>
+      </c>
+      <c r="M5" s="25" t="n"/>
+      <c r="N5" s="25" t="inlineStr">
+        <is>
+          <t>TESTER: fill</t>
+        </is>
+      </c>
+      <c r="O5" s="27" t="inlineStr">
+        <is>
+          <t>TESTER: fill</t>
+        </is>
+      </c>
+      <c r="P5" s="27" t="inlineStr">
+        <is>
+          <t>TESTER: fill</t>
+        </is>
+      </c>
+      <c r="Q5" s="28">
+        <f>IF(OR(L5="",L5="در انتظار"),"",IF(Q5="",TODAY(),Q5))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6" ht="67.5" customHeight="1">
+      <c r="A6" s="19" t="inlineStr">
+        <is>
+          <t>CL-005</t>
+        </is>
+      </c>
+      <c r="B6" s="20" t="inlineStr">
+        <is>
+          <t>محور صعودی نبودن</t>
+        </is>
+      </c>
+      <c r="C6" s="21" t="inlineStr">
+        <is>
+          <t>بالا</t>
+        </is>
+      </c>
+      <c r="D6" s="20" t="inlineStr">
+        <is>
+          <t>لینک برقرار</t>
+        </is>
+      </c>
+      <c r="E6" s="20" t="inlineStr">
+        <is>
+          <t>گام ۱: لینک ESP را وصل کن.
+گام ۲: جدولی بساز که محور زنجیره‌اش (ChainMa) صعودیِ اکید نباشد؛ مثلاً یک نقطهٔ تکراری یا یک نقطه کمتر از قبلی بگذار.
+گام ۳: جدول را کامل بفرست و COMMIT کن.
+گام ۴: پاسخ برد را بخوان: وضعیت باید 4 باشد (CAL_LUT_ST_CHAIN) و جدول نباید فعال شود.</t>
+        </is>
+      </c>
+      <c r="F6" s="22" t="inlineStr">
+        <is>
+          <t>نقطهٔ تکراری یا نزولی در ChainMa</t>
+        </is>
+      </c>
+      <c r="G6" s="22" t="inlineStr">
+        <is>
+          <t>یک تبادل</t>
+        </is>
+      </c>
+      <c r="H6" s="20" t="inlineStr">
+        <is>
+          <t>رد با CAL_LUT_ST_CHAIN</t>
+        </is>
+      </c>
+      <c r="I6" s="20" t="inlineStr">
+        <is>
+          <t>بدون تغییر فلش</t>
+        </is>
+      </c>
+      <c r="J6" s="20" t="inlineStr">
+        <is>
+          <t>status=4</t>
+        </is>
+      </c>
+      <c r="K6" s="20" t="inlineStr">
+        <is>
+          <t>در انتظار</t>
+        </is>
+      </c>
+      <c r="L6" s="23" t="inlineStr">
+        <is>
+          <t>در انتظار</t>
+        </is>
+      </c>
+      <c r="M6" s="20" t="n"/>
+      <c r="N6" s="20" t="inlineStr">
+        <is>
+          <t>TESTER: fill</t>
+        </is>
+      </c>
+      <c r="O6" s="22" t="inlineStr">
+        <is>
+          <t>TESTER: fill</t>
+        </is>
+      </c>
+      <c r="P6" s="22" t="inlineStr">
+        <is>
+          <t>TESTER: fill</t>
+        </is>
+      </c>
+      <c r="Q6" s="24">
+        <f>IF(OR(L6="",L6="در انتظار"),"",IF(Q6="",TODAY(),Q6))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7" ht="54" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
+          <t>CL-006</t>
+        </is>
+      </c>
+      <c r="B7" s="25" t="inlineStr">
+        <is>
+          <t>افت محور جریان</t>
+        </is>
+      </c>
+      <c r="C7" s="27" t="inlineStr">
+        <is>
+          <t>متوسط</t>
+        </is>
+      </c>
+      <c r="D7" s="25" t="inlineStr">
+        <is>
+          <t>لینک برقرار</t>
+        </is>
+      </c>
+      <c r="E7" s="25" t="inlineStr">
+        <is>
+          <t>گام ۱: لینک ESP را وصل کن.
+گام ۲: جدولی بساز که جریان باتری در یکی از نقطه‌ها از نقطهٔ قبلی کمتر باشد (افت داشته باشد).
+گام ۳: جدول را کامل بفرست و COMMIT کن.
+گام ۴: پاسخ برد را بخوان: وضعیت باید 5 باشد (CAL_LUT_ST_DIP) و جدول نباید فعال شود.</t>
+        </is>
+      </c>
+      <c r="F7" s="27" t="inlineStr">
+        <is>
+          <t>نقطه‌ای کمتر از نقطهٔ قبل</t>
+        </is>
+      </c>
+      <c r="G7" s="27" t="inlineStr">
+        <is>
+          <t>یک تبادل</t>
+        </is>
+      </c>
+      <c r="H7" s="25" t="inlineStr">
+        <is>
+          <t>رد با CAL_LUT_ST_DIP (جریان باتری افت دارد)</t>
+        </is>
+      </c>
+      <c r="I7" s="25" t="inlineStr">
+        <is>
+          <t>بدون تغییر فلش</t>
+        </is>
+      </c>
+      <c r="J7" s="25" t="inlineStr">
+        <is>
+          <t>status=5</t>
+        </is>
+      </c>
+      <c r="K7" s="25" t="inlineStr">
+        <is>
+          <t>در انتظار</t>
+        </is>
+      </c>
+      <c r="L7" s="23" t="inlineStr">
+        <is>
+          <t>در انتظار</t>
+        </is>
+      </c>
+      <c r="M7" s="25" t="n"/>
+      <c r="N7" s="25" t="inlineStr">
+        <is>
+          <t>TESTER: fill</t>
+        </is>
+      </c>
+      <c r="O7" s="27" t="inlineStr">
+        <is>
+          <t>TESTER: fill</t>
+        </is>
+      </c>
+      <c r="P7" s="27" t="inlineStr">
+        <is>
+          <t>TESTER: fill</t>
+        </is>
+      </c>
+      <c r="Q7" s="28">
+        <f>IF(OR(L7="",L7="در انتظار"),"",IF(Q7="",TODAY(),Q7))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8" ht="54" customHeight="1">
+      <c r="A8" s="19" t="inlineStr">
+        <is>
+          <t>CL-007</t>
+        </is>
+      </c>
+      <c r="B8" s="20" t="inlineStr">
+        <is>
+          <t>تعداد نقاط نامعتبر</t>
+        </is>
+      </c>
+      <c r="C8" s="22" t="inlineStr">
+        <is>
+          <t>متوسط</t>
+        </is>
+      </c>
+      <c r="D8" s="20" t="inlineStr">
+        <is>
+          <t>لینک برقرار</t>
+        </is>
+      </c>
+      <c r="E8" s="20" t="inlineStr">
+        <is>
+          <t>گام ۱: لینک ESP را وصل کن.
+گام ۲: یک جدول فقط با 1 نقطه بفرست و COMMIT کن؛ پاسخ را بخوان.
+گام ۳: یک جدول با 25 نقطه بفرست و COMMIT کن؛ پاسخ را بخوان.
+گام ۴: هر دو بار وضعیت باید 2 باشد (CAL_LUT_ST_COUNT)، چون تعداد نقطهٔ مجاز 2 تا 24 است.</t>
+        </is>
+      </c>
+      <c r="F8" s="22" t="inlineStr">
+        <is>
+          <t>points &lt; 2 یا &gt; 24</t>
+        </is>
+      </c>
+      <c r="G8" s="22" t="inlineStr">
+        <is>
+          <t>دو تبادل</t>
+        </is>
+      </c>
+      <c r="H8" s="20" t="inlineStr">
+        <is>
+          <t>هر دو با CAL_LUT_ST_COUNT رد می‌شوند</t>
+        </is>
+      </c>
+      <c r="I8" s="20" t="inlineStr">
+        <is>
+          <t>بدون تغییر فلش</t>
+        </is>
+      </c>
+      <c r="J8" s="20" t="inlineStr">
+        <is>
+          <t>status=2 در هر دو</t>
+        </is>
+      </c>
+      <c r="K8" s="20" t="inlineStr">
+        <is>
+          <t>در انتظار</t>
+        </is>
+      </c>
+      <c r="L8" s="23" t="inlineStr">
+        <is>
+          <t>در انتظار</t>
+        </is>
+      </c>
+      <c r="M8" s="20" t="n"/>
+      <c r="N8" s="20" t="inlineStr">
+        <is>
+          <t>TESTER: fill</t>
+        </is>
+      </c>
+      <c r="O8" s="22" t="inlineStr">
+        <is>
+          <t>TESTER: fill</t>
+        </is>
+      </c>
+      <c r="P8" s="22" t="inlineStr">
+        <is>
+          <t>TESTER: fill</t>
+        </is>
+      </c>
+      <c r="Q8" s="24">
+        <f>IF(OR(L8="",L8="در انتظار"),"",IF(Q8="",TODAY(),Q8))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9" ht="54" customHeight="1">
+      <c r="A9" s="19" t="inlineStr">
+        <is>
+          <t>CL-008</t>
+        </is>
+      </c>
+      <c r="B9" s="25" t="inlineStr">
+        <is>
+          <t>تکهٔ گم‌شده</t>
+        </is>
+      </c>
+      <c r="C9" s="27" t="inlineStr">
+        <is>
+          <t>متوسط</t>
+        </is>
+      </c>
+      <c r="D9" s="25" t="inlineStr">
+        <is>
+          <t>لینک برقرار</t>
+        </is>
+      </c>
+      <c r="E9" s="25" t="inlineStr">
+        <is>
+          <t>گام ۱: لینک ESP را وصل کن و یک جدول چندچانکه آماده کن.
+گام ۲: همهٔ چانک‌ها را بفرست به‌جز یکی؛ عمداً یک چانک را نفرست.
+گام ۳: COMMIT را بفرست.
+گام ۴: پاسخ برد را بخوان: وضعیت باید 3 باشد (CAL_LUT_ST_MISSING) و هیچ جدولی فعال نشود.</t>
+        </is>
+      </c>
+      <c r="F9" s="27" t="inlineStr">
+        <is>
+          <t>یک تکه نرسیده</t>
+        </is>
+      </c>
+      <c r="G9" s="27" t="inlineStr">
+        <is>
+          <t>یک تبادل</t>
+        </is>
+      </c>
+      <c r="H9" s="25" t="inlineStr">
+        <is>
+          <t>رد با CAL_LUT_ST_MISSING</t>
+        </is>
+      </c>
+      <c r="I9" s="25" t="inlineStr">
+        <is>
+          <t>بدون تغییر فلش</t>
+        </is>
+      </c>
+      <c r="J9" s="25" t="inlineStr">
+        <is>
+          <t>status=3</t>
+        </is>
+      </c>
+      <c r="K9" s="25" t="inlineStr">
+        <is>
+          <t>در انتظار</t>
+        </is>
+      </c>
+      <c r="L9" s="23" t="inlineStr">
+        <is>
+          <t>در انتظار</t>
+        </is>
+      </c>
+      <c r="M9" s="25" t="n"/>
+      <c r="N9" s="25" t="inlineStr">
+        <is>
+          <t>TESTER: fill</t>
+        </is>
+      </c>
+      <c r="O9" s="27" t="inlineStr">
+        <is>
+          <t>TESTER: fill</t>
+        </is>
+      </c>
+      <c r="P9" s="27" t="inlineStr">
+        <is>
+          <t>TESTER: fill</t>
+        </is>
+      </c>
+      <c r="Q9" s="28">
+        <f>IF(OR(L9="",L9="در انتظار"),"",IF(Q9="",TODAY(),Q9))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10" ht="54" customHeight="1">
+      <c r="A10" s="19" t="inlineStr">
+        <is>
+          <t>CL-009</t>
+        </is>
+      </c>
+      <c r="B10" s="20" t="inlineStr">
+        <is>
+          <t>commit بدون begin</t>
+        </is>
+      </c>
+      <c r="C10" s="22" t="inlineStr">
+        <is>
+          <t>پایین</t>
+        </is>
+      </c>
+      <c r="D10" s="20" t="inlineStr">
+        <is>
+          <t>لینک برقرار</t>
+        </is>
+      </c>
+      <c r="E10" s="20" t="inlineStr">
+        <is>
+          <t>گام ۱: لینک ESP را وصل کن.
+گام ۲: بدون اینکه LUT_BEGIN بفرستی، مستقیم COMMIT بفرست.
+گام ۳: پاسخ برد را بخوان: وضعیت باید 1 باشد (CAL_LUT_ST_NO_STAGE) و هیچ اتفاقی برای جدول فعال نیفتد.</t>
+        </is>
+      </c>
+      <c r="F10" s="22" t="inlineStr">
+        <is>
+          <t>بدون مرحلهٔ چیدن</t>
+        </is>
+      </c>
+      <c r="G10" s="22" t="inlineStr">
+        <is>
+          <t>یک تبادل</t>
+        </is>
+      </c>
+      <c r="H10" s="20" t="inlineStr">
+        <is>
+          <t>رد با CAL_LUT_ST_NO_STAGE</t>
+        </is>
+      </c>
+      <c r="I10" s="20" t="inlineStr">
+        <is>
+          <t>بدون تغییر فلش</t>
+        </is>
+      </c>
+      <c r="J10" s="20" t="inlineStr">
+        <is>
+          <t>status=1</t>
+        </is>
+      </c>
+      <c r="K10" s="20" t="inlineStr">
+        <is>
+          <t>در انتظار</t>
+        </is>
+      </c>
+      <c r="L10" s="23" t="inlineStr">
+        <is>
+          <t>در انتظار</t>
+        </is>
+      </c>
+      <c r="M10" s="20" t="n"/>
+      <c r="N10" s="20" t="inlineStr">
+        <is>
+          <t>TESTER: fill</t>
+        </is>
+      </c>
+      <c r="O10" s="22" t="inlineStr">
+        <is>
+          <t>TESTER: fill</t>
+        </is>
+      </c>
+      <c r="P10" s="22" t="inlineStr">
+        <is>
+          <t>TESTER: fill</t>
+        </is>
+      </c>
+      <c r="Q10" s="24">
+        <f>IF(OR(L10="",L10="در انتظار"),"",IF(Q10="",TODAY(),Q10))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11" ht="54" customHeight="1">
+      <c r="A11" s="19" t="inlineStr">
+        <is>
+          <t>CL-013</t>
+        </is>
+      </c>
+      <c r="B11" s="20" t="inlineStr">
+        <is>
+          <t>تغییر نسخهٔ قالب</t>
+        </is>
+      </c>
+      <c r="C11" s="22" t="inlineStr">
+        <is>
+          <t>پایین</t>
+        </is>
+      </c>
+      <c r="D11" s="20" t="inlineStr">
+        <is>
+          <t>رکورد معتبر نسخهٔ ۱</t>
+        </is>
+      </c>
+      <c r="E11" s="20" t="inlineStr">
+        <is>
+          <t>گام ۱: روی برد یک رکورد LUT معتبر با نسخهٔ 1 داشته باش (قبلاً commit شده باشد).
+گام ۲: ثابت CAL_LUT_VERSION را در کد بالا ببر و فرم‌ور جدید را روی همان برد فلش کن.
+گام ۳: برد را بوت کن و وضعیت جدول فعال را بخوان.
+گام ۴: باید جدول فعال نباشد (Active = false) و خوانش جریان به جدول کامپایل‌شده (خط گین و آفست) برگشته باشد.</t>
+        </is>
+      </c>
+      <c r="F11" s="22" t="inlineStr">
+        <is>
+          <t>نسخهٔ رکورد قدیمی</t>
+        </is>
+      </c>
+      <c r="G11" s="22" t="inlineStr">
+        <is>
+          <t>یک بوت</t>
+        </is>
+      </c>
+      <c r="H11" s="20" t="inlineStr">
+        <is>
+          <t>رکورد قدیمی نامعتبر و بازگشت به جدول کامپایل‌شده</t>
+        </is>
+      </c>
+      <c r="I11" s="20" t="inlineStr">
+        <is>
+          <t>بدون نیم‌ارتقای بی‌صدا</t>
+        </is>
+      </c>
+      <c r="J11" s="20" t="inlineStr">
+        <is>
+          <t>Active=false و خوانش‌ها برابر خط گین و آفست</t>
+        </is>
+      </c>
+      <c r="K11" s="20" t="inlineStr">
+        <is>
+          <t>در انتظار</t>
+        </is>
+      </c>
+      <c r="L11" s="23" t="inlineStr">
+        <is>
+          <t>در انتظار</t>
+        </is>
+      </c>
+      <c r="M11" s="20" t="n"/>
+      <c r="N11" s="20" t="inlineStr">
+        <is>
+          <t>TESTER: fill</t>
+        </is>
+      </c>
+      <c r="O11" s="22" t="inlineStr">
+        <is>
+          <t>TESTER: fill</t>
+        </is>
+      </c>
+      <c r="P11" s="22" t="inlineStr">
+        <is>
+          <t>TESTER: fill</t>
+        </is>
+      </c>
+      <c r="Q11" s="24">
+        <f>IF(OR(L11="",L11="در انتظار"),"",IF(Q11="",TODAY(),Q11))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12" ht="54" customHeight="1"/>
+    <row r="13" ht="40.5" customHeight="1"/>
+    <row r="14" ht="54" customHeight="1"/>
+    <row r="15" ht="54" customHeight="1"/>
+    <row r="16" ht="54" customHeight="1"/>
+    <row r="17" ht="54" customHeight="1"/>
+    <row r="18" ht="54" customHeight="1"/>
+    <row r="19" ht="67.5" customHeight="1"/>
+    <row r="20" ht="67.5" customHeight="1"/>
+    <row r="21" ht="54" customHeight="1"/>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
+</worksheet>
 </file>
--- a/Firmware/Modules/CalLut/CalLut_Validation.xlsx
+++ b/Firmware/Modules/CalLut/CalLut_Validation.xlsx
@@ -32,7 +32,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
   </numFmts>
-  <fonts count="19">
+  <fonts count="26">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -131,6 +131,46 @@
       <sz val="8"/>
       <u val="single"/>
     </font>
+    <font>
+      <name val="Vazirmatn"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Vazirmatn"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Vazirmatn"/>
+      <color rgb="000563C1"/>
+      <sz val="8"/>
+      <u val="single"/>
+    </font>
+    <font>
+      <name val="Vazirmatn"/>
+      <b val="1"/>
+      <color rgb="001F3864"/>
+      <sz val="13"/>
+    </font>
+    <font>
+      <name val="Vazirmatn"/>
+      <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Vazirmatn"/>
+      <b val="1"/>
+      <color rgb="00C00000"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Vazirmatn"/>
+      <b val="1"/>
+      <sz val="8"/>
+    </font>
   </fonts>
   <fills count="8">
     <fill>
@@ -210,7 +250,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="45">
+  <cellXfs count="73">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -328,6 +368,78 @@
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="23" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="25" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -701,66 +813,66 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="14" t="inlineStr">
+      <c r="A1" s="45" t="inlineStr">
         <is>
           <t>برگه تست و اعتبارسنجی عملی ماژول CalLut</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="15" t="inlineStr">
+      <c r="A2" s="46" t="inlineStr">
         <is>
           <t>CalLut | نگهداری جدول کالیبراسیون بنچ در بلوک فلش اختصاصی با CRC32 و بازگشت به جدول کامپایل‌شده</t>
         </is>
       </c>
     </row>
     <row r="3" ht="30" customHeight="1">
-      <c r="A3" s="16" t="inlineStr">
+      <c r="A3" s="47" t="inlineStr">
         <is>
           <t>هدف فایل</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="n"/>
+      <c r="A4" s="46" t="n"/>
     </row>
     <row r="5">
-      <c r="A5" s="15" t="inlineStr">
+      <c r="A5" s="46" t="inlineStr">
         <is>
           <t>مسیر ذخیرهٔ جدول کالیبراسیون بنچ در «بلوک فلش مخصوص خودش»: دو صفحهٔ ۱KB در 0x0800F000 و 0x0800F400، پینگ‌پنگ امن در برابر قطع برق، مجیک/نسخه/CRC32 مستقل.</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="42" t="inlineStr">
+      <c r="A6" s="48" t="inlineStr">
         <is>
           <t>هیچ اشتراکی با esp_link_nvm.c جز درایور فلش ندارد؛ پس فرستادن جدول هرگز رکورد پارامترها را خراب نمی‌کند و برعکس.</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="15" t="inlineStr">
+      <c r="A7" s="46" t="inlineStr">
         <is>
           <t>جدول کامپایل‌شده وجود ندارد. وقتی رکورد معتبر در فلش نباشد، خط گین و آفست (پیش‌فرض گین 3000، آفست 0) استفاده می‌شود؛ وقتی رکورد معتبر در فلش باشد از آن استفاده می‌شود.</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="15" t="inlineStr">
+      <c r="A8" s="46" t="inlineStr">
         <is>
           <t>دست‌دادن: LUT_BEGIN → LUT_CHUNK → LUT_COMMIT (با CRC32 پنل) → LUT_ACK (با CRC32 خودِ برد از آنچه در فلش است) → تنها در صورت برابری، LUT_RESET.</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="15" t="inlineStr">
+      <c r="A9" s="46" t="inlineStr">
         <is>
           <t>هدف این برگه: اثبات روی برد که نوشتن، بازخوانی، اعتبارسنجی و بازگشت به پشتیبان همگی همان‌طور کار می‌کنند که هدر ادعا می‌کند.</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="15" t="inlineStr">
+      <c r="A10" s="46" t="inlineStr">
         <is>
           <t>تست Host (کامپایل و اجرا روی PC با شبیه‌سازی RAM) جایگزین این تست‌ها نیست.</t>
         </is>
@@ -804,1132 +916,1814 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="17" t="inlineStr">
+      <c r="A1" s="49" t="inlineStr">
         <is>
           <t>برنامهٔ تست عملی — ماژول CalLut</t>
         </is>
       </c>
+      <c r="B1" s="50" t="n"/>
+      <c r="C1" s="50" t="n"/>
+      <c r="D1" s="50" t="n"/>
+      <c r="E1" s="50" t="n"/>
+      <c r="F1" s="50" t="n"/>
+      <c r="G1" s="50" t="n"/>
+      <c r="H1" s="50" t="n"/>
+      <c r="I1" s="50" t="n"/>
+      <c r="J1" s="50" t="n"/>
+      <c r="K1" s="50" t="n"/>
+      <c r="L1" s="50" t="n"/>
+      <c r="M1" s="50" t="n"/>
+      <c r="N1" s="50" t="n"/>
+      <c r="O1" s="50" t="n"/>
+      <c r="P1" s="50" t="n"/>
+      <c r="Q1" s="50" t="n"/>
     </row>
     <row r="2">
-      <c r="A2" s="18" t="inlineStr">
+      <c r="A2" s="51" t="inlineStr">
         <is>
           <t>وضعیت فقط یکی از: در انتظار / قبول / رد / مسدود / نیاز به تکرار. تست Host جایگزین تست برد نیست.</t>
         </is>
       </c>
+      <c r="B2" s="50" t="n"/>
+      <c r="C2" s="50" t="n"/>
+      <c r="D2" s="50" t="n"/>
+      <c r="E2" s="50" t="n"/>
+      <c r="F2" s="50" t="n"/>
+      <c r="G2" s="50" t="n"/>
+      <c r="H2" s="50" t="n"/>
+      <c r="I2" s="50" t="n"/>
+      <c r="J2" s="50" t="n"/>
+      <c r="K2" s="50" t="n"/>
+      <c r="L2" s="50" t="n"/>
+      <c r="M2" s="50" t="n"/>
+      <c r="N2" s="50" t="n"/>
+      <c r="O2" s="50" t="n"/>
+      <c r="P2" s="50" t="n"/>
+      <c r="Q2" s="50" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" s="18" t="inlineStr">
+      <c r="A3" s="51" t="inlineStr">
         <is>
           <t>برای هر ردیف پیش‌شرط، ورودی، انتظار و معیار قبولی صریح است؛ نتیجهٔ واقعی فقط با اندازه‌گیری روی برد پر می‌شود.</t>
         </is>
       </c>
+      <c r="B3" s="50" t="n"/>
+      <c r="C3" s="50" t="n"/>
+      <c r="D3" s="50" t="n"/>
+      <c r="E3" s="50" t="n"/>
+      <c r="F3" s="50" t="n"/>
+      <c r="G3" s="50" t="n"/>
+      <c r="H3" s="50" t="n"/>
+      <c r="I3" s="50" t="n"/>
+      <c r="J3" s="50" t="n"/>
+      <c r="K3" s="50" t="n"/>
+      <c r="L3" s="50" t="n"/>
+      <c r="M3" s="50" t="n"/>
+      <c r="N3" s="50" t="n"/>
+      <c r="O3" s="50" t="n"/>
+      <c r="P3" s="50" t="n"/>
+      <c r="Q3" s="50" t="n"/>
     </row>
     <row r="4" ht="30" customHeight="1">
-      <c r="A4" s="16" t="inlineStr">
+      <c r="A4" s="47" t="inlineStr">
         <is>
           <t>شناسه</t>
         </is>
       </c>
-      <c r="B4" s="16" t="inlineStr">
+      <c r="B4" s="47" t="inlineStr">
         <is>
           <t>دسته</t>
         </is>
       </c>
-      <c r="C4" s="16" t="inlineStr">
+      <c r="C4" s="47" t="inlineStr">
         <is>
           <t>اولویت</t>
         </is>
       </c>
-      <c r="D4" s="16" t="inlineStr">
+      <c r="D4" s="47" t="inlineStr">
         <is>
           <t>پیش‌شرط</t>
         </is>
       </c>
-      <c r="E4" s="16" t="inlineStr">
+      <c r="E4" s="47" t="inlineStr">
         <is>
           <t>روش اجرای دقیق</t>
         </is>
       </c>
-      <c r="F4" s="16" t="inlineStr">
+      <c r="F4" s="47" t="inlineStr">
         <is>
           <t>ورودی‌ها / شرایط</t>
         </is>
       </c>
-      <c r="G4" s="16" t="inlineStr">
+      <c r="G4" s="47" t="inlineStr">
         <is>
           <t>مدت مشاهده</t>
         </is>
       </c>
-      <c r="H4" s="16" t="inlineStr">
+      <c r="H4" s="47" t="inlineStr">
         <is>
           <t>رفتار مورد انتظار</t>
         </is>
       </c>
-      <c r="I4" s="16" t="inlineStr">
+      <c r="I4" s="47" t="inlineStr">
         <is>
           <t>وضعیت حفظ / latch</t>
         </is>
       </c>
-      <c r="J4" s="16" t="inlineStr">
+      <c r="J4" s="47" t="inlineStr">
         <is>
           <t>معیار قبولی</t>
         </is>
       </c>
-      <c r="K4" s="16" t="inlineStr">
+      <c r="K4" s="47" t="inlineStr">
         <is>
           <t>نتیجهٔ واقعی / اندازه‌گیری</t>
         </is>
       </c>
-      <c r="L4" s="16" t="inlineStr">
+      <c r="L4" s="47" t="inlineStr">
         <is>
           <t>وضعیت</t>
         </is>
       </c>
-      <c r="M4" s="16" t="inlineStr">
+      <c r="M4" s="47" t="inlineStr">
         <is>
           <t>شرح ایراد / تفاوت</t>
         </is>
       </c>
-      <c r="N4" s="16" t="inlineStr">
+      <c r="N4" s="47" t="inlineStr">
         <is>
           <t>مدرک تست / scope</t>
         </is>
       </c>
-      <c r="O4" s="16" t="inlineStr">
+      <c r="O4" s="47" t="inlineStr">
         <is>
           <t>commit</t>
         </is>
       </c>
-      <c r="P4" s="16" t="inlineStr">
+      <c r="P4" s="47" t="inlineStr">
         <is>
           <t>نام تست‌کننده</t>
         </is>
       </c>
-      <c r="Q4" s="16" t="inlineStr">
+      <c r="Q4" s="47" t="inlineStr">
         <is>
           <t>تاریخ</t>
         </is>
       </c>
     </row>
     <row r="5" ht="54" customHeight="1">
-      <c r="A5" s="19" t="inlineStr">
+      <c r="A5" s="52" t="inlineStr">
         <is>
           <t>CL-001</t>
         </is>
       </c>
-      <c r="B5" s="20" t="inlineStr">
+      <c r="B5" s="53" t="inlineStr">
         <is>
           <t>بوت بدون رکورد</t>
         </is>
       </c>
-      <c r="C5" s="21" t="inlineStr">
+      <c r="C5" s="54" t="inlineStr">
         <is>
           <t>بالا</t>
         </is>
       </c>
-      <c r="D5" s="29" t="inlineStr">
+      <c r="D5" s="55" t="inlineStr">
         <is>
           <t>دستگاه تازه است یا جدولش را تازه پاک کرده‌ای (CL-016)؛ باتری و برق شهر آماده</t>
         </is>
       </c>
-      <c r="E5" s="20" t="inlineStr">
+      <c r="E5" s="53" t="inlineStr">
         <is>
           <t>گام ۱: دستگاه را روشن کن و یک باتری نیمه‌خالی را به شارژ بزن.
 گام ۲: چند دقیقه رفتار شارژ را نگاه کن.</t>
         </is>
       </c>
-      <c r="F5" s="22" t="inlineStr">
+      <c r="F5" s="56" t="inlineStr">
         <is>
           <t>روشن‌کردن و شارژ بدون جدول سفارشی</t>
         </is>
       </c>
-      <c r="G5" s="22" t="inlineStr">
+      <c r="G5" s="56" t="inlineStr">
         <is>
           <t>پنج دقیقه</t>
         </is>
       </c>
-      <c r="H5" s="20" t="inlineStr">
+      <c r="H5" s="53" t="inlineStr">
         <is>
           <t>شارژ با جدول پیش‌فرض کارخانه کاملاً عادی کار می‌کند؛ هیچ خطای جدولی نیست</t>
         </is>
       </c>
-      <c r="I5" s="20" t="inlineStr">
+      <c r="I5" s="53" t="inlineStr">
         <is>
           <t>رفتار پیش‌فرض</t>
         </is>
       </c>
-      <c r="J5" s="20" t="inlineStr">
+      <c r="J5" s="53" t="inlineStr">
         <is>
           <t>شارژ عادی بی‌جدول = قبول؛ شارژ خراب یا خطا = رد</t>
         </is>
       </c>
-      <c r="K5" s="20" t="inlineStr">
+      <c r="K5" s="53" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="L5" s="23" t="inlineStr">
+      <c r="L5" s="57" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="M5" s="20" t="n"/>
-      <c r="N5" s="20" t="inlineStr">
+      <c r="M5" s="53" t="n"/>
+      <c r="N5" s="53" t="inlineStr">
         <is>
           <t>TESTER: fill</t>
         </is>
       </c>
-      <c r="O5" s="22" t="inlineStr">
+      <c r="O5" s="56" t="inlineStr">
         <is>
           <t>TESTER: fill</t>
         </is>
       </c>
-      <c r="P5" s="22" t="inlineStr">
+      <c r="P5" s="56" t="inlineStr">
         <is>
           <t>TESTER: fill</t>
         </is>
       </c>
-      <c r="Q5" s="24" t="inlineStr">
+      <c r="Q5" s="58" t="inlineStr">
         <is>
           <t>2026-10-05</t>
         </is>
       </c>
     </row>
     <row r="6" ht="67.5" customHeight="1">
-      <c r="A6" s="19" t="inlineStr">
+      <c r="A6" s="52" t="inlineStr">
         <is>
           <t>CL-002</t>
         </is>
       </c>
-      <c r="B6" s="25" t="inlineStr">
+      <c r="B6" s="59" t="inlineStr">
         <is>
           <t>push سالم کانال ۱</t>
         </is>
       </c>
-      <c r="C6" s="26" t="inlineStr">
+      <c r="C6" s="60" t="inlineStr">
         <is>
           <t>بالا</t>
         </is>
       </c>
-      <c r="D6" s="25" t="inlineStr">
+      <c r="D6" s="59" t="inlineStr">
         <is>
           <t>پنل باز است و جدول درست یک کانال را آماده داری</t>
         </is>
       </c>
-      <c r="E6" s="25" t="inlineStr">
+      <c r="E6" s="59" t="inlineStr">
         <is>
           <t>گام ۱: جدول را از پنل برای کانال ۱ بفرست.
 گام ۲: همان جدول را از پنل بخوان و عددها را مقایسه کن.
 گام ۳: با همان کانال یک شارژ واقعی انجام بده.</t>
         </is>
       </c>
-      <c r="F6" s="27" t="inlineStr">
+      <c r="F6" s="61" t="inlineStr">
         <is>
           <t>فرستادن جدول کانال ۱ از پنل</t>
         </is>
       </c>
-      <c r="G6" s="27" t="inlineStr">
+      <c r="G6" s="61" t="inlineStr">
         <is>
           <t>ده دقیقه</t>
         </is>
       </c>
-      <c r="H6" s="25" t="inlineStr">
+      <c r="H6" s="59" t="inlineStr">
         <is>
           <t>جدول درست نشسته (خواندن برعکس همان است) و شارژ کانال ۱ با همان اعداد کار می‌کند</t>
         </is>
       </c>
-      <c r="I6" s="25" t="inlineStr">
+      <c r="I6" s="59" t="inlineStr">
         <is>
           <t>ماندگار</t>
         </is>
       </c>
-      <c r="J6" s="25" t="inlineStr">
+      <c r="J6" s="59" t="inlineStr">
         <is>
           <t>نشستن جدول و شارژ درست = قبول؛ اختلاف عدد یا شارژ خراب = رد</t>
         </is>
       </c>
-      <c r="K6" s="25" t="inlineStr">
+      <c r="K6" s="59" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="L6" s="23" t="inlineStr">
+      <c r="L6" s="57" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="M6" s="25" t="n"/>
-      <c r="N6" s="25" t="inlineStr">
+      <c r="M6" s="59" t="n"/>
+      <c r="N6" s="59" t="inlineStr">
         <is>
           <t>TESTER: fill</t>
         </is>
       </c>
-      <c r="O6" s="27" t="inlineStr">
+      <c r="O6" s="61" t="inlineStr">
         <is>
           <t>TESTER: fill</t>
         </is>
       </c>
-      <c r="P6" s="27" t="inlineStr">
+      <c r="P6" s="61" t="inlineStr">
         <is>
           <t>TESTER: fill</t>
         </is>
       </c>
-      <c r="Q6" s="28" t="inlineStr">
+      <c r="Q6" s="62" t="inlineStr">
         <is>
           <t>2026-10-05</t>
         </is>
       </c>
     </row>
     <row r="7" ht="54" customHeight="1">
-      <c r="A7" s="19" t="inlineStr">
+      <c r="A7" s="52" t="inlineStr">
         <is>
           <t>CL-003</t>
         </is>
       </c>
-      <c r="B7" s="20" t="inlineStr">
+      <c r="B7" s="53" t="inlineStr">
         <is>
           <t>ماندگاری پس از قطع برق</t>
         </is>
       </c>
-      <c r="C7" s="21" t="inlineStr">
+      <c r="C7" s="54" t="inlineStr">
         <is>
           <t>بالا</t>
         </is>
       </c>
-      <c r="D7" s="29" t="inlineStr">
+      <c r="D7" s="55" t="inlineStr">
         <is>
           <t>جدول سفارشی را فرستاده‌ای و نشسته است (CL-002)</t>
         </is>
       </c>
-      <c r="E7" s="20" t="inlineStr">
+      <c r="E7" s="53" t="inlineStr">
         <is>
           <t>گام ۱: برق دستگاه را کامل قطع کن و یک دقیقه صبر کن.
 گام ۲: روشن کن و جدول را از پنل دوباره بخوان.</t>
         </is>
       </c>
-      <c r="F7" s="22" t="inlineStr">
+      <c r="F7" s="56" t="inlineStr">
         <is>
           <t>قطع و وصل کامل برق</t>
         </is>
       </c>
-      <c r="G7" s="22" t="inlineStr">
+      <c r="G7" s="56" t="inlineStr">
         <is>
           <t>پنج دقیقه</t>
         </is>
       </c>
-      <c r="H7" s="20" t="inlineStr">
+      <c r="H7" s="53" t="inlineStr">
         <is>
           <t>جدول سفارشی بعد از روشن‌شدن سر جاست</t>
         </is>
       </c>
-      <c r="I7" s="20" t="inlineStr">
+      <c r="I7" s="53" t="inlineStr">
         <is>
           <t>ماندگار در قطع برق</t>
         </is>
       </c>
-      <c r="J7" s="20" t="inlineStr">
+      <c r="J7" s="53" t="inlineStr">
         <is>
           <t>حفظ جدول = قبول؛ پاک‌شدن = رد</t>
         </is>
       </c>
-      <c r="K7" s="20" t="inlineStr">
+      <c r="K7" s="53" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="L7" s="23" t="inlineStr">
+      <c r="L7" s="57" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="M7" s="20" t="n"/>
-      <c r="N7" s="20" t="inlineStr">
+      <c r="M7" s="53" t="n"/>
+      <c r="N7" s="53" t="inlineStr">
         <is>
           <t>TESTER: fill</t>
         </is>
       </c>
-      <c r="O7" s="22" t="inlineStr">
+      <c r="O7" s="56" t="inlineStr">
         <is>
           <t>TESTER: fill</t>
         </is>
       </c>
-      <c r="P7" s="22" t="inlineStr">
+      <c r="P7" s="56" t="inlineStr">
         <is>
           <t>TESTER: fill</t>
         </is>
       </c>
-      <c r="Q7" s="24" t="inlineStr">
+      <c r="Q7" s="58" t="inlineStr">
         <is>
           <t>2026-10-05</t>
         </is>
       </c>
     </row>
     <row r="8" ht="54" customHeight="1">
-      <c r="A8" s="19" t="inlineStr">
+      <c r="A8" s="52" t="inlineStr">
         <is>
           <t>CL-010</t>
         </is>
       </c>
-      <c r="B8" s="25" t="inlineStr">
+      <c r="B8" s="59" t="inlineStr">
         <is>
           <t>قطع برق وسط نوشتن</t>
         </is>
       </c>
-      <c r="C8" s="26" t="inlineStr">
+      <c r="C8" s="60" t="inlineStr">
         <is>
           <t>بالا</t>
         </is>
       </c>
-      <c r="D8" s="30" t="inlineStr">
+      <c r="D8" s="63" t="inlineStr">
         <is>
           <t>پنل باز و دستگاه روشن است؛ دستت روی کلید برق دستگاه باشد</t>
         </is>
       </c>
-      <c r="E8" s="30" t="inlineStr">
+      <c r="E8" s="63" t="inlineStr">
         <is>
           <t>گام ۱: فرستادن یک جدول تازه از پنل را شروع کن.
 گام ۲: وسط فرستادن، برق دستگاه را بکش.
 گام ۳: دوباره روشن کن و جدول را بخوان: یا جدول قبلی سالم است یا پیش‌فرض؛ بعد یک شارژ واقعی بگیر.</t>
         </is>
       </c>
-      <c r="F8" s="27" t="inlineStr">
+      <c r="F8" s="61" t="inlineStr">
         <is>
           <t>قطع برق وسط فرستادن جدول</t>
         </is>
       </c>
-      <c r="G8" s="27" t="inlineStr">
+      <c r="G8" s="61" t="inlineStr">
         <is>
           <t>ده دقیقه</t>
         </is>
       </c>
-      <c r="H8" s="25" t="inlineStr">
+      <c r="H8" s="59" t="inlineStr">
         <is>
           <t>جدول نصفه‌نیمه ذخیره نشده؛ شارژ با جدول قبلی یا پیش‌فرض سالم کار می‌کند</t>
         </is>
       </c>
-      <c r="I8" s="25" t="inlineStr">
+      <c r="I8" s="59" t="inlineStr">
         <is>
           <t>بدون جدول خراب</t>
         </is>
       </c>
-      <c r="J8" s="25" t="inlineStr">
+      <c r="J8" s="59" t="inlineStr">
         <is>
           <t>شارژ سالم بعد از قطع وسط کار = قبول؛ جدول خراب یا شارژ به‌هم‌ریخته = رد</t>
         </is>
       </c>
-      <c r="K8" s="25" t="inlineStr">
+      <c r="K8" s="59" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="L8" s="23" t="inlineStr">
+      <c r="L8" s="57" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="M8" s="25" t="n"/>
-      <c r="N8" s="25" t="inlineStr">
+      <c r="M8" s="59" t="n"/>
+      <c r="N8" s="59" t="inlineStr">
         <is>
           <t>TESTER: fill</t>
         </is>
       </c>
-      <c r="O8" s="27" t="inlineStr">
+      <c r="O8" s="61" t="inlineStr">
         <is>
           <t>TESTER: fill</t>
         </is>
       </c>
-      <c r="P8" s="27" t="inlineStr">
+      <c r="P8" s="61" t="inlineStr">
         <is>
           <t>TESTER: fill</t>
         </is>
       </c>
-      <c r="Q8" s="28" t="inlineStr">
+      <c r="Q8" s="62" t="inlineStr">
         <is>
           <t>2026-10-05</t>
         </is>
       </c>
     </row>
     <row r="9" ht="54" customHeight="1">
-      <c r="A9" s="19" t="inlineStr">
+      <c r="A9" s="52" t="inlineStr">
         <is>
           <t>CL-011</t>
         </is>
       </c>
-      <c r="B9" s="20" t="inlineStr">
+      <c r="B9" s="53" t="inlineStr">
         <is>
           <t>استقلال از NVM پارامترها</t>
         </is>
       </c>
-      <c r="C9" s="21" t="inlineStr">
+      <c r="C9" s="54" t="inlineStr">
         <is>
           <t>بالا</t>
         </is>
       </c>
-      <c r="D9" s="20" t="inlineStr">
+      <c r="D9" s="53" t="inlineStr">
         <is>
           <t>جدول سفارشی نشسته و پنل باز است</t>
         </is>
       </c>
-      <c r="E9" s="20" t="inlineStr">
+      <c r="E9" s="53" t="inlineStr">
         <is>
           <t>گام ۱: چند پارامتر معمولی پنل (نه جدولی) را عوض کن.
 گام ۲: برق را قطع و وصل کن.
 گام ۳: جدول را بخوان.</t>
         </is>
       </c>
-      <c r="F9" s="22" t="inlineStr">
+      <c r="F9" s="56" t="inlineStr">
         <is>
           <t>تغییر پارامترهای معمولی و قطع‌ووصل</t>
         </is>
       </c>
-      <c r="G9" s="22" t="inlineStr">
+      <c r="G9" s="56" t="inlineStr">
         <is>
           <t>پنج دقیقه</t>
         </is>
       </c>
-      <c r="H9" s="20" t="inlineStr">
+      <c r="H9" s="53" t="inlineStr">
         <is>
           <t>جدول سفارشی دست‌نخورده مانده است</t>
         </is>
       </c>
-      <c r="I9" s="20" t="inlineStr">
+      <c r="I9" s="53" t="inlineStr">
         <is>
           <t>استقلال جدول از بقیهٔ تنظیم‌ها</t>
         </is>
       </c>
-      <c r="J9" s="20" t="inlineStr">
+      <c r="J9" s="53" t="inlineStr">
         <is>
           <t>سالم‌ماندن جدول = قبول؛ دست‌خوردن جدول = رد</t>
         </is>
       </c>
-      <c r="K9" s="20" t="inlineStr">
+      <c r="K9" s="53" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="L9" s="23" t="inlineStr">
+      <c r="L9" s="57" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="M9" s="20" t="n"/>
-      <c r="N9" s="20" t="inlineStr">
+      <c r="M9" s="53" t="n"/>
+      <c r="N9" s="53" t="inlineStr">
         <is>
           <t>TESTER: fill</t>
         </is>
       </c>
-      <c r="O9" s="22" t="inlineStr">
+      <c r="O9" s="56" t="inlineStr">
         <is>
           <t>TESTER: fill</t>
         </is>
       </c>
-      <c r="P9" s="22" t="inlineStr">
+      <c r="P9" s="56" t="inlineStr">
         <is>
           <t>TESTER: fill</t>
         </is>
       </c>
-      <c r="Q9" s="24" t="inlineStr">
+      <c r="Q9" s="58" t="inlineStr">
         <is>
           <t>2026-10-05</t>
         </is>
       </c>
     </row>
     <row r="10" ht="54" customHeight="1">
-      <c r="A10" s="19" t="inlineStr">
+      <c r="A10" s="52" t="inlineStr">
         <is>
           <t>CL-014</t>
         </is>
       </c>
-      <c r="B10" s="25" t="inlineStr">
+      <c r="B10" s="59" t="inlineStr">
         <is>
           <t>LUT_READ بازخوانی واقعی هر دو کانال</t>
         </is>
       </c>
-      <c r="C10" s="26" t="inlineStr">
+      <c r="C10" s="60" t="inlineStr">
         <is>
           <t>بالا</t>
         </is>
       </c>
-      <c r="D10" s="25" t="inlineStr">
+      <c r="D10" s="59" t="inlineStr">
         <is>
           <t>برای هر دو کانال جدول ذخیره کرده‌ای</t>
         </is>
       </c>
-      <c r="E10" s="25" t="inlineStr">
+      <c r="E10" s="59" t="inlineStr">
         <is>
           <t>گام ۱: از پنل جدول هر دو کانال را کامل بخوان.
 گام ۲: عددها را با چیزی که فرستاده بودی مقایسه کن.</t>
         </is>
       </c>
-      <c r="F10" s="27" t="inlineStr">
+      <c r="F10" s="61" t="inlineStr">
         <is>
           <t>خواندن جدول هر دو کانال</t>
         </is>
       </c>
-      <c r="G10" s="27" t="inlineStr">
+      <c r="G10" s="61" t="inlineStr">
         <is>
           <t>پنج دقیقه</t>
         </is>
       </c>
-      <c r="H10" s="25" t="inlineStr">
+      <c r="H10" s="59" t="inlineStr">
         <is>
           <t>هر دو جدول عددبه‌عدد درست و سر جای خودشان‌اند؛ کانال‌ها قاطی نشده‌اند</t>
         </is>
       </c>
-      <c r="I10" s="25" t="inlineStr">
+      <c r="I10" s="59" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J10" s="25" t="inlineStr">
+      <c r="J10" s="59" t="inlineStr">
         <is>
           <t>درستی هر دو = قبول؛ قاطی یا ناقص = رد</t>
         </is>
       </c>
-      <c r="K10" s="25" t="inlineStr">
+      <c r="K10" s="59" t="inlineStr">
         <is>
           <t>Host PASS: 159 check؛ شامل دو فریم واقعی LUT_DATA، battery 2 مستقل و transition غیرصفر→صفر؛ برد فیزیکی pending</t>
         </is>
       </c>
-      <c r="L10" s="23" t="inlineStr">
+      <c r="L10" s="57" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="M10" s="25" t="inlineStr">
+      <c r="M10" s="59" t="inlineStr">
         <is>
           <t>Host جای اندازه‌گیری برد را نمی‌گیرد؛ فلش و readback روی برد واقعی لازم است</t>
         </is>
       </c>
-      <c r="N10" s="25" t="inlineStr">
+      <c r="N10" s="59" t="inlineStr">
         <is>
           <t>Firmware/Modules/CalLut/Tester/run_host_test_cal_lut.sh</t>
         </is>
       </c>
-      <c r="O10" s="27" t="inlineStr">
+      <c r="O10" s="61" t="inlineStr">
         <is>
           <t>WORKTREE</t>
         </is>
       </c>
-      <c r="P10" s="27" t="inlineStr"/>
-      <c r="Q10" s="28" t="inlineStr">
+      <c r="P10" s="61" t="inlineStr"/>
+      <c r="Q10" s="62" t="inlineStr">
         <is>
           <t>2026-10-07</t>
         </is>
       </c>
     </row>
     <row r="11" ht="54" customHeight="1">
-      <c r="A11" s="19" t="inlineStr">
+      <c r="A11" s="52" t="inlineStr">
         <is>
           <t>CL-015</t>
         </is>
       </c>
-      <c r="B11" s="20" t="inlineStr">
+      <c r="B11" s="53" t="inlineStr">
         <is>
           <t>حذف override با صفرنقطه</t>
         </is>
       </c>
-      <c r="C11" s="21" t="inlineStr">
+      <c r="C11" s="54" t="inlineStr">
         <is>
           <t>بالا</t>
         </is>
       </c>
-      <c r="D11" s="29" t="inlineStr">
+      <c r="D11" s="55" t="inlineStr">
         <is>
           <t>یک کانال جدول سفارشی (override) دارد و با آن شارژ می‌کند</t>
         </is>
       </c>
-      <c r="E11" s="29" t="inlineStr">
+      <c r="E11" s="55" t="inlineStr">
         <is>
           <t>گام ۱: از پنل override همان کانال را با نقطهٔ صفر پاک کن.
 گام ۲: یک شارژ واقعی با همان کانال بگیر.</t>
         </is>
       </c>
-      <c r="F11" s="22" t="inlineStr">
+      <c r="F11" s="56" t="inlineStr">
         <is>
           <t>پاک‌کردن override از پنل</t>
         </is>
       </c>
-      <c r="G11" s="22" t="inlineStr">
+      <c r="G11" s="56" t="inlineStr">
         <is>
           <t>ده دقیقه</t>
         </is>
       </c>
-      <c r="H11" s="20" t="inlineStr">
+      <c r="H11" s="53" t="inlineStr">
         <is>
           <t>کانال به رفتار پیش‌فرض کارخانه برمی‌گردد و شارژ عادی می‌شود</t>
         </is>
       </c>
-      <c r="I11" s="20" t="inlineStr">
+      <c r="I11" s="53" t="inlineStr">
         <is>
           <t>برگشت به پیش‌فرض</t>
         </is>
       </c>
-      <c r="J11" s="20" t="inlineStr">
+      <c r="J11" s="53" t="inlineStr">
         <is>
           <t>برگشت به پیش‌فرض = قبول؛ ماندن روی جدول پاک‌شده = رد</t>
         </is>
       </c>
-      <c r="K11" s="20" t="inlineStr">
+      <c r="K11" s="53" t="inlineStr">
         <is>
           <t>Host PASS: 159 check؛ board physical pending</t>
         </is>
       </c>
-      <c r="L11" s="23" t="inlineStr">
+      <c r="L11" s="57" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="M11" s="20" t="inlineStr">
+      <c r="M11" s="53" t="inlineStr">
         <is>
           <t>Host جای تست برد را نمی‌گیرد؛ حذف override و ماندگاری پس از reset روی برد واقعی لازم است</t>
         </is>
       </c>
-      <c r="N11" s="29" t="inlineStr">
+      <c r="N11" s="55" t="inlineStr">
         <is>
           <t>Firmware/Modules/CalLut/Tester/run_host_test_cal_lut.sh؛ esp_link_panel/Tester/host_test_scenario_cards.js</t>
         </is>
       </c>
-      <c r="O11" s="22" t="inlineStr">
+      <c r="O11" s="56" t="inlineStr">
         <is>
           <t>WORKTREE</t>
         </is>
       </c>
-      <c r="P11" s="22" t="n"/>
-      <c r="Q11" s="24" t="inlineStr">
+      <c r="P11" s="56" t="n"/>
+      <c r="Q11" s="58" t="inlineStr">
         <is>
           <t>2026-10-07</t>
         </is>
       </c>
     </row>
     <row r="12" ht="54" customHeight="1">
-      <c r="A12" s="19" t="inlineStr">
+      <c r="A12" s="52" t="inlineStr">
         <is>
           <t>CL-016</t>
         </is>
       </c>
-      <c r="B12" s="25" t="inlineStr">
+      <c r="B12" s="59" t="inlineStr">
         <is>
           <t>reset با grant و flush NVM</t>
         </is>
       </c>
-      <c r="C12" s="26" t="inlineStr">
+      <c r="C12" s="60" t="inlineStr">
         <is>
           <t>بالا</t>
         </is>
       </c>
-      <c r="D12" s="25" t="inlineStr">
+      <c r="D12" s="59" t="inlineStr">
         <is>
           <t>جدول سفارشی ذخیره است و پنل باز</t>
         </is>
       </c>
-      <c r="E12" s="25" t="inlineStr">
+      <c r="E12" s="59" t="inlineStr">
         <is>
           <t>گام ۱: ریست جدول را از پنل با تأیید انجام بده.
 گام ۲: برق را قطع و وصل کن.
 گام ۳: جدول را بخوان و یک شارژ بگیر.</t>
         </is>
       </c>
-      <c r="F12" s="27" t="inlineStr">
+      <c r="F12" s="61" t="inlineStr">
         <is>
           <t>ریست جدول و قطع‌ووصل برق</t>
         </is>
       </c>
-      <c r="G12" s="27" t="inlineStr">
+      <c r="G12" s="61" t="inlineStr">
         <is>
           <t>ده دقیقه</t>
         </is>
       </c>
-      <c r="H12" s="25" t="inlineStr">
+      <c r="H12" s="59" t="inlineStr">
         <is>
           <t>جدول پاک شده، بعد از روشن‌شدن هم برنمی‌گردد و شارژ پیش‌فرض عادی است</t>
         </is>
       </c>
-      <c r="I12" s="25" t="inlineStr">
+      <c r="I12" s="59" t="inlineStr">
         <is>
           <t>ماندگار</t>
         </is>
       </c>
-      <c r="J12" s="25" t="inlineStr">
+      <c r="J12" s="59" t="inlineStr">
         <is>
           <t>پاک‌ماندن و شارژ عادی = قبول؛ برگشتن جدول = رد</t>
         </is>
       </c>
-      <c r="K12" s="25" t="inlineStr">
+      <c r="K12" s="59" t="inlineStr">
         <is>
           <t>Host PASS: CalLut=159، parser=14 و NVM؛ تست فیزیکی فلش/ریست/باتری انجام نشده و pending است</t>
         </is>
       </c>
-      <c r="L12" s="23" t="inlineStr">
+      <c r="L12" s="57" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="M12" s="25" t="inlineStr">
+      <c r="M12" s="59" t="inlineStr">
         <is>
           <t>Host جای تست فیزیکی برد و fault واقعی NVM را نمی‌گیرد؛ commit zero-point، reset و flush روی برد واقعی تکرار شود</t>
         </is>
       </c>
-      <c r="N12" s="30" t="inlineStr">
+      <c r="N12" s="63" t="inlineStr">
         <is>
           <t>Firmware/Modules/CalLut/Tester/run_host_test_cal_lut.sh؛ Firmware/Modules/EspLink/Tester/run_host_test_nvm.sh؛ Firmware/Modules/EspLink/esp_link.c</t>
         </is>
       </c>
-      <c r="O12" s="27" t="inlineStr">
+      <c r="O12" s="61" t="inlineStr">
         <is>
           <t>WORKTREE</t>
         </is>
       </c>
-      <c r="P12" s="27" t="n"/>
-      <c r="Q12" s="28" t="inlineStr">
+      <c r="P12" s="61" t="n"/>
+      <c r="Q12" s="62" t="inlineStr">
         <is>
           <t>2026-10-08</t>
         </is>
       </c>
     </row>
     <row r="13" ht="40.5" customHeight="1">
-      <c r="A13" s="19" t="inlineStr">
+      <c r="A13" s="52" t="inlineStr">
         <is>
           <t>CL-020</t>
         </is>
       </c>
-      <c r="B13" s="20" t="inlineStr">
+      <c r="B13" s="53" t="inlineStr">
         <is>
           <t>پنل دیالوگ LUT</t>
         </is>
       </c>
-      <c r="C13" s="22" t="inlineStr">
+      <c r="C13" s="56" t="inlineStr">
         <is>
           <t>متوسط</t>
         </is>
       </c>
-      <c r="D13" s="20" t="inlineStr">
+      <c r="D13" s="53" t="inlineStr">
         <is>
           <t>پنل باز و دستگاه روشن است</t>
         </is>
       </c>
-      <c r="E13" s="20" t="inlineStr">
+      <c r="E13" s="53" t="inlineStr">
         <is>
           <t>گام ۱: دیالوگ جدول را در پنل باز کن و یک عدد را عوض کن.
 گام ۲: لغو بزن؛ جدول را بخوان که عوض نشده باشد.
 گام ۳: دوباره عوض کن و این بار تأیید بزن؛ بخوان که نشسته باشد.</t>
         </is>
       </c>
-      <c r="F13" s="22" t="inlineStr">
+      <c r="F13" s="56" t="inlineStr">
         <is>
           <t>لغو و تأیید در دیالوگ جدول پنل</t>
         </is>
       </c>
-      <c r="G13" s="22" t="inlineStr">
+      <c r="G13" s="56" t="inlineStr">
         <is>
           <t>پنج دقیقه</t>
         </is>
       </c>
-      <c r="H13" s="20" t="inlineStr">
+      <c r="H13" s="53" t="inlineStr">
         <is>
           <t>لغو هیچ اثری ندارد و تأیید دقیقاً همان تغییر را می‌نشاند</t>
         </is>
       </c>
-      <c r="I13" s="20" t="inlineStr">
+      <c r="I13" s="53" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J13" s="20" t="inlineStr">
+      <c r="J13" s="53" t="inlineStr">
         <is>
           <t>رفتار درست لغو/تأیید = قبول؛ اعمال با لغو یا گم‌شدن با تأیید = رد</t>
         </is>
       </c>
-      <c r="K13" s="20" t="n"/>
-      <c r="L13" s="31" t="inlineStr">
+      <c r="K13" s="53" t="n"/>
+      <c r="L13" s="64" t="inlineStr">
         <is>
           <t>نیاز به تکرار</t>
         </is>
       </c>
-      <c r="M13" s="20" t="n"/>
-      <c r="N13" s="20" t="inlineStr">
+      <c r="M13" s="53" t="n"/>
+      <c r="N13" s="53" t="inlineStr">
         <is>
           <t>../EspLink/esp_link.c</t>
         </is>
       </c>
-      <c r="O13" s="22" t="inlineStr">
+      <c r="O13" s="56" t="inlineStr">
         <is>
           <t>62f3782</t>
         </is>
       </c>
-      <c r="P13" s="22" t="n"/>
-      <c r="Q13" s="24" t="inlineStr">
+      <c r="P13" s="56" t="n"/>
+      <c r="Q13" s="58" t="inlineStr">
         <is>
           <t>2026-10-12</t>
         </is>
       </c>
     </row>
     <row r="14" ht="54" customHeight="1">
-      <c r="D14" t="inlineStr">
+      <c r="A14" s="50" t="n"/>
+      <c r="B14" s="50" t="n"/>
+      <c r="C14" s="50" t="n"/>
+      <c r="D14" s="50" t="inlineStr">
         <is>
           <t>'برنامه تست'!A6</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
+      <c r="E14" s="50" t="inlineStr">
         <is>
           <t>'برنامه تست'!A6</t>
         </is>
       </c>
-      <c r="Q14" s="32">
+      <c r="F14" s="50" t="n"/>
+      <c r="G14" s="50" t="n"/>
+      <c r="H14" s="50" t="n"/>
+      <c r="I14" s="50" t="n"/>
+      <c r="J14" s="50" t="n"/>
+      <c r="K14" s="50" t="n"/>
+      <c r="L14" s="50" t="n"/>
+      <c r="M14" s="50" t="n"/>
+      <c r="N14" s="50" t="n"/>
+      <c r="O14" s="50" t="n"/>
+      <c r="P14" s="50" t="n"/>
+      <c r="Q14" s="65">
         <f>IF(OR(L22="",L22="در انتظار"),"",IF(Q22="",TODAY(),Q22))</f>
         <v/>
       </c>
     </row>
     <row r="15" ht="54" customHeight="1">
-      <c r="Q15" s="32">
+      <c r="A15" s="50" t="n"/>
+      <c r="B15" s="50" t="n"/>
+      <c r="C15" s="50" t="n"/>
+      <c r="D15" s="50" t="n"/>
+      <c r="E15" s="50" t="n"/>
+      <c r="F15" s="50" t="n"/>
+      <c r="G15" s="50" t="n"/>
+      <c r="H15" s="50" t="n"/>
+      <c r="I15" s="50" t="n"/>
+      <c r="J15" s="50" t="n"/>
+      <c r="K15" s="50" t="n"/>
+      <c r="L15" s="50" t="n"/>
+      <c r="M15" s="50" t="n"/>
+      <c r="N15" s="50" t="n"/>
+      <c r="O15" s="50" t="n"/>
+      <c r="P15" s="50" t="n"/>
+      <c r="Q15" s="65">
         <f>IF(OR(L23="",L23="در انتظار"),"",IF(Q23="",TODAY(),Q23))</f>
         <v/>
       </c>
     </row>
     <row r="16" ht="54" customHeight="1">
-      <c r="Q16" s="32">
+      <c r="A16" s="50" t="n"/>
+      <c r="B16" s="50" t="n"/>
+      <c r="C16" s="50" t="n"/>
+      <c r="D16" s="50" t="n"/>
+      <c r="E16" s="50" t="n"/>
+      <c r="F16" s="50" t="n"/>
+      <c r="G16" s="50" t="n"/>
+      <c r="H16" s="50" t="n"/>
+      <c r="I16" s="50" t="n"/>
+      <c r="J16" s="50" t="n"/>
+      <c r="K16" s="50" t="n"/>
+      <c r="L16" s="50" t="n"/>
+      <c r="M16" s="50" t="n"/>
+      <c r="N16" s="50" t="n"/>
+      <c r="O16" s="50" t="n"/>
+      <c r="P16" s="50" t="n"/>
+      <c r="Q16" s="65">
         <f>IF(OR(L24="",L24="در انتظار"),"",IF(Q24="",TODAY(),Q24))</f>
         <v/>
       </c>
     </row>
     <row r="17" ht="54" customHeight="1">
-      <c r="Q17" s="32">
+      <c r="A17" s="50" t="n"/>
+      <c r="B17" s="50" t="n"/>
+      <c r="C17" s="50" t="n"/>
+      <c r="D17" s="50" t="n"/>
+      <c r="E17" s="50" t="n"/>
+      <c r="F17" s="50" t="n"/>
+      <c r="G17" s="50" t="n"/>
+      <c r="H17" s="50" t="n"/>
+      <c r="I17" s="50" t="n"/>
+      <c r="J17" s="50" t="n"/>
+      <c r="K17" s="50" t="n"/>
+      <c r="L17" s="50" t="n"/>
+      <c r="M17" s="50" t="n"/>
+      <c r="N17" s="50" t="n"/>
+      <c r="O17" s="50" t="n"/>
+      <c r="P17" s="50" t="n"/>
+      <c r="Q17" s="65">
         <f>IF(OR(L25="",L25="در انتظار"),"",IF(Q25="",TODAY(),Q25))</f>
         <v/>
       </c>
     </row>
     <row r="18" ht="54" customHeight="1">
-      <c r="D18" t="inlineStr">
+      <c r="A18" s="50" t="n"/>
+      <c r="B18" s="50" t="n"/>
+      <c r="C18" s="50" t="n"/>
+      <c r="D18" s="50" t="inlineStr">
         <is>
           <t>'برنامه تست'!A6</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr">
+      <c r="E18" s="50" t="inlineStr">
         <is>
           <t>'برنامه تست'!A6</t>
         </is>
       </c>
-      <c r="Q18" s="32">
+      <c r="F18" s="50" t="n"/>
+      <c r="G18" s="50" t="n"/>
+      <c r="H18" s="50" t="n"/>
+      <c r="I18" s="50" t="n"/>
+      <c r="J18" s="50" t="n"/>
+      <c r="K18" s="50" t="n"/>
+      <c r="L18" s="50" t="n"/>
+      <c r="M18" s="50" t="n"/>
+      <c r="N18" s="50" t="n"/>
+      <c r="O18" s="50" t="n"/>
+      <c r="P18" s="50" t="n"/>
+      <c r="Q18" s="65">
         <f>IF(OR(L26="",L26="در انتظار"),"",IF(Q26="",TODAY(),Q26))</f>
         <v/>
       </c>
     </row>
     <row r="19" ht="67.5" customHeight="1">
-      <c r="N19" t="inlineStr">
+      <c r="A19" s="50" t="n"/>
+      <c r="B19" s="50" t="n"/>
+      <c r="C19" s="50" t="n"/>
+      <c r="D19" s="50" t="n"/>
+      <c r="E19" s="50" t="n"/>
+      <c r="F19" s="50" t="n"/>
+      <c r="G19" s="50" t="n"/>
+      <c r="H19" s="50" t="n"/>
+      <c r="I19" s="50" t="n"/>
+      <c r="J19" s="50" t="n"/>
+      <c r="K19" s="50" t="n"/>
+      <c r="L19" s="50" t="n"/>
+      <c r="M19" s="50" t="n"/>
+      <c r="N19" s="50" t="inlineStr">
         <is>
           <t>../../../esp_link_panel/Tester/host_test_scenario_cards.js</t>
         </is>
       </c>
-      <c r="Q19" s="32">
+      <c r="O19" s="50" t="n"/>
+      <c r="P19" s="50" t="n"/>
+      <c r="Q19" s="65">
         <f>IF(OR(L27="",L27="در انتظار"),"",IF(Q27="",TODAY(),Q27))</f>
         <v/>
       </c>
     </row>
     <row r="20" ht="67.5" customHeight="1">
-      <c r="N20" t="inlineStr">
+      <c r="A20" s="50" t="n"/>
+      <c r="B20" s="50" t="n"/>
+      <c r="C20" s="50" t="n"/>
+      <c r="D20" s="50" t="n"/>
+      <c r="E20" s="50" t="n"/>
+      <c r="F20" s="50" t="n"/>
+      <c r="G20" s="50" t="n"/>
+      <c r="H20" s="50" t="n"/>
+      <c r="I20" s="50" t="n"/>
+      <c r="J20" s="50" t="n"/>
+      <c r="K20" s="50" t="n"/>
+      <c r="L20" s="50" t="n"/>
+      <c r="M20" s="50" t="n"/>
+      <c r="N20" s="50" t="inlineStr">
         <is>
           <t>../EspLink/esp_link.c</t>
         </is>
       </c>
-      <c r="Q20" s="32">
+      <c r="O20" s="50" t="n"/>
+      <c r="P20" s="50" t="n"/>
+      <c r="Q20" s="65">
         <f>IF(OR(L28="",L28="در انتظار"),"",IF(Q28="",TODAY(),Q28))</f>
         <v/>
       </c>
     </row>
     <row r="21" ht="54" customHeight="1">
-      <c r="Q21" s="32">
+      <c r="A21" s="50" t="n"/>
+      <c r="B21" s="50" t="n"/>
+      <c r="C21" s="50" t="n"/>
+      <c r="D21" s="50" t="n"/>
+      <c r="E21" s="50" t="n"/>
+      <c r="F21" s="50" t="n"/>
+      <c r="G21" s="50" t="n"/>
+      <c r="H21" s="50" t="n"/>
+      <c r="I21" s="50" t="n"/>
+      <c r="J21" s="50" t="n"/>
+      <c r="K21" s="50" t="n"/>
+      <c r="L21" s="50" t="n"/>
+      <c r="M21" s="50" t="n"/>
+      <c r="N21" s="50" t="n"/>
+      <c r="O21" s="50" t="n"/>
+      <c r="P21" s="50" t="n"/>
+      <c r="Q21" s="65">
         <f>IF(OR(L29="",L29="در انتظار"),"",IF(Q29="",TODAY(),Q29))</f>
         <v/>
       </c>
     </row>
     <row r="22">
-      <c r="Q22" s="32">
+      <c r="A22" s="50" t="n"/>
+      <c r="B22" s="50" t="n"/>
+      <c r="C22" s="50" t="n"/>
+      <c r="D22" s="50" t="n"/>
+      <c r="E22" s="50" t="n"/>
+      <c r="F22" s="50" t="n"/>
+      <c r="G22" s="50" t="n"/>
+      <c r="H22" s="50" t="n"/>
+      <c r="I22" s="50" t="n"/>
+      <c r="J22" s="50" t="n"/>
+      <c r="K22" s="50" t="n"/>
+      <c r="L22" s="50" t="n"/>
+      <c r="M22" s="50" t="n"/>
+      <c r="N22" s="50" t="n"/>
+      <c r="O22" s="50" t="n"/>
+      <c r="P22" s="50" t="n"/>
+      <c r="Q22" s="65">
         <f>IF(OR(L30="",L30="در انتظار"),"",IF(Q30="",TODAY(),Q30))</f>
         <v/>
       </c>
     </row>
     <row r="23">
-      <c r="Q23" s="32">
+      <c r="A23" s="50" t="n"/>
+      <c r="B23" s="50" t="n"/>
+      <c r="C23" s="50" t="n"/>
+      <c r="D23" s="50" t="n"/>
+      <c r="E23" s="50" t="n"/>
+      <c r="F23" s="50" t="n"/>
+      <c r="G23" s="50" t="n"/>
+      <c r="H23" s="50" t="n"/>
+      <c r="I23" s="50" t="n"/>
+      <c r="J23" s="50" t="n"/>
+      <c r="K23" s="50" t="n"/>
+      <c r="L23" s="50" t="n"/>
+      <c r="M23" s="50" t="n"/>
+      <c r="N23" s="50" t="n"/>
+      <c r="O23" s="50" t="n"/>
+      <c r="P23" s="50" t="n"/>
+      <c r="Q23" s="65">
         <f>IF(OR(L31="",L31="در انتظار"),"",IF(Q31="",TODAY(),Q31))</f>
         <v/>
       </c>
     </row>
     <row r="24">
-      <c r="Q24" s="32">
+      <c r="A24" s="50" t="n"/>
+      <c r="B24" s="50" t="n"/>
+      <c r="C24" s="50" t="n"/>
+      <c r="D24" s="50" t="n"/>
+      <c r="E24" s="50" t="n"/>
+      <c r="F24" s="50" t="n"/>
+      <c r="G24" s="50" t="n"/>
+      <c r="H24" s="50" t="n"/>
+      <c r="I24" s="50" t="n"/>
+      <c r="J24" s="50" t="n"/>
+      <c r="K24" s="50" t="n"/>
+      <c r="L24" s="50" t="n"/>
+      <c r="M24" s="50" t="n"/>
+      <c r="N24" s="50" t="n"/>
+      <c r="O24" s="50" t="n"/>
+      <c r="P24" s="50" t="n"/>
+      <c r="Q24" s="65">
         <f>IF(OR(L32="",L32="در انتظار"),"",IF(Q32="",TODAY(),Q32))</f>
         <v/>
       </c>
     </row>
     <row r="25">
-      <c r="Q25" s="32">
+      <c r="A25" s="50" t="n"/>
+      <c r="B25" s="50" t="n"/>
+      <c r="C25" s="50" t="n"/>
+      <c r="D25" s="50" t="n"/>
+      <c r="E25" s="50" t="n"/>
+      <c r="F25" s="50" t="n"/>
+      <c r="G25" s="50" t="n"/>
+      <c r="H25" s="50" t="n"/>
+      <c r="I25" s="50" t="n"/>
+      <c r="J25" s="50" t="n"/>
+      <c r="K25" s="50" t="n"/>
+      <c r="L25" s="50" t="n"/>
+      <c r="M25" s="50" t="n"/>
+      <c r="N25" s="50" t="n"/>
+      <c r="O25" s="50" t="n"/>
+      <c r="P25" s="50" t="n"/>
+      <c r="Q25" s="65">
         <f>IF(OR(L33="",L33="در انتظار"),"",IF(Q33="",TODAY(),Q33))</f>
         <v/>
       </c>
     </row>
     <row r="26">
-      <c r="Q26" s="32">
+      <c r="A26" s="50" t="n"/>
+      <c r="B26" s="50" t="n"/>
+      <c r="C26" s="50" t="n"/>
+      <c r="D26" s="50" t="n"/>
+      <c r="E26" s="50" t="n"/>
+      <c r="F26" s="50" t="n"/>
+      <c r="G26" s="50" t="n"/>
+      <c r="H26" s="50" t="n"/>
+      <c r="I26" s="50" t="n"/>
+      <c r="J26" s="50" t="n"/>
+      <c r="K26" s="50" t="n"/>
+      <c r="L26" s="50" t="n"/>
+      <c r="M26" s="50" t="n"/>
+      <c r="N26" s="50" t="n"/>
+      <c r="O26" s="50" t="n"/>
+      <c r="P26" s="50" t="n"/>
+      <c r="Q26" s="65">
         <f>IF(OR(L34="",L34="در انتظار"),"",IF(Q34="",TODAY(),Q34))</f>
         <v/>
       </c>
     </row>
     <row r="27">
-      <c r="Q27" s="32">
+      <c r="A27" s="50" t="n"/>
+      <c r="B27" s="50" t="n"/>
+      <c r="C27" s="50" t="n"/>
+      <c r="D27" s="50" t="n"/>
+      <c r="E27" s="50" t="n"/>
+      <c r="F27" s="50" t="n"/>
+      <c r="G27" s="50" t="n"/>
+      <c r="H27" s="50" t="n"/>
+      <c r="I27" s="50" t="n"/>
+      <c r="J27" s="50" t="n"/>
+      <c r="K27" s="50" t="n"/>
+      <c r="L27" s="50" t="n"/>
+      <c r="M27" s="50" t="n"/>
+      <c r="N27" s="50" t="n"/>
+      <c r="O27" s="50" t="n"/>
+      <c r="P27" s="50" t="n"/>
+      <c r="Q27" s="65">
         <f>IF(OR(L35="",L35="در انتظار"),"",IF(Q35="",TODAY(),Q35))</f>
         <v/>
       </c>
     </row>
     <row r="28">
-      <c r="Q28" s="32">
+      <c r="A28" s="50" t="n"/>
+      <c r="B28" s="50" t="n"/>
+      <c r="C28" s="50" t="n"/>
+      <c r="D28" s="50" t="n"/>
+      <c r="E28" s="50" t="n"/>
+      <c r="F28" s="50" t="n"/>
+      <c r="G28" s="50" t="n"/>
+      <c r="H28" s="50" t="n"/>
+      <c r="I28" s="50" t="n"/>
+      <c r="J28" s="50" t="n"/>
+      <c r="K28" s="50" t="n"/>
+      <c r="L28" s="50" t="n"/>
+      <c r="M28" s="50" t="n"/>
+      <c r="N28" s="50" t="n"/>
+      <c r="O28" s="50" t="n"/>
+      <c r="P28" s="50" t="n"/>
+      <c r="Q28" s="65">
         <f>IF(OR(L36="",L36="در انتظار"),"",IF(Q36="",TODAY(),Q36))</f>
         <v/>
       </c>
     </row>
     <row r="29">
-      <c r="Q29" s="32">
+      <c r="A29" s="50" t="n"/>
+      <c r="B29" s="50" t="n"/>
+      <c r="C29" s="50" t="n"/>
+      <c r="D29" s="50" t="n"/>
+      <c r="E29" s="50" t="n"/>
+      <c r="F29" s="50" t="n"/>
+      <c r="G29" s="50" t="n"/>
+      <c r="H29" s="50" t="n"/>
+      <c r="I29" s="50" t="n"/>
+      <c r="J29" s="50" t="n"/>
+      <c r="K29" s="50" t="n"/>
+      <c r="L29" s="50" t="n"/>
+      <c r="M29" s="50" t="n"/>
+      <c r="N29" s="50" t="n"/>
+      <c r="O29" s="50" t="n"/>
+      <c r="P29" s="50" t="n"/>
+      <c r="Q29" s="65">
         <f>IF(OR(L37="",L37="در انتظار"),"",IF(Q37="",TODAY(),Q37))</f>
         <v/>
       </c>
     </row>
     <row r="30">
-      <c r="Q30" s="32">
+      <c r="A30" s="50" t="n"/>
+      <c r="B30" s="50" t="n"/>
+      <c r="C30" s="50" t="n"/>
+      <c r="D30" s="50" t="n"/>
+      <c r="E30" s="50" t="n"/>
+      <c r="F30" s="50" t="n"/>
+      <c r="G30" s="50" t="n"/>
+      <c r="H30" s="50" t="n"/>
+      <c r="I30" s="50" t="n"/>
+      <c r="J30" s="50" t="n"/>
+      <c r="K30" s="50" t="n"/>
+      <c r="L30" s="50" t="n"/>
+      <c r="M30" s="50" t="n"/>
+      <c r="N30" s="50" t="n"/>
+      <c r="O30" s="50" t="n"/>
+      <c r="P30" s="50" t="n"/>
+      <c r="Q30" s="65">
         <f>IF(OR(L38="",L38="در انتظار"),"",IF(Q38="",TODAY(),Q38))</f>
         <v/>
       </c>
     </row>
     <row r="31">
-      <c r="Q31" s="32">
+      <c r="A31" s="50" t="n"/>
+      <c r="B31" s="50" t="n"/>
+      <c r="C31" s="50" t="n"/>
+      <c r="D31" s="50" t="n"/>
+      <c r="E31" s="50" t="n"/>
+      <c r="F31" s="50" t="n"/>
+      <c r="G31" s="50" t="n"/>
+      <c r="H31" s="50" t="n"/>
+      <c r="I31" s="50" t="n"/>
+      <c r="J31" s="50" t="n"/>
+      <c r="K31" s="50" t="n"/>
+      <c r="L31" s="50" t="n"/>
+      <c r="M31" s="50" t="n"/>
+      <c r="N31" s="50" t="n"/>
+      <c r="O31" s="50" t="n"/>
+      <c r="P31" s="50" t="n"/>
+      <c r="Q31" s="65">
         <f>IF(OR(L39="",L39="در انتظار"),"",IF(Q39="",TODAY(),Q39))</f>
         <v/>
       </c>
     </row>
     <row r="32">
-      <c r="Q32" s="32">
+      <c r="A32" s="50" t="n"/>
+      <c r="B32" s="50" t="n"/>
+      <c r="C32" s="50" t="n"/>
+      <c r="D32" s="50" t="n"/>
+      <c r="E32" s="50" t="n"/>
+      <c r="F32" s="50" t="n"/>
+      <c r="G32" s="50" t="n"/>
+      <c r="H32" s="50" t="n"/>
+      <c r="I32" s="50" t="n"/>
+      <c r="J32" s="50" t="n"/>
+      <c r="K32" s="50" t="n"/>
+      <c r="L32" s="50" t="n"/>
+      <c r="M32" s="50" t="n"/>
+      <c r="N32" s="50" t="n"/>
+      <c r="O32" s="50" t="n"/>
+      <c r="P32" s="50" t="n"/>
+      <c r="Q32" s="65">
         <f>IF(OR(L40="",L40="در انتظار"),"",IF(Q40="",TODAY(),Q40))</f>
         <v/>
       </c>
     </row>
     <row r="33">
-      <c r="Q33" s="32">
+      <c r="A33" s="50" t="n"/>
+      <c r="B33" s="50" t="n"/>
+      <c r="C33" s="50" t="n"/>
+      <c r="D33" s="50" t="n"/>
+      <c r="E33" s="50" t="n"/>
+      <c r="F33" s="50" t="n"/>
+      <c r="G33" s="50" t="n"/>
+      <c r="H33" s="50" t="n"/>
+      <c r="I33" s="50" t="n"/>
+      <c r="J33" s="50" t="n"/>
+      <c r="K33" s="50" t="n"/>
+      <c r="L33" s="50" t="n"/>
+      <c r="M33" s="50" t="n"/>
+      <c r="N33" s="50" t="n"/>
+      <c r="O33" s="50" t="n"/>
+      <c r="P33" s="50" t="n"/>
+      <c r="Q33" s="65">
         <f>IF(OR(L41="",L41="در انتظار"),"",IF(Q41="",TODAY(),Q41))</f>
         <v/>
       </c>
     </row>
     <row r="34">
-      <c r="Q34" s="32">
+      <c r="A34" s="50" t="n"/>
+      <c r="B34" s="50" t="n"/>
+      <c r="C34" s="50" t="n"/>
+      <c r="D34" s="50" t="n"/>
+      <c r="E34" s="50" t="n"/>
+      <c r="F34" s="50" t="n"/>
+      <c r="G34" s="50" t="n"/>
+      <c r="H34" s="50" t="n"/>
+      <c r="I34" s="50" t="n"/>
+      <c r="J34" s="50" t="n"/>
+      <c r="K34" s="50" t="n"/>
+      <c r="L34" s="50" t="n"/>
+      <c r="M34" s="50" t="n"/>
+      <c r="N34" s="50" t="n"/>
+      <c r="O34" s="50" t="n"/>
+      <c r="P34" s="50" t="n"/>
+      <c r="Q34" s="65">
         <f>IF(OR(L42="",L42="در انتظار"),"",IF(Q42="",TODAY(),Q42))</f>
         <v/>
       </c>
     </row>
     <row r="35">
-      <c r="Q35" s="32">
+      <c r="A35" s="50" t="n"/>
+      <c r="B35" s="50" t="n"/>
+      <c r="C35" s="50" t="n"/>
+      <c r="D35" s="50" t="n"/>
+      <c r="E35" s="50" t="n"/>
+      <c r="F35" s="50" t="n"/>
+      <c r="G35" s="50" t="n"/>
+      <c r="H35" s="50" t="n"/>
+      <c r="I35" s="50" t="n"/>
+      <c r="J35" s="50" t="n"/>
+      <c r="K35" s="50" t="n"/>
+      <c r="L35" s="50" t="n"/>
+      <c r="M35" s="50" t="n"/>
+      <c r="N35" s="50" t="n"/>
+      <c r="O35" s="50" t="n"/>
+      <c r="P35" s="50" t="n"/>
+      <c r="Q35" s="65">
         <f>IF(OR(L43="",L43="در انتظار"),"",IF(Q43="",TODAY(),Q43))</f>
         <v/>
       </c>
     </row>
     <row r="36">
-      <c r="Q36" s="32">
+      <c r="A36" s="50" t="n"/>
+      <c r="B36" s="50" t="n"/>
+      <c r="C36" s="50" t="n"/>
+      <c r="D36" s="50" t="n"/>
+      <c r="E36" s="50" t="n"/>
+      <c r="F36" s="50" t="n"/>
+      <c r="G36" s="50" t="n"/>
+      <c r="H36" s="50" t="n"/>
+      <c r="I36" s="50" t="n"/>
+      <c r="J36" s="50" t="n"/>
+      <c r="K36" s="50" t="n"/>
+      <c r="L36" s="50" t="n"/>
+      <c r="M36" s="50" t="n"/>
+      <c r="N36" s="50" t="n"/>
+      <c r="O36" s="50" t="n"/>
+      <c r="P36" s="50" t="n"/>
+      <c r="Q36" s="65">
         <f>IF(OR(L44="",L44="در انتظار"),"",IF(Q44="",TODAY(),Q44))</f>
         <v/>
       </c>
     </row>
     <row r="37">
-      <c r="Q37" s="32">
+      <c r="A37" s="50" t="n"/>
+      <c r="B37" s="50" t="n"/>
+      <c r="C37" s="50" t="n"/>
+      <c r="D37" s="50" t="n"/>
+      <c r="E37" s="50" t="n"/>
+      <c r="F37" s="50" t="n"/>
+      <c r="G37" s="50" t="n"/>
+      <c r="H37" s="50" t="n"/>
+      <c r="I37" s="50" t="n"/>
+      <c r="J37" s="50" t="n"/>
+      <c r="K37" s="50" t="n"/>
+      <c r="L37" s="50" t="n"/>
+      <c r="M37" s="50" t="n"/>
+      <c r="N37" s="50" t="n"/>
+      <c r="O37" s="50" t="n"/>
+      <c r="P37" s="50" t="n"/>
+      <c r="Q37" s="65">
         <f>IF(OR(L45="",L45="در انتظار"),"",IF(Q45="",TODAY(),Q45))</f>
         <v/>
       </c>
     </row>
     <row r="38">
-      <c r="Q38" s="32">
+      <c r="A38" s="50" t="n"/>
+      <c r="B38" s="50" t="n"/>
+      <c r="C38" s="50" t="n"/>
+      <c r="D38" s="50" t="n"/>
+      <c r="E38" s="50" t="n"/>
+      <c r="F38" s="50" t="n"/>
+      <c r="G38" s="50" t="n"/>
+      <c r="H38" s="50" t="n"/>
+      <c r="I38" s="50" t="n"/>
+      <c r="J38" s="50" t="n"/>
+      <c r="K38" s="50" t="n"/>
+      <c r="L38" s="50" t="n"/>
+      <c r="M38" s="50" t="n"/>
+      <c r="N38" s="50" t="n"/>
+      <c r="O38" s="50" t="n"/>
+      <c r="P38" s="50" t="n"/>
+      <c r="Q38" s="65">
         <f>IF(OR(L46="",L46="در انتظار"),"",IF(Q46="",TODAY(),Q46))</f>
         <v/>
       </c>
     </row>
     <row r="39">
-      <c r="Q39" s="32">
+      <c r="A39" s="50" t="n"/>
+      <c r="B39" s="50" t="n"/>
+      <c r="C39" s="50" t="n"/>
+      <c r="D39" s="50" t="n"/>
+      <c r="E39" s="50" t="n"/>
+      <c r="F39" s="50" t="n"/>
+      <c r="G39" s="50" t="n"/>
+      <c r="H39" s="50" t="n"/>
+      <c r="I39" s="50" t="n"/>
+      <c r="J39" s="50" t="n"/>
+      <c r="K39" s="50" t="n"/>
+      <c r="L39" s="50" t="n"/>
+      <c r="M39" s="50" t="n"/>
+      <c r="N39" s="50" t="n"/>
+      <c r="O39" s="50" t="n"/>
+      <c r="P39" s="50" t="n"/>
+      <c r="Q39" s="65">
         <f>IF(OR(L47="",L47="در انتظار"),"",IF(Q47="",TODAY(),Q47))</f>
         <v/>
       </c>
     </row>
     <row r="40">
-      <c r="Q40" s="32">
+      <c r="A40" s="50" t="n"/>
+      <c r="B40" s="50" t="n"/>
+      <c r="C40" s="50" t="n"/>
+      <c r="D40" s="50" t="n"/>
+      <c r="E40" s="50" t="n"/>
+      <c r="F40" s="50" t="n"/>
+      <c r="G40" s="50" t="n"/>
+      <c r="H40" s="50" t="n"/>
+      <c r="I40" s="50" t="n"/>
+      <c r="J40" s="50" t="n"/>
+      <c r="K40" s="50" t="n"/>
+      <c r="L40" s="50" t="n"/>
+      <c r="M40" s="50" t="n"/>
+      <c r="N40" s="50" t="n"/>
+      <c r="O40" s="50" t="n"/>
+      <c r="P40" s="50" t="n"/>
+      <c r="Q40" s="65">
         <f>IF(OR(L48="",L48="در انتظار"),"",IF(Q48="",TODAY(),Q48))</f>
         <v/>
       </c>
     </row>
     <row r="41">
-      <c r="Q41" s="32">
+      <c r="A41" s="50" t="n"/>
+      <c r="B41" s="50" t="n"/>
+      <c r="C41" s="50" t="n"/>
+      <c r="D41" s="50" t="n"/>
+      <c r="E41" s="50" t="n"/>
+      <c r="F41" s="50" t="n"/>
+      <c r="G41" s="50" t="n"/>
+      <c r="H41" s="50" t="n"/>
+      <c r="I41" s="50" t="n"/>
+      <c r="J41" s="50" t="n"/>
+      <c r="K41" s="50" t="n"/>
+      <c r="L41" s="50" t="n"/>
+      <c r="M41" s="50" t="n"/>
+      <c r="N41" s="50" t="n"/>
+      <c r="O41" s="50" t="n"/>
+      <c r="P41" s="50" t="n"/>
+      <c r="Q41" s="65">
         <f>IF(OR(L49="",L49="در انتظار"),"",IF(Q49="",TODAY(),Q49))</f>
         <v/>
       </c>
     </row>
     <row r="42">
-      <c r="Q42" s="32">
+      <c r="A42" s="50" t="n"/>
+      <c r="B42" s="50" t="n"/>
+      <c r="C42" s="50" t="n"/>
+      <c r="D42" s="50" t="n"/>
+      <c r="E42" s="50" t="n"/>
+      <c r="F42" s="50" t="n"/>
+      <c r="G42" s="50" t="n"/>
+      <c r="H42" s="50" t="n"/>
+      <c r="I42" s="50" t="n"/>
+      <c r="J42" s="50" t="n"/>
+      <c r="K42" s="50" t="n"/>
+      <c r="L42" s="50" t="n"/>
+      <c r="M42" s="50" t="n"/>
+      <c r="N42" s="50" t="n"/>
+      <c r="O42" s="50" t="n"/>
+      <c r="P42" s="50" t="n"/>
+      <c r="Q42" s="65">
         <f>IF(OR(L50="",L50="در انتظار"),"",IF(Q50="",TODAY(),Q50))</f>
         <v/>
       </c>
     </row>
     <row r="43">
-      <c r="Q43" s="32">
+      <c r="A43" s="50" t="n"/>
+      <c r="B43" s="50" t="n"/>
+      <c r="C43" s="50" t="n"/>
+      <c r="D43" s="50" t="n"/>
+      <c r="E43" s="50" t="n"/>
+      <c r="F43" s="50" t="n"/>
+      <c r="G43" s="50" t="n"/>
+      <c r="H43" s="50" t="n"/>
+      <c r="I43" s="50" t="n"/>
+      <c r="J43" s="50" t="n"/>
+      <c r="K43" s="50" t="n"/>
+      <c r="L43" s="50" t="n"/>
+      <c r="M43" s="50" t="n"/>
+      <c r="N43" s="50" t="n"/>
+      <c r="O43" s="50" t="n"/>
+      <c r="P43" s="50" t="n"/>
+      <c r="Q43" s="65">
         <f>IF(OR(L51="",L51="در انتظار"),"",IF(Q51="",TODAY(),Q51))</f>
         <v/>
       </c>
     </row>
     <row r="44">
-      <c r="Q44" s="32">
+      <c r="A44" s="50" t="n"/>
+      <c r="B44" s="50" t="n"/>
+      <c r="C44" s="50" t="n"/>
+      <c r="D44" s="50" t="n"/>
+      <c r="E44" s="50" t="n"/>
+      <c r="F44" s="50" t="n"/>
+      <c r="G44" s="50" t="n"/>
+      <c r="H44" s="50" t="n"/>
+      <c r="I44" s="50" t="n"/>
+      <c r="J44" s="50" t="n"/>
+      <c r="K44" s="50" t="n"/>
+      <c r="L44" s="50" t="n"/>
+      <c r="M44" s="50" t="n"/>
+      <c r="N44" s="50" t="n"/>
+      <c r="O44" s="50" t="n"/>
+      <c r="P44" s="50" t="n"/>
+      <c r="Q44" s="65">
         <f>IF(OR(L52="",L52="در انتظار"),"",IF(Q52="",TODAY(),Q52))</f>
         <v/>
       </c>
     </row>
     <row r="45">
-      <c r="Q45" s="32">
+      <c r="A45" s="50" t="n"/>
+      <c r="B45" s="50" t="n"/>
+      <c r="C45" s="50" t="n"/>
+      <c r="D45" s="50" t="n"/>
+      <c r="E45" s="50" t="n"/>
+      <c r="F45" s="50" t="n"/>
+      <c r="G45" s="50" t="n"/>
+      <c r="H45" s="50" t="n"/>
+      <c r="I45" s="50" t="n"/>
+      <c r="J45" s="50" t="n"/>
+      <c r="K45" s="50" t="n"/>
+      <c r="L45" s="50" t="n"/>
+      <c r="M45" s="50" t="n"/>
+      <c r="N45" s="50" t="n"/>
+      <c r="O45" s="50" t="n"/>
+      <c r="P45" s="50" t="n"/>
+      <c r="Q45" s="65">
         <f>IF(OR(L53="",L53="در انتظار"),"",IF(Q53="",TODAY(),Q53))</f>
         <v/>
       </c>
     </row>
     <row r="46">
-      <c r="Q46" s="32">
+      <c r="A46" s="50" t="n"/>
+      <c r="B46" s="50" t="n"/>
+      <c r="C46" s="50" t="n"/>
+      <c r="D46" s="50" t="n"/>
+      <c r="E46" s="50" t="n"/>
+      <c r="F46" s="50" t="n"/>
+      <c r="G46" s="50" t="n"/>
+      <c r="H46" s="50" t="n"/>
+      <c r="I46" s="50" t="n"/>
+      <c r="J46" s="50" t="n"/>
+      <c r="K46" s="50" t="n"/>
+      <c r="L46" s="50" t="n"/>
+      <c r="M46" s="50" t="n"/>
+      <c r="N46" s="50" t="n"/>
+      <c r="O46" s="50" t="n"/>
+      <c r="P46" s="50" t="n"/>
+      <c r="Q46" s="65">
         <f>IF(OR(L54="",L54="در انتظار"),"",IF(Q54="",TODAY(),Q54))</f>
         <v/>
       </c>
     </row>
     <row r="47">
-      <c r="Q47" s="32">
+      <c r="A47" s="50" t="n"/>
+      <c r="B47" s="50" t="n"/>
+      <c r="C47" s="50" t="n"/>
+      <c r="D47" s="50" t="n"/>
+      <c r="E47" s="50" t="n"/>
+      <c r="F47" s="50" t="n"/>
+      <c r="G47" s="50" t="n"/>
+      <c r="H47" s="50" t="n"/>
+      <c r="I47" s="50" t="n"/>
+      <c r="J47" s="50" t="n"/>
+      <c r="K47" s="50" t="n"/>
+      <c r="L47" s="50" t="n"/>
+      <c r="M47" s="50" t="n"/>
+      <c r="N47" s="50" t="n"/>
+      <c r="O47" s="50" t="n"/>
+      <c r="P47" s="50" t="n"/>
+      <c r="Q47" s="65">
         <f>IF(OR(L55="",L55="در انتظار"),"",IF(Q55="",TODAY(),Q55))</f>
         <v/>
       </c>
     </row>
     <row r="48">
-      <c r="Q48" s="32">
+      <c r="A48" s="50" t="n"/>
+      <c r="B48" s="50" t="n"/>
+      <c r="C48" s="50" t="n"/>
+      <c r="D48" s="50" t="n"/>
+      <c r="E48" s="50" t="n"/>
+      <c r="F48" s="50" t="n"/>
+      <c r="G48" s="50" t="n"/>
+      <c r="H48" s="50" t="n"/>
+      <c r="I48" s="50" t="n"/>
+      <c r="J48" s="50" t="n"/>
+      <c r="K48" s="50" t="n"/>
+      <c r="L48" s="50" t="n"/>
+      <c r="M48" s="50" t="n"/>
+      <c r="N48" s="50" t="n"/>
+      <c r="O48" s="50" t="n"/>
+      <c r="P48" s="50" t="n"/>
+      <c r="Q48" s="65">
         <f>IF(OR(L56="",L56="در انتظار"),"",IF(Q56="",TODAY(),Q56))</f>
         <v/>
       </c>
     </row>
     <row r="49">
-      <c r="Q49" s="32">
+      <c r="A49" s="50" t="n"/>
+      <c r="B49" s="50" t="n"/>
+      <c r="C49" s="50" t="n"/>
+      <c r="D49" s="50" t="n"/>
+      <c r="E49" s="50" t="n"/>
+      <c r="F49" s="50" t="n"/>
+      <c r="G49" s="50" t="n"/>
+      <c r="H49" s="50" t="n"/>
+      <c r="I49" s="50" t="n"/>
+      <c r="J49" s="50" t="n"/>
+      <c r="K49" s="50" t="n"/>
+      <c r="L49" s="50" t="n"/>
+      <c r="M49" s="50" t="n"/>
+      <c r="N49" s="50" t="n"/>
+      <c r="O49" s="50" t="n"/>
+      <c r="P49" s="50" t="n"/>
+      <c r="Q49" s="65">
         <f>IF(OR(L57="",L57="در انتظار"),"",IF(Q57="",TODAY(),Q57))</f>
         <v/>
       </c>
     </row>
     <row r="50">
-      <c r="Q50" s="32">
+      <c r="A50" s="50" t="n"/>
+      <c r="B50" s="50" t="n"/>
+      <c r="C50" s="50" t="n"/>
+      <c r="D50" s="50" t="n"/>
+      <c r="E50" s="50" t="n"/>
+      <c r="F50" s="50" t="n"/>
+      <c r="G50" s="50" t="n"/>
+      <c r="H50" s="50" t="n"/>
+      <c r="I50" s="50" t="n"/>
+      <c r="J50" s="50" t="n"/>
+      <c r="K50" s="50" t="n"/>
+      <c r="L50" s="50" t="n"/>
+      <c r="M50" s="50" t="n"/>
+      <c r="N50" s="50" t="n"/>
+      <c r="O50" s="50" t="n"/>
+      <c r="P50" s="50" t="n"/>
+      <c r="Q50" s="65">
         <f>IF(OR(L58="",L58="در انتظار"),"",IF(Q58="",TODAY(),Q58))</f>
         <v/>
       </c>
     </row>
     <row r="51">
-      <c r="Q51" s="32">
+      <c r="A51" s="50" t="n"/>
+      <c r="B51" s="50" t="n"/>
+      <c r="C51" s="50" t="n"/>
+      <c r="D51" s="50" t="n"/>
+      <c r="E51" s="50" t="n"/>
+      <c r="F51" s="50" t="n"/>
+      <c r="G51" s="50" t="n"/>
+      <c r="H51" s="50" t="n"/>
+      <c r="I51" s="50" t="n"/>
+      <c r="J51" s="50" t="n"/>
+      <c r="K51" s="50" t="n"/>
+      <c r="L51" s="50" t="n"/>
+      <c r="M51" s="50" t="n"/>
+      <c r="N51" s="50" t="n"/>
+      <c r="O51" s="50" t="n"/>
+      <c r="P51" s="50" t="n"/>
+      <c r="Q51" s="65">
         <f>IF(OR(L59="",L59="در انتظار"),"",IF(Q59="",TODAY(),Q59))</f>
         <v/>
       </c>
     </row>
     <row r="52">
-      <c r="Q52" s="32">
+      <c r="A52" s="50" t="n"/>
+      <c r="B52" s="50" t="n"/>
+      <c r="C52" s="50" t="n"/>
+      <c r="D52" s="50" t="n"/>
+      <c r="E52" s="50" t="n"/>
+      <c r="F52" s="50" t="n"/>
+      <c r="G52" s="50" t="n"/>
+      <c r="H52" s="50" t="n"/>
+      <c r="I52" s="50" t="n"/>
+      <c r="J52" s="50" t="n"/>
+      <c r="K52" s="50" t="n"/>
+      <c r="L52" s="50" t="n"/>
+      <c r="M52" s="50" t="n"/>
+      <c r="N52" s="50" t="n"/>
+      <c r="O52" s="50" t="n"/>
+      <c r="P52" s="50" t="n"/>
+      <c r="Q52" s="65">
         <f>IF(OR(L60="",L60="در انتظار"),"",IF(Q60="",TODAY(),Q60))</f>
         <v/>
       </c>
     </row>
     <row r="53">
-      <c r="Q53" s="32">
+      <c r="A53" s="50" t="n"/>
+      <c r="B53" s="50" t="n"/>
+      <c r="C53" s="50" t="n"/>
+      <c r="D53" s="50" t="n"/>
+      <c r="E53" s="50" t="n"/>
+      <c r="F53" s="50" t="n"/>
+      <c r="G53" s="50" t="n"/>
+      <c r="H53" s="50" t="n"/>
+      <c r="I53" s="50" t="n"/>
+      <c r="J53" s="50" t="n"/>
+      <c r="K53" s="50" t="n"/>
+      <c r="L53" s="50" t="n"/>
+      <c r="M53" s="50" t="n"/>
+      <c r="N53" s="50" t="n"/>
+      <c r="O53" s="50" t="n"/>
+      <c r="P53" s="50" t="n"/>
+      <c r="Q53" s="65">
         <f>IF(OR(L61="",L61="در انتظار"),"",IF(Q61="",TODAY(),Q61))</f>
         <v/>
       </c>
@@ -1985,129 +2779,179 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="17" t="inlineStr">
+      <c r="A1" s="49" t="inlineStr">
         <is>
           <t>تست‌های آزمایشگاهی (پایه، اسیلوسکوپ و زمان‌بندی دقیق — جدا از تست عملی)</t>
         </is>
       </c>
+      <c r="B1" s="50" t="n"/>
+      <c r="C1" s="50" t="n"/>
+      <c r="D1" s="50" t="n"/>
+      <c r="E1" s="50" t="n"/>
+      <c r="F1" s="50" t="n"/>
+      <c r="G1" s="50" t="n"/>
+      <c r="H1" s="50" t="n"/>
+      <c r="I1" s="50" t="n"/>
+      <c r="J1" s="50" t="n"/>
+      <c r="K1" s="50" t="n"/>
+      <c r="L1" s="50" t="n"/>
+      <c r="M1" s="50" t="n"/>
+      <c r="N1" s="50" t="n"/>
+      <c r="O1" s="50" t="n"/>
+      <c r="P1" s="50" t="n"/>
+      <c r="Q1" s="50" t="n"/>
     </row>
     <row r="2" ht="42" customHeight="1">
-      <c r="A2" s="44" t="inlineStr">
+      <c r="A2" s="66" t="inlineStr">
         <is>
           <t>این شیت جدا از تست عملی است: اندازه‌گیری روی پایه‌ها، اسیلوسکوپ و تلرانس‌های دقیق میلی‌ثانیه/میکروثانیه. برای بررسی عملکرد واقعی دستگاه لازم نیست؛ برای اعتبارسنجی دقیق سخت‌افزار و زمان‌بندی‌هاست.</t>
         </is>
       </c>
-    </row>
-    <row r="3"/>
+      <c r="B2" s="50" t="n"/>
+      <c r="C2" s="50" t="n"/>
+      <c r="D2" s="50" t="n"/>
+      <c r="E2" s="50" t="n"/>
+      <c r="F2" s="50" t="n"/>
+      <c r="G2" s="50" t="n"/>
+      <c r="H2" s="50" t="n"/>
+      <c r="I2" s="50" t="n"/>
+      <c r="J2" s="50" t="n"/>
+      <c r="K2" s="50" t="n"/>
+      <c r="L2" s="50" t="n"/>
+      <c r="M2" s="50" t="n"/>
+      <c r="N2" s="50" t="n"/>
+      <c r="O2" s="50" t="n"/>
+      <c r="P2" s="50" t="n"/>
+      <c r="Q2" s="50" t="n"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="50" t="n"/>
+      <c r="B3" s="50" t="n"/>
+      <c r="C3" s="50" t="n"/>
+      <c r="D3" s="50" t="n"/>
+      <c r="E3" s="50" t="n"/>
+      <c r="F3" s="50" t="n"/>
+      <c r="G3" s="50" t="n"/>
+      <c r="H3" s="50" t="n"/>
+      <c r="I3" s="50" t="n"/>
+      <c r="J3" s="50" t="n"/>
+      <c r="K3" s="50" t="n"/>
+      <c r="L3" s="50" t="n"/>
+      <c r="M3" s="50" t="n"/>
+      <c r="N3" s="50" t="n"/>
+      <c r="O3" s="50" t="n"/>
+      <c r="P3" s="50" t="n"/>
+      <c r="Q3" s="50" t="n"/>
+    </row>
     <row r="4" ht="30" customHeight="1">
-      <c r="A4" s="16" t="inlineStr">
+      <c r="A4" s="47" t="inlineStr">
         <is>
           <t>شناسه</t>
         </is>
       </c>
-      <c r="B4" s="16" t="inlineStr">
+      <c r="B4" s="47" t="inlineStr">
         <is>
           <t>دسته</t>
         </is>
       </c>
-      <c r="C4" s="16" t="inlineStr">
+      <c r="C4" s="47" t="inlineStr">
         <is>
           <t>اولویت</t>
         </is>
       </c>
-      <c r="D4" s="16" t="inlineStr">
+      <c r="D4" s="47" t="inlineStr">
         <is>
           <t>پیش‌شرط</t>
         </is>
       </c>
-      <c r="E4" s="16" t="inlineStr">
+      <c r="E4" s="47" t="inlineStr">
         <is>
           <t>روش اجرای دقیق</t>
         </is>
       </c>
-      <c r="F4" s="16" t="inlineStr">
+      <c r="F4" s="47" t="inlineStr">
         <is>
           <t>ورودی‌ها / شرایط</t>
         </is>
       </c>
-      <c r="G4" s="16" t="inlineStr">
+      <c r="G4" s="47" t="inlineStr">
         <is>
           <t>مدت مشاهده</t>
         </is>
       </c>
-      <c r="H4" s="16" t="inlineStr">
+      <c r="H4" s="47" t="inlineStr">
         <is>
           <t>رفتار مورد انتظار</t>
         </is>
       </c>
-      <c r="I4" s="16" t="inlineStr">
+      <c r="I4" s="47" t="inlineStr">
         <is>
           <t>وضعیت حفظ / latch</t>
         </is>
       </c>
-      <c r="J4" s="16" t="inlineStr">
+      <c r="J4" s="47" t="inlineStr">
         <is>
           <t>معیار قبولی</t>
         </is>
       </c>
-      <c r="K4" s="16" t="inlineStr">
+      <c r="K4" s="47" t="inlineStr">
         <is>
           <t>نتیجهٔ واقعی / اندازه‌گیری</t>
         </is>
       </c>
-      <c r="L4" s="16" t="inlineStr">
+      <c r="L4" s="47" t="inlineStr">
         <is>
           <t>وضعیت</t>
         </is>
       </c>
-      <c r="M4" s="16" t="inlineStr">
+      <c r="M4" s="47" t="inlineStr">
         <is>
           <t>شرح ایراد / تفاوت</t>
         </is>
       </c>
-      <c r="N4" s="16" t="inlineStr">
+      <c r="N4" s="47" t="inlineStr">
         <is>
           <t>مدرک تست / scope</t>
         </is>
       </c>
-      <c r="O4" s="16" t="inlineStr">
+      <c r="O4" s="47" t="inlineStr">
         <is>
           <t>commit</t>
         </is>
       </c>
-      <c r="P4" s="16" t="inlineStr">
+      <c r="P4" s="47" t="inlineStr">
         <is>
           <t>نام تست‌کننده</t>
         </is>
       </c>
-      <c r="Q4" s="16" t="inlineStr">
+      <c r="Q4" s="47" t="inlineStr">
         <is>
           <t>تاریخ</t>
         </is>
       </c>
     </row>
     <row r="5" ht="54" customHeight="1">
-      <c r="A5" s="19" t="inlineStr">
+      <c r="A5" s="52" t="inlineStr">
         <is>
           <t>CL-012</t>
         </is>
       </c>
-      <c r="B5" s="25" t="inlineStr">
+      <c r="B5" s="59" t="inlineStr">
         <is>
           <t>idle شدن شارژر هنگام ریست</t>
         </is>
       </c>
-      <c r="C5" s="26" t="inlineStr">
+      <c r="C5" s="60" t="inlineStr">
         <is>
           <t>بالا</t>
         </is>
       </c>
-      <c r="D5" s="25" t="inlineStr">
+      <c r="D5" s="59" t="inlineStr">
         <is>
           <t>جدول فعال، شارژ در جریان</t>
         </is>
       </c>
-      <c r="E5" s="25" t="inlineStr">
+      <c r="E5" s="59" t="inlineStr">
         <is>
           <t>گام ۱: یک جدول فعال کن و شارژ را در حالت BULK راه بینداز تا کانال در حال شارژ PWM داشته باشد.
 گام ۲: اسیلوسکوپ را روی گیت همان کانال بگذار.
@@ -2115,179 +2959,499 @@
 گام ۴: روی اسکوپ ببین که پیش از ریست، duty اول صفر شده و شارژر idle شده باشد؛ ریست نباید وسط پالس اتفاق بیفتد.</t>
         </is>
       </c>
-      <c r="F5" s="27" t="inlineStr">
+      <c r="F5" s="61" t="inlineStr">
         <is>
           <t>درخواست ریست با PWM فعال</t>
         </is>
       </c>
-      <c r="G5" s="27" t="inlineStr">
+      <c r="G5" s="61" t="inlineStr">
         <is>
           <t>یک تبادل</t>
         </is>
       </c>
-      <c r="H5" s="25" t="inlineStr">
+      <c r="H5" s="59" t="inlineStr">
         <is>
           <t>قبل از ریست هر دو دیوتی صفر و شارژر idle می‌شود</t>
         </is>
       </c>
-      <c r="I5" s="25" t="inlineStr">
+      <c r="I5" s="59" t="inlineStr">
         <is>
           <t>بدون latch</t>
         </is>
       </c>
-      <c r="J5" s="25" t="inlineStr">
+      <c r="J5" s="59" t="inlineStr">
         <is>
           <t>اسیلوسکوپ روی گیت: صفر پیش از ریست</t>
         </is>
       </c>
-      <c r="K5" s="25" t="inlineStr">
+      <c r="K5" s="59" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="L5" s="23" t="inlineStr">
+      <c r="L5" s="57" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="M5" s="25" t="n"/>
-      <c r="N5" s="25" t="inlineStr">
+      <c r="M5" s="59" t="n"/>
+      <c r="N5" s="59" t="inlineStr">
         <is>
           <t>TESTER: fill</t>
         </is>
       </c>
-      <c r="O5" s="27" t="inlineStr">
+      <c r="O5" s="61" t="inlineStr">
         <is>
           <t>TESTER: fill</t>
         </is>
       </c>
-      <c r="P5" s="27" t="inlineStr">
+      <c r="P5" s="61" t="inlineStr">
         <is>
           <t>TESTER: fill</t>
         </is>
       </c>
-      <c r="Q5" s="28" t="inlineStr">
+      <c r="Q5" s="62" t="inlineStr">
         <is>
           <t>2026-10-05</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="Q6" s="32">
+      <c r="A6" s="50" t="n"/>
+      <c r="B6" s="50" t="n"/>
+      <c r="C6" s="50" t="n"/>
+      <c r="D6" s="50" t="n"/>
+      <c r="E6" s="50" t="n"/>
+      <c r="F6" s="50" t="n"/>
+      <c r="G6" s="50" t="n"/>
+      <c r="H6" s="50" t="n"/>
+      <c r="I6" s="50" t="n"/>
+      <c r="J6" s="50" t="n"/>
+      <c r="K6" s="50" t="n"/>
+      <c r="L6" s="50" t="n"/>
+      <c r="M6" s="50" t="n"/>
+      <c r="N6" s="50" t="n"/>
+      <c r="O6" s="50" t="n"/>
+      <c r="P6" s="50" t="n"/>
+      <c r="Q6" s="65">
         <f>IF(OR(L6="",L6="در انتظار"),"",IF(Q6="",TODAY(),Q6))</f>
         <v/>
       </c>
     </row>
     <row r="7">
-      <c r="Q7" s="32">
+      <c r="A7" s="50" t="n"/>
+      <c r="B7" s="50" t="n"/>
+      <c r="C7" s="50" t="n"/>
+      <c r="D7" s="50" t="n"/>
+      <c r="E7" s="50" t="n"/>
+      <c r="F7" s="50" t="n"/>
+      <c r="G7" s="50" t="n"/>
+      <c r="H7" s="50" t="n"/>
+      <c r="I7" s="50" t="n"/>
+      <c r="J7" s="50" t="n"/>
+      <c r="K7" s="50" t="n"/>
+      <c r="L7" s="50" t="n"/>
+      <c r="M7" s="50" t="n"/>
+      <c r="N7" s="50" t="n"/>
+      <c r="O7" s="50" t="n"/>
+      <c r="P7" s="50" t="n"/>
+      <c r="Q7" s="65">
         <f>IF(OR(L7="",L7="در انتظار"),"",IF(Q7="",TODAY(),Q7))</f>
         <v/>
       </c>
     </row>
     <row r="8">
-      <c r="Q8" s="32">
+      <c r="A8" s="50" t="n"/>
+      <c r="B8" s="50" t="n"/>
+      <c r="C8" s="50" t="n"/>
+      <c r="D8" s="50" t="n"/>
+      <c r="E8" s="50" t="n"/>
+      <c r="F8" s="50" t="n"/>
+      <c r="G8" s="50" t="n"/>
+      <c r="H8" s="50" t="n"/>
+      <c r="I8" s="50" t="n"/>
+      <c r="J8" s="50" t="n"/>
+      <c r="K8" s="50" t="n"/>
+      <c r="L8" s="50" t="n"/>
+      <c r="M8" s="50" t="n"/>
+      <c r="N8" s="50" t="n"/>
+      <c r="O8" s="50" t="n"/>
+      <c r="P8" s="50" t="n"/>
+      <c r="Q8" s="65">
         <f>IF(OR(L8="",L8="در انتظار"),"",IF(Q8="",TODAY(),Q8))</f>
         <v/>
       </c>
     </row>
     <row r="9">
-      <c r="Q9" s="32">
+      <c r="A9" s="50" t="n"/>
+      <c r="B9" s="50" t="n"/>
+      <c r="C9" s="50" t="n"/>
+      <c r="D9" s="50" t="n"/>
+      <c r="E9" s="50" t="n"/>
+      <c r="F9" s="50" t="n"/>
+      <c r="G9" s="50" t="n"/>
+      <c r="H9" s="50" t="n"/>
+      <c r="I9" s="50" t="n"/>
+      <c r="J9" s="50" t="n"/>
+      <c r="K9" s="50" t="n"/>
+      <c r="L9" s="50" t="n"/>
+      <c r="M9" s="50" t="n"/>
+      <c r="N9" s="50" t="n"/>
+      <c r="O9" s="50" t="n"/>
+      <c r="P9" s="50" t="n"/>
+      <c r="Q9" s="65">
         <f>IF(OR(L9="",L9="در انتظار"),"",IF(Q9="",TODAY(),Q9))</f>
         <v/>
       </c>
     </row>
     <row r="10">
-      <c r="Q10" s="32">
+      <c r="A10" s="50" t="n"/>
+      <c r="B10" s="50" t="n"/>
+      <c r="C10" s="50" t="n"/>
+      <c r="D10" s="50" t="n"/>
+      <c r="E10" s="50" t="n"/>
+      <c r="F10" s="50" t="n"/>
+      <c r="G10" s="50" t="n"/>
+      <c r="H10" s="50" t="n"/>
+      <c r="I10" s="50" t="n"/>
+      <c r="J10" s="50" t="n"/>
+      <c r="K10" s="50" t="n"/>
+      <c r="L10" s="50" t="n"/>
+      <c r="M10" s="50" t="n"/>
+      <c r="N10" s="50" t="n"/>
+      <c r="O10" s="50" t="n"/>
+      <c r="P10" s="50" t="n"/>
+      <c r="Q10" s="65">
         <f>IF(OR(L10="",L10="در انتظار"),"",IF(Q10="",TODAY(),Q10))</f>
         <v/>
       </c>
     </row>
     <row r="11">
-      <c r="Q11" s="32">
+      <c r="A11" s="50" t="n"/>
+      <c r="B11" s="50" t="n"/>
+      <c r="C11" s="50" t="n"/>
+      <c r="D11" s="50" t="n"/>
+      <c r="E11" s="50" t="n"/>
+      <c r="F11" s="50" t="n"/>
+      <c r="G11" s="50" t="n"/>
+      <c r="H11" s="50" t="n"/>
+      <c r="I11" s="50" t="n"/>
+      <c r="J11" s="50" t="n"/>
+      <c r="K11" s="50" t="n"/>
+      <c r="L11" s="50" t="n"/>
+      <c r="M11" s="50" t="n"/>
+      <c r="N11" s="50" t="n"/>
+      <c r="O11" s="50" t="n"/>
+      <c r="P11" s="50" t="n"/>
+      <c r="Q11" s="65">
         <f>IF(OR(L11="",L11="در انتظار"),"",IF(Q11="",TODAY(),Q11))</f>
         <v/>
       </c>
     </row>
     <row r="12">
-      <c r="Q12" s="32">
+      <c r="A12" s="50" t="n"/>
+      <c r="B12" s="50" t="n"/>
+      <c r="C12" s="50" t="n"/>
+      <c r="D12" s="50" t="n"/>
+      <c r="E12" s="50" t="n"/>
+      <c r="F12" s="50" t="n"/>
+      <c r="G12" s="50" t="n"/>
+      <c r="H12" s="50" t="n"/>
+      <c r="I12" s="50" t="n"/>
+      <c r="J12" s="50" t="n"/>
+      <c r="K12" s="50" t="n"/>
+      <c r="L12" s="50" t="n"/>
+      <c r="M12" s="50" t="n"/>
+      <c r="N12" s="50" t="n"/>
+      <c r="O12" s="50" t="n"/>
+      <c r="P12" s="50" t="n"/>
+      <c r="Q12" s="65">
         <f>IF(OR(L12="",L12="در انتظار"),"",IF(Q12="",TODAY(),Q12))</f>
         <v/>
       </c>
     </row>
     <row r="13">
-      <c r="Q13" s="32">
+      <c r="A13" s="50" t="n"/>
+      <c r="B13" s="50" t="n"/>
+      <c r="C13" s="50" t="n"/>
+      <c r="D13" s="50" t="n"/>
+      <c r="E13" s="50" t="n"/>
+      <c r="F13" s="50" t="n"/>
+      <c r="G13" s="50" t="n"/>
+      <c r="H13" s="50" t="n"/>
+      <c r="I13" s="50" t="n"/>
+      <c r="J13" s="50" t="n"/>
+      <c r="K13" s="50" t="n"/>
+      <c r="L13" s="50" t="n"/>
+      <c r="M13" s="50" t="n"/>
+      <c r="N13" s="50" t="n"/>
+      <c r="O13" s="50" t="n"/>
+      <c r="P13" s="50" t="n"/>
+      <c r="Q13" s="65">
         <f>IF(OR(L13="",L13="در انتظار"),"",IF(Q13="",TODAY(),Q13))</f>
         <v/>
       </c>
     </row>
     <row r="14">
-      <c r="Q14" s="32">
+      <c r="A14" s="50" t="n"/>
+      <c r="B14" s="50" t="n"/>
+      <c r="C14" s="50" t="n"/>
+      <c r="D14" s="50" t="n"/>
+      <c r="E14" s="50" t="n"/>
+      <c r="F14" s="50" t="n"/>
+      <c r="G14" s="50" t="n"/>
+      <c r="H14" s="50" t="n"/>
+      <c r="I14" s="50" t="n"/>
+      <c r="J14" s="50" t="n"/>
+      <c r="K14" s="50" t="n"/>
+      <c r="L14" s="50" t="n"/>
+      <c r="M14" s="50" t="n"/>
+      <c r="N14" s="50" t="n"/>
+      <c r="O14" s="50" t="n"/>
+      <c r="P14" s="50" t="n"/>
+      <c r="Q14" s="65">
         <f>IF(OR(L14="",L14="در انتظار"),"",IF(Q14="",TODAY(),Q14))</f>
         <v/>
       </c>
     </row>
     <row r="15">
-      <c r="Q15" s="32">
+      <c r="A15" s="50" t="n"/>
+      <c r="B15" s="50" t="n"/>
+      <c r="C15" s="50" t="n"/>
+      <c r="D15" s="50" t="n"/>
+      <c r="E15" s="50" t="n"/>
+      <c r="F15" s="50" t="n"/>
+      <c r="G15" s="50" t="n"/>
+      <c r="H15" s="50" t="n"/>
+      <c r="I15" s="50" t="n"/>
+      <c r="J15" s="50" t="n"/>
+      <c r="K15" s="50" t="n"/>
+      <c r="L15" s="50" t="n"/>
+      <c r="M15" s="50" t="n"/>
+      <c r="N15" s="50" t="n"/>
+      <c r="O15" s="50" t="n"/>
+      <c r="P15" s="50" t="n"/>
+      <c r="Q15" s="65">
         <f>IF(OR(L15="",L15="در انتظار"),"",IF(Q15="",TODAY(),Q15))</f>
         <v/>
       </c>
     </row>
     <row r="16">
-      <c r="Q16" s="32">
+      <c r="A16" s="50" t="n"/>
+      <c r="B16" s="50" t="n"/>
+      <c r="C16" s="50" t="n"/>
+      <c r="D16" s="50" t="n"/>
+      <c r="E16" s="50" t="n"/>
+      <c r="F16" s="50" t="n"/>
+      <c r="G16" s="50" t="n"/>
+      <c r="H16" s="50" t="n"/>
+      <c r="I16" s="50" t="n"/>
+      <c r="J16" s="50" t="n"/>
+      <c r="K16" s="50" t="n"/>
+      <c r="L16" s="50" t="n"/>
+      <c r="M16" s="50" t="n"/>
+      <c r="N16" s="50" t="n"/>
+      <c r="O16" s="50" t="n"/>
+      <c r="P16" s="50" t="n"/>
+      <c r="Q16" s="65">
         <f>IF(OR(L16="",L16="در انتظار"),"",IF(Q16="",TODAY(),Q16))</f>
         <v/>
       </c>
     </row>
     <row r="17">
-      <c r="Q17" s="32">
+      <c r="A17" s="50" t="n"/>
+      <c r="B17" s="50" t="n"/>
+      <c r="C17" s="50" t="n"/>
+      <c r="D17" s="50" t="n"/>
+      <c r="E17" s="50" t="n"/>
+      <c r="F17" s="50" t="n"/>
+      <c r="G17" s="50" t="n"/>
+      <c r="H17" s="50" t="n"/>
+      <c r="I17" s="50" t="n"/>
+      <c r="J17" s="50" t="n"/>
+      <c r="K17" s="50" t="n"/>
+      <c r="L17" s="50" t="n"/>
+      <c r="M17" s="50" t="n"/>
+      <c r="N17" s="50" t="n"/>
+      <c r="O17" s="50" t="n"/>
+      <c r="P17" s="50" t="n"/>
+      <c r="Q17" s="65">
         <f>IF(OR(L17="",L17="در انتظار"),"",IF(Q17="",TODAY(),Q17))</f>
         <v/>
       </c>
     </row>
     <row r="18">
-      <c r="Q18" s="32">
+      <c r="A18" s="50" t="n"/>
+      <c r="B18" s="50" t="n"/>
+      <c r="C18" s="50" t="n"/>
+      <c r="D18" s="50" t="n"/>
+      <c r="E18" s="50" t="n"/>
+      <c r="F18" s="50" t="n"/>
+      <c r="G18" s="50" t="n"/>
+      <c r="H18" s="50" t="n"/>
+      <c r="I18" s="50" t="n"/>
+      <c r="J18" s="50" t="n"/>
+      <c r="K18" s="50" t="n"/>
+      <c r="L18" s="50" t="n"/>
+      <c r="M18" s="50" t="n"/>
+      <c r="N18" s="50" t="n"/>
+      <c r="O18" s="50" t="n"/>
+      <c r="P18" s="50" t="n"/>
+      <c r="Q18" s="65">
         <f>IF(OR(L18="",L18="در انتظار"),"",IF(Q18="",TODAY(),Q18))</f>
         <v/>
       </c>
     </row>
     <row r="19">
-      <c r="Q19" s="32">
+      <c r="A19" s="50" t="n"/>
+      <c r="B19" s="50" t="n"/>
+      <c r="C19" s="50" t="n"/>
+      <c r="D19" s="50" t="n"/>
+      <c r="E19" s="50" t="n"/>
+      <c r="F19" s="50" t="n"/>
+      <c r="G19" s="50" t="n"/>
+      <c r="H19" s="50" t="n"/>
+      <c r="I19" s="50" t="n"/>
+      <c r="J19" s="50" t="n"/>
+      <c r="K19" s="50" t="n"/>
+      <c r="L19" s="50" t="n"/>
+      <c r="M19" s="50" t="n"/>
+      <c r="N19" s="50" t="n"/>
+      <c r="O19" s="50" t="n"/>
+      <c r="P19" s="50" t="n"/>
+      <c r="Q19" s="65">
         <f>IF(OR(L19="",L19="در انتظار"),"",IF(Q19="",TODAY(),Q19))</f>
         <v/>
       </c>
     </row>
     <row r="20">
-      <c r="Q20" s="32">
+      <c r="A20" s="50" t="n"/>
+      <c r="B20" s="50" t="n"/>
+      <c r="C20" s="50" t="n"/>
+      <c r="D20" s="50" t="n"/>
+      <c r="E20" s="50" t="n"/>
+      <c r="F20" s="50" t="n"/>
+      <c r="G20" s="50" t="n"/>
+      <c r="H20" s="50" t="n"/>
+      <c r="I20" s="50" t="n"/>
+      <c r="J20" s="50" t="n"/>
+      <c r="K20" s="50" t="n"/>
+      <c r="L20" s="50" t="n"/>
+      <c r="M20" s="50" t="n"/>
+      <c r="N20" s="50" t="n"/>
+      <c r="O20" s="50" t="n"/>
+      <c r="P20" s="50" t="n"/>
+      <c r="Q20" s="65">
         <f>IF(OR(L20="",L20="در انتظار"),"",IF(Q20="",TODAY(),Q20))</f>
         <v/>
       </c>
     </row>
     <row r="21">
-      <c r="Q21" s="32">
+      <c r="A21" s="50" t="n"/>
+      <c r="B21" s="50" t="n"/>
+      <c r="C21" s="50" t="n"/>
+      <c r="D21" s="50" t="n"/>
+      <c r="E21" s="50" t="n"/>
+      <c r="F21" s="50" t="n"/>
+      <c r="G21" s="50" t="n"/>
+      <c r="H21" s="50" t="n"/>
+      <c r="I21" s="50" t="n"/>
+      <c r="J21" s="50" t="n"/>
+      <c r="K21" s="50" t="n"/>
+      <c r="L21" s="50" t="n"/>
+      <c r="M21" s="50" t="n"/>
+      <c r="N21" s="50" t="n"/>
+      <c r="O21" s="50" t="n"/>
+      <c r="P21" s="50" t="n"/>
+      <c r="Q21" s="65">
         <f>IF(OR(L21="",L21="در انتظار"),"",IF(Q21="",TODAY(),Q21))</f>
         <v/>
       </c>
     </row>
     <row r="22">
-      <c r="Q22" s="32">
+      <c r="A22" s="50" t="n"/>
+      <c r="B22" s="50" t="n"/>
+      <c r="C22" s="50" t="n"/>
+      <c r="D22" s="50" t="n"/>
+      <c r="E22" s="50" t="n"/>
+      <c r="F22" s="50" t="n"/>
+      <c r="G22" s="50" t="n"/>
+      <c r="H22" s="50" t="n"/>
+      <c r="I22" s="50" t="n"/>
+      <c r="J22" s="50" t="n"/>
+      <c r="K22" s="50" t="n"/>
+      <c r="L22" s="50" t="n"/>
+      <c r="M22" s="50" t="n"/>
+      <c r="N22" s="50" t="n"/>
+      <c r="O22" s="50" t="n"/>
+      <c r="P22" s="50" t="n"/>
+      <c r="Q22" s="65">
         <f>IF(OR(L22="",L22="در انتظار"),"",IF(Q22="",TODAY(),Q22))</f>
         <v/>
       </c>
     </row>
     <row r="23">
-      <c r="Q23" s="32">
+      <c r="A23" s="50" t="n"/>
+      <c r="B23" s="50" t="n"/>
+      <c r="C23" s="50" t="n"/>
+      <c r="D23" s="50" t="n"/>
+      <c r="E23" s="50" t="n"/>
+      <c r="F23" s="50" t="n"/>
+      <c r="G23" s="50" t="n"/>
+      <c r="H23" s="50" t="n"/>
+      <c r="I23" s="50" t="n"/>
+      <c r="J23" s="50" t="n"/>
+      <c r="K23" s="50" t="n"/>
+      <c r="L23" s="50" t="n"/>
+      <c r="M23" s="50" t="n"/>
+      <c r="N23" s="50" t="n"/>
+      <c r="O23" s="50" t="n"/>
+      <c r="P23" s="50" t="n"/>
+      <c r="Q23" s="65">
         <f>IF(OR(L23="",L23="در انتظار"),"",IF(Q23="",TODAY(),Q23))</f>
         <v/>
       </c>
     </row>
     <row r="24">
-      <c r="Q24" s="32">
+      <c r="A24" s="50" t="n"/>
+      <c r="B24" s="50" t="n"/>
+      <c r="C24" s="50" t="n"/>
+      <c r="D24" s="50" t="n"/>
+      <c r="E24" s="50" t="n"/>
+      <c r="F24" s="50" t="n"/>
+      <c r="G24" s="50" t="n"/>
+      <c r="H24" s="50" t="n"/>
+      <c r="I24" s="50" t="n"/>
+      <c r="J24" s="50" t="n"/>
+      <c r="K24" s="50" t="n"/>
+      <c r="L24" s="50" t="n"/>
+      <c r="M24" s="50" t="n"/>
+      <c r="N24" s="50" t="n"/>
+      <c r="O24" s="50" t="n"/>
+      <c r="P24" s="50" t="n"/>
+      <c r="Q24" s="65">
         <f>IF(OR(L24="",L24="در انتظار"),"",IF(Q24="",TODAY(),Q24))</f>
         <v/>
       </c>
     </row>
     <row r="25">
-      <c r="Q25" s="32">
+      <c r="A25" s="50" t="n"/>
+      <c r="B25" s="50" t="n"/>
+      <c r="C25" s="50" t="n"/>
+      <c r="D25" s="50" t="n"/>
+      <c r="E25" s="50" t="n"/>
+      <c r="F25" s="50" t="n"/>
+      <c r="G25" s="50" t="n"/>
+      <c r="H25" s="50" t="n"/>
+      <c r="I25" s="50" t="n"/>
+      <c r="J25" s="50" t="n"/>
+      <c r="K25" s="50" t="n"/>
+      <c r="L25" s="50" t="n"/>
+      <c r="M25" s="50" t="n"/>
+      <c r="N25" s="50" t="n"/>
+      <c r="O25" s="50" t="n"/>
+      <c r="P25" s="50" t="n"/>
+      <c r="Q25" s="65">
         <f>IF(OR(L25="",L25="در انتظار"),"",IF(Q25="",TODAY(),Q25))</f>
         <v/>
       </c>
@@ -2322,228 +3486,234 @@
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
-      <c r="A1" s="16" t="inlineStr">
+      <c r="A1" s="47" t="inlineStr">
         <is>
           <t>مرجع سریع سناریوها و ثابت‌های ماژول CalLut</t>
         </is>
       </c>
-      <c r="B1" s="16" t="n"/>
-      <c r="C1" s="16" t="n"/>
-      <c r="D1" s="16" t="n"/>
-      <c r="E1" s="16" t="n"/>
-    </row>
-    <row r="2"/>
+      <c r="B1" s="47" t="n"/>
+      <c r="C1" s="47" t="n"/>
+      <c r="D1" s="47" t="n"/>
+      <c r="E1" s="47" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="50" t="n"/>
+      <c r="B2" s="50" t="n"/>
+      <c r="C2" s="50" t="n"/>
+      <c r="D2" s="50" t="n"/>
+      <c r="E2" s="50" t="n"/>
+    </row>
     <row r="3">
-      <c r="A3" s="33" t="inlineStr">
+      <c r="A3" s="67" t="inlineStr">
         <is>
           <t>موضوع</t>
         </is>
       </c>
-      <c r="B3" s="33" t="inlineStr">
+      <c r="B3" s="67" t="inlineStr">
         <is>
           <t>شرط / مقدار</t>
         </is>
       </c>
-      <c r="C3" s="33" t="inlineStr">
+      <c r="C3" s="67" t="inlineStr">
         <is>
           <t>رفتار مورد انتظار</t>
         </is>
       </c>
-      <c r="D3" s="33" t="inlineStr">
+      <c r="D3" s="67" t="inlineStr">
         <is>
           <t>ثابت / محل کد</t>
         </is>
       </c>
-      <c r="E3" s="33" t="inlineStr">
+      <c r="E3" s="67" t="inlineStr">
         <is>
           <t>توضیح</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="34" t="inlineStr">
+      <c r="A4" s="68" t="inlineStr">
         <is>
           <t>صفحه‌های اختصاصی</t>
         </is>
       </c>
-      <c r="B4" s="34" t="inlineStr">
+      <c r="B4" s="68" t="inlineStr">
         <is>
           <t>0x0800F000 و 0x0800F400</t>
         </is>
       </c>
-      <c r="C4" s="34" t="inlineStr">
+      <c r="C4" s="68" t="inlineStr">
         <is>
           <t>پینگ‌پنگ امن در برابر قطع برق</t>
         </is>
       </c>
-      <c r="D4" s="34" t="inlineStr">
+      <c r="D4" s="68" t="inlineStr">
         <is>
           <t>CAL_LUT_PAGE_A_ADDR / CAL_LUT_PAGE_B_ADDR</t>
         </is>
       </c>
-      <c r="E4" s="34" t="inlineStr">
+      <c r="E4" s="68" t="inlineStr">
         <is>
           <t>پایین‌تر از صفحه‌های پارامتر</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="34" t="inlineStr">
+      <c r="A5" s="68" t="inlineStr">
         <is>
           <t>مجیک و نسخه</t>
         </is>
       </c>
-      <c r="B5" s="34" t="inlineStr">
+      <c r="B5" s="68" t="inlineStr">
         <is>
           <t>0x434C5554 («CLUT») و ۱</t>
         </is>
       </c>
-      <c r="C5" s="34" t="inlineStr">
+      <c r="C5" s="68" t="inlineStr">
         <is>
           <t>ناهمخوانی = بازگشت به جدول کامپایل‌شده</t>
         </is>
       </c>
-      <c r="D5" s="34" t="inlineStr">
+      <c r="D5" s="68" t="inlineStr">
         <is>
           <t>CAL_LUT_MAGIC / CAL_LUT_VERSION</t>
         </is>
       </c>
-      <c r="E5" s="34" t="inlineStr">
+      <c r="E5" s="68" t="inlineStr">
         <is>
           <t>هرگز نیم‌ارتقای بی‌صدا</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="34" t="inlineStr">
+      <c r="A6" s="68" t="inlineStr">
         <is>
           <t>سقف نقاط</t>
         </is>
       </c>
-      <c r="B6" s="34" t="inlineStr">
+      <c r="B6" s="68" t="inlineStr">
         <is>
           <t>۲ تا ۲۴ نقطه در هر کانال</t>
         </is>
       </c>
-      <c r="C6" s="34" t="inlineStr">
+      <c r="C6" s="68" t="inlineStr">
         <is>
           <t>بیرون از بازه = رد با status=2</t>
         </is>
       </c>
-      <c r="D6" s="34" t="inlineStr">
+      <c r="D6" s="68" t="inlineStr">
         <is>
           <t>CAL_LUT_POINTS_MIN / CAL_LUT_POINTS_MAX</t>
         </is>
       </c>
-      <c r="E6" s="34" t="inlineStr">
+      <c r="E6" s="68" t="inlineStr">
         <is>
           <t>۲۴×۲×۲×۴ = ۳۸۴ بایت رکورد</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="34" t="inlineStr">
+      <c r="A7" s="68" t="inlineStr">
         <is>
           <t>کدهای وضعیت</t>
         </is>
       </c>
-      <c r="B7" s="34" t="inlineStr">
+      <c r="B7" s="68" t="inlineStr">
         <is>
           <t>۰ تا ۷</t>
         </is>
       </c>
-      <c r="C7" s="34" t="inlineStr">
+      <c r="C7" s="68" t="inlineStr">
         <is>
           <t>هر خطا دلیل خودش را در LUT_ACK می‌گوید</t>
         </is>
       </c>
-      <c r="D7" s="34" t="inlineStr">
+      <c r="D7" s="68" t="inlineStr">
         <is>
           <t>CAL_LUT_ST_*</t>
         </is>
       </c>
-      <c r="E7" s="34" t="inlineStr">
+      <c r="E7" s="68" t="inlineStr">
         <is>
           <t>۰=OK، ۶=CRC، ۷=فلش</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="34" t="inlineStr">
+      <c r="A8" s="68" t="inlineStr">
         <is>
           <t>دست‌دادن</t>
         </is>
       </c>
-      <c r="B8" s="34" t="inlineStr">
+      <c r="B8" s="68" t="inlineStr">
         <is>
           <t>BEGIN → CHUNK → COMMIT → ACK → RESET</t>
         </is>
       </c>
-      <c r="C8" s="34" t="inlineStr">
+      <c r="C8" s="68" t="inlineStr">
         <is>
           <t>ریست فقط با برابری دو CRC32</t>
         </is>
       </c>
-      <c r="D8" s="43" t="inlineStr">
+      <c r="D8" s="69" t="inlineStr">
         <is>
           <t>cal_lut.c</t>
         </is>
       </c>
-      <c r="E8" s="34" t="inlineStr">
+      <c r="E8" s="68" t="inlineStr">
         <is>
           <t>پنل CRC را می‌سازد، برد بازخوانی می‌کند</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="34" t="inlineStr">
+      <c r="A9" s="68" t="inlineStr">
         <is>
           <t>پشتیبان</t>
         </is>
       </c>
-      <c r="B9" s="34" t="inlineStr">
+      <c r="B9" s="68" t="inlineStr">
         <is>
           <t>جدول‌های فلش (CalLut) و خط گین و آفست</t>
         </is>
       </c>
-      <c r="C9" s="34" t="inlineStr">
+      <c r="C9" s="68" t="inlineStr">
         <is>
           <t>رکورد نامعتبر = جدول کامپایل‌شده</t>
         </is>
       </c>
-      <c r="D9" s="34" t="inlineStr">
+      <c r="D9" s="68" t="inlineStr">
         <is>
           <t>CAL_CURRENT*_LUT_ENABLE</t>
         </is>
       </c>
-      <c r="E9" s="34" t="inlineStr">
+      <c r="E9" s="68" t="inlineStr">
         <is>
           <t>روش قبلی حذف نشده</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="34" t="inlineStr">
+      <c r="A10" s="68" t="inlineStr">
         <is>
           <t>reset grant و flush NVM</t>
         </is>
       </c>
-      <c r="B10" s="34" t="inlineStr">
+      <c r="B10" s="68" t="inlineStr">
         <is>
           <t>magic + commit grant؛ flush NVM پیش از arm</t>
         </is>
       </c>
-      <c r="C10" s="34" t="inlineStr">
+      <c r="C10" s="68" t="inlineStr">
         <is>
           <t>flush failure = no reset؛ success = reset one-shot</t>
         </is>
       </c>
-      <c r="D10" s="43" t="inlineStr">
+      <c r="D10" s="69" t="inlineStr">
         <is>
           <t>cal_lut.c / esp_link.c / esp_link_nvm.c</t>
         </is>
       </c>
-      <c r="E10" s="34" t="inlineStr">
+      <c r="E10" s="68" t="inlineStr">
         <is>
           <t>zero-point commit حتی بدون active table معتبر است</t>
         </is>
@@ -2584,93 +3754,105 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="35" t="inlineStr">
+      <c r="A1" s="70" t="inlineStr">
         <is>
           <t>ثبت ایرادهای مشاهده‌شده — ماژول CalLut</t>
         </is>
       </c>
+      <c r="B1" s="50" t="n"/>
+      <c r="C1" s="50" t="n"/>
+      <c r="D1" s="50" t="n"/>
+      <c r="E1" s="50" t="n"/>
+      <c r="F1" s="50" t="n"/>
+      <c r="G1" s="50" t="n"/>
+      <c r="H1" s="50" t="n"/>
+      <c r="I1" s="50" t="n"/>
+      <c r="J1" s="50" t="n"/>
+      <c r="K1" s="50" t="n"/>
+      <c r="L1" s="50" t="n"/>
+      <c r="M1" s="50" t="n"/>
     </row>
     <row r="2" ht="30" customHeight="1">
-      <c r="A2" s="16" t="inlineStr">
+      <c r="A2" s="47" t="inlineStr">
         <is>
           <t>برای هر وضعیت «رد» یا تفاوت مهم، یک ردیف با شناسهٔ یکتا ثبت و پس از اصلاح دوباره تست شود.</t>
         </is>
       </c>
-      <c r="B2" s="16" t="n"/>
-      <c r="C2" s="16" t="n"/>
-      <c r="D2" s="16" t="n"/>
-      <c r="E2" s="16" t="n"/>
-      <c r="F2" s="16" t="n"/>
-      <c r="G2" s="16" t="n"/>
-      <c r="H2" s="16" t="n"/>
-      <c r="I2" s="16" t="n"/>
-      <c r="J2" s="16" t="n"/>
-      <c r="K2" s="16" t="n"/>
-      <c r="L2" s="16" t="n"/>
-      <c r="M2" s="16" t="n"/>
+      <c r="B2" s="47" t="n"/>
+      <c r="C2" s="47" t="n"/>
+      <c r="D2" s="47" t="n"/>
+      <c r="E2" s="47" t="n"/>
+      <c r="F2" s="47" t="n"/>
+      <c r="G2" s="47" t="n"/>
+      <c r="H2" s="47" t="n"/>
+      <c r="I2" s="47" t="n"/>
+      <c r="J2" s="47" t="n"/>
+      <c r="K2" s="47" t="n"/>
+      <c r="L2" s="47" t="n"/>
+      <c r="M2" s="47" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" s="33" t="inlineStr">
+      <c r="A3" s="67" t="inlineStr">
         <is>
           <t>شماره ایراد</t>
         </is>
       </c>
-      <c r="B3" s="33" t="inlineStr">
+      <c r="B3" s="67" t="inlineStr">
         <is>
           <t>شناسه تست</t>
         </is>
       </c>
-      <c r="C3" s="33" t="inlineStr">
+      <c r="C3" s="67" t="inlineStr">
         <is>
           <t>تاریخ کشف</t>
         </is>
       </c>
-      <c r="D3" s="33" t="inlineStr">
+      <c r="D3" s="67" t="inlineStr">
         <is>
           <t>شدت</t>
         </is>
       </c>
-      <c r="E3" s="33" t="inlineStr">
+      <c r="E3" s="67" t="inlineStr">
         <is>
           <t>شرح کوتاه ایراد</t>
         </is>
       </c>
-      <c r="F3" s="33" t="inlineStr">
+      <c r="F3" s="67" t="inlineStr">
         <is>
           <t>مراحل بازتولید</t>
         </is>
       </c>
-      <c r="G3" s="33" t="inlineStr">
+      <c r="G3" s="67" t="inlineStr">
         <is>
           <t>انتظار</t>
         </is>
       </c>
-      <c r="H3" s="33" t="inlineStr">
+      <c r="H3" s="67" t="inlineStr">
         <is>
           <t>واقعیت</t>
         </is>
       </c>
-      <c r="I3" s="33" t="inlineStr">
+      <c r="I3" s="67" t="inlineStr">
         <is>
           <t>مدرک/مسیر عکس یا scope</t>
         </is>
       </c>
-      <c r="J3" s="33" t="inlineStr">
+      <c r="J3" s="67" t="inlineStr">
         <is>
           <t>commit firmware</t>
         </is>
       </c>
-      <c r="K3" s="33" t="inlineStr">
+      <c r="K3" s="67" t="inlineStr">
         <is>
           <t>محل احتمالی</t>
         </is>
       </c>
-      <c r="L3" s="33" t="inlineStr">
+      <c r="L3" s="67" t="inlineStr">
         <is>
           <t>وضعیت ایراد</t>
         </is>
       </c>
-      <c r="M3" s="33" t="inlineStr">
+      <c r="M3" s="67" t="inlineStr">
         <is>
           <t>تأیید رفع / توضیحات</t>
         </is>
@@ -2697,211 +3879,235 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="14" t="inlineStr">
+      <c r="A1" s="45" t="inlineStr">
         <is>
           <t>تأیید نهایی اعتبارسنجی — ماژول CalLut</t>
         </is>
       </c>
+      <c r="B1" s="50" t="n"/>
+      <c r="C1" s="50" t="n"/>
     </row>
     <row r="2">
-      <c r="A2" s="15" t="inlineStr">
+      <c r="A2" s="46" t="inlineStr">
         <is>
           <t>این صفحه فقط پس از تکمیل تست‌ها و بسته‌شدن ایرادها پر می‌شود.</t>
         </is>
       </c>
+      <c r="B2" s="50" t="n"/>
+      <c r="C2" s="50" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" s="36" t="inlineStr">
+      <c r="A3" s="71" t="inlineStr">
         <is>
           <t>مشخصات تست</t>
         </is>
       </c>
+      <c r="B3" s="50" t="n"/>
+      <c r="C3" s="50" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" s="15" t="inlineStr">
+      <c r="A4" s="46" t="inlineStr">
         <is>
           <t>پروژه</t>
         </is>
       </c>
-      <c r="B4" s="15" t="inlineStr">
+      <c r="B4" s="46" t="inlineStr">
         <is>
           <t>ChangeOver</t>
         </is>
       </c>
+      <c r="C4" s="50" t="n"/>
     </row>
     <row r="5">
-      <c r="A5" s="15" t="inlineStr">
+      <c r="A5" s="46" t="inlineStr">
         <is>
           <t>ماژول</t>
         </is>
       </c>
-      <c r="B5" s="15" t="inlineStr">
+      <c r="B5" s="46" t="inlineStr">
         <is>
           <t>CalLut — جدول کالیبراسیون در فلش اختصاصی</t>
         </is>
       </c>
+      <c r="C5" s="50" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="15" t="inlineStr">
+      <c r="A6" s="46" t="inlineStr">
         <is>
           <t>تاریخ ساخت فرم</t>
         </is>
       </c>
-      <c r="B6" s="15" t="inlineStr">
+      <c r="B6" s="46" t="inlineStr">
         <is>
           <t>2026-10-05 (1.0 — ساخته‌شده در ممیزی کل برنامه)</t>
         </is>
       </c>
+      <c r="C6" s="50" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="15" t="inlineStr">
+      <c r="A7" s="46" t="inlineStr">
         <is>
           <t>نسخه فرم</t>
         </is>
       </c>
-      <c r="B7" s="15" t="inlineStr">
+      <c r="B7" s="46" t="inlineStr">
         <is>
           <t>1.0</t>
         </is>
       </c>
+      <c r="C7" s="50" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="15" t="inlineStr">
+      <c r="A8" s="46" t="inlineStr">
         <is>
           <t>commit firmware</t>
         </is>
       </c>
-      <c r="B8" s="15" t="inlineStr">
+      <c r="B8" s="46" t="inlineStr">
         <is>
           <t>TESTER: fill</t>
         </is>
       </c>
+      <c r="C8" s="50" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="15" t="inlineStr">
+      <c r="A9" s="46" t="inlineStr">
         <is>
           <t>ابزار</t>
         </is>
       </c>
-      <c r="B9" s="15" t="inlineStr">
+      <c r="B9" s="46" t="inlineStr">
         <is>
           <t>پنل ESP + مولتی‌متر + منبع تغذیه قابل قطع + اسیلوسکوپ</t>
         </is>
       </c>
-    </row>
-    <row r="10"/>
+      <c r="C9" s="50" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="50" t="n"/>
+      <c r="B10" s="50" t="n"/>
+      <c r="C10" s="50" t="n"/>
+    </row>
     <row r="11">
-      <c r="A11" s="36" t="inlineStr">
+      <c r="A11" s="71" t="inlineStr">
         <is>
           <t>خلاصهٔ خودکار وضعیت تست‌ها</t>
         </is>
       </c>
+      <c r="B11" s="50" t="n"/>
+      <c r="C11" s="50" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" s="36" t="inlineStr">
+      <c r="A12" s="71" t="inlineStr">
         <is>
           <t>شاخص</t>
         </is>
       </c>
-      <c r="B12" s="36" t="inlineStr">
+      <c r="B12" s="71" t="inlineStr">
         <is>
           <t>مقدار</t>
         </is>
       </c>
-      <c r="C12" s="36" t="inlineStr">
+      <c r="C12" s="71" t="inlineStr">
         <is>
           <t>توضیح</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="15" t="inlineStr">
+      <c r="A13" s="46" t="inlineStr">
         <is>
           <t>کل تست‌ها</t>
         </is>
       </c>
-      <c r="B13" s="15" t="inlineStr">
+      <c r="B13" s="46" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="C13" s="15" t="inlineStr">
+      <c r="C13" s="46" t="inlineStr">
         <is>
           <t>همهٔ ردیف‌های برنامه تست</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="15" t="inlineStr">
+      <c r="A14" s="46" t="inlineStr">
         <is>
           <t>قبول</t>
         </is>
       </c>
-      <c r="B14" s="15">
+      <c r="B14" s="46">
         <f>COUNTIF('برنامه تست'!L:L,"قبول")</f>
         <v/>
       </c>
-      <c r="C14" s="15" t="inlineStr">
+      <c r="C14" s="46" t="inlineStr">
         <is>
           <t>COUNTIF برنامه تست</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="15" t="inlineStr">
+      <c r="A15" s="46" t="inlineStr">
         <is>
           <t>رد</t>
         </is>
       </c>
-      <c r="B15" s="15">
+      <c r="B15" s="46">
         <f>COUNTIF('برنامه تست'!L:L,"رد")</f>
         <v/>
       </c>
-      <c r="C15" s="15" t="inlineStr">
+      <c r="C15" s="46" t="inlineStr">
         <is>
           <t>COUNTIF رد</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="15" t="inlineStr">
+      <c r="A16" s="46" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="B16" s="15">
+      <c r="B16" s="46">
         <f>IF(16=0,0,COUNTIF('برنامه تست'!L:L,"قبول")/16)</f>
         <v/>
       </c>
-      <c r="C16" s="15" t="inlineStr">
+      <c r="C16" s="46" t="inlineStr">
         <is>
           <t>پیش از تست برد</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="15" t="inlineStr">
+      <c r="A17" s="46" t="inlineStr">
         <is>
           <t>نرخ قبولی</t>
         </is>
       </c>
-      <c r="B17" s="15">
+      <c r="B17" s="46">
         <f>IF(15=0,0,COUNTIF('برنامه تست'!L:L,"قبول")/15)</f>
         <v/>
       </c>
-      <c r="C17" s="15" t="inlineStr">
+      <c r="C17" s="46" t="inlineStr">
         <is>
           <t>قبول/کل</t>
         </is>
       </c>
     </row>
-    <row r="18"/>
+    <row r="18">
+      <c r="A18" s="50" t="n"/>
+      <c r="B18" s="50" t="n"/>
+      <c r="C18" s="50" t="n"/>
+    </row>
     <row r="19">
-      <c r="A19" s="15" t="inlineStr">
+      <c r="A19" s="46" t="inlineStr">
         <is>
           <t>امضا و تأیید: تست‌کننده ______  بازبین ______  تاریخ ______</t>
         </is>
       </c>
+      <c r="B19" s="50" t="n"/>
+      <c r="C19" s="50" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2923,77 +4129,88 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="37" t="inlineStr">
+      <c r="A1" s="72" t="inlineStr">
         <is>
           <t>وضعیت</t>
         </is>
       </c>
+      <c r="B1" s="50" t="n"/>
     </row>
     <row r="2">
-      <c r="A2" s="18" t="inlineStr">
+      <c r="A2" s="51" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
+      <c r="B2" s="50" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" s="18" t="inlineStr">
+      <c r="A3" s="51" t="inlineStr">
         <is>
           <t>انجام شد</t>
         </is>
       </c>
+      <c r="B3" s="50" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" s="18" t="inlineStr">
+      <c r="A4" s="51" t="inlineStr">
         <is>
           <t>قبول</t>
         </is>
       </c>
+      <c r="B4" s="50" t="n"/>
     </row>
     <row r="5">
-      <c r="A5" s="18" t="inlineStr">
+      <c r="A5" s="51" t="inlineStr">
         <is>
           <t>رد</t>
         </is>
       </c>
+      <c r="B5" s="50" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="18" t="inlineStr">
+      <c r="A6" s="51" t="inlineStr">
         <is>
           <t>مسدود</t>
         </is>
       </c>
+      <c r="B6" s="50" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
+      <c r="A7" s="50" t="inlineStr">
         <is>
           <t>نیاز به تکرار</t>
         </is>
       </c>
+      <c r="B7" s="50" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="37" t="inlineStr">
+      <c r="A8" s="72" t="inlineStr">
         <is>
           <t>اولویت</t>
         </is>
       </c>
+      <c r="B8" s="50" t="n"/>
     </row>
     <row r="9">
-      <c r="B9" s="18" t="inlineStr">
+      <c r="A9" s="50" t="n"/>
+      <c r="B9" s="51" t="inlineStr">
         <is>
           <t>بالا</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="B10" s="18" t="inlineStr">
+      <c r="A10" s="50" t="n"/>
+      <c r="B10" s="51" t="inlineStr">
         <is>
           <t>متوسط</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="B11" s="18" t="inlineStr">
+      <c r="A11" s="50" t="n"/>
+      <c r="B11" s="51" t="inlineStr">
         <is>
           <t>پایین</t>
         </is>
@@ -3019,60 +4236,70 @@
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
-      <c r="A1" s="38" t="inlineStr">
+      <c r="A1" s="10" t="inlineStr">
         <is>
           <t>ماشین حالت ماژول جدول کالیبراسیون (CalLut)</t>
         </is>
       </c>
-    </row>
-    <row r="2"/>
+      <c r="B1" s="50" t="n"/>
+      <c r="C1" s="50" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="50" t="n"/>
+      <c r="B2" s="50" t="n"/>
+      <c r="C2" s="50" t="n"/>
+    </row>
     <row r="3" ht="24" customHeight="1">
-      <c r="A3" s="39" t="inlineStr">
+      <c r="A3" s="11" t="inlineStr">
         <is>
           <t>حالت‌ها و گذارهای همین ماژول</t>
         </is>
       </c>
-      <c r="B3" s="40" t="inlineStr">
+      <c r="B3" s="12" t="inlineStr">
         <is>
           <t>CalLut_State_Machine.xlsx</t>
         </is>
       </c>
+      <c r="C3" s="50" t="n"/>
     </row>
     <row r="4" ht="24" customHeight="1">
-      <c r="A4" s="39" t="inlineStr">
+      <c r="A4" s="11" t="inlineStr">
         <is>
           <t>ماشین حالت کل برنامه (نمای سیستمی)</t>
         </is>
       </c>
-      <c r="B4" s="40" t="inlineStr">
+      <c r="B4" s="12" t="inlineStr">
         <is>
           <t>../../../Documentation/System_State_Machine.xlsx</t>
         </is>
       </c>
+      <c r="C4" s="50" t="n"/>
     </row>
     <row r="5" ht="24" customHeight="1">
-      <c r="A5" s="39" t="inlineStr">
+      <c r="A5" s="11" t="inlineStr">
         <is>
           <t>راهنمای رنگ‌ها</t>
         </is>
       </c>
-      <c r="B5" s="41" t="inlineStr">
+      <c r="B5" s="13" t="inlineStr">
         <is>
           <t>سبز = عادی/سالم · زرد = هشدار یا انتظار · قرمز = خطا یا قفل · نارنجی = در حال کار · خاکستری = بی‌کار · آبی = اطلاعاتی</t>
         </is>
       </c>
+      <c r="C5" s="50" t="n"/>
     </row>
     <row r="6" ht="24" customHeight="1">
-      <c r="A6" s="39" t="inlineStr">
+      <c r="A6" s="11" t="inlineStr">
         <is>
           <t>بازتولید</t>
         </is>
       </c>
-      <c r="B6" s="40" t="inlineStr">
+      <c r="B6" s="12" t="inlineStr">
         <is>
           <t>python3 tools/make_module_state_machines.py</t>
         </is>
       </c>
+      <c r="C6" s="50" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -3117,135 +4344,183 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="17" t="inlineStr">
+      <c r="A1" s="49" t="inlineStr">
         <is>
           <t>برنامهٔ تست برنامه‌نویسی — ماژول CalLut</t>
         </is>
       </c>
+      <c r="B1" s="50" t="n"/>
+      <c r="C1" s="50" t="n"/>
+      <c r="D1" s="50" t="n"/>
+      <c r="E1" s="50" t="n"/>
+      <c r="F1" s="50" t="n"/>
+      <c r="G1" s="50" t="n"/>
+      <c r="H1" s="50" t="n"/>
+      <c r="I1" s="50" t="n"/>
+      <c r="J1" s="50" t="n"/>
+      <c r="K1" s="50" t="n"/>
+      <c r="L1" s="50" t="n"/>
+      <c r="M1" s="50" t="n"/>
+      <c r="N1" s="50" t="n"/>
+      <c r="O1" s="50" t="n"/>
+      <c r="P1" s="50" t="n"/>
+      <c r="Q1" s="50" t="n"/>
     </row>
     <row r="2">
-      <c r="A2" s="18" t="inlineStr">
+      <c r="A2" s="51" t="inlineStr">
         <is>
           <t>وضعیت فقط یکی از: در انتظار / قبول / رد / مسدود / نیاز به تکرار. تست Host جایگزین تست برد نیست.</t>
         </is>
       </c>
+      <c r="B2" s="50" t="n"/>
+      <c r="C2" s="50" t="n"/>
+      <c r="D2" s="50" t="n"/>
+      <c r="E2" s="50" t="n"/>
+      <c r="F2" s="50" t="n"/>
+      <c r="G2" s="50" t="n"/>
+      <c r="H2" s="50" t="n"/>
+      <c r="I2" s="50" t="n"/>
+      <c r="J2" s="50" t="n"/>
+      <c r="K2" s="50" t="n"/>
+      <c r="L2" s="50" t="n"/>
+      <c r="M2" s="50" t="n"/>
+      <c r="N2" s="50" t="n"/>
+      <c r="O2" s="50" t="n"/>
+      <c r="P2" s="50" t="n"/>
+      <c r="Q2" s="50" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" s="18" t="inlineStr">
+      <c r="A3" s="51" t="inlineStr">
         <is>
           <t>برای هر ردیف پیش‌شرط، ورودی، انتظار و معیار قبولی صریح است؛ نتیجهٔ واقعی فقط با اندازه‌گیری روی برد پر می‌شود.</t>
         </is>
       </c>
+      <c r="B3" s="50" t="n"/>
+      <c r="C3" s="50" t="n"/>
+      <c r="D3" s="50" t="n"/>
+      <c r="E3" s="50" t="n"/>
+      <c r="F3" s="50" t="n"/>
+      <c r="G3" s="50" t="n"/>
+      <c r="H3" s="50" t="n"/>
+      <c r="I3" s="50" t="n"/>
+      <c r="J3" s="50" t="n"/>
+      <c r="K3" s="50" t="n"/>
+      <c r="L3" s="50" t="n"/>
+      <c r="M3" s="50" t="n"/>
+      <c r="N3" s="50" t="n"/>
+      <c r="O3" s="50" t="n"/>
+      <c r="P3" s="50" t="n"/>
+      <c r="Q3" s="50" t="n"/>
     </row>
     <row r="4" ht="30" customHeight="1">
-      <c r="A4" s="16" t="inlineStr">
+      <c r="A4" s="47" t="inlineStr">
         <is>
           <t>شناسه</t>
         </is>
       </c>
-      <c r="B4" s="16" t="inlineStr">
+      <c r="B4" s="47" t="inlineStr">
         <is>
           <t>دسته</t>
         </is>
       </c>
-      <c r="C4" s="16" t="inlineStr">
+      <c r="C4" s="47" t="inlineStr">
         <is>
           <t>اولویت</t>
         </is>
       </c>
-      <c r="D4" s="16" t="inlineStr">
+      <c r="D4" s="47" t="inlineStr">
         <is>
           <t>پیش‌شرط</t>
         </is>
       </c>
-      <c r="E4" s="16" t="inlineStr">
+      <c r="E4" s="47" t="inlineStr">
         <is>
           <t>روش اجرای دقیق</t>
         </is>
       </c>
-      <c r="F4" s="16" t="inlineStr">
+      <c r="F4" s="47" t="inlineStr">
         <is>
           <t>ورودی‌ها / شرایط</t>
         </is>
       </c>
-      <c r="G4" s="16" t="inlineStr">
+      <c r="G4" s="47" t="inlineStr">
         <is>
           <t>مدت مشاهده</t>
         </is>
       </c>
-      <c r="H4" s="16" t="inlineStr">
+      <c r="H4" s="47" t="inlineStr">
         <is>
           <t>رفتار مورد انتظار</t>
         </is>
       </c>
-      <c r="I4" s="16" t="inlineStr">
+      <c r="I4" s="47" t="inlineStr">
         <is>
           <t>وضعیت حفظ / latch</t>
         </is>
       </c>
-      <c r="J4" s="16" t="inlineStr">
+      <c r="J4" s="47" t="inlineStr">
         <is>
           <t>معیار قبولی</t>
         </is>
       </c>
-      <c r="K4" s="16" t="inlineStr">
+      <c r="K4" s="47" t="inlineStr">
         <is>
           <t>نتیجهٔ واقعی / اندازه‌گیری</t>
         </is>
       </c>
-      <c r="L4" s="16" t="inlineStr">
+      <c r="L4" s="47" t="inlineStr">
         <is>
           <t>وضعیت</t>
         </is>
       </c>
-      <c r="M4" s="16" t="inlineStr">
+      <c r="M4" s="47" t="inlineStr">
         <is>
           <t>شرح ایراد / تفاوت</t>
         </is>
       </c>
-      <c r="N4" s="16" t="inlineStr">
+      <c r="N4" s="47" t="inlineStr">
         <is>
           <t>مدرک تست / scope</t>
         </is>
       </c>
-      <c r="O4" s="16" t="inlineStr">
+      <c r="O4" s="47" t="inlineStr">
         <is>
           <t>commit</t>
         </is>
       </c>
-      <c r="P4" s="16" t="inlineStr">
+      <c r="P4" s="47" t="inlineStr">
         <is>
           <t>نام تست‌کننده</t>
         </is>
       </c>
-      <c r="Q4" s="16" t="inlineStr">
+      <c r="Q4" s="47" t="inlineStr">
         <is>
           <t>تاریخ</t>
         </is>
       </c>
     </row>
     <row r="5" ht="54" customHeight="1">
-      <c r="A5" s="19" t="inlineStr">
+      <c r="A5" s="52" t="inlineStr">
         <is>
           <t>CL-004</t>
         </is>
       </c>
-      <c r="B5" s="25" t="inlineStr">
+      <c r="B5" s="59" t="inlineStr">
         <is>
           <t>CRC ناهمخوان</t>
         </is>
       </c>
-      <c r="C5" s="26" t="inlineStr">
+      <c r="C5" s="60" t="inlineStr">
         <is>
           <t>بالا</t>
         </is>
       </c>
-      <c r="D5" s="25" t="inlineStr">
+      <c r="D5" s="59" t="inlineStr">
         <is>
           <t>لینک برقرار</t>
         </is>
       </c>
-      <c r="E5" s="25" t="inlineStr">
+      <c r="E5" s="59" t="inlineStr">
         <is>
           <t>گام ۱: لینک ESP را وصل کن و CRC32 جدول فعال فعلی را یادداشت کن.
 گام ۲: یک جدول بفرست ولی در مرحلهٔ COMMIT عمداً CRC32 اشتباه بده (با CRC واقعی جدول یکی نباشد).
@@ -3253,84 +4528,84 @@
 گام ۴: CRC32 جدول فعال را دوباره بخوان؛ باید با گام ۱ یکی باشد، یعنی فلش دست‌نخورده مانده است.</t>
         </is>
       </c>
-      <c r="F5" s="27" t="inlineStr">
+      <c r="F5" s="61" t="inlineStr">
         <is>
           <t>CRC پنل ≠ CRC چیده‌شده</t>
         </is>
       </c>
-      <c r="G5" s="27" t="inlineStr">
+      <c r="G5" s="61" t="inlineStr">
         <is>
           <t>یک تبادل</t>
         </is>
       </c>
-      <c r="H5" s="25" t="inlineStr">
+      <c r="H5" s="59" t="inlineStr">
         <is>
           <t>رد شدن commit با CAL_LUT_ST_CRC؛ فلش دست‌نخورده</t>
         </is>
       </c>
-      <c r="I5" s="25" t="inlineStr">
+      <c r="I5" s="59" t="inlineStr">
         <is>
           <t>رکورد قبلی حفظ</t>
         </is>
       </c>
-      <c r="J5" s="25" t="inlineStr">
+      <c r="J5" s="59" t="inlineStr">
         <is>
           <t>status=6 و ActiveCrc32 تغییر نکرده</t>
         </is>
       </c>
-      <c r="K5" s="25" t="inlineStr">
+      <c r="K5" s="59" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="L5" s="23" t="inlineStr">
+      <c r="L5" s="57" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="M5" s="25" t="n"/>
-      <c r="N5" s="25" t="inlineStr">
+      <c r="M5" s="59" t="n"/>
+      <c r="N5" s="59" t="inlineStr">
         <is>
           <t>TESTER: fill</t>
         </is>
       </c>
-      <c r="O5" s="27" t="inlineStr">
+      <c r="O5" s="61" t="inlineStr">
         <is>
           <t>TESTER: fill</t>
         </is>
       </c>
-      <c r="P5" s="27" t="inlineStr">
+      <c r="P5" s="61" t="inlineStr">
         <is>
           <t>TESTER: fill</t>
         </is>
       </c>
-      <c r="Q5" s="28">
+      <c r="Q5" s="62">
         <f>IF(OR(L5="",L5="در انتظار"),"",IF(Q5="",TODAY(),Q5))</f>
         <v/>
       </c>
     </row>
     <row r="6" ht="67.5" customHeight="1">
-      <c r="A6" s="19" t="inlineStr">
+      <c r="A6" s="52" t="inlineStr">
         <is>
           <t>CL-005</t>
         </is>
       </c>
-      <c r="B6" s="20" t="inlineStr">
+      <c r="B6" s="53" t="inlineStr">
         <is>
           <t>محور صعودی نبودن</t>
         </is>
       </c>
-      <c r="C6" s="21" t="inlineStr">
+      <c r="C6" s="54" t="inlineStr">
         <is>
           <t>بالا</t>
         </is>
       </c>
-      <c r="D6" s="20" t="inlineStr">
+      <c r="D6" s="53" t="inlineStr">
         <is>
           <t>لینک برقرار</t>
         </is>
       </c>
-      <c r="E6" s="20" t="inlineStr">
+      <c r="E6" s="53" t="inlineStr">
         <is>
           <t>گام ۱: لینک ESP را وصل کن.
 گام ۲: جدولی بساز که محور زنجیره‌اش (ChainMa) صعودیِ اکید نباشد؛ مثلاً یک نقطهٔ تکراری یا یک نقطه کمتر از قبلی بگذار.
@@ -3338,84 +4613,84 @@
 گام ۴: پاسخ برد را بخوان: وضعیت باید 4 باشد (CAL_LUT_ST_CHAIN) و جدول نباید فعال شود.</t>
         </is>
       </c>
-      <c r="F6" s="22" t="inlineStr">
+      <c r="F6" s="56" t="inlineStr">
         <is>
           <t>نقطهٔ تکراری یا نزولی در ChainMa</t>
         </is>
       </c>
-      <c r="G6" s="22" t="inlineStr">
+      <c r="G6" s="56" t="inlineStr">
         <is>
           <t>یک تبادل</t>
         </is>
       </c>
-      <c r="H6" s="20" t="inlineStr">
+      <c r="H6" s="53" t="inlineStr">
         <is>
           <t>رد با CAL_LUT_ST_CHAIN</t>
         </is>
       </c>
-      <c r="I6" s="20" t="inlineStr">
+      <c r="I6" s="53" t="inlineStr">
         <is>
           <t>بدون تغییر فلش</t>
         </is>
       </c>
-      <c r="J6" s="20" t="inlineStr">
+      <c r="J6" s="53" t="inlineStr">
         <is>
           <t>status=4</t>
         </is>
       </c>
-      <c r="K6" s="20" t="inlineStr">
+      <c r="K6" s="53" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="L6" s="23" t="inlineStr">
+      <c r="L6" s="57" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="M6" s="20" t="n"/>
-      <c r="N6" s="20" t="inlineStr">
+      <c r="M6" s="53" t="n"/>
+      <c r="N6" s="53" t="inlineStr">
         <is>
           <t>TESTER: fill</t>
         </is>
       </c>
-      <c r="O6" s="22" t="inlineStr">
+      <c r="O6" s="56" t="inlineStr">
         <is>
           <t>TESTER: fill</t>
         </is>
       </c>
-      <c r="P6" s="22" t="inlineStr">
+      <c r="P6" s="56" t="inlineStr">
         <is>
           <t>TESTER: fill</t>
         </is>
       </c>
-      <c r="Q6" s="24">
+      <c r="Q6" s="58">
         <f>IF(OR(L6="",L6="در انتظار"),"",IF(Q6="",TODAY(),Q6))</f>
         <v/>
       </c>
     </row>
     <row r="7" ht="54" customHeight="1">
-      <c r="A7" s="19" t="inlineStr">
+      <c r="A7" s="52" t="inlineStr">
         <is>
           <t>CL-006</t>
         </is>
       </c>
-      <c r="B7" s="25" t="inlineStr">
+      <c r="B7" s="59" t="inlineStr">
         <is>
           <t>افت محور جریان</t>
         </is>
       </c>
-      <c r="C7" s="27" t="inlineStr">
+      <c r="C7" s="61" t="inlineStr">
         <is>
           <t>متوسط</t>
         </is>
       </c>
-      <c r="D7" s="25" t="inlineStr">
+      <c r="D7" s="59" t="inlineStr">
         <is>
           <t>لینک برقرار</t>
         </is>
       </c>
-      <c r="E7" s="25" t="inlineStr">
+      <c r="E7" s="59" t="inlineStr">
         <is>
           <t>گام ۱: لینک ESP را وصل کن.
 گام ۲: جدولی بساز که جریان باتری در یکی از نقطه‌ها از نقطهٔ قبلی کمتر باشد (افت داشته باشد).
@@ -3423,84 +4698,84 @@
 گام ۴: پاسخ برد را بخوان: وضعیت باید 5 باشد (CAL_LUT_ST_DIP) و جدول نباید فعال شود.</t>
         </is>
       </c>
-      <c r="F7" s="27" t="inlineStr">
+      <c r="F7" s="61" t="inlineStr">
         <is>
           <t>نقطه‌ای کمتر از نقطهٔ قبل</t>
         </is>
       </c>
-      <c r="G7" s="27" t="inlineStr">
+      <c r="G7" s="61" t="inlineStr">
         <is>
           <t>یک تبادل</t>
         </is>
       </c>
-      <c r="H7" s="25" t="inlineStr">
+      <c r="H7" s="59" t="inlineStr">
         <is>
           <t>رد با CAL_LUT_ST_DIP (جریان باتری افت دارد)</t>
         </is>
       </c>
-      <c r="I7" s="25" t="inlineStr">
+      <c r="I7" s="59" t="inlineStr">
         <is>
           <t>بدون تغییر فلش</t>
         </is>
       </c>
-      <c r="J7" s="25" t="inlineStr">
+      <c r="J7" s="59" t="inlineStr">
         <is>
           <t>status=5</t>
         </is>
       </c>
-      <c r="K7" s="25" t="inlineStr">
+      <c r="K7" s="59" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="L7" s="23" t="inlineStr">
+      <c r="L7" s="57" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="M7" s="25" t="n"/>
-      <c r="N7" s="25" t="inlineStr">
+      <c r="M7" s="59" t="n"/>
+      <c r="N7" s="59" t="inlineStr">
         <is>
           <t>TESTER: fill</t>
         </is>
       </c>
-      <c r="O7" s="27" t="inlineStr">
+      <c r="O7" s="61" t="inlineStr">
         <is>
           <t>TESTER: fill</t>
         </is>
       </c>
-      <c r="P7" s="27" t="inlineStr">
+      <c r="P7" s="61" t="inlineStr">
         <is>
           <t>TESTER: fill</t>
         </is>
       </c>
-      <c r="Q7" s="28">
+      <c r="Q7" s="62">
         <f>IF(OR(L7="",L7="در انتظار"),"",IF(Q7="",TODAY(),Q7))</f>
         <v/>
       </c>
     </row>
     <row r="8" ht="54" customHeight="1">
-      <c r="A8" s="19" t="inlineStr">
+      <c r="A8" s="52" t="inlineStr">
         <is>
           <t>CL-007</t>
         </is>
       </c>
-      <c r="B8" s="20" t="inlineStr">
+      <c r="B8" s="53" t="inlineStr">
         <is>
           <t>تعداد نقاط نامعتبر</t>
         </is>
       </c>
-      <c r="C8" s="22" t="inlineStr">
+      <c r="C8" s="56" t="inlineStr">
         <is>
           <t>متوسط</t>
         </is>
       </c>
-      <c r="D8" s="20" t="inlineStr">
+      <c r="D8" s="53" t="inlineStr">
         <is>
           <t>لینک برقرار</t>
         </is>
       </c>
-      <c r="E8" s="20" t="inlineStr">
+      <c r="E8" s="53" t="inlineStr">
         <is>
           <t>گام ۱: لینک ESP را وصل کن.
 گام ۲: یک جدول فقط با 1 نقطه بفرست و COMMIT کن؛ پاسخ را بخوان.
@@ -3508,84 +4783,84 @@
 گام ۴: هر دو بار وضعیت باید 2 باشد (CAL_LUT_ST_COUNT)، چون تعداد نقطهٔ مجاز 2 تا 24 است.</t>
         </is>
       </c>
-      <c r="F8" s="22" t="inlineStr">
+      <c r="F8" s="56" t="inlineStr">
         <is>
           <t>points &lt; 2 یا &gt; 24</t>
         </is>
       </c>
-      <c r="G8" s="22" t="inlineStr">
+      <c r="G8" s="56" t="inlineStr">
         <is>
           <t>دو تبادل</t>
         </is>
       </c>
-      <c r="H8" s="20" t="inlineStr">
+      <c r="H8" s="53" t="inlineStr">
         <is>
           <t>هر دو با CAL_LUT_ST_COUNT رد می‌شوند</t>
         </is>
       </c>
-      <c r="I8" s="20" t="inlineStr">
+      <c r="I8" s="53" t="inlineStr">
         <is>
           <t>بدون تغییر فلش</t>
         </is>
       </c>
-      <c r="J8" s="20" t="inlineStr">
+      <c r="J8" s="53" t="inlineStr">
         <is>
           <t>status=2 در هر دو</t>
         </is>
       </c>
-      <c r="K8" s="20" t="inlineStr">
+      <c r="K8" s="53" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="L8" s="23" t="inlineStr">
+      <c r="L8" s="57" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="M8" s="20" t="n"/>
-      <c r="N8" s="20" t="inlineStr">
+      <c r="M8" s="53" t="n"/>
+      <c r="N8" s="53" t="inlineStr">
         <is>
           <t>TESTER: fill</t>
         </is>
       </c>
-      <c r="O8" s="22" t="inlineStr">
+      <c r="O8" s="56" t="inlineStr">
         <is>
           <t>TESTER: fill</t>
         </is>
       </c>
-      <c r="P8" s="22" t="inlineStr">
+      <c r="P8" s="56" t="inlineStr">
         <is>
           <t>TESTER: fill</t>
         </is>
       </c>
-      <c r="Q8" s="24">
+      <c r="Q8" s="58">
         <f>IF(OR(L8="",L8="در انتظار"),"",IF(Q8="",TODAY(),Q8))</f>
         <v/>
       </c>
     </row>
     <row r="9" ht="54" customHeight="1">
-      <c r="A9" s="19" t="inlineStr">
+      <c r="A9" s="52" t="inlineStr">
         <is>
           <t>CL-008</t>
         </is>
       </c>
-      <c r="B9" s="25" t="inlineStr">
+      <c r="B9" s="59" t="inlineStr">
         <is>
           <t>تکهٔ گم‌شده</t>
         </is>
       </c>
-      <c r="C9" s="27" t="inlineStr">
+      <c r="C9" s="61" t="inlineStr">
         <is>
           <t>متوسط</t>
         </is>
       </c>
-      <c r="D9" s="25" t="inlineStr">
+      <c r="D9" s="59" t="inlineStr">
         <is>
           <t>لینک برقرار</t>
         </is>
       </c>
-      <c r="E9" s="25" t="inlineStr">
+      <c r="E9" s="59" t="inlineStr">
         <is>
           <t>گام ۱: لینک ESP را وصل کن و یک جدول چندچانکه آماده کن.
 گام ۲: همهٔ چانک‌ها را بفرست به‌جز یکی؛ عمداً یک چانک را نفرست.
@@ -3593,168 +4868,168 @@
 گام ۴: پاسخ برد را بخوان: وضعیت باید 3 باشد (CAL_LUT_ST_MISSING) و هیچ جدولی فعال نشود.</t>
         </is>
       </c>
-      <c r="F9" s="27" t="inlineStr">
+      <c r="F9" s="61" t="inlineStr">
         <is>
           <t>یک تکه نرسیده</t>
         </is>
       </c>
-      <c r="G9" s="27" t="inlineStr">
+      <c r="G9" s="61" t="inlineStr">
         <is>
           <t>یک تبادل</t>
         </is>
       </c>
-      <c r="H9" s="25" t="inlineStr">
+      <c r="H9" s="59" t="inlineStr">
         <is>
           <t>رد با CAL_LUT_ST_MISSING</t>
         </is>
       </c>
-      <c r="I9" s="25" t="inlineStr">
+      <c r="I9" s="59" t="inlineStr">
         <is>
           <t>بدون تغییر فلش</t>
         </is>
       </c>
-      <c r="J9" s="25" t="inlineStr">
+      <c r="J9" s="59" t="inlineStr">
         <is>
           <t>status=3</t>
         </is>
       </c>
-      <c r="K9" s="25" t="inlineStr">
+      <c r="K9" s="59" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="L9" s="23" t="inlineStr">
+      <c r="L9" s="57" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="M9" s="25" t="n"/>
-      <c r="N9" s="25" t="inlineStr">
+      <c r="M9" s="59" t="n"/>
+      <c r="N9" s="59" t="inlineStr">
         <is>
           <t>TESTER: fill</t>
         </is>
       </c>
-      <c r="O9" s="27" t="inlineStr">
+      <c r="O9" s="61" t="inlineStr">
         <is>
           <t>TESTER: fill</t>
         </is>
       </c>
-      <c r="P9" s="27" t="inlineStr">
+      <c r="P9" s="61" t="inlineStr">
         <is>
           <t>TESTER: fill</t>
         </is>
       </c>
-      <c r="Q9" s="28">
+      <c r="Q9" s="62">
         <f>IF(OR(L9="",L9="در انتظار"),"",IF(Q9="",TODAY(),Q9))</f>
         <v/>
       </c>
     </row>
     <row r="10" ht="54" customHeight="1">
-      <c r="A10" s="19" t="inlineStr">
+      <c r="A10" s="52" t="inlineStr">
         <is>
           <t>CL-009</t>
         </is>
       </c>
-      <c r="B10" s="20" t="inlineStr">
+      <c r="B10" s="53" t="inlineStr">
         <is>
           <t>commit بدون begin</t>
         </is>
       </c>
-      <c r="C10" s="22" t="inlineStr">
+      <c r="C10" s="56" t="inlineStr">
         <is>
           <t>پایین</t>
         </is>
       </c>
-      <c r="D10" s="20" t="inlineStr">
+      <c r="D10" s="53" t="inlineStr">
         <is>
           <t>لینک برقرار</t>
         </is>
       </c>
-      <c r="E10" s="20" t="inlineStr">
+      <c r="E10" s="53" t="inlineStr">
         <is>
           <t>گام ۱: لینک ESP را وصل کن.
 گام ۲: بدون اینکه LUT_BEGIN بفرستی، مستقیم COMMIT بفرست.
 گام ۳: پاسخ برد را بخوان: وضعیت باید 1 باشد (CAL_LUT_ST_NO_STAGE) و هیچ اتفاقی برای جدول فعال نیفتد.</t>
         </is>
       </c>
-      <c r="F10" s="22" t="inlineStr">
+      <c r="F10" s="56" t="inlineStr">
         <is>
           <t>بدون مرحلهٔ چیدن</t>
         </is>
       </c>
-      <c r="G10" s="22" t="inlineStr">
+      <c r="G10" s="56" t="inlineStr">
         <is>
           <t>یک تبادل</t>
         </is>
       </c>
-      <c r="H10" s="20" t="inlineStr">
+      <c r="H10" s="53" t="inlineStr">
         <is>
           <t>رد با CAL_LUT_ST_NO_STAGE</t>
         </is>
       </c>
-      <c r="I10" s="20" t="inlineStr">
+      <c r="I10" s="53" t="inlineStr">
         <is>
           <t>بدون تغییر فلش</t>
         </is>
       </c>
-      <c r="J10" s="20" t="inlineStr">
+      <c r="J10" s="53" t="inlineStr">
         <is>
           <t>status=1</t>
         </is>
       </c>
-      <c r="K10" s="20" t="inlineStr">
+      <c r="K10" s="53" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="L10" s="23" t="inlineStr">
+      <c r="L10" s="57" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="M10" s="20" t="n"/>
-      <c r="N10" s="20" t="inlineStr">
+      <c r="M10" s="53" t="n"/>
+      <c r="N10" s="53" t="inlineStr">
         <is>
           <t>TESTER: fill</t>
         </is>
       </c>
-      <c r="O10" s="22" t="inlineStr">
+      <c r="O10" s="56" t="inlineStr">
         <is>
           <t>TESTER: fill</t>
         </is>
       </c>
-      <c r="P10" s="22" t="inlineStr">
+      <c r="P10" s="56" t="inlineStr">
         <is>
           <t>TESTER: fill</t>
         </is>
       </c>
-      <c r="Q10" s="24">
+      <c r="Q10" s="58">
         <f>IF(OR(L10="",L10="در انتظار"),"",IF(Q10="",TODAY(),Q10))</f>
         <v/>
       </c>
     </row>
     <row r="11" ht="54" customHeight="1">
-      <c r="A11" s="19" t="inlineStr">
+      <c r="A11" s="52" t="inlineStr">
         <is>
           <t>CL-013</t>
         </is>
       </c>
-      <c r="B11" s="20" t="inlineStr">
+      <c r="B11" s="53" t="inlineStr">
         <is>
           <t>تغییر نسخهٔ قالب</t>
         </is>
       </c>
-      <c r="C11" s="22" t="inlineStr">
+      <c r="C11" s="56" t="inlineStr">
         <is>
           <t>پایین</t>
         </is>
       </c>
-      <c r="D11" s="20" t="inlineStr">
+      <c r="D11" s="53" t="inlineStr">
         <is>
           <t>رکورد معتبر نسخهٔ ۱</t>
         </is>
       </c>
-      <c r="E11" s="20" t="inlineStr">
+      <c r="E11" s="53" t="inlineStr">
         <is>
           <t>گام ۱: روی برد یک رکورد LUT معتبر با نسخهٔ 1 داشته باش (قبلاً commit شده باشد).
 گام ۲: ثابت CAL_LUT_VERSION را در کد بالا ببر و فرم‌ور جدید را روی همان برد فلش کن.
@@ -3762,58 +5037,58 @@
 گام ۴: باید جدول فعال نباشد (Active = false) و خوانش جریان به جدول کامپایل‌شده (خط گین و آفست) برگشته باشد.</t>
         </is>
       </c>
-      <c r="F11" s="22" t="inlineStr">
+      <c r="F11" s="56" t="inlineStr">
         <is>
           <t>نسخهٔ رکورد قدیمی</t>
         </is>
       </c>
-      <c r="G11" s="22" t="inlineStr">
+      <c r="G11" s="56" t="inlineStr">
         <is>
           <t>یک بوت</t>
         </is>
       </c>
-      <c r="H11" s="20" t="inlineStr">
+      <c r="H11" s="53" t="inlineStr">
         <is>
           <t>رکورد قدیمی نامعتبر و بازگشت به جدول کامپایل‌شده</t>
         </is>
       </c>
-      <c r="I11" s="20" t="inlineStr">
+      <c r="I11" s="53" t="inlineStr">
         <is>
           <t>بدون نیم‌ارتقای بی‌صدا</t>
         </is>
       </c>
-      <c r="J11" s="20" t="inlineStr">
+      <c r="J11" s="53" t="inlineStr">
         <is>
           <t>Active=false و خوانش‌ها برابر خط گین و آفست</t>
         </is>
       </c>
-      <c r="K11" s="20" t="inlineStr">
+      <c r="K11" s="53" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="L11" s="23" t="inlineStr">
+      <c r="L11" s="57" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="M11" s="20" t="n"/>
-      <c r="N11" s="20" t="inlineStr">
+      <c r="M11" s="53" t="n"/>
+      <c r="N11" s="53" t="inlineStr">
         <is>
           <t>TESTER: fill</t>
         </is>
       </c>
-      <c r="O11" s="22" t="inlineStr">
+      <c r="O11" s="56" t="inlineStr">
         <is>
           <t>TESTER: fill</t>
         </is>
       </c>
-      <c r="P11" s="22" t="inlineStr">
+      <c r="P11" s="56" t="inlineStr">
         <is>
           <t>TESTER: fill</t>
         </is>
       </c>
-      <c r="Q11" s="24">
+      <c r="Q11" s="58">
         <f>IF(OR(L11="",L11="در انتظار"),"",IF(Q11="",TODAY(),Q11))</f>
         <v/>
       </c>

--- a/Firmware/Modules/CalLut/CalLut_Validation.xlsx
+++ b/Firmware/Modules/CalLut/CalLut_Validation.xlsx
@@ -32,7 +32,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
   </numFmts>
-  <fonts count="26">
+  <fonts count="27">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -171,6 +171,10 @@
       <b val="1"/>
       <sz val="8"/>
     </font>
+    <font>
+      <name val="Vazirmatn"/>
+      <sz val="11"/>
+    </font>
   </fonts>
   <fills count="8">
     <fill>
@@ -210,7 +214,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -246,11 +250,12 @@
         <color rgb="00B4C6E7"/>
       </bottom>
     </border>
+    <border/>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="73">
+  <cellXfs count="76">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -440,6 +445,9 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="25" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="26" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -806,7 +814,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A10"/>
+  <dimension ref="A1:A12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="120" customWidth="1" min="1" max="1"/>
@@ -875,6 +883,14 @@
       <c r="A10" s="46" t="inlineStr">
         <is>
           <t>تست Host (کامپایل و اجرا روی PC با شبیه‌سازی RAM) جایگزین این تست‌ها نیست.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="73" t="inlineStr">
+        <is>
+          <t>اولویت تست‌های عملی: «بالا» یعنی رفتار اصلی‌ای که در کار عادی دستگاه می‌بینید (روشن‌شدن، شروع و پایان شارژ، چهره‌های اصلی چراغ‌ها، رفتن تغذیه روی برق ورودی، خطاهای اصلی)؛ اول همین‌ها را انجام دهید. «متوسط» رفتارهای فرعیِ کاربردی است و «پایین» ریزه‌کاری‌ها (مثل اثر نوسان چند درصدی روی ریتم چشمک یا لبه‌های دقیق درصد و زمان).
+ستون «چه چیزی باید ببینید تا بگویید درست است» می‌گوید دقیقاً چه چیزی را باید ببینید یا بشنوید تا آن تست را قبول کنید؛ اگر چیز دیگری دیدید، وضعیت را «رد» بزنید و در شرح ایراد بنویسید چه دیدید.</t>
         </is>
       </c>
     </row>
@@ -1032,7 +1048,7 @@
       </c>
       <c r="J4" s="47" t="inlineStr">
         <is>
-          <t>معیار قبولی</t>
+          <t>چه چیزی باید ببینید تا بگویید درست است</t>
         </is>
       </c>
       <c r="K4" s="47" t="inlineStr">
@@ -1120,7 +1136,7 @@
       </c>
       <c r="J5" s="53" t="inlineStr">
         <is>
-          <t>شارژ عادی بی‌جدول = قبول؛ شارژ خراب یا خطا = رد</t>
+          <t>باید ببینید: شارژ با جدول پیش‌فرض کارخانه کاملاً عادی کار می‌کند و هیچ خطای جدولی نیست. اگر شارژ خراب بود یا خطا آمد، قبول نیست.</t>
         </is>
       </c>
       <c r="K5" s="53" t="inlineStr">
@@ -1149,10 +1165,9 @@
           <t>TESTER: fill</t>
         </is>
       </c>
-      <c r="Q5" s="58" t="inlineStr">
-        <is>
-          <t>2026-10-05</t>
-        </is>
+      <c r="Q5" s="58">
+        <f>IF(OR(L5="",L5="در انتظار"),"",IF(Q5="",TODAY(),Q5))</f>
+        <v/>
       </c>
     </row>
     <row r="6" ht="67.5" customHeight="1">
@@ -1205,7 +1220,7 @@
       </c>
       <c r="J6" s="59" t="inlineStr">
         <is>
-          <t>نشستن جدول و شارژ درست = قبول؛ اختلاف عدد یا شارژ خراب = رد</t>
+          <t>باید ببینید: جدول درست نشسته (بازخوانی همان است) و شارژ کانال ۱ با همان اعداد کار می‌کند. اگر عددی اختلاف داشت یا شارژ خراب بود، قبول نیست.</t>
         </is>
       </c>
       <c r="K6" s="59" t="inlineStr">
@@ -1234,10 +1249,9 @@
           <t>TESTER: fill</t>
         </is>
       </c>
-      <c r="Q6" s="62" t="inlineStr">
-        <is>
-          <t>2026-10-05</t>
-        </is>
+      <c r="Q6" s="62">
+        <f>IF(OR(L6="",L6="در انتظار"),"",IF(Q6="",TODAY(),Q6))</f>
+        <v/>
       </c>
     </row>
     <row r="7" ht="54" customHeight="1">
@@ -1289,7 +1303,7 @@
       </c>
       <c r="J7" s="53" t="inlineStr">
         <is>
-          <t>حفظ جدول = قبول؛ پاک‌شدن = رد</t>
+          <t>باید ببینید: جدول سفارشی بعد از خاموش و روشن‌کردن سر جاست. اگر پاک شده بود، قبول نیست.</t>
         </is>
       </c>
       <c r="K7" s="53" t="inlineStr">
@@ -1318,10 +1332,9 @@
           <t>TESTER: fill</t>
         </is>
       </c>
-      <c r="Q7" s="58" t="inlineStr">
-        <is>
-          <t>2026-10-05</t>
-        </is>
+      <c r="Q7" s="58">
+        <f>IF(OR(L7="",L7="در انتظار"),"",IF(Q7="",TODAY(),Q7))</f>
+        <v/>
       </c>
     </row>
     <row r="8" ht="54" customHeight="1">
@@ -1337,7 +1350,7 @@
       </c>
       <c r="C8" s="60" t="inlineStr">
         <is>
-          <t>بالا</t>
+          <t>متوسط</t>
         </is>
       </c>
       <c r="D8" s="63" t="inlineStr">
@@ -1374,7 +1387,7 @@
       </c>
       <c r="J8" s="59" t="inlineStr">
         <is>
-          <t>شارژ سالم بعد از قطع وسط کار = قبول؛ جدول خراب یا شارژ به‌هم‌ریخته = رد</t>
+          <t>باید ببینید: بعد از قطع برق وسط نوشتن، شارژ با جدول قبلی یا پیش‌فرض سالم کار می‌کند و جدول نصفه ذخیره نشده است. اگر جدول خراب یا شارژ به‌هم‌ریخته بود، قبول نیست.</t>
         </is>
       </c>
       <c r="K8" s="59" t="inlineStr">
@@ -1403,10 +1416,9 @@
           <t>TESTER: fill</t>
         </is>
       </c>
-      <c r="Q8" s="62" t="inlineStr">
-        <is>
-          <t>2026-10-05</t>
-        </is>
+      <c r="Q8" s="62">
+        <f>IF(OR(L8="",L8="در انتظار"),"",IF(Q8="",TODAY(),Q8))</f>
+        <v/>
       </c>
     </row>
     <row r="9" ht="54" customHeight="1">
@@ -1422,7 +1434,7 @@
       </c>
       <c r="C9" s="54" t="inlineStr">
         <is>
-          <t>بالا</t>
+          <t>متوسط</t>
         </is>
       </c>
       <c r="D9" s="53" t="inlineStr">
@@ -1459,7 +1471,7 @@
       </c>
       <c r="J9" s="53" t="inlineStr">
         <is>
-          <t>سالم‌ماندن جدول = قبول؛ دست‌خوردن جدول = رد</t>
+          <t>باید ببینید: جدول سفارشی دست‌نخورده مانده است. اگر دست خورده بود، قبول نیست.</t>
         </is>
       </c>
       <c r="K9" s="53" t="inlineStr">
@@ -1488,10 +1500,9 @@
           <t>TESTER: fill</t>
         </is>
       </c>
-      <c r="Q9" s="58" t="inlineStr">
-        <is>
-          <t>2026-10-05</t>
-        </is>
+      <c r="Q9" s="58">
+        <f>IF(OR(L9="",L9="در انتظار"),"",IF(Q9="",TODAY(),Q9))</f>
+        <v/>
       </c>
     </row>
     <row r="10" ht="54" customHeight="1">
@@ -1507,7 +1518,7 @@
       </c>
       <c r="C10" s="60" t="inlineStr">
         <is>
-          <t>بالا</t>
+          <t>متوسط</t>
         </is>
       </c>
       <c r="D10" s="59" t="inlineStr">
@@ -1543,7 +1554,7 @@
       </c>
       <c r="J10" s="59" t="inlineStr">
         <is>
-          <t>درستی هر دو = قبول؛ قاطی یا ناقص = رد</t>
+          <t>باید ببینید: هر دو جدول عددبه‌عدد درست و سر جای خودشان‌اند و کانال‌ها قاطی نشده‌اند. اگر قاطی یا ناقص بود، قبول نیست.</t>
         </is>
       </c>
       <c r="K10" s="59" t="inlineStr">
@@ -1571,11 +1582,10 @@
           <t>WORKTREE</t>
         </is>
       </c>
-      <c r="P10" s="61" t="inlineStr"/>
-      <c r="Q10" s="62" t="inlineStr">
-        <is>
-          <t>2026-10-07</t>
-        </is>
+      <c r="P10" s="61" t="n"/>
+      <c r="Q10" s="62">
+        <f>IF(OR(L10="",L10="در انتظار"),"",IF(Q10="",TODAY(),Q10))</f>
+        <v/>
       </c>
     </row>
     <row r="11" ht="54" customHeight="1">
@@ -1591,7 +1601,7 @@
       </c>
       <c r="C11" s="54" t="inlineStr">
         <is>
-          <t>بالا</t>
+          <t>متوسط</t>
         </is>
       </c>
       <c r="D11" s="55" t="inlineStr">
@@ -1627,7 +1637,7 @@
       </c>
       <c r="J11" s="53" t="inlineStr">
         <is>
-          <t>برگشت به پیش‌فرض = قبول؛ ماندن روی جدول پاک‌شده = رد</t>
+          <t>باید ببینید: کانال به رفتار پیش‌فرض کارخانه برمی‌گردد و شارژ عادی می‌شود. اگر روی جدول پاک‌شده ماند، قبول نیست.</t>
         </is>
       </c>
       <c r="K11" s="53" t="inlineStr">
@@ -1656,10 +1666,9 @@
         </is>
       </c>
       <c r="P11" s="56" t="n"/>
-      <c r="Q11" s="58" t="inlineStr">
-        <is>
-          <t>2026-10-07</t>
-        </is>
+      <c r="Q11" s="58">
+        <f>IF(OR(L11="",L11="در انتظار"),"",IF(Q11="",TODAY(),Q11))</f>
+        <v/>
       </c>
     </row>
     <row r="12" ht="54" customHeight="1">
@@ -1675,7 +1684,7 @@
       </c>
       <c r="C12" s="60" t="inlineStr">
         <is>
-          <t>بالا</t>
+          <t>متوسط</t>
         </is>
       </c>
       <c r="D12" s="59" t="inlineStr">
@@ -1712,7 +1721,7 @@
       </c>
       <c r="J12" s="59" t="inlineStr">
         <is>
-          <t>پاک‌ماندن و شارژ عادی = قبول؛ برگشتن جدول = رد</t>
+          <t>باید ببینید: جدول پاک شده و بعد از روشن‌شدن هم برنمی‌گردد و شارژ پیش‌فرض عادی است. اگر جدول برگشت، قبول نیست.</t>
         </is>
       </c>
       <c r="K12" s="59" t="inlineStr">
@@ -1741,10 +1750,9 @@
         </is>
       </c>
       <c r="P12" s="61" t="n"/>
-      <c r="Q12" s="62" t="inlineStr">
-        <is>
-          <t>2026-10-08</t>
-        </is>
+      <c r="Q12" s="62">
+        <f>IF(OR(L12="",L12="در انتظار"),"",IF(Q12="",TODAY(),Q12))</f>
+        <v/>
       </c>
     </row>
     <row r="13" ht="40.5" customHeight="1">
@@ -1797,7 +1805,7 @@
       </c>
       <c r="J13" s="53" t="inlineStr">
         <is>
-          <t>رفتار درست لغو/تأیید = قبول؛ اعمال با لغو یا گم‌شدن با تأیید = رد</t>
+          <t>باید ببینید: لغو هیچ اثری ندارد و تأیید دقیقاً همان تغییر را می‌نشاند. اگر با لغو اعمال شد یا با تأیید گم شد، قبول نیست.</t>
         </is>
       </c>
       <c r="K13" s="53" t="n"/>
@@ -1818,931 +1826,784 @@
         </is>
       </c>
       <c r="P13" s="56" t="n"/>
-      <c r="Q13" s="58" t="inlineStr">
-        <is>
-          <t>2026-10-12</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="54" customHeight="1">
-      <c r="A14" s="50" t="n"/>
-      <c r="B14" s="50" t="n"/>
-      <c r="C14" s="50" t="n"/>
-      <c r="D14" s="50" t="inlineStr">
-        <is>
-          <t>'برنامه تست'!A6</t>
-        </is>
-      </c>
-      <c r="E14" s="50" t="inlineStr">
-        <is>
-          <t>'برنامه تست'!A6</t>
-        </is>
-      </c>
-      <c r="F14" s="50" t="n"/>
-      <c r="G14" s="50" t="n"/>
-      <c r="H14" s="50" t="n"/>
-      <c r="I14" s="50" t="n"/>
-      <c r="J14" s="50" t="n"/>
-      <c r="K14" s="50" t="n"/>
-      <c r="L14" s="50" t="n"/>
-      <c r="M14" s="50" t="n"/>
-      <c r="N14" s="50" t="n"/>
-      <c r="O14" s="50" t="n"/>
-      <c r="P14" s="50" t="n"/>
-      <c r="Q14" s="65">
-        <f>IF(OR(L22="",L22="در انتظار"),"",IF(Q22="",TODAY(),Q22))</f>
+      <c r="Q13" s="58">
+        <f>IF(OR(L13="",L13="در انتظار"),"",IF(Q13="",TODAY(),Q13))</f>
         <v/>
       </c>
     </row>
-    <row r="15" ht="54" customHeight="1">
-      <c r="A15" s="50" t="n"/>
-      <c r="B15" s="50" t="n"/>
-      <c r="C15" s="50" t="n"/>
-      <c r="D15" s="50" t="n"/>
-      <c r="E15" s="50" t="n"/>
-      <c r="F15" s="50" t="n"/>
-      <c r="G15" s="50" t="n"/>
-      <c r="H15" s="50" t="n"/>
-      <c r="I15" s="50" t="n"/>
-      <c r="J15" s="50" t="n"/>
-      <c r="K15" s="50" t="n"/>
-      <c r="L15" s="50" t="n"/>
-      <c r="M15" s="50" t="n"/>
-      <c r="N15" s="50" t="n"/>
-      <c r="O15" s="50" t="n"/>
-      <c r="P15" s="50" t="n"/>
-      <c r="Q15" s="65">
-        <f>IF(OR(L23="",L23="در انتظار"),"",IF(Q23="",TODAY(),Q23))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="16" ht="54" customHeight="1">
-      <c r="A16" s="50" t="n"/>
-      <c r="B16" s="50" t="n"/>
-      <c r="C16" s="50" t="n"/>
-      <c r="D16" s="50" t="n"/>
-      <c r="E16" s="50" t="n"/>
-      <c r="F16" s="50" t="n"/>
-      <c r="G16" s="50" t="n"/>
-      <c r="H16" s="50" t="n"/>
-      <c r="I16" s="50" t="n"/>
-      <c r="J16" s="50" t="n"/>
-      <c r="K16" s="50" t="n"/>
-      <c r="L16" s="50" t="n"/>
-      <c r="M16" s="50" t="n"/>
-      <c r="N16" s="50" t="n"/>
-      <c r="O16" s="50" t="n"/>
-      <c r="P16" s="50" t="n"/>
-      <c r="Q16" s="65">
-        <f>IF(OR(L24="",L24="در انتظار"),"",IF(Q24="",TODAY(),Q24))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="17" ht="54" customHeight="1">
-      <c r="A17" s="50" t="n"/>
-      <c r="B17" s="50" t="n"/>
-      <c r="C17" s="50" t="n"/>
-      <c r="D17" s="50" t="n"/>
-      <c r="E17" s="50" t="n"/>
-      <c r="F17" s="50" t="n"/>
-      <c r="G17" s="50" t="n"/>
-      <c r="H17" s="50" t="n"/>
-      <c r="I17" s="50" t="n"/>
-      <c r="J17" s="50" t="n"/>
-      <c r="K17" s="50" t="n"/>
-      <c r="L17" s="50" t="n"/>
-      <c r="M17" s="50" t="n"/>
-      <c r="N17" s="50" t="n"/>
-      <c r="O17" s="50" t="n"/>
-      <c r="P17" s="50" t="n"/>
-      <c r="Q17" s="65">
-        <f>IF(OR(L25="",L25="در انتظار"),"",IF(Q25="",TODAY(),Q25))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="18" ht="54" customHeight="1">
-      <c r="A18" s="50" t="n"/>
-      <c r="B18" s="50" t="n"/>
-      <c r="C18" s="50" t="n"/>
-      <c r="D18" s="50" t="inlineStr">
-        <is>
-          <t>'برنامه تست'!A6</t>
-        </is>
-      </c>
-      <c r="E18" s="50" t="inlineStr">
-        <is>
-          <t>'برنامه تست'!A6</t>
-        </is>
-      </c>
-      <c r="F18" s="50" t="n"/>
-      <c r="G18" s="50" t="n"/>
-      <c r="H18" s="50" t="n"/>
-      <c r="I18" s="50" t="n"/>
-      <c r="J18" s="50" t="n"/>
-      <c r="K18" s="50" t="n"/>
-      <c r="L18" s="50" t="n"/>
-      <c r="M18" s="50" t="n"/>
-      <c r="N18" s="50" t="n"/>
-      <c r="O18" s="50" t="n"/>
-      <c r="P18" s="50" t="n"/>
-      <c r="Q18" s="65">
-        <f>IF(OR(L26="",L26="در انتظار"),"",IF(Q26="",TODAY(),Q26))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="19" ht="67.5" customHeight="1">
-      <c r="A19" s="50" t="n"/>
-      <c r="B19" s="50" t="n"/>
-      <c r="C19" s="50" t="n"/>
-      <c r="D19" s="50" t="n"/>
-      <c r="E19" s="50" t="n"/>
-      <c r="F19" s="50" t="n"/>
-      <c r="G19" s="50" t="n"/>
-      <c r="H19" s="50" t="n"/>
-      <c r="I19" s="50" t="n"/>
-      <c r="J19" s="50" t="n"/>
-      <c r="K19" s="50" t="n"/>
-      <c r="L19" s="50" t="n"/>
-      <c r="M19" s="50" t="n"/>
-      <c r="N19" s="50" t="inlineStr">
-        <is>
-          <t>../../../esp_link_panel/Tester/host_test_scenario_cards.js</t>
-        </is>
-      </c>
-      <c r="O19" s="50" t="n"/>
-      <c r="P19" s="50" t="n"/>
-      <c r="Q19" s="65">
-        <f>IF(OR(L27="",L27="در انتظار"),"",IF(Q27="",TODAY(),Q27))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="20" ht="67.5" customHeight="1">
-      <c r="A20" s="50" t="n"/>
-      <c r="B20" s="50" t="n"/>
-      <c r="C20" s="50" t="n"/>
-      <c r="D20" s="50" t="n"/>
-      <c r="E20" s="50" t="n"/>
-      <c r="F20" s="50" t="n"/>
-      <c r="G20" s="50" t="n"/>
-      <c r="H20" s="50" t="n"/>
-      <c r="I20" s="50" t="n"/>
-      <c r="J20" s="50" t="n"/>
-      <c r="K20" s="50" t="n"/>
-      <c r="L20" s="50" t="n"/>
-      <c r="M20" s="50" t="n"/>
-      <c r="N20" s="50" t="inlineStr">
-        <is>
-          <t>../EspLink/esp_link.c</t>
-        </is>
-      </c>
-      <c r="O20" s="50" t="n"/>
-      <c r="P20" s="50" t="n"/>
-      <c r="Q20" s="65">
-        <f>IF(OR(L28="",L28="در انتظار"),"",IF(Q28="",TODAY(),Q28))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="21" ht="54" customHeight="1">
-      <c r="A21" s="50" t="n"/>
-      <c r="B21" s="50" t="n"/>
-      <c r="C21" s="50" t="n"/>
-      <c r="D21" s="50" t="n"/>
-      <c r="E21" s="50" t="n"/>
-      <c r="F21" s="50" t="n"/>
-      <c r="G21" s="50" t="n"/>
-      <c r="H21" s="50" t="n"/>
-      <c r="I21" s="50" t="n"/>
-      <c r="J21" s="50" t="n"/>
-      <c r="K21" s="50" t="n"/>
-      <c r="L21" s="50" t="n"/>
-      <c r="M21" s="50" t="n"/>
-      <c r="N21" s="50" t="n"/>
-      <c r="O21" s="50" t="n"/>
-      <c r="P21" s="50" t="n"/>
-      <c r="Q21" s="65">
-        <f>IF(OR(L29="",L29="در انتظار"),"",IF(Q29="",TODAY(),Q29))</f>
-        <v/>
-      </c>
+    <row r="14">
+      <c r="A14" s="74" t="n"/>
+      <c r="B14" s="74" t="n"/>
+      <c r="C14" s="74" t="n"/>
+      <c r="D14" s="74" t="n"/>
+      <c r="E14" s="74" t="n"/>
+      <c r="F14" s="74" t="n"/>
+      <c r="G14" s="74" t="n"/>
+      <c r="H14" s="74" t="n"/>
+      <c r="I14" s="74" t="n"/>
+      <c r="J14" s="74" t="n"/>
+      <c r="K14" s="74" t="n"/>
+      <c r="L14" s="74" t="n"/>
+      <c r="M14" s="74" t="n"/>
+      <c r="N14" s="74" t="n"/>
+      <c r="O14" s="74" t="n"/>
+      <c r="P14" s="74" t="n"/>
+      <c r="Q14" s="75" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="74" t="n"/>
+      <c r="B15" s="74" t="n"/>
+      <c r="C15" s="74" t="n"/>
+      <c r="D15" s="74" t="n"/>
+      <c r="E15" s="74" t="n"/>
+      <c r="F15" s="74" t="n"/>
+      <c r="G15" s="74" t="n"/>
+      <c r="H15" s="74" t="n"/>
+      <c r="I15" s="74" t="n"/>
+      <c r="J15" s="74" t="n"/>
+      <c r="K15" s="74" t="n"/>
+      <c r="L15" s="74" t="n"/>
+      <c r="M15" s="74" t="n"/>
+      <c r="N15" s="74" t="n"/>
+      <c r="O15" s="74" t="n"/>
+      <c r="P15" s="74" t="n"/>
+      <c r="Q15" s="75" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="74" t="n"/>
+      <c r="B16" s="74" t="n"/>
+      <c r="C16" s="74" t="n"/>
+      <c r="D16" s="74" t="n"/>
+      <c r="E16" s="74" t="n"/>
+      <c r="F16" s="74" t="n"/>
+      <c r="G16" s="74" t="n"/>
+      <c r="H16" s="74" t="n"/>
+      <c r="I16" s="74" t="n"/>
+      <c r="J16" s="74" t="n"/>
+      <c r="K16" s="74" t="n"/>
+      <c r="L16" s="74" t="n"/>
+      <c r="M16" s="74" t="n"/>
+      <c r="N16" s="74" t="n"/>
+      <c r="O16" s="74" t="n"/>
+      <c r="P16" s="74" t="n"/>
+      <c r="Q16" s="75" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="74" t="n"/>
+      <c r="B17" s="74" t="n"/>
+      <c r="C17" s="74" t="n"/>
+      <c r="D17" s="74" t="n"/>
+      <c r="E17" s="74" t="n"/>
+      <c r="F17" s="74" t="n"/>
+      <c r="G17" s="74" t="n"/>
+      <c r="H17" s="74" t="n"/>
+      <c r="I17" s="74" t="n"/>
+      <c r="J17" s="74" t="n"/>
+      <c r="K17" s="74" t="n"/>
+      <c r="L17" s="74" t="n"/>
+      <c r="M17" s="74" t="n"/>
+      <c r="N17" s="74" t="n"/>
+      <c r="O17" s="74" t="n"/>
+      <c r="P17" s="74" t="n"/>
+      <c r="Q17" s="75" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="74" t="n"/>
+      <c r="B18" s="74" t="n"/>
+      <c r="C18" s="74" t="n"/>
+      <c r="D18" s="74" t="n"/>
+      <c r="E18" s="74" t="n"/>
+      <c r="F18" s="74" t="n"/>
+      <c r="G18" s="74" t="n"/>
+      <c r="H18" s="74" t="n"/>
+      <c r="I18" s="74" t="n"/>
+      <c r="J18" s="74" t="n"/>
+      <c r="K18" s="74" t="n"/>
+      <c r="L18" s="74" t="n"/>
+      <c r="M18" s="74" t="n"/>
+      <c r="N18" s="74" t="n"/>
+      <c r="O18" s="74" t="n"/>
+      <c r="P18" s="74" t="n"/>
+      <c r="Q18" s="75" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="74" t="n"/>
+      <c r="B19" s="74" t="n"/>
+      <c r="C19" s="74" t="n"/>
+      <c r="D19" s="74" t="n"/>
+      <c r="E19" s="74" t="n"/>
+      <c r="F19" s="74" t="n"/>
+      <c r="G19" s="74" t="n"/>
+      <c r="H19" s="74" t="n"/>
+      <c r="I19" s="74" t="n"/>
+      <c r="J19" s="74" t="n"/>
+      <c r="K19" s="74" t="n"/>
+      <c r="L19" s="74" t="n"/>
+      <c r="M19" s="74" t="n"/>
+      <c r="N19" s="74" t="n"/>
+      <c r="O19" s="74" t="n"/>
+      <c r="P19" s="74" t="n"/>
+      <c r="Q19" s="75" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="74" t="n"/>
+      <c r="B20" s="74" t="n"/>
+      <c r="C20" s="74" t="n"/>
+      <c r="D20" s="74" t="n"/>
+      <c r="E20" s="74" t="n"/>
+      <c r="F20" s="74" t="n"/>
+      <c r="G20" s="74" t="n"/>
+      <c r="H20" s="74" t="n"/>
+      <c r="I20" s="74" t="n"/>
+      <c r="J20" s="74" t="n"/>
+      <c r="K20" s="74" t="n"/>
+      <c r="L20" s="74" t="n"/>
+      <c r="M20" s="74" t="n"/>
+      <c r="N20" s="74" t="n"/>
+      <c r="O20" s="74" t="n"/>
+      <c r="P20" s="74" t="n"/>
+      <c r="Q20" s="75" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="74" t="n"/>
+      <c r="B21" s="74" t="n"/>
+      <c r="C21" s="74" t="n"/>
+      <c r="D21" s="74" t="n"/>
+      <c r="E21" s="74" t="n"/>
+      <c r="F21" s="74" t="n"/>
+      <c r="G21" s="74" t="n"/>
+      <c r="H21" s="74" t="n"/>
+      <c r="I21" s="74" t="n"/>
+      <c r="J21" s="74" t="n"/>
+      <c r="K21" s="74" t="n"/>
+      <c r="L21" s="74" t="n"/>
+      <c r="M21" s="74" t="n"/>
+      <c r="N21" s="74" t="n"/>
+      <c r="O21" s="74" t="n"/>
+      <c r="P21" s="74" t="n"/>
+      <c r="Q21" s="75" t="n"/>
     </row>
     <row r="22">
-      <c r="A22" s="50" t="n"/>
-      <c r="B22" s="50" t="n"/>
-      <c r="C22" s="50" t="n"/>
-      <c r="D22" s="50" t="n"/>
-      <c r="E22" s="50" t="n"/>
-      <c r="F22" s="50" t="n"/>
-      <c r="G22" s="50" t="n"/>
-      <c r="H22" s="50" t="n"/>
-      <c r="I22" s="50" t="n"/>
-      <c r="J22" s="50" t="n"/>
-      <c r="K22" s="50" t="n"/>
-      <c r="L22" s="50" t="n"/>
-      <c r="M22" s="50" t="n"/>
-      <c r="N22" s="50" t="n"/>
-      <c r="O22" s="50" t="n"/>
-      <c r="P22" s="50" t="n"/>
-      <c r="Q22" s="65">
-        <f>IF(OR(L30="",L30="در انتظار"),"",IF(Q30="",TODAY(),Q30))</f>
-        <v/>
-      </c>
+      <c r="A22" s="74" t="n"/>
+      <c r="B22" s="74" t="n"/>
+      <c r="C22" s="74" t="n"/>
+      <c r="D22" s="74" t="n"/>
+      <c r="E22" s="74" t="n"/>
+      <c r="F22" s="74" t="n"/>
+      <c r="G22" s="74" t="n"/>
+      <c r="H22" s="74" t="n"/>
+      <c r="I22" s="74" t="n"/>
+      <c r="J22" s="74" t="n"/>
+      <c r="K22" s="74" t="n"/>
+      <c r="L22" s="74" t="n"/>
+      <c r="M22" s="74" t="n"/>
+      <c r="N22" s="74" t="n"/>
+      <c r="O22" s="74" t="n"/>
+      <c r="P22" s="74" t="n"/>
+      <c r="Q22" s="75" t="n"/>
     </row>
     <row r="23">
-      <c r="A23" s="50" t="n"/>
-      <c r="B23" s="50" t="n"/>
-      <c r="C23" s="50" t="n"/>
-      <c r="D23" s="50" t="n"/>
-      <c r="E23" s="50" t="n"/>
-      <c r="F23" s="50" t="n"/>
-      <c r="G23" s="50" t="n"/>
-      <c r="H23" s="50" t="n"/>
-      <c r="I23" s="50" t="n"/>
-      <c r="J23" s="50" t="n"/>
-      <c r="K23" s="50" t="n"/>
-      <c r="L23" s="50" t="n"/>
-      <c r="M23" s="50" t="n"/>
-      <c r="N23" s="50" t="n"/>
-      <c r="O23" s="50" t="n"/>
-      <c r="P23" s="50" t="n"/>
-      <c r="Q23" s="65">
-        <f>IF(OR(L31="",L31="در انتظار"),"",IF(Q31="",TODAY(),Q31))</f>
-        <v/>
-      </c>
+      <c r="A23" s="74" t="n"/>
+      <c r="B23" s="74" t="n"/>
+      <c r="C23" s="74" t="n"/>
+      <c r="D23" s="74" t="n"/>
+      <c r="E23" s="74" t="n"/>
+      <c r="F23" s="74" t="n"/>
+      <c r="G23" s="74" t="n"/>
+      <c r="H23" s="74" t="n"/>
+      <c r="I23" s="74" t="n"/>
+      <c r="J23" s="74" t="n"/>
+      <c r="K23" s="74" t="n"/>
+      <c r="L23" s="74" t="n"/>
+      <c r="M23" s="74" t="n"/>
+      <c r="N23" s="74" t="n"/>
+      <c r="O23" s="74" t="n"/>
+      <c r="P23" s="74" t="n"/>
+      <c r="Q23" s="75" t="n"/>
     </row>
     <row r="24">
-      <c r="A24" s="50" t="n"/>
-      <c r="B24" s="50" t="n"/>
-      <c r="C24" s="50" t="n"/>
-      <c r="D24" s="50" t="n"/>
-      <c r="E24" s="50" t="n"/>
-      <c r="F24" s="50" t="n"/>
-      <c r="G24" s="50" t="n"/>
-      <c r="H24" s="50" t="n"/>
-      <c r="I24" s="50" t="n"/>
-      <c r="J24" s="50" t="n"/>
-      <c r="K24" s="50" t="n"/>
-      <c r="L24" s="50" t="n"/>
-      <c r="M24" s="50" t="n"/>
-      <c r="N24" s="50" t="n"/>
-      <c r="O24" s="50" t="n"/>
-      <c r="P24" s="50" t="n"/>
-      <c r="Q24" s="65">
-        <f>IF(OR(L32="",L32="در انتظار"),"",IF(Q32="",TODAY(),Q32))</f>
-        <v/>
-      </c>
+      <c r="A24" s="74" t="n"/>
+      <c r="B24" s="74" t="n"/>
+      <c r="C24" s="74" t="n"/>
+      <c r="D24" s="74" t="n"/>
+      <c r="E24" s="74" t="n"/>
+      <c r="F24" s="74" t="n"/>
+      <c r="G24" s="74" t="n"/>
+      <c r="H24" s="74" t="n"/>
+      <c r="I24" s="74" t="n"/>
+      <c r="J24" s="74" t="n"/>
+      <c r="K24" s="74" t="n"/>
+      <c r="L24" s="74" t="n"/>
+      <c r="M24" s="74" t="n"/>
+      <c r="N24" s="74" t="n"/>
+      <c r="O24" s="74" t="n"/>
+      <c r="P24" s="74" t="n"/>
+      <c r="Q24" s="75" t="n"/>
     </row>
     <row r="25">
-      <c r="A25" s="50" t="n"/>
-      <c r="B25" s="50" t="n"/>
-      <c r="C25" s="50" t="n"/>
-      <c r="D25" s="50" t="n"/>
-      <c r="E25" s="50" t="n"/>
-      <c r="F25" s="50" t="n"/>
-      <c r="G25" s="50" t="n"/>
-      <c r="H25" s="50" t="n"/>
-      <c r="I25" s="50" t="n"/>
-      <c r="J25" s="50" t="n"/>
-      <c r="K25" s="50" t="n"/>
-      <c r="L25" s="50" t="n"/>
-      <c r="M25" s="50" t="n"/>
-      <c r="N25" s="50" t="n"/>
-      <c r="O25" s="50" t="n"/>
-      <c r="P25" s="50" t="n"/>
-      <c r="Q25" s="65">
-        <f>IF(OR(L33="",L33="در انتظار"),"",IF(Q33="",TODAY(),Q33))</f>
-        <v/>
-      </c>
+      <c r="A25" s="74" t="n"/>
+      <c r="B25" s="74" t="n"/>
+      <c r="C25" s="74" t="n"/>
+      <c r="D25" s="74" t="n"/>
+      <c r="E25" s="74" t="n"/>
+      <c r="F25" s="74" t="n"/>
+      <c r="G25" s="74" t="n"/>
+      <c r="H25" s="74" t="n"/>
+      <c r="I25" s="74" t="n"/>
+      <c r="J25" s="74" t="n"/>
+      <c r="K25" s="74" t="n"/>
+      <c r="L25" s="74" t="n"/>
+      <c r="M25" s="74" t="n"/>
+      <c r="N25" s="74" t="n"/>
+      <c r="O25" s="74" t="n"/>
+      <c r="P25" s="74" t="n"/>
+      <c r="Q25" s="75" t="n"/>
     </row>
     <row r="26">
-      <c r="A26" s="50" t="n"/>
-      <c r="B26" s="50" t="n"/>
-      <c r="C26" s="50" t="n"/>
-      <c r="D26" s="50" t="n"/>
-      <c r="E26" s="50" t="n"/>
-      <c r="F26" s="50" t="n"/>
-      <c r="G26" s="50" t="n"/>
-      <c r="H26" s="50" t="n"/>
-      <c r="I26" s="50" t="n"/>
-      <c r="J26" s="50" t="n"/>
-      <c r="K26" s="50" t="n"/>
-      <c r="L26" s="50" t="n"/>
-      <c r="M26" s="50" t="n"/>
-      <c r="N26" s="50" t="n"/>
-      <c r="O26" s="50" t="n"/>
-      <c r="P26" s="50" t="n"/>
-      <c r="Q26" s="65">
-        <f>IF(OR(L34="",L34="در انتظار"),"",IF(Q34="",TODAY(),Q34))</f>
-        <v/>
-      </c>
+      <c r="A26" s="74" t="n"/>
+      <c r="B26" s="74" t="n"/>
+      <c r="C26" s="74" t="n"/>
+      <c r="D26" s="74" t="n"/>
+      <c r="E26" s="74" t="n"/>
+      <c r="F26" s="74" t="n"/>
+      <c r="G26" s="74" t="n"/>
+      <c r="H26" s="74" t="n"/>
+      <c r="I26" s="74" t="n"/>
+      <c r="J26" s="74" t="n"/>
+      <c r="K26" s="74" t="n"/>
+      <c r="L26" s="74" t="n"/>
+      <c r="M26" s="74" t="n"/>
+      <c r="N26" s="74" t="n"/>
+      <c r="O26" s="74" t="n"/>
+      <c r="P26" s="74" t="n"/>
+      <c r="Q26" s="75" t="n"/>
     </row>
     <row r="27">
-      <c r="A27" s="50" t="n"/>
-      <c r="B27" s="50" t="n"/>
-      <c r="C27" s="50" t="n"/>
-      <c r="D27" s="50" t="n"/>
-      <c r="E27" s="50" t="n"/>
-      <c r="F27" s="50" t="n"/>
-      <c r="G27" s="50" t="n"/>
-      <c r="H27" s="50" t="n"/>
-      <c r="I27" s="50" t="n"/>
-      <c r="J27" s="50" t="n"/>
-      <c r="K27" s="50" t="n"/>
-      <c r="L27" s="50" t="n"/>
-      <c r="M27" s="50" t="n"/>
-      <c r="N27" s="50" t="n"/>
-      <c r="O27" s="50" t="n"/>
-      <c r="P27" s="50" t="n"/>
-      <c r="Q27" s="65">
-        <f>IF(OR(L35="",L35="در انتظار"),"",IF(Q35="",TODAY(),Q35))</f>
-        <v/>
-      </c>
+      <c r="A27" s="74" t="n"/>
+      <c r="B27" s="74" t="n"/>
+      <c r="C27" s="74" t="n"/>
+      <c r="D27" s="74" t="n"/>
+      <c r="E27" s="74" t="n"/>
+      <c r="F27" s="74" t="n"/>
+      <c r="G27" s="74" t="n"/>
+      <c r="H27" s="74" t="n"/>
+      <c r="I27" s="74" t="n"/>
+      <c r="J27" s="74" t="n"/>
+      <c r="K27" s="74" t="n"/>
+      <c r="L27" s="74" t="n"/>
+      <c r="M27" s="74" t="n"/>
+      <c r="N27" s="74" t="n"/>
+      <c r="O27" s="74" t="n"/>
+      <c r="P27" s="74" t="n"/>
+      <c r="Q27" s="75" t="n"/>
     </row>
     <row r="28">
-      <c r="A28" s="50" t="n"/>
-      <c r="B28" s="50" t="n"/>
-      <c r="C28" s="50" t="n"/>
-      <c r="D28" s="50" t="n"/>
-      <c r="E28" s="50" t="n"/>
-      <c r="F28" s="50" t="n"/>
-      <c r="G28" s="50" t="n"/>
-      <c r="H28" s="50" t="n"/>
-      <c r="I28" s="50" t="n"/>
-      <c r="J28" s="50" t="n"/>
-      <c r="K28" s="50" t="n"/>
-      <c r="L28" s="50" t="n"/>
-      <c r="M28" s="50" t="n"/>
-      <c r="N28" s="50" t="n"/>
-      <c r="O28" s="50" t="n"/>
-      <c r="P28" s="50" t="n"/>
-      <c r="Q28" s="65">
-        <f>IF(OR(L36="",L36="در انتظار"),"",IF(Q36="",TODAY(),Q36))</f>
-        <v/>
-      </c>
+      <c r="A28" s="74" t="n"/>
+      <c r="B28" s="74" t="n"/>
+      <c r="C28" s="74" t="n"/>
+      <c r="D28" s="74" t="n"/>
+      <c r="E28" s="74" t="n"/>
+      <c r="F28" s="74" t="n"/>
+      <c r="G28" s="74" t="n"/>
+      <c r="H28" s="74" t="n"/>
+      <c r="I28" s="74" t="n"/>
+      <c r="J28" s="74" t="n"/>
+      <c r="K28" s="74" t="n"/>
+      <c r="L28" s="74" t="n"/>
+      <c r="M28" s="74" t="n"/>
+      <c r="N28" s="74" t="n"/>
+      <c r="O28" s="74" t="n"/>
+      <c r="P28" s="74" t="n"/>
+      <c r="Q28" s="75" t="n"/>
     </row>
     <row r="29">
-      <c r="A29" s="50" t="n"/>
-      <c r="B29" s="50" t="n"/>
-      <c r="C29" s="50" t="n"/>
-      <c r="D29" s="50" t="n"/>
-      <c r="E29" s="50" t="n"/>
-      <c r="F29" s="50" t="n"/>
-      <c r="G29" s="50" t="n"/>
-      <c r="H29" s="50" t="n"/>
-      <c r="I29" s="50" t="n"/>
-      <c r="J29" s="50" t="n"/>
-      <c r="K29" s="50" t="n"/>
-      <c r="L29" s="50" t="n"/>
-      <c r="M29" s="50" t="n"/>
-      <c r="N29" s="50" t="n"/>
-      <c r="O29" s="50" t="n"/>
-      <c r="P29" s="50" t="n"/>
-      <c r="Q29" s="65">
-        <f>IF(OR(L37="",L37="در انتظار"),"",IF(Q37="",TODAY(),Q37))</f>
-        <v/>
-      </c>
+      <c r="A29" s="74" t="n"/>
+      <c r="B29" s="74" t="n"/>
+      <c r="C29" s="74" t="n"/>
+      <c r="D29" s="74" t="n"/>
+      <c r="E29" s="74" t="n"/>
+      <c r="F29" s="74" t="n"/>
+      <c r="G29" s="74" t="n"/>
+      <c r="H29" s="74" t="n"/>
+      <c r="I29" s="74" t="n"/>
+      <c r="J29" s="74" t="n"/>
+      <c r="K29" s="74" t="n"/>
+      <c r="L29" s="74" t="n"/>
+      <c r="M29" s="74" t="n"/>
+      <c r="N29" s="74" t="n"/>
+      <c r="O29" s="74" t="n"/>
+      <c r="P29" s="74" t="n"/>
+      <c r="Q29" s="75" t="n"/>
     </row>
     <row r="30">
-      <c r="A30" s="50" t="n"/>
-      <c r="B30" s="50" t="n"/>
-      <c r="C30" s="50" t="n"/>
-      <c r="D30" s="50" t="n"/>
-      <c r="E30" s="50" t="n"/>
-      <c r="F30" s="50" t="n"/>
-      <c r="G30" s="50" t="n"/>
-      <c r="H30" s="50" t="n"/>
-      <c r="I30" s="50" t="n"/>
-      <c r="J30" s="50" t="n"/>
-      <c r="K30" s="50" t="n"/>
-      <c r="L30" s="50" t="n"/>
-      <c r="M30" s="50" t="n"/>
-      <c r="N30" s="50" t="n"/>
-      <c r="O30" s="50" t="n"/>
-      <c r="P30" s="50" t="n"/>
-      <c r="Q30" s="65">
-        <f>IF(OR(L38="",L38="در انتظار"),"",IF(Q38="",TODAY(),Q38))</f>
-        <v/>
-      </c>
+      <c r="A30" s="74" t="n"/>
+      <c r="B30" s="74" t="n"/>
+      <c r="C30" s="74" t="n"/>
+      <c r="D30" s="74" t="n"/>
+      <c r="E30" s="74" t="n"/>
+      <c r="F30" s="74" t="n"/>
+      <c r="G30" s="74" t="n"/>
+      <c r="H30" s="74" t="n"/>
+      <c r="I30" s="74" t="n"/>
+      <c r="J30" s="74" t="n"/>
+      <c r="K30" s="74" t="n"/>
+      <c r="L30" s="74" t="n"/>
+      <c r="M30" s="74" t="n"/>
+      <c r="N30" s="74" t="n"/>
+      <c r="O30" s="74" t="n"/>
+      <c r="P30" s="74" t="n"/>
+      <c r="Q30" s="75" t="n"/>
     </row>
     <row r="31">
-      <c r="A31" s="50" t="n"/>
-      <c r="B31" s="50" t="n"/>
-      <c r="C31" s="50" t="n"/>
-      <c r="D31" s="50" t="n"/>
-      <c r="E31" s="50" t="n"/>
-      <c r="F31" s="50" t="n"/>
-      <c r="G31" s="50" t="n"/>
-      <c r="H31" s="50" t="n"/>
-      <c r="I31" s="50" t="n"/>
-      <c r="J31" s="50" t="n"/>
-      <c r="K31" s="50" t="n"/>
-      <c r="L31" s="50" t="n"/>
-      <c r="M31" s="50" t="n"/>
-      <c r="N31" s="50" t="n"/>
-      <c r="O31" s="50" t="n"/>
-      <c r="P31" s="50" t="n"/>
-      <c r="Q31" s="65">
-        <f>IF(OR(L39="",L39="در انتظار"),"",IF(Q39="",TODAY(),Q39))</f>
-        <v/>
-      </c>
+      <c r="A31" s="74" t="n"/>
+      <c r="B31" s="74" t="n"/>
+      <c r="C31" s="74" t="n"/>
+      <c r="D31" s="74" t="n"/>
+      <c r="E31" s="74" t="n"/>
+      <c r="F31" s="74" t="n"/>
+      <c r="G31" s="74" t="n"/>
+      <c r="H31" s="74" t="n"/>
+      <c r="I31" s="74" t="n"/>
+      <c r="J31" s="74" t="n"/>
+      <c r="K31" s="74" t="n"/>
+      <c r="L31" s="74" t="n"/>
+      <c r="M31" s="74" t="n"/>
+      <c r="N31" s="74" t="n"/>
+      <c r="O31" s="74" t="n"/>
+      <c r="P31" s="74" t="n"/>
+      <c r="Q31" s="75" t="n"/>
     </row>
     <row r="32">
-      <c r="A32" s="50" t="n"/>
-      <c r="B32" s="50" t="n"/>
-      <c r="C32" s="50" t="n"/>
-      <c r="D32" s="50" t="n"/>
-      <c r="E32" s="50" t="n"/>
-      <c r="F32" s="50" t="n"/>
-      <c r="G32" s="50" t="n"/>
-      <c r="H32" s="50" t="n"/>
-      <c r="I32" s="50" t="n"/>
-      <c r="J32" s="50" t="n"/>
-      <c r="K32" s="50" t="n"/>
-      <c r="L32" s="50" t="n"/>
-      <c r="M32" s="50" t="n"/>
-      <c r="N32" s="50" t="n"/>
-      <c r="O32" s="50" t="n"/>
-      <c r="P32" s="50" t="n"/>
-      <c r="Q32" s="65">
-        <f>IF(OR(L40="",L40="در انتظار"),"",IF(Q40="",TODAY(),Q40))</f>
-        <v/>
-      </c>
+      <c r="A32" s="74" t="n"/>
+      <c r="B32" s="74" t="n"/>
+      <c r="C32" s="74" t="n"/>
+      <c r="D32" s="74" t="n"/>
+      <c r="E32" s="74" t="n"/>
+      <c r="F32" s="74" t="n"/>
+      <c r="G32" s="74" t="n"/>
+      <c r="H32" s="74" t="n"/>
+      <c r="I32" s="74" t="n"/>
+      <c r="J32" s="74" t="n"/>
+      <c r="K32" s="74" t="n"/>
+      <c r="L32" s="74" t="n"/>
+      <c r="M32" s="74" t="n"/>
+      <c r="N32" s="74" t="n"/>
+      <c r="O32" s="74" t="n"/>
+      <c r="P32" s="74" t="n"/>
+      <c r="Q32" s="75" t="n"/>
     </row>
     <row r="33">
-      <c r="A33" s="50" t="n"/>
-      <c r="B33" s="50" t="n"/>
-      <c r="C33" s="50" t="n"/>
-      <c r="D33" s="50" t="n"/>
-      <c r="E33" s="50" t="n"/>
-      <c r="F33" s="50" t="n"/>
-      <c r="G33" s="50" t="n"/>
-      <c r="H33" s="50" t="n"/>
-      <c r="I33" s="50" t="n"/>
-      <c r="J33" s="50" t="n"/>
-      <c r="K33" s="50" t="n"/>
-      <c r="L33" s="50" t="n"/>
-      <c r="M33" s="50" t="n"/>
-      <c r="N33" s="50" t="n"/>
-      <c r="O33" s="50" t="n"/>
-      <c r="P33" s="50" t="n"/>
-      <c r="Q33" s="65">
-        <f>IF(OR(L41="",L41="در انتظار"),"",IF(Q41="",TODAY(),Q41))</f>
-        <v/>
-      </c>
+      <c r="A33" s="74" t="n"/>
+      <c r="B33" s="74" t="n"/>
+      <c r="C33" s="74" t="n"/>
+      <c r="D33" s="74" t="n"/>
+      <c r="E33" s="74" t="n"/>
+      <c r="F33" s="74" t="n"/>
+      <c r="G33" s="74" t="n"/>
+      <c r="H33" s="74" t="n"/>
+      <c r="I33" s="74" t="n"/>
+      <c r="J33" s="74" t="n"/>
+      <c r="K33" s="74" t="n"/>
+      <c r="L33" s="74" t="n"/>
+      <c r="M33" s="74" t="n"/>
+      <c r="N33" s="74" t="n"/>
+      <c r="O33" s="74" t="n"/>
+      <c r="P33" s="74" t="n"/>
+      <c r="Q33" s="75" t="n"/>
     </row>
     <row r="34">
-      <c r="A34" s="50" t="n"/>
-      <c r="B34" s="50" t="n"/>
-      <c r="C34" s="50" t="n"/>
-      <c r="D34" s="50" t="n"/>
-      <c r="E34" s="50" t="n"/>
-      <c r="F34" s="50" t="n"/>
-      <c r="G34" s="50" t="n"/>
-      <c r="H34" s="50" t="n"/>
-      <c r="I34" s="50" t="n"/>
-      <c r="J34" s="50" t="n"/>
-      <c r="K34" s="50" t="n"/>
-      <c r="L34" s="50" t="n"/>
-      <c r="M34" s="50" t="n"/>
-      <c r="N34" s="50" t="n"/>
-      <c r="O34" s="50" t="n"/>
-      <c r="P34" s="50" t="n"/>
-      <c r="Q34" s="65">
-        <f>IF(OR(L42="",L42="در انتظار"),"",IF(Q42="",TODAY(),Q42))</f>
-        <v/>
-      </c>
+      <c r="A34" s="74" t="n"/>
+      <c r="B34" s="74" t="n"/>
+      <c r="C34" s="74" t="n"/>
+      <c r="D34" s="74" t="n"/>
+      <c r="E34" s="74" t="n"/>
+      <c r="F34" s="74" t="n"/>
+      <c r="G34" s="74" t="n"/>
+      <c r="H34" s="74" t="n"/>
+      <c r="I34" s="74" t="n"/>
+      <c r="J34" s="74" t="n"/>
+      <c r="K34" s="74" t="n"/>
+      <c r="L34" s="74" t="n"/>
+      <c r="M34" s="74" t="n"/>
+      <c r="N34" s="74" t="n"/>
+      <c r="O34" s="74" t="n"/>
+      <c r="P34" s="74" t="n"/>
+      <c r="Q34" s="75" t="n"/>
     </row>
     <row r="35">
-      <c r="A35" s="50" t="n"/>
-      <c r="B35" s="50" t="n"/>
-      <c r="C35" s="50" t="n"/>
-      <c r="D35" s="50" t="n"/>
-      <c r="E35" s="50" t="n"/>
-      <c r="F35" s="50" t="n"/>
-      <c r="G35" s="50" t="n"/>
-      <c r="H35" s="50" t="n"/>
-      <c r="I35" s="50" t="n"/>
-      <c r="J35" s="50" t="n"/>
-      <c r="K35" s="50" t="n"/>
-      <c r="L35" s="50" t="n"/>
-      <c r="M35" s="50" t="n"/>
-      <c r="N35" s="50" t="n"/>
-      <c r="O35" s="50" t="n"/>
-      <c r="P35" s="50" t="n"/>
-      <c r="Q35" s="65">
-        <f>IF(OR(L43="",L43="در انتظار"),"",IF(Q43="",TODAY(),Q43))</f>
-        <v/>
-      </c>
+      <c r="A35" s="74" t="n"/>
+      <c r="B35" s="74" t="n"/>
+      <c r="C35" s="74" t="n"/>
+      <c r="D35" s="74" t="n"/>
+      <c r="E35" s="74" t="n"/>
+      <c r="F35" s="74" t="n"/>
+      <c r="G35" s="74" t="n"/>
+      <c r="H35" s="74" t="n"/>
+      <c r="I35" s="74" t="n"/>
+      <c r="J35" s="74" t="n"/>
+      <c r="K35" s="74" t="n"/>
+      <c r="L35" s="74" t="n"/>
+      <c r="M35" s="74" t="n"/>
+      <c r="N35" s="74" t="n"/>
+      <c r="O35" s="74" t="n"/>
+      <c r="P35" s="74" t="n"/>
+      <c r="Q35" s="75" t="n"/>
     </row>
     <row r="36">
-      <c r="A36" s="50" t="n"/>
-      <c r="B36" s="50" t="n"/>
-      <c r="C36" s="50" t="n"/>
-      <c r="D36" s="50" t="n"/>
-      <c r="E36" s="50" t="n"/>
-      <c r="F36" s="50" t="n"/>
-      <c r="G36" s="50" t="n"/>
-      <c r="H36" s="50" t="n"/>
-      <c r="I36" s="50" t="n"/>
-      <c r="J36" s="50" t="n"/>
-      <c r="K36" s="50" t="n"/>
-      <c r="L36" s="50" t="n"/>
-      <c r="M36" s="50" t="n"/>
-      <c r="N36" s="50" t="n"/>
-      <c r="O36" s="50" t="n"/>
-      <c r="P36" s="50" t="n"/>
-      <c r="Q36" s="65">
-        <f>IF(OR(L44="",L44="در انتظار"),"",IF(Q44="",TODAY(),Q44))</f>
-        <v/>
-      </c>
+      <c r="A36" s="74" t="n"/>
+      <c r="B36" s="74" t="n"/>
+      <c r="C36" s="74" t="n"/>
+      <c r="D36" s="74" t="n"/>
+      <c r="E36" s="74" t="n"/>
+      <c r="F36" s="74" t="n"/>
+      <c r="G36" s="74" t="n"/>
+      <c r="H36" s="74" t="n"/>
+      <c r="I36" s="74" t="n"/>
+      <c r="J36" s="74" t="n"/>
+      <c r="K36" s="74" t="n"/>
+      <c r="L36" s="74" t="n"/>
+      <c r="M36" s="74" t="n"/>
+      <c r="N36" s="74" t="n"/>
+      <c r="O36" s="74" t="n"/>
+      <c r="P36" s="74" t="n"/>
+      <c r="Q36" s="75" t="n"/>
     </row>
     <row r="37">
-      <c r="A37" s="50" t="n"/>
-      <c r="B37" s="50" t="n"/>
-      <c r="C37" s="50" t="n"/>
-      <c r="D37" s="50" t="n"/>
-      <c r="E37" s="50" t="n"/>
-      <c r="F37" s="50" t="n"/>
-      <c r="G37" s="50" t="n"/>
-      <c r="H37" s="50" t="n"/>
-      <c r="I37" s="50" t="n"/>
-      <c r="J37" s="50" t="n"/>
-      <c r="K37" s="50" t="n"/>
-      <c r="L37" s="50" t="n"/>
-      <c r="M37" s="50" t="n"/>
-      <c r="N37" s="50" t="n"/>
-      <c r="O37" s="50" t="n"/>
-      <c r="P37" s="50" t="n"/>
-      <c r="Q37" s="65">
-        <f>IF(OR(L45="",L45="در انتظار"),"",IF(Q45="",TODAY(),Q45))</f>
-        <v/>
-      </c>
+      <c r="A37" s="74" t="n"/>
+      <c r="B37" s="74" t="n"/>
+      <c r="C37" s="74" t="n"/>
+      <c r="D37" s="74" t="n"/>
+      <c r="E37" s="74" t="n"/>
+      <c r="F37" s="74" t="n"/>
+      <c r="G37" s="74" t="n"/>
+      <c r="H37" s="74" t="n"/>
+      <c r="I37" s="74" t="n"/>
+      <c r="J37" s="74" t="n"/>
+      <c r="K37" s="74" t="n"/>
+      <c r="L37" s="74" t="n"/>
+      <c r="M37" s="74" t="n"/>
+      <c r="N37" s="74" t="n"/>
+      <c r="O37" s="74" t="n"/>
+      <c r="P37" s="74" t="n"/>
+      <c r="Q37" s="75" t="n"/>
     </row>
     <row r="38">
-      <c r="A38" s="50" t="n"/>
-      <c r="B38" s="50" t="n"/>
-      <c r="C38" s="50" t="n"/>
-      <c r="D38" s="50" t="n"/>
-      <c r="E38" s="50" t="n"/>
-      <c r="F38" s="50" t="n"/>
-      <c r="G38" s="50" t="n"/>
-      <c r="H38" s="50" t="n"/>
-      <c r="I38" s="50" t="n"/>
-      <c r="J38" s="50" t="n"/>
-      <c r="K38" s="50" t="n"/>
-      <c r="L38" s="50" t="n"/>
-      <c r="M38" s="50" t="n"/>
-      <c r="N38" s="50" t="n"/>
-      <c r="O38" s="50" t="n"/>
-      <c r="P38" s="50" t="n"/>
-      <c r="Q38" s="65">
-        <f>IF(OR(L46="",L46="در انتظار"),"",IF(Q46="",TODAY(),Q46))</f>
-        <v/>
-      </c>
+      <c r="A38" s="74" t="n"/>
+      <c r="B38" s="74" t="n"/>
+      <c r="C38" s="74" t="n"/>
+      <c r="D38" s="74" t="n"/>
+      <c r="E38" s="74" t="n"/>
+      <c r="F38" s="74" t="n"/>
+      <c r="G38" s="74" t="n"/>
+      <c r="H38" s="74" t="n"/>
+      <c r="I38" s="74" t="n"/>
+      <c r="J38" s="74" t="n"/>
+      <c r="K38" s="74" t="n"/>
+      <c r="L38" s="74" t="n"/>
+      <c r="M38" s="74" t="n"/>
+      <c r="N38" s="74" t="n"/>
+      <c r="O38" s="74" t="n"/>
+      <c r="P38" s="74" t="n"/>
+      <c r="Q38" s="75" t="n"/>
     </row>
     <row r="39">
-      <c r="A39" s="50" t="n"/>
-      <c r="B39" s="50" t="n"/>
-      <c r="C39" s="50" t="n"/>
-      <c r="D39" s="50" t="n"/>
-      <c r="E39" s="50" t="n"/>
-      <c r="F39" s="50" t="n"/>
-      <c r="G39" s="50" t="n"/>
-      <c r="H39" s="50" t="n"/>
-      <c r="I39" s="50" t="n"/>
-      <c r="J39" s="50" t="n"/>
-      <c r="K39" s="50" t="n"/>
-      <c r="L39" s="50" t="n"/>
-      <c r="M39" s="50" t="n"/>
-      <c r="N39" s="50" t="n"/>
-      <c r="O39" s="50" t="n"/>
-      <c r="P39" s="50" t="n"/>
-      <c r="Q39" s="65">
-        <f>IF(OR(L47="",L47="در انتظار"),"",IF(Q47="",TODAY(),Q47))</f>
-        <v/>
-      </c>
+      <c r="A39" s="74" t="n"/>
+      <c r="B39" s="74" t="n"/>
+      <c r="C39" s="74" t="n"/>
+      <c r="D39" s="74" t="n"/>
+      <c r="E39" s="74" t="n"/>
+      <c r="F39" s="74" t="n"/>
+      <c r="G39" s="74" t="n"/>
+      <c r="H39" s="74" t="n"/>
+      <c r="I39" s="74" t="n"/>
+      <c r="J39" s="74" t="n"/>
+      <c r="K39" s="74" t="n"/>
+      <c r="L39" s="74" t="n"/>
+      <c r="M39" s="74" t="n"/>
+      <c r="N39" s="74" t="n"/>
+      <c r="O39" s="74" t="n"/>
+      <c r="P39" s="74" t="n"/>
+      <c r="Q39" s="75" t="n"/>
     </row>
     <row r="40">
-      <c r="A40" s="50" t="n"/>
-      <c r="B40" s="50" t="n"/>
-      <c r="C40" s="50" t="n"/>
-      <c r="D40" s="50" t="n"/>
-      <c r="E40" s="50" t="n"/>
-      <c r="F40" s="50" t="n"/>
-      <c r="G40" s="50" t="n"/>
-      <c r="H40" s="50" t="n"/>
-      <c r="I40" s="50" t="n"/>
-      <c r="J40" s="50" t="n"/>
-      <c r="K40" s="50" t="n"/>
-      <c r="L40" s="50" t="n"/>
-      <c r="M40" s="50" t="n"/>
-      <c r="N40" s="50" t="n"/>
-      <c r="O40" s="50" t="n"/>
-      <c r="P40" s="50" t="n"/>
-      <c r="Q40" s="65">
-        <f>IF(OR(L48="",L48="در انتظار"),"",IF(Q48="",TODAY(),Q48))</f>
-        <v/>
-      </c>
+      <c r="A40" s="74" t="n"/>
+      <c r="B40" s="74" t="n"/>
+      <c r="C40" s="74" t="n"/>
+      <c r="D40" s="74" t="n"/>
+      <c r="E40" s="74" t="n"/>
+      <c r="F40" s="74" t="n"/>
+      <c r="G40" s="74" t="n"/>
+      <c r="H40" s="74" t="n"/>
+      <c r="I40" s="74" t="n"/>
+      <c r="J40" s="74" t="n"/>
+      <c r="K40" s="74" t="n"/>
+      <c r="L40" s="74" t="n"/>
+      <c r="M40" s="74" t="n"/>
+      <c r="N40" s="74" t="n"/>
+      <c r="O40" s="74" t="n"/>
+      <c r="P40" s="74" t="n"/>
+      <c r="Q40" s="75" t="n"/>
     </row>
     <row r="41">
-      <c r="A41" s="50" t="n"/>
-      <c r="B41" s="50" t="n"/>
-      <c r="C41" s="50" t="n"/>
-      <c r="D41" s="50" t="n"/>
-      <c r="E41" s="50" t="n"/>
-      <c r="F41" s="50" t="n"/>
-      <c r="G41" s="50" t="n"/>
-      <c r="H41" s="50" t="n"/>
-      <c r="I41" s="50" t="n"/>
-      <c r="J41" s="50" t="n"/>
-      <c r="K41" s="50" t="n"/>
-      <c r="L41" s="50" t="n"/>
-      <c r="M41" s="50" t="n"/>
-      <c r="N41" s="50" t="n"/>
-      <c r="O41" s="50" t="n"/>
-      <c r="P41" s="50" t="n"/>
-      <c r="Q41" s="65">
-        <f>IF(OR(L49="",L49="در انتظار"),"",IF(Q49="",TODAY(),Q49))</f>
-        <v/>
-      </c>
+      <c r="A41" s="74" t="n"/>
+      <c r="B41" s="74" t="n"/>
+      <c r="C41" s="74" t="n"/>
+      <c r="D41" s="74" t="n"/>
+      <c r="E41" s="74" t="n"/>
+      <c r="F41" s="74" t="n"/>
+      <c r="G41" s="74" t="n"/>
+      <c r="H41" s="74" t="n"/>
+      <c r="I41" s="74" t="n"/>
+      <c r="J41" s="74" t="n"/>
+      <c r="K41" s="74" t="n"/>
+      <c r="L41" s="74" t="n"/>
+      <c r="M41" s="74" t="n"/>
+      <c r="N41" s="74" t="n"/>
+      <c r="O41" s="74" t="n"/>
+      <c r="P41" s="74" t="n"/>
+      <c r="Q41" s="75" t="n"/>
     </row>
     <row r="42">
-      <c r="A42" s="50" t="n"/>
-      <c r="B42" s="50" t="n"/>
-      <c r="C42" s="50" t="n"/>
-      <c r="D42" s="50" t="n"/>
-      <c r="E42" s="50" t="n"/>
-      <c r="F42" s="50" t="n"/>
-      <c r="G42" s="50" t="n"/>
-      <c r="H42" s="50" t="n"/>
-      <c r="I42" s="50" t="n"/>
-      <c r="J42" s="50" t="n"/>
-      <c r="K42" s="50" t="n"/>
-      <c r="L42" s="50" t="n"/>
-      <c r="M42" s="50" t="n"/>
-      <c r="N42" s="50" t="n"/>
-      <c r="O42" s="50" t="n"/>
-      <c r="P42" s="50" t="n"/>
-      <c r="Q42" s="65">
-        <f>IF(OR(L50="",L50="در انتظار"),"",IF(Q50="",TODAY(),Q50))</f>
-        <v/>
-      </c>
+      <c r="A42" s="74" t="n"/>
+      <c r="B42" s="74" t="n"/>
+      <c r="C42" s="74" t="n"/>
+      <c r="D42" s="74" t="n"/>
+      <c r="E42" s="74" t="n"/>
+      <c r="F42" s="74" t="n"/>
+      <c r="G42" s="74" t="n"/>
+      <c r="H42" s="74" t="n"/>
+      <c r="I42" s="74" t="n"/>
+      <c r="J42" s="74" t="n"/>
+      <c r="K42" s="74" t="n"/>
+      <c r="L42" s="74" t="n"/>
+      <c r="M42" s="74" t="n"/>
+      <c r="N42" s="74" t="n"/>
+      <c r="O42" s="74" t="n"/>
+      <c r="P42" s="74" t="n"/>
+      <c r="Q42" s="75" t="n"/>
     </row>
     <row r="43">
-      <c r="A43" s="50" t="n"/>
-      <c r="B43" s="50" t="n"/>
-      <c r="C43" s="50" t="n"/>
-      <c r="D43" s="50" t="n"/>
-      <c r="E43" s="50" t="n"/>
-      <c r="F43" s="50" t="n"/>
-      <c r="G43" s="50" t="n"/>
-      <c r="H43" s="50" t="n"/>
-      <c r="I43" s="50" t="n"/>
-      <c r="J43" s="50" t="n"/>
-      <c r="K43" s="50" t="n"/>
-      <c r="L43" s="50" t="n"/>
-      <c r="M43" s="50" t="n"/>
-      <c r="N43" s="50" t="n"/>
-      <c r="O43" s="50" t="n"/>
-      <c r="P43" s="50" t="n"/>
-      <c r="Q43" s="65">
-        <f>IF(OR(L51="",L51="در انتظار"),"",IF(Q51="",TODAY(),Q51))</f>
-        <v/>
-      </c>
+      <c r="A43" s="74" t="n"/>
+      <c r="B43" s="74" t="n"/>
+      <c r="C43" s="74" t="n"/>
+      <c r="D43" s="74" t="n"/>
+      <c r="E43" s="74" t="n"/>
+      <c r="F43" s="74" t="n"/>
+      <c r="G43" s="74" t="n"/>
+      <c r="H43" s="74" t="n"/>
+      <c r="I43" s="74" t="n"/>
+      <c r="J43" s="74" t="n"/>
+      <c r="K43" s="74" t="n"/>
+      <c r="L43" s="74" t="n"/>
+      <c r="M43" s="74" t="n"/>
+      <c r="N43" s="74" t="n"/>
+      <c r="O43" s="74" t="n"/>
+      <c r="P43" s="74" t="n"/>
+      <c r="Q43" s="75" t="n"/>
     </row>
     <row r="44">
-      <c r="A44" s="50" t="n"/>
-      <c r="B44" s="50" t="n"/>
-      <c r="C44" s="50" t="n"/>
-      <c r="D44" s="50" t="n"/>
-      <c r="E44" s="50" t="n"/>
-      <c r="F44" s="50" t="n"/>
-      <c r="G44" s="50" t="n"/>
-      <c r="H44" s="50" t="n"/>
-      <c r="I44" s="50" t="n"/>
-      <c r="J44" s="50" t="n"/>
-      <c r="K44" s="50" t="n"/>
-      <c r="L44" s="50" t="n"/>
-      <c r="M44" s="50" t="n"/>
-      <c r="N44" s="50" t="n"/>
-      <c r="O44" s="50" t="n"/>
-      <c r="P44" s="50" t="n"/>
-      <c r="Q44" s="65">
-        <f>IF(OR(L52="",L52="در انتظار"),"",IF(Q52="",TODAY(),Q52))</f>
-        <v/>
-      </c>
+      <c r="A44" s="74" t="n"/>
+      <c r="B44" s="74" t="n"/>
+      <c r="C44" s="74" t="n"/>
+      <c r="D44" s="74" t="n"/>
+      <c r="E44" s="74" t="n"/>
+      <c r="F44" s="74" t="n"/>
+      <c r="G44" s="74" t="n"/>
+      <c r="H44" s="74" t="n"/>
+      <c r="I44" s="74" t="n"/>
+      <c r="J44" s="74" t="n"/>
+      <c r="K44" s="74" t="n"/>
+      <c r="L44" s="74" t="n"/>
+      <c r="M44" s="74" t="n"/>
+      <c r="N44" s="74" t="n"/>
+      <c r="O44" s="74" t="n"/>
+      <c r="P44" s="74" t="n"/>
+      <c r="Q44" s="75" t="n"/>
     </row>
     <row r="45">
-      <c r="A45" s="50" t="n"/>
-      <c r="B45" s="50" t="n"/>
-      <c r="C45" s="50" t="n"/>
-      <c r="D45" s="50" t="n"/>
-      <c r="E45" s="50" t="n"/>
-      <c r="F45" s="50" t="n"/>
-      <c r="G45" s="50" t="n"/>
-      <c r="H45" s="50" t="n"/>
-      <c r="I45" s="50" t="n"/>
-      <c r="J45" s="50" t="n"/>
-      <c r="K45" s="50" t="n"/>
-      <c r="L45" s="50" t="n"/>
-      <c r="M45" s="50" t="n"/>
-      <c r="N45" s="50" t="n"/>
-      <c r="O45" s="50" t="n"/>
-      <c r="P45" s="50" t="n"/>
-      <c r="Q45" s="65">
-        <f>IF(OR(L53="",L53="در انتظار"),"",IF(Q53="",TODAY(),Q53))</f>
-        <v/>
-      </c>
+      <c r="A45" s="74" t="n"/>
+      <c r="B45" s="74" t="n"/>
+      <c r="C45" s="74" t="n"/>
+      <c r="D45" s="74" t="n"/>
+      <c r="E45" s="74" t="n"/>
+      <c r="F45" s="74" t="n"/>
+      <c r="G45" s="74" t="n"/>
+      <c r="H45" s="74" t="n"/>
+      <c r="I45" s="74" t="n"/>
+      <c r="J45" s="74" t="n"/>
+      <c r="K45" s="74" t="n"/>
+      <c r="L45" s="74" t="n"/>
+      <c r="M45" s="74" t="n"/>
+      <c r="N45" s="74" t="n"/>
+      <c r="O45" s="74" t="n"/>
+      <c r="P45" s="74" t="n"/>
+      <c r="Q45" s="75" t="n"/>
     </row>
     <row r="46">
-      <c r="A46" s="50" t="n"/>
-      <c r="B46" s="50" t="n"/>
-      <c r="C46" s="50" t="n"/>
-      <c r="D46" s="50" t="n"/>
-      <c r="E46" s="50" t="n"/>
-      <c r="F46" s="50" t="n"/>
-      <c r="G46" s="50" t="n"/>
-      <c r="H46" s="50" t="n"/>
-      <c r="I46" s="50" t="n"/>
-      <c r="J46" s="50" t="n"/>
-      <c r="K46" s="50" t="n"/>
-      <c r="L46" s="50" t="n"/>
-      <c r="M46" s="50" t="n"/>
-      <c r="N46" s="50" t="n"/>
-      <c r="O46" s="50" t="n"/>
-      <c r="P46" s="50" t="n"/>
-      <c r="Q46" s="65">
-        <f>IF(OR(L54="",L54="در انتظار"),"",IF(Q54="",TODAY(),Q54))</f>
-        <v/>
-      </c>
+      <c r="A46" s="74" t="n"/>
+      <c r="B46" s="74" t="n"/>
+      <c r="C46" s="74" t="n"/>
+      <c r="D46" s="74" t="n"/>
+      <c r="E46" s="74" t="n"/>
+      <c r="F46" s="74" t="n"/>
+      <c r="G46" s="74" t="n"/>
+      <c r="H46" s="74" t="n"/>
+      <c r="I46" s="74" t="n"/>
+      <c r="J46" s="74" t="n"/>
+      <c r="K46" s="74" t="n"/>
+      <c r="L46" s="74" t="n"/>
+      <c r="M46" s="74" t="n"/>
+      <c r="N46" s="74" t="n"/>
+      <c r="O46" s="74" t="n"/>
+      <c r="P46" s="74" t="n"/>
+      <c r="Q46" s="75" t="n"/>
     </row>
     <row r="47">
-      <c r="A47" s="50" t="n"/>
-      <c r="B47" s="50" t="n"/>
-      <c r="C47" s="50" t="n"/>
-      <c r="D47" s="50" t="n"/>
-      <c r="E47" s="50" t="n"/>
-      <c r="F47" s="50" t="n"/>
-      <c r="G47" s="50" t="n"/>
-      <c r="H47" s="50" t="n"/>
-      <c r="I47" s="50" t="n"/>
-      <c r="J47" s="50" t="n"/>
-      <c r="K47" s="50" t="n"/>
-      <c r="L47" s="50" t="n"/>
-      <c r="M47" s="50" t="n"/>
-      <c r="N47" s="50" t="n"/>
-      <c r="O47" s="50" t="n"/>
-      <c r="P47" s="50" t="n"/>
-      <c r="Q47" s="65">
-        <f>IF(OR(L55="",L55="در انتظار"),"",IF(Q55="",TODAY(),Q55))</f>
-        <v/>
-      </c>
+      <c r="A47" s="74" t="n"/>
+      <c r="B47" s="74" t="n"/>
+      <c r="C47" s="74" t="n"/>
+      <c r="D47" s="74" t="n"/>
+      <c r="E47" s="74" t="n"/>
+      <c r="F47" s="74" t="n"/>
+      <c r="G47" s="74" t="n"/>
+      <c r="H47" s="74" t="n"/>
+      <c r="I47" s="74" t="n"/>
+      <c r="J47" s="74" t="n"/>
+      <c r="K47" s="74" t="n"/>
+      <c r="L47" s="74" t="n"/>
+      <c r="M47" s="74" t="n"/>
+      <c r="N47" s="74" t="n"/>
+      <c r="O47" s="74" t="n"/>
+      <c r="P47" s="74" t="n"/>
+      <c r="Q47" s="75" t="n"/>
     </row>
     <row r="48">
-      <c r="A48" s="50" t="n"/>
-      <c r="B48" s="50" t="n"/>
-      <c r="C48" s="50" t="n"/>
-      <c r="D48" s="50" t="n"/>
-      <c r="E48" s="50" t="n"/>
-      <c r="F48" s="50" t="n"/>
-      <c r="G48" s="50" t="n"/>
-      <c r="H48" s="50" t="n"/>
-      <c r="I48" s="50" t="n"/>
-      <c r="J48" s="50" t="n"/>
-      <c r="K48" s="50" t="n"/>
-      <c r="L48" s="50" t="n"/>
-      <c r="M48" s="50" t="n"/>
-      <c r="N48" s="50" t="n"/>
-      <c r="O48" s="50" t="n"/>
-      <c r="P48" s="50" t="n"/>
-      <c r="Q48" s="65">
-        <f>IF(OR(L56="",L56="در انتظار"),"",IF(Q56="",TODAY(),Q56))</f>
-        <v/>
-      </c>
+      <c r="A48" s="74" t="n"/>
+      <c r="B48" s="74" t="n"/>
+      <c r="C48" s="74" t="n"/>
+      <c r="D48" s="74" t="n"/>
+      <c r="E48" s="74" t="n"/>
+      <c r="F48" s="74" t="n"/>
+      <c r="G48" s="74" t="n"/>
+      <c r="H48" s="74" t="n"/>
+      <c r="I48" s="74" t="n"/>
+      <c r="J48" s="74" t="n"/>
+      <c r="K48" s="74" t="n"/>
+      <c r="L48" s="74" t="n"/>
+      <c r="M48" s="74" t="n"/>
+      <c r="N48" s="74" t="n"/>
+      <c r="O48" s="74" t="n"/>
+      <c r="P48" s="74" t="n"/>
+      <c r="Q48" s="75" t="n"/>
     </row>
     <row r="49">
-      <c r="A49" s="50" t="n"/>
-      <c r="B49" s="50" t="n"/>
-      <c r="C49" s="50" t="n"/>
-      <c r="D49" s="50" t="n"/>
-      <c r="E49" s="50" t="n"/>
-      <c r="F49" s="50" t="n"/>
-      <c r="G49" s="50" t="n"/>
-      <c r="H49" s="50" t="n"/>
-      <c r="I49" s="50" t="n"/>
-      <c r="J49" s="50" t="n"/>
-      <c r="K49" s="50" t="n"/>
-      <c r="L49" s="50" t="n"/>
-      <c r="M49" s="50" t="n"/>
-      <c r="N49" s="50" t="n"/>
-      <c r="O49" s="50" t="n"/>
-      <c r="P49" s="50" t="n"/>
-      <c r="Q49" s="65">
-        <f>IF(OR(L57="",L57="در انتظار"),"",IF(Q57="",TODAY(),Q57))</f>
-        <v/>
-      </c>
+      <c r="A49" s="74" t="n"/>
+      <c r="B49" s="74" t="n"/>
+      <c r="C49" s="74" t="n"/>
+      <c r="D49" s="74" t="n"/>
+      <c r="E49" s="74" t="n"/>
+      <c r="F49" s="74" t="n"/>
+      <c r="G49" s="74" t="n"/>
+      <c r="H49" s="74" t="n"/>
+      <c r="I49" s="74" t="n"/>
+      <c r="J49" s="74" t="n"/>
+      <c r="K49" s="74" t="n"/>
+      <c r="L49" s="74" t="n"/>
+      <c r="M49" s="74" t="n"/>
+      <c r="N49" s="74" t="n"/>
+      <c r="O49" s="74" t="n"/>
+      <c r="P49" s="74" t="n"/>
+      <c r="Q49" s="75" t="n"/>
     </row>
     <row r="50">
-      <c r="A50" s="50" t="n"/>
-      <c r="B50" s="50" t="n"/>
-      <c r="C50" s="50" t="n"/>
-      <c r="D50" s="50" t="n"/>
-      <c r="E50" s="50" t="n"/>
-      <c r="F50" s="50" t="n"/>
-      <c r="G50" s="50" t="n"/>
-      <c r="H50" s="50" t="n"/>
-      <c r="I50" s="50" t="n"/>
-      <c r="J50" s="50" t="n"/>
-      <c r="K50" s="50" t="n"/>
-      <c r="L50" s="50" t="n"/>
-      <c r="M50" s="50" t="n"/>
-      <c r="N50" s="50" t="n"/>
-      <c r="O50" s="50" t="n"/>
-      <c r="P50" s="50" t="n"/>
-      <c r="Q50" s="65">
-        <f>IF(OR(L58="",L58="در انتظار"),"",IF(Q58="",TODAY(),Q58))</f>
-        <v/>
-      </c>
+      <c r="A50" s="74" t="n"/>
+      <c r="B50" s="74" t="n"/>
+      <c r="C50" s="74" t="n"/>
+      <c r="D50" s="74" t="n"/>
+      <c r="E50" s="74" t="n"/>
+      <c r="F50" s="74" t="n"/>
+      <c r="G50" s="74" t="n"/>
+      <c r="H50" s="74" t="n"/>
+      <c r="I50" s="74" t="n"/>
+      <c r="J50" s="74" t="n"/>
+      <c r="K50" s="74" t="n"/>
+      <c r="L50" s="74" t="n"/>
+      <c r="M50" s="74" t="n"/>
+      <c r="N50" s="74" t="n"/>
+      <c r="O50" s="74" t="n"/>
+      <c r="P50" s="74" t="n"/>
+      <c r="Q50" s="75" t="n"/>
     </row>
     <row r="51">
-      <c r="A51" s="50" t="n"/>
-      <c r="B51" s="50" t="n"/>
-      <c r="C51" s="50" t="n"/>
-      <c r="D51" s="50" t="n"/>
-      <c r="E51" s="50" t="n"/>
-      <c r="F51" s="50" t="n"/>
-      <c r="G51" s="50" t="n"/>
-      <c r="H51" s="50" t="n"/>
-      <c r="I51" s="50" t="n"/>
-      <c r="J51" s="50" t="n"/>
-      <c r="K51" s="50" t="n"/>
-      <c r="L51" s="50" t="n"/>
-      <c r="M51" s="50" t="n"/>
-      <c r="N51" s="50" t="n"/>
-      <c r="O51" s="50" t="n"/>
-      <c r="P51" s="50" t="n"/>
-      <c r="Q51" s="65">
-        <f>IF(OR(L59="",L59="در انتظار"),"",IF(Q59="",TODAY(),Q59))</f>
-        <v/>
-      </c>
+      <c r="A51" s="74" t="n"/>
+      <c r="B51" s="74" t="n"/>
+      <c r="C51" s="74" t="n"/>
+      <c r="D51" s="74" t="n"/>
+      <c r="E51" s="74" t="n"/>
+      <c r="F51" s="74" t="n"/>
+      <c r="G51" s="74" t="n"/>
+      <c r="H51" s="74" t="n"/>
+      <c r="I51" s="74" t="n"/>
+      <c r="J51" s="74" t="n"/>
+      <c r="K51" s="74" t="n"/>
+      <c r="L51" s="74" t="n"/>
+      <c r="M51" s="74" t="n"/>
+      <c r="N51" s="74" t="n"/>
+      <c r="O51" s="74" t="n"/>
+      <c r="P51" s="74" t="n"/>
+      <c r="Q51" s="75" t="n"/>
     </row>
     <row r="52">
-      <c r="A52" s="50" t="n"/>
-      <c r="B52" s="50" t="n"/>
-      <c r="C52" s="50" t="n"/>
-      <c r="D52" s="50" t="n"/>
-      <c r="E52" s="50" t="n"/>
-      <c r="F52" s="50" t="n"/>
-      <c r="G52" s="50" t="n"/>
-      <c r="H52" s="50" t="n"/>
-      <c r="I52" s="50" t="n"/>
-      <c r="J52" s="50" t="n"/>
-      <c r="K52" s="50" t="n"/>
-      <c r="L52" s="50" t="n"/>
-      <c r="M52" s="50" t="n"/>
-      <c r="N52" s="50" t="n"/>
-      <c r="O52" s="50" t="n"/>
-      <c r="P52" s="50" t="n"/>
-      <c r="Q52" s="65">
-        <f>IF(OR(L60="",L60="در انتظار"),"",IF(Q60="",TODAY(),Q60))</f>
-        <v/>
-      </c>
+      <c r="A52" s="74" t="n"/>
+      <c r="B52" s="74" t="n"/>
+      <c r="C52" s="74" t="n"/>
+      <c r="D52" s="74" t="n"/>
+      <c r="E52" s="74" t="n"/>
+      <c r="F52" s="74" t="n"/>
+      <c r="G52" s="74" t="n"/>
+      <c r="H52" s="74" t="n"/>
+      <c r="I52" s="74" t="n"/>
+      <c r="J52" s="74" t="n"/>
+      <c r="K52" s="74" t="n"/>
+      <c r="L52" s="74" t="n"/>
+      <c r="M52" s="74" t="n"/>
+      <c r="N52" s="74" t="n"/>
+      <c r="O52" s="74" t="n"/>
+      <c r="P52" s="74" t="n"/>
+      <c r="Q52" s="75" t="n"/>
     </row>
     <row r="53">
-      <c r="A53" s="50" t="n"/>
-      <c r="B53" s="50" t="n"/>
-      <c r="C53" s="50" t="n"/>
-      <c r="D53" s="50" t="n"/>
-      <c r="E53" s="50" t="n"/>
-      <c r="F53" s="50" t="n"/>
-      <c r="G53" s="50" t="n"/>
-      <c r="H53" s="50" t="n"/>
-      <c r="I53" s="50" t="n"/>
-      <c r="J53" s="50" t="n"/>
-      <c r="K53" s="50" t="n"/>
-      <c r="L53" s="50" t="n"/>
-      <c r="M53" s="50" t="n"/>
-      <c r="N53" s="50" t="n"/>
-      <c r="O53" s="50" t="n"/>
-      <c r="P53" s="50" t="n"/>
-      <c r="Q53" s="65">
-        <f>IF(OR(L61="",L61="در انتظار"),"",IF(Q61="",TODAY(),Q61))</f>
-        <v/>
-      </c>
+      <c r="A53" s="74" t="n"/>
+      <c r="B53" s="74" t="n"/>
+      <c r="C53" s="74" t="n"/>
+      <c r="D53" s="74" t="n"/>
+      <c r="E53" s="74" t="n"/>
+      <c r="F53" s="74" t="n"/>
+      <c r="G53" s="74" t="n"/>
+      <c r="H53" s="74" t="n"/>
+      <c r="I53" s="74" t="n"/>
+      <c r="J53" s="74" t="n"/>
+      <c r="K53" s="74" t="n"/>
+      <c r="L53" s="74" t="n"/>
+      <c r="M53" s="74" t="n"/>
+      <c r="N53" s="74" t="n"/>
+      <c r="O53" s="74" t="n"/>
+      <c r="P53" s="74" t="n"/>
+      <c r="Q53" s="75" t="n"/>
     </row>
   </sheetData>
   <autoFilter ref="A4:Q60"/>
   <dataValidations count="2">
-    <dataValidation sqref="C5:C101" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="C5:C13" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>='فهرست‌ها'!$B$9:$B$11</formula1>
     </dataValidation>
-    <dataValidation sqref="L5:L101" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" prompt="وضعیت تست را از فهرست انتخاب کنید" type="list">
+    <dataValidation sqref="L5:L13" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>='فهرست‌ها'!$A$2:$A$7</formula1>
     </dataValidation>
   </dataValidations>
   <hyperlinks>
     <hyperlink ref="D5" location="'برنامه تست'!A12"/>
     <hyperlink ref="D7" location="'برنامه تست'!A6"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N19" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N20" r:id="rId2"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
@@ -4241,8 +4102,6 @@
           <t>ماشین حالت ماژول جدول کالیبراسیون (CalLut)</t>
         </is>
       </c>
-      <c r="B1" s="50" t="n"/>
-      <c r="C1" s="50" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="50" t="n"/>

--- a/Firmware/Modules/CalLut/CalLut_Validation.xlsx
+++ b/Firmware/Modules/CalLut/CalLut_Validation.xlsx
@@ -886,6 +886,7 @@
         </is>
       </c>
     </row>
+    <row r="11"/>
     <row r="12">
       <c r="A12" s="73" t="inlineStr">
         <is>
@@ -1183,7 +1184,7 @@
       </c>
       <c r="C6" s="60" t="inlineStr">
         <is>
-          <t>بالا</t>
+          <t>متوسط</t>
         </is>
       </c>
       <c r="D6" s="59" t="inlineStr">
@@ -1267,7 +1268,7 @@
       </c>
       <c r="C7" s="54" t="inlineStr">
         <is>
-          <t>بالا</t>
+          <t>متوسط</t>
         </is>
       </c>
       <c r="D7" s="55" t="inlineStr">

--- a/Firmware/Modules/CalLut/CalLut_Validation.xlsx
+++ b/Firmware/Modules/CalLut/CalLut_Validation.xlsx
@@ -830,7 +830,7 @@
     <row r="2">
       <c r="A2" s="46" t="inlineStr">
         <is>
-          <t>CalLut | نگهداری جدول کالیبراسیون بنچ در بلوک فلش اختصاصی با CRC32 و بازگشت به جدول کامپایل‌شده</t>
+          <t>CalLut | جدول کالیبراسیون در جای جدا در حافظهٔ ماندگار (فلش) ذخیره می‌شود. برایش کنترل صحت (CRC32) داریم. اگر جدول خراب شود، دستگاه به جدول پیش‌فرض برمی‌گردد.</t>
         </is>
       </c>
     </row>
@@ -847,42 +847,52 @@
     <row r="5">
       <c r="A5" s="46" t="inlineStr">
         <is>
-          <t>مسیر ذخیرهٔ جدول کالیبراسیون بنچ در «بلوک فلش مخصوص خودش»: دو صفحهٔ ۱KB در 0x0800F000 و 0x0800F400، پینگ‌پنگ امن در برابر قطع برق، مجیک/نسخه/CRC32 مستقل.</t>
+          <t>جدول در دو صفحهٔ جدا از فلش ذخیره می‌شود. هر صفحه ۱ کیلوبایت است. نشانی دو صفحه: 0x0800F000 و 0x0800F400.
+هر بار فقط یکی از دو صفحه نوشته می‌شود. پس اگر وسط نوشتن برق برود، صفحهٔ دیگر سالم می‌ماند.
+هر رکورد برای خودش نسخه و کنترل صحت (CRC32) دارد.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="48" t="inlineStr">
         <is>
-          <t>هیچ اشتراکی با esp_link_nvm.c جز درایور فلش ندارد؛ پس فرستادن جدول هرگز رکورد پارامترها را خراب نمی‌کند و برعکس.</t>
+          <t>این جدول جای جدا دارد و با رکورد تنظیمات (esp_link_nvm.c) قاطی نمی‌شود.
+پس فرستادن جدول، تنظیمات را خراب نمی‌کند. فرستادن تنظیمات هم جدول را خراب نمی‌کند.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="46" t="inlineStr">
         <is>
-          <t>جدول کامپایل‌شده وجود ندارد. وقتی رکورد معتبر در فلش نباشد، خط گین و آفست (پیش‌فرض گین 3000، آفست 0) استفاده می‌شود؛ وقتی رکورد معتبر در فلش باشد از آن استفاده می‌شود.</t>
+          <t>جدول آماده‌ای داخل برنامه نیست.
+اگر در فلش رکورد سالمی نباشد، دستگاه با خط پیش‌فرض کار می‌کند: گین 3000 و آفست 0.
+اگر رکورد سالم باشد، همان رکورد استفاده می‌شود.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="46" t="inlineStr">
         <is>
-          <t>دست‌دادن: LUT_BEGIN → LUT_CHUNK → LUT_COMMIT (با CRC32 پنل) → LUT_ACK (با CRC32 خودِ برد از آنچه در فلش است) → تنها در صورت برابری، LUT_RESET.</t>
+          <t>ترتیب فرستادن جدول از پنل:
+۱) شروع (LUT_BEGIN)
+۲) تکه‌تکه فرستادن جدول (LUT_CHUNK)
+۳) پایان و اعلام کنترل صحت (CRC32) از پنل (LUT_COMMIT)
+۴) برد از چیزی که در فلش نوشته، کنترل صحت (CRC32) می‌گیرد و برمی‌گرداند (LUT_ACK)
+۵) فقط اگر دو کنترل صحت یکی بود، برد ریست می‌شود (LUT_RESET) تا جدول تازه فعال شود.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="46" t="inlineStr">
         <is>
-          <t>هدف این برگه: اثبات روی برد که نوشتن، بازخوانی، اعتبارسنجی و بازگشت به پشتیبان همگی همان‌طور کار می‌کنند که هدر ادعا می‌کند.</t>
+          <t>هدف این برگه ساده است: روی برد واقعی ثابت کنیم که نوشتن جدول، خواندن دوباره‌اش، چک‌کردن درستی‌اش و برگشت به جدول پشتیبان، همه درست کار می‌کنند.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="46" t="inlineStr">
         <is>
-          <t>تست Host (کامپایل و اجرا روی PC با شبیه‌سازی RAM) جایگزین این تست‌ها نیست.</t>
+          <t>تست روی کامپیوتر (اجرای برنامه روی PC با حافظهٔ شبیه‌سازی‌شده) جای این تست‌های برد را نمی‌گیرد.</t>
         </is>
       </c>
     </row>
@@ -890,8 +900,12 @@
     <row r="12">
       <c r="A12" s="73" t="inlineStr">
         <is>
-          <t>اولویت تست‌های عملی: «بالا» یعنی رفتار اصلی‌ای که در کار عادی دستگاه می‌بینید (روشن‌شدن، شروع و پایان شارژ، چهره‌های اصلی چراغ‌ها، رفتن تغذیه روی برق ورودی، خطاهای اصلی)؛ اول همین‌ها را انجام دهید. «متوسط» رفتارهای فرعیِ کاربردی است و «پایین» ریزه‌کاری‌ها (مثل اثر نوسان چند درصدی روی ریتم چشمک یا لبه‌های دقیق درصد و زمان).
-ستون «چه چیزی باید ببینید تا بگویید درست است» می‌گوید دقیقاً چه چیزی را باید ببینید یا بشنوید تا آن تست را قبول کنید؛ اگر چیز دیگری دیدید، وضعیت را «رد» بزنید و در شرح ایراد بنویسید چه دیدید.</t>
+          <t>اولویت‌ها ساده‌اند:
+«بالا» یعنی اول همین‌ها را تست کن. این‌ها کارهای اصلی دستگاه‌اند: روشن‌شدن، شروع و پایان شارژ، چراغ‌های اصلی، رفتن تغذیه روی برق ورودی و خطاهای اصلی.
+«متوسط» یعنی کارهای فرعی ولی کاربردی.
+«پایین» یعنی ریزه‌کاری‌ها؛ مثل اثر نوسان کوچک روی ریتم چشمک.
+در ستون «چه چیزی باید ببینید تا بگویید درست است» نوشته‌ایم دقیقاً چه باید ببینی یا بشنوی.
+اگر چیز دیگری دیدی، وضعیت را «رد» بزن و در «شرح ایراد» بنویس چه دیدی.</t>
         </is>
       </c>
     </row>
@@ -1044,7 +1058,7 @@
       </c>
       <c r="I4" s="47" t="inlineStr">
         <is>
-          <t>وضعیت حفظ / latch</t>
+          <t>می‌ماند یا پاک می‌شود</t>
         </is>
       </c>
       <c r="J4" s="47" t="inlineStr">
@@ -1069,12 +1083,12 @@
       </c>
       <c r="N4" s="47" t="inlineStr">
         <is>
-          <t>مدرک تست / scope</t>
+          <t>مدرک تست</t>
         </is>
       </c>
       <c r="O4" s="47" t="inlineStr">
         <is>
-          <t>commit</t>
+          <t>نسخهٔ برنامه</t>
         </is>
       </c>
       <c r="P4" s="47" t="inlineStr">
@@ -1153,17 +1167,17 @@
       <c r="M5" s="53" t="n"/>
       <c r="N5" s="53" t="inlineStr">
         <is>
-          <t>TESTER: fill</t>
+          <t>(بعد از تست پر شود)</t>
         </is>
       </c>
       <c r="O5" s="56" t="inlineStr">
         <is>
-          <t>TESTER: fill</t>
+          <t>(بعد از تست پر شود)</t>
         </is>
       </c>
       <c r="P5" s="56" t="inlineStr">
         <is>
-          <t>TESTER: fill</t>
+          <t>(بعد از تست پر شود)</t>
         </is>
       </c>
       <c r="Q5" s="58">
@@ -1237,17 +1251,17 @@
       <c r="M6" s="59" t="n"/>
       <c r="N6" s="59" t="inlineStr">
         <is>
-          <t>TESTER: fill</t>
+          <t>(بعد از تست پر شود)</t>
         </is>
       </c>
       <c r="O6" s="61" t="inlineStr">
         <is>
-          <t>TESTER: fill</t>
+          <t>(بعد از تست پر شود)</t>
         </is>
       </c>
       <c r="P6" s="61" t="inlineStr">
         <is>
-          <t>TESTER: fill</t>
+          <t>(بعد از تست پر شود)</t>
         </is>
       </c>
       <c r="Q6" s="62">
@@ -1320,17 +1334,17 @@
       <c r="M7" s="53" t="n"/>
       <c r="N7" s="53" t="inlineStr">
         <is>
-          <t>TESTER: fill</t>
+          <t>(بعد از تست پر شود)</t>
         </is>
       </c>
       <c r="O7" s="56" t="inlineStr">
         <is>
-          <t>TESTER: fill</t>
+          <t>(بعد از تست پر شود)</t>
         </is>
       </c>
       <c r="P7" s="56" t="inlineStr">
         <is>
-          <t>TESTER: fill</t>
+          <t>(بعد از تست پر شود)</t>
         </is>
       </c>
       <c r="Q7" s="58">
@@ -1404,17 +1418,17 @@
       <c r="M8" s="59" t="n"/>
       <c r="N8" s="59" t="inlineStr">
         <is>
-          <t>TESTER: fill</t>
+          <t>(بعد از تست پر شود)</t>
         </is>
       </c>
       <c r="O8" s="61" t="inlineStr">
         <is>
-          <t>TESTER: fill</t>
+          <t>(بعد از تست پر شود)</t>
         </is>
       </c>
       <c r="P8" s="61" t="inlineStr">
         <is>
-          <t>TESTER: fill</t>
+          <t>(بعد از تست پر شود)</t>
         </is>
       </c>
       <c r="Q8" s="62">
@@ -1488,17 +1502,17 @@
       <c r="M9" s="53" t="n"/>
       <c r="N9" s="53" t="inlineStr">
         <is>
-          <t>TESTER: fill</t>
+          <t>(بعد از تست پر شود)</t>
         </is>
       </c>
       <c r="O9" s="56" t="inlineStr">
         <is>
-          <t>TESTER: fill</t>
+          <t>(بعد از تست پر شود)</t>
         </is>
       </c>
       <c r="P9" s="56" t="inlineStr">
         <is>
-          <t>TESTER: fill</t>
+          <t>(بعد از تست پر شود)</t>
         </is>
       </c>
       <c r="Q9" s="58">
@@ -1560,7 +1574,8 @@
       </c>
       <c r="K10" s="59" t="inlineStr">
         <is>
-          <t>Host PASS: 159 check؛ شامل دو فریم واقعی LUT_DATA، battery 2 مستقل و transition غیرصفر→صفر؛ برد فیزیکی pending</t>
+          <t>تست روی کامپیوتر قبول شد: 159 بررسی. دو فریم واقعی جدول (LUT_DATA) هم بود، باتری ۲ جدا بود و گذر از ناصفر به صفر هم چک شد.
+تست روی برد هنوز انجام نشده است.</t>
         </is>
       </c>
       <c r="L10" s="57" t="inlineStr">
@@ -1570,7 +1585,7 @@
       </c>
       <c r="M10" s="59" t="inlineStr">
         <is>
-          <t>Host جای اندازه‌گیری برد را نمی‌گیرد؛ فلش و readback روی برد واقعی لازم است</t>
+          <t>تست روی کامپیوتر جای اندازه‌گیری روی برد را نمی‌گیرد. فلش و خواندن دوبارهٔ جدول باید روی برد واقعی انجام شود.</t>
         </is>
       </c>
       <c r="N10" s="59" t="inlineStr">
@@ -1607,18 +1622,18 @@
       </c>
       <c r="D11" s="55" t="inlineStr">
         <is>
-          <t>یک کانال جدول سفارشی (override) دارد و با آن شارژ می‌کند</t>
+          <t>یک کانال جدول سفارشی دارد و با همان شارژ می‌کند.</t>
         </is>
       </c>
       <c r="E11" s="55" t="inlineStr">
         <is>
-          <t>گام ۱: از پنل override همان کانال را با نقطهٔ صفر پاک کن.
-گام ۲: یک شارژ واقعی با همان کانال بگیر.</t>
+          <t>گام ۱: از پنل، جدول سفارشی همان کانال را با نقطهٔ صفر پاک کن.
+گام ۲: با همان کانال یک شارژ واقعی انجام بده.</t>
         </is>
       </c>
       <c r="F11" s="56" t="inlineStr">
         <is>
-          <t>پاک‌کردن override از پنل</t>
+          <t>پاک‌کردن جدول سفارشی از پنل</t>
         </is>
       </c>
       <c r="G11" s="56" t="inlineStr">
@@ -1643,7 +1658,8 @@
       </c>
       <c r="K11" s="53" t="inlineStr">
         <is>
-          <t>Host PASS: 159 check؛ board physical pending</t>
+          <t>تست روی کامپیوتر قبول شد: 159 بررسی.
+تست روی برد هنوز انجام نشده است.</t>
         </is>
       </c>
       <c r="L11" s="57" t="inlineStr">
@@ -1653,7 +1669,7 @@
       </c>
       <c r="M11" s="53" t="inlineStr">
         <is>
-          <t>Host جای تست برد را نمی‌گیرد؛ حذف override و ماندگاری پس از reset روی برد واقعی لازم است</t>
+          <t>تست روی کامپیوتر جای تست برد را نمی‌گیرد. پاک‌شدن جدول سفارشی و ماندنش بعد از ریست باید روی برد واقعی چک شود.</t>
         </is>
       </c>
       <c r="N11" s="55" t="inlineStr">
@@ -1727,7 +1743,8 @@
       </c>
       <c r="K12" s="59" t="inlineStr">
         <is>
-          <t>Host PASS: CalLut=159، parser=14 و NVM؛ تست فیزیکی فلش/ریست/باتری انجام نشده و pending است</t>
+          <t>تست روی کامپیوتر قبول شد: برای CalLut تعداد 159 بررسی، برای پارسر 14 بررسی و برای حافظهٔ ماندگار (NVM) هم قبول شد.
+تست فیزیکی فلش و ریست و باتری هنوز انجام نشده است.</t>
         </is>
       </c>
       <c r="L12" s="57" t="inlineStr">
@@ -1737,7 +1754,8 @@
       </c>
       <c r="M12" s="59" t="inlineStr">
         <is>
-          <t>Host جای تست فیزیکی برد و fault واقعی NVM را نمی‌گیرد؛ commit zero-point، reset و flush روی برد واقعی تکرار شود</t>
+          <t>تست روی کامپیوتر جای تست فیزیکی برد و خطای واقعی حافظه (NVM) را نمی‌گیرد.
+ثبت نقطهٔ صفر، ریست و خالی‌کردن حافظه (flush) باید روی برد واقعی دوباره انجام شود.</t>
         </is>
       </c>
       <c r="N12" s="63" t="inlineStr">
@@ -2748,7 +2766,7 @@
       </c>
       <c r="I4" s="47" t="inlineStr">
         <is>
-          <t>وضعیت حفظ / latch</t>
+          <t>می‌ماند یا پاک می‌شود</t>
         </is>
       </c>
       <c r="J4" s="47" t="inlineStr">
@@ -2773,12 +2791,12 @@
       </c>
       <c r="N4" s="47" t="inlineStr">
         <is>
-          <t>مدرک تست / scope</t>
+          <t>مدرک تست</t>
         </is>
       </c>
       <c r="O4" s="47" t="inlineStr">
         <is>
-          <t>commit</t>
+          <t>نسخهٔ برنامه</t>
         </is>
       </c>
       <c r="P4" s="47" t="inlineStr">
@@ -2859,17 +2877,17 @@
       <c r="M5" s="59" t="n"/>
       <c r="N5" s="59" t="inlineStr">
         <is>
-          <t>TESTER: fill</t>
+          <t>(بعد از تست پر شود)</t>
         </is>
       </c>
       <c r="O5" s="61" t="inlineStr">
         <is>
-          <t>TESTER: fill</t>
+          <t>(بعد از تست پر شود)</t>
         </is>
       </c>
       <c r="P5" s="61" t="inlineStr">
         <is>
-          <t>TESTER: fill</t>
+          <t>(بعد از تست پر شود)</t>
         </is>
       </c>
       <c r="Q5" s="62" t="inlineStr">
@@ -3701,7 +3719,7 @@
       </c>
       <c r="J3" s="67" t="inlineStr">
         <is>
-          <t>commit firmware</t>
+          <t>نسخهٔ برنامه</t>
         </is>
       </c>
       <c r="K3" s="67" t="inlineStr">
@@ -3822,12 +3840,12 @@
     <row r="8">
       <c r="A8" s="46" t="inlineStr">
         <is>
-          <t>commit firmware</t>
+          <t>نسخهٔ برنامه</t>
         </is>
       </c>
       <c r="B8" s="46" t="inlineStr">
         <is>
-          <t>TESTER: fill</t>
+          <t>(بعد از تست پر شود)</t>
         </is>
       </c>
       <c r="C8" s="50" t="n"/>
@@ -4315,7 +4333,7 @@
       </c>
       <c r="I4" s="47" t="inlineStr">
         <is>
-          <t>وضعیت حفظ / latch</t>
+          <t>می‌ماند یا پاک می‌شود</t>
         </is>
       </c>
       <c r="J4" s="47" t="inlineStr">
@@ -4340,12 +4358,12 @@
       </c>
       <c r="N4" s="47" t="inlineStr">
         <is>
-          <t>مدرک تست / scope</t>
+          <t>مدرک تست</t>
         </is>
       </c>
       <c r="O4" s="47" t="inlineStr">
         <is>
-          <t>commit</t>
+          <t>نسخهٔ برنامه</t>
         </is>
       </c>
       <c r="P4" s="47" t="inlineStr">
@@ -4426,17 +4444,17 @@
       <c r="M5" s="59" t="n"/>
       <c r="N5" s="59" t="inlineStr">
         <is>
-          <t>TESTER: fill</t>
+          <t>(بعد از تست پر شود)</t>
         </is>
       </c>
       <c r="O5" s="61" t="inlineStr">
         <is>
-          <t>TESTER: fill</t>
+          <t>(بعد از تست پر شود)</t>
         </is>
       </c>
       <c r="P5" s="61" t="inlineStr">
         <is>
-          <t>TESTER: fill</t>
+          <t>(بعد از تست پر شود)</t>
         </is>
       </c>
       <c r="Q5" s="62">
@@ -4511,17 +4529,17 @@
       <c r="M6" s="53" t="n"/>
       <c r="N6" s="53" t="inlineStr">
         <is>
-          <t>TESTER: fill</t>
+          <t>(بعد از تست پر شود)</t>
         </is>
       </c>
       <c r="O6" s="56" t="inlineStr">
         <is>
-          <t>TESTER: fill</t>
+          <t>(بعد از تست پر شود)</t>
         </is>
       </c>
       <c r="P6" s="56" t="inlineStr">
         <is>
-          <t>TESTER: fill</t>
+          <t>(بعد از تست پر شود)</t>
         </is>
       </c>
       <c r="Q6" s="58">
@@ -4596,17 +4614,17 @@
       <c r="M7" s="59" t="n"/>
       <c r="N7" s="59" t="inlineStr">
         <is>
-          <t>TESTER: fill</t>
+          <t>(بعد از تست پر شود)</t>
         </is>
       </c>
       <c r="O7" s="61" t="inlineStr">
         <is>
-          <t>TESTER: fill</t>
+          <t>(بعد از تست پر شود)</t>
         </is>
       </c>
       <c r="P7" s="61" t="inlineStr">
         <is>
-          <t>TESTER: fill</t>
+          <t>(بعد از تست پر شود)</t>
         </is>
       </c>
       <c r="Q7" s="62">
@@ -4681,17 +4699,17 @@
       <c r="M8" s="53" t="n"/>
       <c r="N8" s="53" t="inlineStr">
         <is>
-          <t>TESTER: fill</t>
+          <t>(بعد از تست پر شود)</t>
         </is>
       </c>
       <c r="O8" s="56" t="inlineStr">
         <is>
-          <t>TESTER: fill</t>
+          <t>(بعد از تست پر شود)</t>
         </is>
       </c>
       <c r="P8" s="56" t="inlineStr">
         <is>
-          <t>TESTER: fill</t>
+          <t>(بعد از تست پر شود)</t>
         </is>
       </c>
       <c r="Q8" s="58">
@@ -4766,17 +4784,17 @@
       <c r="M9" s="59" t="n"/>
       <c r="N9" s="59" t="inlineStr">
         <is>
-          <t>TESTER: fill</t>
+          <t>(بعد از تست پر شود)</t>
         </is>
       </c>
       <c r="O9" s="61" t="inlineStr">
         <is>
-          <t>TESTER: fill</t>
+          <t>(بعد از تست پر شود)</t>
         </is>
       </c>
       <c r="P9" s="61" t="inlineStr">
         <is>
-          <t>TESTER: fill</t>
+          <t>(بعد از تست پر شود)</t>
         </is>
       </c>
       <c r="Q9" s="62">
@@ -4850,17 +4868,17 @@
       <c r="M10" s="53" t="n"/>
       <c r="N10" s="53" t="inlineStr">
         <is>
-          <t>TESTER: fill</t>
+          <t>(بعد از تست پر شود)</t>
         </is>
       </c>
       <c r="O10" s="56" t="inlineStr">
         <is>
-          <t>TESTER: fill</t>
+          <t>(بعد از تست پر شود)</t>
         </is>
       </c>
       <c r="P10" s="56" t="inlineStr">
         <is>
-          <t>TESTER: fill</t>
+          <t>(بعد از تست پر شود)</t>
         </is>
       </c>
       <c r="Q10" s="58">
@@ -4935,17 +4953,17 @@
       <c r="M11" s="53" t="n"/>
       <c r="N11" s="53" t="inlineStr">
         <is>
-          <t>TESTER: fill</t>
+          <t>(بعد از تست پر شود)</t>
         </is>
       </c>
       <c r="O11" s="56" t="inlineStr">
         <is>
-          <t>TESTER: fill</t>
+          <t>(بعد از تست پر شود)</t>
         </is>
       </c>
       <c r="P11" s="56" t="inlineStr">
         <is>
-          <t>TESTER: fill</t>
+          <t>(بعد از تست پر شود)</t>
         </is>
       </c>
       <c r="Q11" s="58">

--- a/Firmware/Modules/CalLut/CalLut_Validation.xlsx
+++ b/Firmware/Modules/CalLut/CalLut_Validation.xlsx
@@ -14,8 +14,8 @@
     <sheet name="ثبت ایراد" sheetId="5" state="visible" r:id="rId5"/>
     <sheet name="تأیید نهایی" sheetId="6" state="visible" r:id="rId6"/>
     <sheet name="فهرست‌ها" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="ماشین حالت" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="تست‌های برنامه‌نویسی" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="تست‌های برنامه‌نویسی" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="ماشین حالت" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'برنامه تست'!$A$4:$Q$60</definedName>
@@ -176,7 +176,7 @@
       <sz val="11"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="10">
     <fill>
       <patternFill/>
     </fill>
@@ -211,6 +211,16 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00FCE4D6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="001F4E79"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFFFFF"/>
       </patternFill>
     </fill>
   </fills>
@@ -255,7 +265,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="76">
+  <cellXfs count="85">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -448,6 +458,31 @@
     <xf numFmtId="0" fontId="26" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="26" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="26" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="8" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="9" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="9" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="9" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="9" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="9" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -821,7 +856,7 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="45" t="inlineStr">
+      <c r="A1" s="76" t="inlineStr">
         <is>
           <t>برگه تست و اعتبارسنجی عملی ماژول CalLut</t>
         </is>
@@ -835,7 +870,7 @@
       </c>
     </row>
     <row r="3" ht="30" customHeight="1">
-      <c r="A3" s="47" t="inlineStr">
+      <c r="A3" s="77" t="inlineStr">
         <is>
           <t>هدف فایل</t>
         </is>
@@ -947,7 +982,7 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="49" t="inlineStr">
+      <c r="A1" s="78" t="inlineStr">
         <is>
           <t>برنامهٔ تست عملی — ماژول CalLut</t>
         </is>
@@ -1016,87 +1051,87 @@
       <c r="Q3" s="50" t="n"/>
     </row>
     <row r="4" ht="30" customHeight="1">
-      <c r="A4" s="47" t="inlineStr">
+      <c r="A4" s="77" t="inlineStr">
         <is>
           <t>شناسه</t>
         </is>
       </c>
-      <c r="B4" s="47" t="inlineStr">
+      <c r="B4" s="77" t="inlineStr">
         <is>
           <t>دسته</t>
         </is>
       </c>
-      <c r="C4" s="47" t="inlineStr">
+      <c r="C4" s="77" t="inlineStr">
         <is>
           <t>اولویت</t>
         </is>
       </c>
-      <c r="D4" s="47" t="inlineStr">
+      <c r="D4" s="77" t="inlineStr">
         <is>
           <t>پیش‌شرط</t>
         </is>
       </c>
-      <c r="E4" s="47" t="inlineStr">
+      <c r="E4" s="77" t="inlineStr">
         <is>
           <t>روش اجرای دقیق</t>
         </is>
       </c>
-      <c r="F4" s="47" t="inlineStr">
+      <c r="F4" s="77" t="inlineStr">
         <is>
           <t>ورودی‌ها / شرایط</t>
         </is>
       </c>
-      <c r="G4" s="47" t="inlineStr">
+      <c r="G4" s="77" t="inlineStr">
         <is>
           <t>مدت مشاهده</t>
         </is>
       </c>
-      <c r="H4" s="47" t="inlineStr">
+      <c r="H4" s="77" t="inlineStr">
         <is>
           <t>رفتار مورد انتظار</t>
         </is>
       </c>
-      <c r="I4" s="47" t="inlineStr">
+      <c r="I4" s="77" t="inlineStr">
         <is>
           <t>می‌ماند یا پاک می‌شود</t>
         </is>
       </c>
-      <c r="J4" s="47" t="inlineStr">
+      <c r="J4" s="77" t="inlineStr">
         <is>
           <t>چه چیزی باید ببینید تا بگویید درست است</t>
         </is>
       </c>
-      <c r="K4" s="47" t="inlineStr">
+      <c r="K4" s="77" t="inlineStr">
         <is>
           <t>نتیجهٔ واقعی / اندازه‌گیری</t>
         </is>
       </c>
-      <c r="L4" s="47" t="inlineStr">
+      <c r="L4" s="77" t="inlineStr">
         <is>
           <t>وضعیت</t>
         </is>
       </c>
-      <c r="M4" s="47" t="inlineStr">
+      <c r="M4" s="77" t="inlineStr">
         <is>
           <t>شرح ایراد / تفاوت</t>
         </is>
       </c>
-      <c r="N4" s="47" t="inlineStr">
+      <c r="N4" s="77" t="inlineStr">
         <is>
           <t>مدرک تست</t>
         </is>
       </c>
-      <c r="O4" s="47" t="inlineStr">
+      <c r="O4" s="77" t="inlineStr">
         <is>
           <t>نسخهٔ برنامه</t>
         </is>
       </c>
-      <c r="P4" s="47" t="inlineStr">
+      <c r="P4" s="77" t="inlineStr">
         <is>
           <t>نام تست‌کننده</t>
         </is>
       </c>
-      <c r="Q4" s="47" t="inlineStr">
+      <c r="Q4" s="77" t="inlineStr">
         <is>
           <t>تاریخ</t>
         </is>
@@ -1108,53 +1143,53 @@
           <t>CL-001</t>
         </is>
       </c>
-      <c r="B5" s="53" t="inlineStr">
+      <c r="B5" s="59" t="inlineStr">
         <is>
           <t>بوت بدون رکورد</t>
         </is>
       </c>
-      <c r="C5" s="54" t="inlineStr">
+      <c r="C5" s="60" t="inlineStr">
         <is>
           <t>بالا</t>
         </is>
       </c>
-      <c r="D5" s="55" t="inlineStr">
+      <c r="D5" s="63" t="inlineStr">
         <is>
           <t>دستگاه تازه است یا جدولش را تازه پاک کرده‌ای (CL-016)؛ باتری و برق شهر آماده</t>
         </is>
       </c>
-      <c r="E5" s="53" t="inlineStr">
+      <c r="E5" s="59" t="inlineStr">
         <is>
           <t>گام ۱: دستگاه را روشن کن و یک باتری نیمه‌خالی را به شارژ بزن.
 گام ۲: چند دقیقه رفتار شارژ را نگاه کن.</t>
         </is>
       </c>
-      <c r="F5" s="56" t="inlineStr">
+      <c r="F5" s="61" t="inlineStr">
         <is>
           <t>روشن‌کردن و شارژ بدون جدول سفارشی</t>
         </is>
       </c>
-      <c r="G5" s="56" t="inlineStr">
+      <c r="G5" s="61" t="inlineStr">
         <is>
           <t>پنج دقیقه</t>
         </is>
       </c>
-      <c r="H5" s="53" t="inlineStr">
+      <c r="H5" s="59" t="inlineStr">
         <is>
           <t>شارژ با جدول پیش‌فرض کارخانه کاملاً عادی کار می‌کند؛ هیچ خطای جدولی نیست</t>
         </is>
       </c>
-      <c r="I5" s="53" t="inlineStr">
+      <c r="I5" s="59" t="inlineStr">
         <is>
           <t>رفتار پیش‌فرض</t>
         </is>
       </c>
-      <c r="J5" s="53" t="inlineStr">
+      <c r="J5" s="59" t="inlineStr">
         <is>
           <t>باید ببینید: شارژ با جدول پیش‌فرض کارخانه کاملاً عادی کار می‌کند و هیچ خطای جدولی نیست. اگر شارژ خراب بود یا خطا آمد، قبول نیست.</t>
         </is>
       </c>
-      <c r="K5" s="53" t="inlineStr">
+      <c r="K5" s="59" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
@@ -1165,22 +1200,22 @@
         </is>
       </c>
       <c r="M5" s="53" t="n"/>
-      <c r="N5" s="53" t="inlineStr">
+      <c r="N5" s="59" t="inlineStr">
         <is>
           <t>(بعد از تست پر شود)</t>
         </is>
       </c>
-      <c r="O5" s="56" t="inlineStr">
+      <c r="O5" s="61" t="inlineStr">
         <is>
           <t>(بعد از تست پر شود)</t>
         </is>
       </c>
-      <c r="P5" s="56" t="inlineStr">
+      <c r="P5" s="61" t="inlineStr">
         <is>
           <t>(بعد از تست پر شود)</t>
         </is>
       </c>
-      <c r="Q5" s="58">
+      <c r="Q5" s="62">
         <f>IF(OR(L5="",L5="در انتظار"),"",IF(Q5="",TODAY(),Q5))</f>
         <v/>
       </c>
@@ -1191,54 +1226,54 @@
           <t>CL-002</t>
         </is>
       </c>
-      <c r="B6" s="59" t="inlineStr">
+      <c r="B6" s="79" t="inlineStr">
         <is>
           <t>push سالم کانال ۱</t>
         </is>
       </c>
-      <c r="C6" s="60" t="inlineStr">
+      <c r="C6" s="80" t="inlineStr">
         <is>
           <t>متوسط</t>
         </is>
       </c>
-      <c r="D6" s="59" t="inlineStr">
+      <c r="D6" s="79" t="inlineStr">
         <is>
           <t>پنل باز است و جدول درست یک کانال را آماده داری</t>
         </is>
       </c>
-      <c r="E6" s="59" t="inlineStr">
+      <c r="E6" s="79" t="inlineStr">
         <is>
           <t>گام ۱: جدول را از پنل برای کانال ۱ بفرست.
 گام ۲: همان جدول را از پنل بخوان و عددها را مقایسه کن.
 گام ۳: با همان کانال یک شارژ واقعی انجام بده.</t>
         </is>
       </c>
-      <c r="F6" s="61" t="inlineStr">
+      <c r="F6" s="81" t="inlineStr">
         <is>
           <t>فرستادن جدول کانال ۱ از پنل</t>
         </is>
       </c>
-      <c r="G6" s="61" t="inlineStr">
+      <c r="G6" s="81" t="inlineStr">
         <is>
           <t>ده دقیقه</t>
         </is>
       </c>
-      <c r="H6" s="59" t="inlineStr">
+      <c r="H6" s="79" t="inlineStr">
         <is>
           <t>جدول درست نشسته (خواندن برعکس همان است) و شارژ کانال ۱ با همان اعداد کار می‌کند</t>
         </is>
       </c>
-      <c r="I6" s="59" t="inlineStr">
+      <c r="I6" s="79" t="inlineStr">
         <is>
           <t>ماندگار</t>
         </is>
       </c>
-      <c r="J6" s="59" t="inlineStr">
+      <c r="J6" s="79" t="inlineStr">
         <is>
           <t>باید ببینید: جدول درست نشسته (بازخوانی همان است) و شارژ کانال ۱ با همان اعداد کار می‌کند. اگر عددی اختلاف داشت یا شارژ خراب بود، قبول نیست.</t>
         </is>
       </c>
-      <c r="K6" s="59" t="inlineStr">
+      <c r="K6" s="79" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
@@ -1249,22 +1284,22 @@
         </is>
       </c>
       <c r="M6" s="59" t="n"/>
-      <c r="N6" s="59" t="inlineStr">
+      <c r="N6" s="79" t="inlineStr">
         <is>
           <t>(بعد از تست پر شود)</t>
         </is>
       </c>
-      <c r="O6" s="61" t="inlineStr">
+      <c r="O6" s="81" t="inlineStr">
         <is>
           <t>(بعد از تست پر شود)</t>
         </is>
       </c>
-      <c r="P6" s="61" t="inlineStr">
+      <c r="P6" s="81" t="inlineStr">
         <is>
           <t>(بعد از تست پر شود)</t>
         </is>
       </c>
-      <c r="Q6" s="62">
+      <c r="Q6" s="82">
         <f>IF(OR(L6="",L6="در انتظار"),"",IF(Q6="",TODAY(),Q6))</f>
         <v/>
       </c>
@@ -1275,53 +1310,53 @@
           <t>CL-003</t>
         </is>
       </c>
-      <c r="B7" s="53" t="inlineStr">
+      <c r="B7" s="59" t="inlineStr">
         <is>
           <t>ماندگاری پس از قطع برق</t>
         </is>
       </c>
-      <c r="C7" s="54" t="inlineStr">
+      <c r="C7" s="60" t="inlineStr">
         <is>
           <t>متوسط</t>
         </is>
       </c>
-      <c r="D7" s="55" t="inlineStr">
+      <c r="D7" s="63" t="inlineStr">
         <is>
           <t>جدول سفارشی را فرستاده‌ای و نشسته است (CL-002)</t>
         </is>
       </c>
-      <c r="E7" s="53" t="inlineStr">
+      <c r="E7" s="59" t="inlineStr">
         <is>
           <t>گام ۱: برق دستگاه را کامل قطع کن و یک دقیقه صبر کن.
 گام ۲: روشن کن و جدول را از پنل دوباره بخوان.</t>
         </is>
       </c>
-      <c r="F7" s="56" t="inlineStr">
+      <c r="F7" s="61" t="inlineStr">
         <is>
           <t>قطع و وصل کامل برق</t>
         </is>
       </c>
-      <c r="G7" s="56" t="inlineStr">
+      <c r="G7" s="61" t="inlineStr">
         <is>
           <t>پنج دقیقه</t>
         </is>
       </c>
-      <c r="H7" s="53" t="inlineStr">
+      <c r="H7" s="59" t="inlineStr">
         <is>
           <t>جدول سفارشی بعد از روشن‌شدن سر جاست</t>
         </is>
       </c>
-      <c r="I7" s="53" t="inlineStr">
+      <c r="I7" s="59" t="inlineStr">
         <is>
           <t>ماندگار در قطع برق</t>
         </is>
       </c>
-      <c r="J7" s="53" t="inlineStr">
+      <c r="J7" s="59" t="inlineStr">
         <is>
           <t>باید ببینید: جدول سفارشی بعد از خاموش و روشن‌کردن سر جاست. اگر پاک شده بود، قبول نیست.</t>
         </is>
       </c>
-      <c r="K7" s="53" t="inlineStr">
+      <c r="K7" s="59" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
@@ -1332,22 +1367,22 @@
         </is>
       </c>
       <c r="M7" s="53" t="n"/>
-      <c r="N7" s="53" t="inlineStr">
+      <c r="N7" s="59" t="inlineStr">
         <is>
           <t>(بعد از تست پر شود)</t>
         </is>
       </c>
-      <c r="O7" s="56" t="inlineStr">
+      <c r="O7" s="61" t="inlineStr">
         <is>
           <t>(بعد از تست پر شود)</t>
         </is>
       </c>
-      <c r="P7" s="56" t="inlineStr">
+      <c r="P7" s="61" t="inlineStr">
         <is>
           <t>(بعد از تست پر شود)</t>
         </is>
       </c>
-      <c r="Q7" s="58">
+      <c r="Q7" s="62">
         <f>IF(OR(L7="",L7="در انتظار"),"",IF(Q7="",TODAY(),Q7))</f>
         <v/>
       </c>
@@ -1358,54 +1393,54 @@
           <t>CL-010</t>
         </is>
       </c>
-      <c r="B8" s="59" t="inlineStr">
+      <c r="B8" s="79" t="inlineStr">
         <is>
           <t>قطع برق وسط نوشتن</t>
         </is>
       </c>
-      <c r="C8" s="60" t="inlineStr">
+      <c r="C8" s="80" t="inlineStr">
         <is>
           <t>متوسط</t>
         </is>
       </c>
-      <c r="D8" s="63" t="inlineStr">
+      <c r="D8" s="83" t="inlineStr">
         <is>
           <t>پنل باز و دستگاه روشن است؛ دستت روی کلید برق دستگاه باشد</t>
         </is>
       </c>
-      <c r="E8" s="63" t="inlineStr">
+      <c r="E8" s="83" t="inlineStr">
         <is>
           <t>گام ۱: فرستادن یک جدول تازه از پنل را شروع کن.
 گام ۲: وسط فرستادن، برق دستگاه را بکش.
 گام ۳: دوباره روشن کن و جدول را بخوان: یا جدول قبلی سالم است یا پیش‌فرض؛ بعد یک شارژ واقعی بگیر.</t>
         </is>
       </c>
-      <c r="F8" s="61" t="inlineStr">
+      <c r="F8" s="81" t="inlineStr">
         <is>
           <t>قطع برق وسط فرستادن جدول</t>
         </is>
       </c>
-      <c r="G8" s="61" t="inlineStr">
+      <c r="G8" s="81" t="inlineStr">
         <is>
           <t>ده دقیقه</t>
         </is>
       </c>
-      <c r="H8" s="59" t="inlineStr">
+      <c r="H8" s="79" t="inlineStr">
         <is>
           <t>جدول نصفه‌نیمه ذخیره نشده؛ شارژ با جدول قبلی یا پیش‌فرض سالم کار می‌کند</t>
         </is>
       </c>
-      <c r="I8" s="59" t="inlineStr">
+      <c r="I8" s="79" t="inlineStr">
         <is>
           <t>بدون جدول خراب</t>
         </is>
       </c>
-      <c r="J8" s="59" t="inlineStr">
+      <c r="J8" s="79" t="inlineStr">
         <is>
           <t>باید ببینید: بعد از قطع برق وسط نوشتن، شارژ با جدول قبلی یا پیش‌فرض سالم کار می‌کند و جدول نصفه ذخیره نشده است. اگر جدول خراب یا شارژ به‌هم‌ریخته بود، قبول نیست.</t>
         </is>
       </c>
-      <c r="K8" s="59" t="inlineStr">
+      <c r="K8" s="79" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
@@ -1416,22 +1451,22 @@
         </is>
       </c>
       <c r="M8" s="59" t="n"/>
-      <c r="N8" s="59" t="inlineStr">
+      <c r="N8" s="79" t="inlineStr">
         <is>
           <t>(بعد از تست پر شود)</t>
         </is>
       </c>
-      <c r="O8" s="61" t="inlineStr">
+      <c r="O8" s="81" t="inlineStr">
         <is>
           <t>(بعد از تست پر شود)</t>
         </is>
       </c>
-      <c r="P8" s="61" t="inlineStr">
+      <c r="P8" s="81" t="inlineStr">
         <is>
           <t>(بعد از تست پر شود)</t>
         </is>
       </c>
-      <c r="Q8" s="62">
+      <c r="Q8" s="82">
         <f>IF(OR(L8="",L8="در انتظار"),"",IF(Q8="",TODAY(),Q8))</f>
         <v/>
       </c>
@@ -1442,54 +1477,54 @@
           <t>CL-011</t>
         </is>
       </c>
-      <c r="B9" s="53" t="inlineStr">
+      <c r="B9" s="59" t="inlineStr">
         <is>
           <t>استقلال از NVM پارامترها</t>
         </is>
       </c>
-      <c r="C9" s="54" t="inlineStr">
+      <c r="C9" s="60" t="inlineStr">
         <is>
           <t>متوسط</t>
         </is>
       </c>
-      <c r="D9" s="53" t="inlineStr">
+      <c r="D9" s="59" t="inlineStr">
         <is>
           <t>جدول سفارشی نشسته و پنل باز است</t>
         </is>
       </c>
-      <c r="E9" s="53" t="inlineStr">
+      <c r="E9" s="59" t="inlineStr">
         <is>
           <t>گام ۱: چند پارامتر معمولی پنل (نه جدولی) را عوض کن.
 گام ۲: برق را قطع و وصل کن.
 گام ۳: جدول را بخوان.</t>
         </is>
       </c>
-      <c r="F9" s="56" t="inlineStr">
+      <c r="F9" s="61" t="inlineStr">
         <is>
           <t>تغییر پارامترهای معمولی و قطع‌ووصل</t>
         </is>
       </c>
-      <c r="G9" s="56" t="inlineStr">
+      <c r="G9" s="61" t="inlineStr">
         <is>
           <t>پنج دقیقه</t>
         </is>
       </c>
-      <c r="H9" s="53" t="inlineStr">
+      <c r="H9" s="59" t="inlineStr">
         <is>
           <t>جدول سفارشی دست‌نخورده مانده است</t>
         </is>
       </c>
-      <c r="I9" s="53" t="inlineStr">
+      <c r="I9" s="59" t="inlineStr">
         <is>
           <t>استقلال جدول از بقیهٔ تنظیم‌ها</t>
         </is>
       </c>
-      <c r="J9" s="53" t="inlineStr">
+      <c r="J9" s="59" t="inlineStr">
         <is>
           <t>باید ببینید: جدول سفارشی دست‌نخورده مانده است. اگر دست خورده بود، قبول نیست.</t>
         </is>
       </c>
-      <c r="K9" s="53" t="inlineStr">
+      <c r="K9" s="59" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
@@ -1500,22 +1535,22 @@
         </is>
       </c>
       <c r="M9" s="53" t="n"/>
-      <c r="N9" s="53" t="inlineStr">
+      <c r="N9" s="59" t="inlineStr">
         <is>
           <t>(بعد از تست پر شود)</t>
         </is>
       </c>
-      <c r="O9" s="56" t="inlineStr">
+      <c r="O9" s="61" t="inlineStr">
         <is>
           <t>(بعد از تست پر شود)</t>
         </is>
       </c>
-      <c r="P9" s="56" t="inlineStr">
+      <c r="P9" s="61" t="inlineStr">
         <is>
           <t>(بعد از تست پر شود)</t>
         </is>
       </c>
-      <c r="Q9" s="58">
+      <c r="Q9" s="62">
         <f>IF(OR(L9="",L9="در انتظار"),"",IF(Q9="",TODAY(),Q9))</f>
         <v/>
       </c>
@@ -1526,53 +1561,53 @@
           <t>CL-014</t>
         </is>
       </c>
-      <c r="B10" s="59" t="inlineStr">
+      <c r="B10" s="79" t="inlineStr">
         <is>
           <t>LUT_READ بازخوانی واقعی هر دو کانال</t>
         </is>
       </c>
-      <c r="C10" s="60" t="inlineStr">
+      <c r="C10" s="80" t="inlineStr">
         <is>
           <t>متوسط</t>
         </is>
       </c>
-      <c r="D10" s="59" t="inlineStr">
+      <c r="D10" s="79" t="inlineStr">
         <is>
           <t>برای هر دو کانال جدول ذخیره کرده‌ای</t>
         </is>
       </c>
-      <c r="E10" s="59" t="inlineStr">
+      <c r="E10" s="79" t="inlineStr">
         <is>
           <t>گام ۱: از پنل جدول هر دو کانال را کامل بخوان.
 گام ۲: عددها را با چیزی که فرستاده بودی مقایسه کن.</t>
         </is>
       </c>
-      <c r="F10" s="61" t="inlineStr">
+      <c r="F10" s="81" t="inlineStr">
         <is>
           <t>خواندن جدول هر دو کانال</t>
         </is>
       </c>
-      <c r="G10" s="61" t="inlineStr">
+      <c r="G10" s="81" t="inlineStr">
         <is>
           <t>پنج دقیقه</t>
         </is>
       </c>
-      <c r="H10" s="59" t="inlineStr">
+      <c r="H10" s="79" t="inlineStr">
         <is>
           <t>هر دو جدول عددبه‌عدد درست و سر جای خودشان‌اند؛ کانال‌ها قاطی نشده‌اند</t>
         </is>
       </c>
-      <c r="I10" s="59" t="inlineStr">
+      <c r="I10" s="79" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J10" s="59" t="inlineStr">
+      <c r="J10" s="79" t="inlineStr">
         <is>
           <t>باید ببینید: هر دو جدول عددبه‌عدد درست و سر جای خودشان‌اند و کانال‌ها قاطی نشده‌اند. اگر قاطی یا ناقص بود، قبول نیست.</t>
         </is>
       </c>
-      <c r="K10" s="59" t="inlineStr">
+      <c r="K10" s="79" t="inlineStr">
         <is>
           <t>تست روی کامپیوتر قبول شد: 159 بررسی. دو فریم واقعی جدول (LUT_DATA) هم بود، باتری ۲ جدا بود و گذر از ناصفر به صفر هم چک شد.
 تست روی برد هنوز انجام نشده است.</t>
@@ -1583,23 +1618,23 @@
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="M10" s="59" t="inlineStr">
+      <c r="M10" s="79" t="inlineStr">
         <is>
           <t>تست روی کامپیوتر جای اندازه‌گیری روی برد را نمی‌گیرد. فلش و خواندن دوبارهٔ جدول باید روی برد واقعی انجام شود.</t>
         </is>
       </c>
-      <c r="N10" s="59" t="inlineStr">
+      <c r="N10" s="79" t="inlineStr">
         <is>
           <t>Firmware/Modules/CalLut/Tester/run_host_test_cal_lut.sh</t>
         </is>
       </c>
-      <c r="O10" s="61" t="inlineStr">
+      <c r="O10" s="81" t="inlineStr">
         <is>
           <t>WORKTREE</t>
         </is>
       </c>
       <c r="P10" s="61" t="n"/>
-      <c r="Q10" s="62">
+      <c r="Q10" s="82">
         <f>IF(OR(L10="",L10="در انتظار"),"",IF(Q10="",TODAY(),Q10))</f>
         <v/>
       </c>
@@ -1610,53 +1645,53 @@
           <t>CL-015</t>
         </is>
       </c>
-      <c r="B11" s="53" t="inlineStr">
+      <c r="B11" s="59" t="inlineStr">
         <is>
           <t>حذف override با صفرنقطه</t>
         </is>
       </c>
-      <c r="C11" s="54" t="inlineStr">
+      <c r="C11" s="60" t="inlineStr">
         <is>
           <t>متوسط</t>
         </is>
       </c>
-      <c r="D11" s="55" t="inlineStr">
+      <c r="D11" s="63" t="inlineStr">
         <is>
           <t>یک کانال جدول سفارشی دارد و با همان شارژ می‌کند.</t>
         </is>
       </c>
-      <c r="E11" s="55" t="inlineStr">
+      <c r="E11" s="63" t="inlineStr">
         <is>
           <t>گام ۱: از پنل، جدول سفارشی همان کانال را با نقطهٔ صفر پاک کن.
 گام ۲: با همان کانال یک شارژ واقعی انجام بده.</t>
         </is>
       </c>
-      <c r="F11" s="56" t="inlineStr">
+      <c r="F11" s="61" t="inlineStr">
         <is>
           <t>پاک‌کردن جدول سفارشی از پنل</t>
         </is>
       </c>
-      <c r="G11" s="56" t="inlineStr">
+      <c r="G11" s="61" t="inlineStr">
         <is>
           <t>ده دقیقه</t>
         </is>
       </c>
-      <c r="H11" s="53" t="inlineStr">
+      <c r="H11" s="59" t="inlineStr">
         <is>
           <t>کانال به رفتار پیش‌فرض کارخانه برمی‌گردد و شارژ عادی می‌شود</t>
         </is>
       </c>
-      <c r="I11" s="53" t="inlineStr">
+      <c r="I11" s="59" t="inlineStr">
         <is>
           <t>برگشت به پیش‌فرض</t>
         </is>
       </c>
-      <c r="J11" s="53" t="inlineStr">
+      <c r="J11" s="59" t="inlineStr">
         <is>
           <t>باید ببینید: کانال به رفتار پیش‌فرض کارخانه برمی‌گردد و شارژ عادی می‌شود. اگر روی جدول پاک‌شده ماند، قبول نیست.</t>
         </is>
       </c>
-      <c r="K11" s="53" t="inlineStr">
+      <c r="K11" s="59" t="inlineStr">
         <is>
           <t>تست روی کامپیوتر قبول شد: 159 بررسی.
 تست روی برد هنوز انجام نشده است.</t>
@@ -1667,23 +1702,23 @@
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="M11" s="53" t="inlineStr">
+      <c r="M11" s="59" t="inlineStr">
         <is>
           <t>تست روی کامپیوتر جای تست برد را نمی‌گیرد. پاک‌شدن جدول سفارشی و ماندنش بعد از ریست باید روی برد واقعی چک شود.</t>
         </is>
       </c>
-      <c r="N11" s="55" t="inlineStr">
+      <c r="N11" s="63" t="inlineStr">
         <is>
           <t>Firmware/Modules/CalLut/Tester/run_host_test_cal_lut.sh؛ esp_link_panel/Tester/host_test_scenario_cards.js</t>
         </is>
       </c>
-      <c r="O11" s="56" t="inlineStr">
+      <c r="O11" s="61" t="inlineStr">
         <is>
           <t>WORKTREE</t>
         </is>
       </c>
       <c r="P11" s="56" t="n"/>
-      <c r="Q11" s="58">
+      <c r="Q11" s="62">
         <f>IF(OR(L11="",L11="در انتظار"),"",IF(Q11="",TODAY(),Q11))</f>
         <v/>
       </c>
@@ -1694,54 +1729,54 @@
           <t>CL-016</t>
         </is>
       </c>
-      <c r="B12" s="59" t="inlineStr">
+      <c r="B12" s="79" t="inlineStr">
         <is>
           <t>reset با grant و flush NVM</t>
         </is>
       </c>
-      <c r="C12" s="60" t="inlineStr">
+      <c r="C12" s="80" t="inlineStr">
         <is>
           <t>متوسط</t>
         </is>
       </c>
-      <c r="D12" s="59" t="inlineStr">
+      <c r="D12" s="79" t="inlineStr">
         <is>
           <t>جدول سفارشی ذخیره است و پنل باز</t>
         </is>
       </c>
-      <c r="E12" s="59" t="inlineStr">
+      <c r="E12" s="79" t="inlineStr">
         <is>
           <t>گام ۱: ریست جدول را از پنل با تأیید انجام بده.
 گام ۲: برق را قطع و وصل کن.
 گام ۳: جدول را بخوان و یک شارژ بگیر.</t>
         </is>
       </c>
-      <c r="F12" s="61" t="inlineStr">
+      <c r="F12" s="81" t="inlineStr">
         <is>
           <t>ریست جدول و قطع‌ووصل برق</t>
         </is>
       </c>
-      <c r="G12" s="61" t="inlineStr">
+      <c r="G12" s="81" t="inlineStr">
         <is>
           <t>ده دقیقه</t>
         </is>
       </c>
-      <c r="H12" s="59" t="inlineStr">
+      <c r="H12" s="79" t="inlineStr">
         <is>
           <t>جدول پاک شده، بعد از روشن‌شدن هم برنمی‌گردد و شارژ پیش‌فرض عادی است</t>
         </is>
       </c>
-      <c r="I12" s="59" t="inlineStr">
+      <c r="I12" s="79" t="inlineStr">
         <is>
           <t>ماندگار</t>
         </is>
       </c>
-      <c r="J12" s="59" t="inlineStr">
+      <c r="J12" s="79" t="inlineStr">
         <is>
           <t>باید ببینید: جدول پاک شده و بعد از روشن‌شدن هم برنمی‌گردد و شارژ پیش‌فرض عادی است. اگر جدول برگشت، قبول نیست.</t>
         </is>
       </c>
-      <c r="K12" s="59" t="inlineStr">
+      <c r="K12" s="79" t="inlineStr">
         <is>
           <t>تست روی کامپیوتر قبول شد: برای CalLut تعداد 159 بررسی، برای پارسر 14 بررسی و برای حافظهٔ ماندگار (NVM) هم قبول شد.
 تست فیزیکی فلش و ریست و باتری هنوز انجام نشده است.</t>
@@ -1752,24 +1787,24 @@
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="M12" s="59" t="inlineStr">
+      <c r="M12" s="79" t="inlineStr">
         <is>
           <t>تست روی کامپیوتر جای تست فیزیکی برد و خطای واقعی حافظه (NVM) را نمی‌گیرد.
 ثبت نقطهٔ صفر، ریست و خالی‌کردن حافظه (flush) باید روی برد واقعی دوباره انجام شود.</t>
         </is>
       </c>
-      <c r="N12" s="63" t="inlineStr">
+      <c r="N12" s="83" t="inlineStr">
         <is>
           <t>Firmware/Modules/CalLut/Tester/run_host_test_cal_lut.sh؛ Firmware/Modules/EspLink/Tester/run_host_test_nvm.sh؛ Firmware/Modules/EspLink/esp_link.c</t>
         </is>
       </c>
-      <c r="O12" s="61" t="inlineStr">
+      <c r="O12" s="81" t="inlineStr">
         <is>
           <t>WORKTREE</t>
         </is>
       </c>
       <c r="P12" s="61" t="n"/>
-      <c r="Q12" s="62">
+      <c r="Q12" s="82">
         <f>IF(OR(L12="",L12="در انتظار"),"",IF(Q12="",TODAY(),Q12))</f>
         <v/>
       </c>
@@ -1780,49 +1815,49 @@
           <t>CL-020</t>
         </is>
       </c>
-      <c r="B13" s="53" t="inlineStr">
+      <c r="B13" s="59" t="inlineStr">
         <is>
           <t>پنل دیالوگ LUT</t>
         </is>
       </c>
-      <c r="C13" s="56" t="inlineStr">
+      <c r="C13" s="61" t="inlineStr">
         <is>
           <t>متوسط</t>
         </is>
       </c>
-      <c r="D13" s="53" t="inlineStr">
+      <c r="D13" s="59" t="inlineStr">
         <is>
           <t>پنل باز و دستگاه روشن است</t>
         </is>
       </c>
-      <c r="E13" s="53" t="inlineStr">
+      <c r="E13" s="59" t="inlineStr">
         <is>
           <t>گام ۱: دیالوگ جدول را در پنل باز کن و یک عدد را عوض کن.
 گام ۲: لغو بزن؛ جدول را بخوان که عوض نشده باشد.
 گام ۳: دوباره عوض کن و این بار تأیید بزن؛ بخوان که نشسته باشد.</t>
         </is>
       </c>
-      <c r="F13" s="56" t="inlineStr">
+      <c r="F13" s="61" t="inlineStr">
         <is>
           <t>لغو و تأیید در دیالوگ جدول پنل</t>
         </is>
       </c>
-      <c r="G13" s="56" t="inlineStr">
+      <c r="G13" s="61" t="inlineStr">
         <is>
           <t>پنج دقیقه</t>
         </is>
       </c>
-      <c r="H13" s="53" t="inlineStr">
+      <c r="H13" s="59" t="inlineStr">
         <is>
           <t>لغو هیچ اثری ندارد و تأیید دقیقاً همان تغییر را می‌نشاند</t>
         </is>
       </c>
-      <c r="I13" s="53" t="inlineStr">
+      <c r="I13" s="59" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J13" s="53" t="inlineStr">
+      <c r="J13" s="59" t="inlineStr">
         <is>
           <t>باید ببینید: لغو هیچ اثری ندارد و تأیید دقیقاً همان تغییر را می‌نشاند. اگر با لغو اعمال شد یا با تأیید گم شد، قبول نیست.</t>
         </is>
@@ -1834,18 +1869,18 @@
         </is>
       </c>
       <c r="M13" s="53" t="n"/>
-      <c r="N13" s="53" t="inlineStr">
+      <c r="N13" s="59" t="inlineStr">
         <is>
           <t>../EspLink/esp_link.c</t>
         </is>
       </c>
-      <c r="O13" s="56" t="inlineStr">
+      <c r="O13" s="61" t="inlineStr">
         <is>
           <t>62f3782</t>
         </is>
       </c>
       <c r="P13" s="56" t="n"/>
-      <c r="Q13" s="58">
+      <c r="Q13" s="62">
         <f>IF(OR(L13="",L13="در انتظار"),"",IF(Q13="",TODAY(),Q13))</f>
         <v/>
       </c>
@@ -2659,7 +2694,7 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="49" t="inlineStr">
+      <c r="A1" s="78" t="inlineStr">
         <is>
           <t>تست‌های آزمایشگاهی (پایه، اسیلوسکوپ و زمان‌بندی دقیق — جدا از تست عملی)</t>
         </is>
@@ -2724,87 +2759,87 @@
       <c r="Q3" s="50" t="n"/>
     </row>
     <row r="4" ht="30" customHeight="1">
-      <c r="A4" s="47" t="inlineStr">
+      <c r="A4" s="77" t="inlineStr">
         <is>
           <t>شناسه</t>
         </is>
       </c>
-      <c r="B4" s="47" t="inlineStr">
+      <c r="B4" s="77" t="inlineStr">
         <is>
           <t>دسته</t>
         </is>
       </c>
-      <c r="C4" s="47" t="inlineStr">
+      <c r="C4" s="77" t="inlineStr">
         <is>
           <t>اولویت</t>
         </is>
       </c>
-      <c r="D4" s="47" t="inlineStr">
+      <c r="D4" s="77" t="inlineStr">
         <is>
           <t>پیش‌شرط</t>
         </is>
       </c>
-      <c r="E4" s="47" t="inlineStr">
+      <c r="E4" s="77" t="inlineStr">
         <is>
           <t>روش اجرای دقیق</t>
         </is>
       </c>
-      <c r="F4" s="47" t="inlineStr">
+      <c r="F4" s="77" t="inlineStr">
         <is>
           <t>ورودی‌ها / شرایط</t>
         </is>
       </c>
-      <c r="G4" s="47" t="inlineStr">
+      <c r="G4" s="77" t="inlineStr">
         <is>
           <t>مدت مشاهده</t>
         </is>
       </c>
-      <c r="H4" s="47" t="inlineStr">
+      <c r="H4" s="77" t="inlineStr">
         <is>
           <t>رفتار مورد انتظار</t>
         </is>
       </c>
-      <c r="I4" s="47" t="inlineStr">
+      <c r="I4" s="77" t="inlineStr">
         <is>
           <t>می‌ماند یا پاک می‌شود</t>
         </is>
       </c>
-      <c r="J4" s="47" t="inlineStr">
+      <c r="J4" s="77" t="inlineStr">
         <is>
           <t>معیار قبولی</t>
         </is>
       </c>
-      <c r="K4" s="47" t="inlineStr">
+      <c r="K4" s="77" t="inlineStr">
         <is>
           <t>نتیجهٔ واقعی / اندازه‌گیری</t>
         </is>
       </c>
-      <c r="L4" s="47" t="inlineStr">
+      <c r="L4" s="77" t="inlineStr">
         <is>
           <t>وضعیت</t>
         </is>
       </c>
-      <c r="M4" s="47" t="inlineStr">
+      <c r="M4" s="77" t="inlineStr">
         <is>
           <t>شرح ایراد / تفاوت</t>
         </is>
       </c>
-      <c r="N4" s="47" t="inlineStr">
+      <c r="N4" s="77" t="inlineStr">
         <is>
           <t>مدرک تست</t>
         </is>
       </c>
-      <c r="O4" s="47" t="inlineStr">
+      <c r="O4" s="77" t="inlineStr">
         <is>
           <t>نسخهٔ برنامه</t>
         </is>
       </c>
-      <c r="P4" s="47" t="inlineStr">
+      <c r="P4" s="77" t="inlineStr">
         <is>
           <t>نام تست‌کننده</t>
         </is>
       </c>
-      <c r="Q4" s="47" t="inlineStr">
+      <c r="Q4" s="77" t="inlineStr">
         <is>
           <t>تاریخ</t>
         </is>
@@ -3366,15 +3401,15 @@
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
-      <c r="A1" s="47" t="inlineStr">
+      <c r="A1" s="84" t="inlineStr">
         <is>
           <t>مرجع سریع سناریوها و ثابت‌های ماژول CalLut</t>
         </is>
       </c>
-      <c r="B1" s="47" t="n"/>
-      <c r="C1" s="47" t="n"/>
-      <c r="D1" s="47" t="n"/>
-      <c r="E1" s="47" t="n"/>
+      <c r="B1" s="77" t="n"/>
+      <c r="C1" s="77" t="n"/>
+      <c r="D1" s="77" t="n"/>
+      <c r="E1" s="77" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="50" t="n"/>
@@ -3634,7 +3669,7 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="70" t="inlineStr">
+      <c r="A1" s="78" t="inlineStr">
         <is>
           <t>ثبت ایرادهای مشاهده‌شده — ماژول CalLut</t>
         </is>
@@ -3653,23 +3688,23 @@
       <c r="M1" s="50" t="n"/>
     </row>
     <row r="2" ht="30" customHeight="1">
-      <c r="A2" s="47" t="inlineStr">
+      <c r="A2" s="77" t="inlineStr">
         <is>
           <t>برای هر وضعیت «رد» یا تفاوت مهم، یک ردیف با شناسهٔ یکتا ثبت و پس از اصلاح دوباره تست شود.</t>
         </is>
       </c>
-      <c r="B2" s="47" t="n"/>
-      <c r="C2" s="47" t="n"/>
-      <c r="D2" s="47" t="n"/>
-      <c r="E2" s="47" t="n"/>
-      <c r="F2" s="47" t="n"/>
-      <c r="G2" s="47" t="n"/>
-      <c r="H2" s="47" t="n"/>
-      <c r="I2" s="47" t="n"/>
-      <c r="J2" s="47" t="n"/>
-      <c r="K2" s="47" t="n"/>
-      <c r="L2" s="47" t="n"/>
-      <c r="M2" s="47" t="n"/>
+      <c r="B2" s="77" t="n"/>
+      <c r="C2" s="77" t="n"/>
+      <c r="D2" s="77" t="n"/>
+      <c r="E2" s="77" t="n"/>
+      <c r="F2" s="77" t="n"/>
+      <c r="G2" s="77" t="n"/>
+      <c r="H2" s="77" t="n"/>
+      <c r="I2" s="77" t="n"/>
+      <c r="J2" s="77" t="n"/>
+      <c r="K2" s="77" t="n"/>
+      <c r="L2" s="77" t="n"/>
+      <c r="M2" s="77" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="67" t="inlineStr">
@@ -3759,7 +3794,7 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="45" t="inlineStr">
+      <c r="A1" s="76" t="inlineStr">
         <is>
           <t>تأیید نهایی اعتبارسنجی — ماژول CalLut</t>
         </is>
@@ -3997,7 +4032,7 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <tabColor rgb="00808080"/>
+    <tabColor rgb="00A6A6A6"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
@@ -4104,98 +4139,7 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <tabColor rgb="007030A0"/>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:C6"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="34" customWidth="1" min="1" max="1"/>
-    <col width="78" customWidth="1" min="2" max="2"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="30" customHeight="1">
-      <c r="A1" s="10" t="inlineStr">
-        <is>
-          <t>ماشین حالت ماژول جدول کالیبراسیون (CalLut)</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="50" t="n"/>
-      <c r="B2" s="50" t="n"/>
-      <c r="C2" s="50" t="n"/>
-    </row>
-    <row r="3" ht="24" customHeight="1">
-      <c r="A3" s="11" t="inlineStr">
-        <is>
-          <t>حالت‌ها و گذارهای همین ماژول</t>
-        </is>
-      </c>
-      <c r="B3" s="12" t="inlineStr">
-        <is>
-          <t>CalLut_State_Machine.xlsx</t>
-        </is>
-      </c>
-      <c r="C3" s="50" t="n"/>
-    </row>
-    <row r="4" ht="24" customHeight="1">
-      <c r="A4" s="11" t="inlineStr">
-        <is>
-          <t>ماشین حالت کل برنامه (نمای سیستمی)</t>
-        </is>
-      </c>
-      <c r="B4" s="12" t="inlineStr">
-        <is>
-          <t>../../../Documentation/System_State_Machine.xlsx</t>
-        </is>
-      </c>
-      <c r="C4" s="50" t="n"/>
-    </row>
-    <row r="5" ht="24" customHeight="1">
-      <c r="A5" s="11" t="inlineStr">
-        <is>
-          <t>راهنمای رنگ‌ها</t>
-        </is>
-      </c>
-      <c r="B5" s="13" t="inlineStr">
-        <is>
-          <t>سبز = عادی/سالم · زرد = هشدار یا انتظار · قرمز = خطا یا قفل · نارنجی = در حال کار · خاکستری = بی‌کار · آبی = اطلاعاتی</t>
-        </is>
-      </c>
-      <c r="C5" s="50" t="n"/>
-    </row>
-    <row r="6" ht="24" customHeight="1">
-      <c r="A6" s="11" t="inlineStr">
-        <is>
-          <t>بازتولید</t>
-        </is>
-      </c>
-      <c r="B6" s="12" t="inlineStr">
-        <is>
-          <t>python3 tools/make_module_state_machines.py</t>
-        </is>
-      </c>
-      <c r="C6" s="50" t="n"/>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:C1"/>
-  </mergeCells>
-  <hyperlinks>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B3" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B4" r:id="rId2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B6" r:id="rId3"/>
-  </hyperlinks>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <tabColor rgb="001F4E79"/>
+    <tabColor rgb="00385723"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
@@ -4222,7 +4166,7 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="49" t="inlineStr">
+      <c r="A1" s="78" t="inlineStr">
         <is>
           <t>برنامهٔ تست برنامه‌نویسی — ماژول CalLut</t>
         </is>
@@ -4291,87 +4235,87 @@
       <c r="Q3" s="50" t="n"/>
     </row>
     <row r="4" ht="30" customHeight="1">
-      <c r="A4" s="47" t="inlineStr">
+      <c r="A4" s="77" t="inlineStr">
         <is>
           <t>شناسه</t>
         </is>
       </c>
-      <c r="B4" s="47" t="inlineStr">
+      <c r="B4" s="77" t="inlineStr">
         <is>
           <t>دسته</t>
         </is>
       </c>
-      <c r="C4" s="47" t="inlineStr">
+      <c r="C4" s="77" t="inlineStr">
         <is>
           <t>اولویت</t>
         </is>
       </c>
-      <c r="D4" s="47" t="inlineStr">
+      <c r="D4" s="77" t="inlineStr">
         <is>
           <t>پیش‌شرط</t>
         </is>
       </c>
-      <c r="E4" s="47" t="inlineStr">
+      <c r="E4" s="77" t="inlineStr">
         <is>
           <t>روش اجرای دقیق</t>
         </is>
       </c>
-      <c r="F4" s="47" t="inlineStr">
+      <c r="F4" s="77" t="inlineStr">
         <is>
           <t>ورودی‌ها / شرایط</t>
         </is>
       </c>
-      <c r="G4" s="47" t="inlineStr">
+      <c r="G4" s="77" t="inlineStr">
         <is>
           <t>مدت مشاهده</t>
         </is>
       </c>
-      <c r="H4" s="47" t="inlineStr">
+      <c r="H4" s="77" t="inlineStr">
         <is>
           <t>رفتار مورد انتظار</t>
         </is>
       </c>
-      <c r="I4" s="47" t="inlineStr">
+      <c r="I4" s="77" t="inlineStr">
         <is>
           <t>می‌ماند یا پاک می‌شود</t>
         </is>
       </c>
-      <c r="J4" s="47" t="inlineStr">
+      <c r="J4" s="77" t="inlineStr">
         <is>
           <t>معیار قبولی</t>
         </is>
       </c>
-      <c r="K4" s="47" t="inlineStr">
+      <c r="K4" s="77" t="inlineStr">
         <is>
           <t>نتیجهٔ واقعی / اندازه‌گیری</t>
         </is>
       </c>
-      <c r="L4" s="47" t="inlineStr">
+      <c r="L4" s="77" t="inlineStr">
         <is>
           <t>وضعیت</t>
         </is>
       </c>
-      <c r="M4" s="47" t="inlineStr">
+      <c r="M4" s="77" t="inlineStr">
         <is>
           <t>شرح ایراد / تفاوت</t>
         </is>
       </c>
-      <c r="N4" s="47" t="inlineStr">
+      <c r="N4" s="77" t="inlineStr">
         <is>
           <t>مدرک تست</t>
         </is>
       </c>
-      <c r="O4" s="47" t="inlineStr">
+      <c r="O4" s="77" t="inlineStr">
         <is>
           <t>نسخهٔ برنامه</t>
         </is>
       </c>
-      <c r="P4" s="47" t="inlineStr">
+      <c r="P4" s="77" t="inlineStr">
         <is>
           <t>نام تست‌کننده</t>
         </is>
       </c>
-      <c r="Q4" s="47" t="inlineStr">
+      <c r="Q4" s="77" t="inlineStr">
         <is>
           <t>تاریخ</t>
         </is>
@@ -4468,22 +4412,22 @@
           <t>CL-005</t>
         </is>
       </c>
-      <c r="B6" s="53" t="inlineStr">
+      <c r="B6" s="79" t="inlineStr">
         <is>
           <t>محور صعودی نبودن</t>
         </is>
       </c>
-      <c r="C6" s="54" t="inlineStr">
+      <c r="C6" s="80" t="inlineStr">
         <is>
           <t>بالا</t>
         </is>
       </c>
-      <c r="D6" s="53" t="inlineStr">
+      <c r="D6" s="79" t="inlineStr">
         <is>
           <t>لینک برقرار</t>
         </is>
       </c>
-      <c r="E6" s="53" t="inlineStr">
+      <c r="E6" s="79" t="inlineStr">
         <is>
           <t>گام ۱: لینک ESP را وصل کن.
 گام ۲: جدولی بساز که محور زنجیره‌اش (ChainMa) صعودیِ اکید نباشد؛ مثلاً یک نقطهٔ تکراری یا یک نقطه کمتر از قبلی بگذار.
@@ -4491,32 +4435,32 @@
 گام ۴: پاسخ برد را بخوان: وضعیت باید 4 باشد (CAL_LUT_ST_CHAIN) و جدول نباید فعال شود.</t>
         </is>
       </c>
-      <c r="F6" s="56" t="inlineStr">
+      <c r="F6" s="81" t="inlineStr">
         <is>
           <t>نقطهٔ تکراری یا نزولی در ChainMa</t>
         </is>
       </c>
-      <c r="G6" s="56" t="inlineStr">
+      <c r="G6" s="81" t="inlineStr">
         <is>
           <t>یک تبادل</t>
         </is>
       </c>
-      <c r="H6" s="53" t="inlineStr">
+      <c r="H6" s="79" t="inlineStr">
         <is>
           <t>رد با CAL_LUT_ST_CHAIN</t>
         </is>
       </c>
-      <c r="I6" s="53" t="inlineStr">
+      <c r="I6" s="79" t="inlineStr">
         <is>
           <t>بدون تغییر فلش</t>
         </is>
       </c>
-      <c r="J6" s="53" t="inlineStr">
+      <c r="J6" s="79" t="inlineStr">
         <is>
           <t>status=4</t>
         </is>
       </c>
-      <c r="K6" s="53" t="inlineStr">
+      <c r="K6" s="79" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
@@ -4527,22 +4471,22 @@
         </is>
       </c>
       <c r="M6" s="53" t="n"/>
-      <c r="N6" s="53" t="inlineStr">
+      <c r="N6" s="79" t="inlineStr">
         <is>
           <t>(بعد از تست پر شود)</t>
         </is>
       </c>
-      <c r="O6" s="56" t="inlineStr">
+      <c r="O6" s="81" t="inlineStr">
         <is>
           <t>(بعد از تست پر شود)</t>
         </is>
       </c>
-      <c r="P6" s="56" t="inlineStr">
+      <c r="P6" s="81" t="inlineStr">
         <is>
           <t>(بعد از تست پر شود)</t>
         </is>
       </c>
-      <c r="Q6" s="58">
+      <c r="Q6" s="82">
         <f>IF(OR(L6="",L6="در انتظار"),"",IF(Q6="",TODAY(),Q6))</f>
         <v/>
       </c>
@@ -4638,22 +4582,22 @@
           <t>CL-007</t>
         </is>
       </c>
-      <c r="B8" s="53" t="inlineStr">
+      <c r="B8" s="79" t="inlineStr">
         <is>
           <t>تعداد نقاط نامعتبر</t>
         </is>
       </c>
-      <c r="C8" s="56" t="inlineStr">
+      <c r="C8" s="81" t="inlineStr">
         <is>
           <t>متوسط</t>
         </is>
       </c>
-      <c r="D8" s="53" t="inlineStr">
+      <c r="D8" s="79" t="inlineStr">
         <is>
           <t>لینک برقرار</t>
         </is>
       </c>
-      <c r="E8" s="53" t="inlineStr">
+      <c r="E8" s="79" t="inlineStr">
         <is>
           <t>گام ۱: لینک ESP را وصل کن.
 گام ۲: یک جدول فقط با 1 نقطه بفرست و COMMIT کن؛ پاسخ را بخوان.
@@ -4661,32 +4605,32 @@
 گام ۴: هر دو بار وضعیت باید 2 باشد (CAL_LUT_ST_COUNT)، چون تعداد نقطهٔ مجاز 2 تا 24 است.</t>
         </is>
       </c>
-      <c r="F8" s="56" t="inlineStr">
+      <c r="F8" s="81" t="inlineStr">
         <is>
           <t>points &lt; 2 یا &gt; 24</t>
         </is>
       </c>
-      <c r="G8" s="56" t="inlineStr">
+      <c r="G8" s="81" t="inlineStr">
         <is>
           <t>دو تبادل</t>
         </is>
       </c>
-      <c r="H8" s="53" t="inlineStr">
+      <c r="H8" s="79" t="inlineStr">
         <is>
           <t>هر دو با CAL_LUT_ST_COUNT رد می‌شوند</t>
         </is>
       </c>
-      <c r="I8" s="53" t="inlineStr">
+      <c r="I8" s="79" t="inlineStr">
         <is>
           <t>بدون تغییر فلش</t>
         </is>
       </c>
-      <c r="J8" s="53" t="inlineStr">
+      <c r="J8" s="79" t="inlineStr">
         <is>
           <t>status=2 در هر دو</t>
         </is>
       </c>
-      <c r="K8" s="53" t="inlineStr">
+      <c r="K8" s="79" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
@@ -4697,22 +4641,22 @@
         </is>
       </c>
       <c r="M8" s="53" t="n"/>
-      <c r="N8" s="53" t="inlineStr">
+      <c r="N8" s="79" t="inlineStr">
         <is>
           <t>(بعد از تست پر شود)</t>
         </is>
       </c>
-      <c r="O8" s="56" t="inlineStr">
+      <c r="O8" s="81" t="inlineStr">
         <is>
           <t>(بعد از تست پر شود)</t>
         </is>
       </c>
-      <c r="P8" s="56" t="inlineStr">
+      <c r="P8" s="81" t="inlineStr">
         <is>
           <t>(بعد از تست پر شود)</t>
         </is>
       </c>
-      <c r="Q8" s="58">
+      <c r="Q8" s="82">
         <f>IF(OR(L8="",L8="در انتظار"),"",IF(Q8="",TODAY(),Q8))</f>
         <v/>
       </c>
@@ -4808,54 +4752,54 @@
           <t>CL-009</t>
         </is>
       </c>
-      <c r="B10" s="53" t="inlineStr">
+      <c r="B10" s="79" t="inlineStr">
         <is>
           <t>commit بدون begin</t>
         </is>
       </c>
-      <c r="C10" s="56" t="inlineStr">
+      <c r="C10" s="81" t="inlineStr">
         <is>
           <t>پایین</t>
         </is>
       </c>
-      <c r="D10" s="53" t="inlineStr">
+      <c r="D10" s="79" t="inlineStr">
         <is>
           <t>لینک برقرار</t>
         </is>
       </c>
-      <c r="E10" s="53" t="inlineStr">
+      <c r="E10" s="79" t="inlineStr">
         <is>
           <t>گام ۱: لینک ESP را وصل کن.
 گام ۲: بدون اینکه LUT_BEGIN بفرستی، مستقیم COMMIT بفرست.
 گام ۳: پاسخ برد را بخوان: وضعیت باید 1 باشد (CAL_LUT_ST_NO_STAGE) و هیچ اتفاقی برای جدول فعال نیفتد.</t>
         </is>
       </c>
-      <c r="F10" s="56" t="inlineStr">
+      <c r="F10" s="81" t="inlineStr">
         <is>
           <t>بدون مرحلهٔ چیدن</t>
         </is>
       </c>
-      <c r="G10" s="56" t="inlineStr">
+      <c r="G10" s="81" t="inlineStr">
         <is>
           <t>یک تبادل</t>
         </is>
       </c>
-      <c r="H10" s="53" t="inlineStr">
+      <c r="H10" s="79" t="inlineStr">
         <is>
           <t>رد با CAL_LUT_ST_NO_STAGE</t>
         </is>
       </c>
-      <c r="I10" s="53" t="inlineStr">
+      <c r="I10" s="79" t="inlineStr">
         <is>
           <t>بدون تغییر فلش</t>
         </is>
       </c>
-      <c r="J10" s="53" t="inlineStr">
+      <c r="J10" s="79" t="inlineStr">
         <is>
           <t>status=1</t>
         </is>
       </c>
-      <c r="K10" s="53" t="inlineStr">
+      <c r="K10" s="79" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
@@ -4866,22 +4810,22 @@
         </is>
       </c>
       <c r="M10" s="53" t="n"/>
-      <c r="N10" s="53" t="inlineStr">
+      <c r="N10" s="79" t="inlineStr">
         <is>
           <t>(بعد از تست پر شود)</t>
         </is>
       </c>
-      <c r="O10" s="56" t="inlineStr">
+      <c r="O10" s="81" t="inlineStr">
         <is>
           <t>(بعد از تست پر شود)</t>
         </is>
       </c>
-      <c r="P10" s="56" t="inlineStr">
+      <c r="P10" s="81" t="inlineStr">
         <is>
           <t>(بعد از تست پر شود)</t>
         </is>
       </c>
-      <c r="Q10" s="58">
+      <c r="Q10" s="82">
         <f>IF(OR(L10="",L10="در انتظار"),"",IF(Q10="",TODAY(),Q10))</f>
         <v/>
       </c>
@@ -4892,22 +4836,22 @@
           <t>CL-013</t>
         </is>
       </c>
-      <c r="B11" s="53" t="inlineStr">
+      <c r="B11" s="59" t="inlineStr">
         <is>
           <t>تغییر نسخهٔ قالب</t>
         </is>
       </c>
-      <c r="C11" s="56" t="inlineStr">
+      <c r="C11" s="61" t="inlineStr">
         <is>
           <t>پایین</t>
         </is>
       </c>
-      <c r="D11" s="53" t="inlineStr">
+      <c r="D11" s="59" t="inlineStr">
         <is>
           <t>رکورد معتبر نسخهٔ ۱</t>
         </is>
       </c>
-      <c r="E11" s="53" t="inlineStr">
+      <c r="E11" s="59" t="inlineStr">
         <is>
           <t>گام ۱: روی برد یک رکورد LUT معتبر با نسخهٔ 1 داشته باش (قبلاً commit شده باشد).
 گام ۲: ثابت CAL_LUT_VERSION را در کد بالا ببر و فرم‌ور جدید را روی همان برد فلش کن.
@@ -4915,32 +4859,32 @@
 گام ۴: باید جدول فعال نباشد (Active = false) و خوانش جریان به جدول کامپایل‌شده (خط گین و آفست) برگشته باشد.</t>
         </is>
       </c>
-      <c r="F11" s="56" t="inlineStr">
+      <c r="F11" s="61" t="inlineStr">
         <is>
           <t>نسخهٔ رکورد قدیمی</t>
         </is>
       </c>
-      <c r="G11" s="56" t="inlineStr">
+      <c r="G11" s="61" t="inlineStr">
         <is>
           <t>یک بوت</t>
         </is>
       </c>
-      <c r="H11" s="53" t="inlineStr">
+      <c r="H11" s="59" t="inlineStr">
         <is>
           <t>رکورد قدیمی نامعتبر و بازگشت به جدول کامپایل‌شده</t>
         </is>
       </c>
-      <c r="I11" s="53" t="inlineStr">
+      <c r="I11" s="59" t="inlineStr">
         <is>
           <t>بدون نیم‌ارتقای بی‌صدا</t>
         </is>
       </c>
-      <c r="J11" s="53" t="inlineStr">
+      <c r="J11" s="59" t="inlineStr">
         <is>
           <t>Active=false و خوانش‌ها برابر خط گین و آفست</t>
         </is>
       </c>
-      <c r="K11" s="53" t="inlineStr">
+      <c r="K11" s="59" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
@@ -4951,22 +4895,22 @@
         </is>
       </c>
       <c r="M11" s="53" t="n"/>
-      <c r="N11" s="53" t="inlineStr">
+      <c r="N11" s="59" t="inlineStr">
         <is>
           <t>(بعد از تست پر شود)</t>
         </is>
       </c>
-      <c r="O11" s="56" t="inlineStr">
+      <c r="O11" s="61" t="inlineStr">
         <is>
           <t>(بعد از تست پر شود)</t>
         </is>
       </c>
-      <c r="P11" s="56" t="inlineStr">
+      <c r="P11" s="61" t="inlineStr">
         <is>
           <t>(بعد از تست پر شود)</t>
         </is>
       </c>
-      <c r="Q11" s="58">
+      <c r="Q11" s="62">
         <f>IF(OR(L11="",L11="در انتظار"),"",IF(Q11="",TODAY(),Q11))</f>
         <v/>
       </c>
@@ -4985,4 +4929,87 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="007030A0"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="34" customWidth="1" min="1" max="1"/>
+    <col width="78" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="30" customHeight="1">
+      <c r="A1" s="10" t="inlineStr">
+        <is>
+          <t>ماشین حالت ماژول جدول کالیبراسیون (CalLut)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2"/>
+    <row r="3" ht="24" customHeight="1">
+      <c r="A3" s="11" t="inlineStr">
+        <is>
+          <t>حالت‌ها و گذارهای همین ماژول</t>
+        </is>
+      </c>
+      <c r="B3" s="12" t="inlineStr">
+        <is>
+          <t>CalLut_State_Machine.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="24" customHeight="1">
+      <c r="A4" s="11" t="inlineStr">
+        <is>
+          <t>ماشین حالت کل برنامه (نمای سیستمی)</t>
+        </is>
+      </c>
+      <c r="B4" s="12" t="inlineStr">
+        <is>
+          <t>../../../Documentation/System_State_Machine.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="24" customHeight="1">
+      <c r="A5" s="11" t="inlineStr">
+        <is>
+          <t>راهنمای رنگ‌ها</t>
+        </is>
+      </c>
+      <c r="B5" s="13" t="inlineStr">
+        <is>
+          <t>سبز = عادی/سالم · زرد = هشدار یا انتظار · قرمز = خطا یا قفل · نارنجی = در حال کار · خاکستری = بی‌کار · آبی = اطلاعاتی</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="24" customHeight="1">
+      <c r="A6" s="11" t="inlineStr">
+        <is>
+          <t>بازتولید</t>
+        </is>
+      </c>
+      <c r="B6" s="13" t="inlineStr">
+        <is>
+          <t>python3 tools/make_module_state_machines.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="7"/>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:C1"/>
+  </mergeCells>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B3" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B4" r:id="rId2"/>
+  </hyperlinks>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/Firmware/Modules/CalLut/CalLut_Validation.xlsx
+++ b/Firmware/Modules/CalLut/CalLut_Validation.xlsx
@@ -32,7 +32,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
   </numFmts>
-  <fonts count="27">
+  <fonts count="30">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -175,8 +175,24 @@
       <name val="Vazirmatn"/>
       <sz val="11"/>
     </font>
+    <font>
+      <name val="Vazirmatn"/>
+      <color rgb="00808080"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Vazirmatn"/>
+      <b val="1"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Vazirmatn"/>
+      <i val="1"/>
+      <color rgb="00404040"/>
+      <sz val="10"/>
+    </font>
   </fonts>
-  <fills count="10">
+  <fills count="11">
     <fill>
       <patternFill/>
     </fill>
@@ -223,6 +239,11 @@
         <fgColor rgb="00FFFFFF"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF2CC"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="4">
     <border>
@@ -265,7 +286,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="85">
+  <cellXfs count="92">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -482,6 +503,27 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="8" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="10" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -849,7 +891,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A12"/>
+  <dimension ref="A1:B14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="120" customWidth="1" min="1" max="1"/>
@@ -931,7 +973,6 @@
         </is>
       </c>
     </row>
-    <row r="11"/>
     <row r="12">
       <c r="A12" s="73" t="inlineStr">
         <is>
@@ -941,6 +982,18 @@
 «پایین» یعنی ریزه‌کاری‌ها؛ مثل اثر نوسان کوچک روی ریتم چشمک.
 در ستون «چه چیزی باید ببینید تا بگویید درست است» نوشته‌ایم دقیقاً چه باید ببینی یا بشنوی.
 اگر چیز دیگری دیدی، وضعیت را «رد» بزن و در «شرح ایراد» بنویس چه دیدی.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="85" t="inlineStr">
+        <is>
+          <t>پیش‌بینی زندهٔ برنامه</t>
+        </is>
+      </c>
+      <c r="B14" s="86" t="inlineStr">
+        <is>
+          <t>در شیت «برنامه تست»، ستون آخر («پیش‌بینی زندهٔ برنامه») با فرمول اکسل حساب می‌کند که برنامهٔ روی برد با ورودی‌های فعلی چه کار می‌کند. ورودی‌ها خانه‌های زرد بالای همان شیت‌اند؛ عددشان را عوض کن، نتیجه را بخوان و با رفتار واقعی برد مقایسه کن. هر جا «—» است، آن تست پیش‌بینی فرمولی ندارد (مثل دیالوگ پنل یا تست‌های حافظه).</t>
         </is>
       </c>
     </row>
@@ -959,7 +1012,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:Q53"/>
+  <dimension ref="A1:U53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -979,9 +1032,12 @@
     <col width="12" customWidth="1" min="15" max="15"/>
     <col width="13" customWidth="1" min="16" max="16"/>
     <col width="12" customWidth="1" min="17" max="17"/>
+    <col width="52" customWidth="1" min="18" max="18"/>
+    <col width="34" customWidth="1" min="20" max="20"/>
+    <col width="14" customWidth="1" min="21" max="21"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="30" customHeight="1">
       <c r="A1" s="78" t="inlineStr">
         <is>
           <t>برنامهٔ تست عملی — ماژول CalLut</t>
@@ -1003,6 +1059,11 @@
       <c r="O1" s="50" t="n"/>
       <c r="P1" s="50" t="n"/>
       <c r="Q1" s="50" t="n"/>
+      <c r="T1" s="87" t="inlineStr">
+        <is>
+          <t>ورودی‌های پیش‌بینی — خانه‌های زرد را عوض کن و ستون «پیش‌بینی زنده» را ببین</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="51" t="inlineStr">
@@ -1026,6 +1087,14 @@
       <c r="O2" s="50" t="n"/>
       <c r="P2" s="50" t="n"/>
       <c r="Q2" s="50" t="n"/>
+      <c r="T2" s="88" t="inlineStr">
+        <is>
+          <t>مقدار خام</t>
+        </is>
+      </c>
+      <c r="U2" s="89" t="n">
+        <v>1000</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="51" t="inlineStr">
@@ -1049,6 +1118,14 @@
       <c r="O3" s="50" t="n"/>
       <c r="P3" s="50" t="n"/>
       <c r="Q3" s="50" t="n"/>
+      <c r="T3" s="88" t="inlineStr">
+        <is>
+          <t>گین (پیش‌فرض 3000)</t>
+        </is>
+      </c>
+      <c r="U3" s="89" t="n">
+        <v>3000</v>
+      </c>
     </row>
     <row r="4" ht="30" customHeight="1">
       <c r="A4" s="77" t="inlineStr">
@@ -1135,6 +1212,19 @@
         <is>
           <t>تاریخ</t>
         </is>
+      </c>
+      <c r="R4" s="77" t="inlineStr">
+        <is>
+          <t>پیش‌بینی زندهٔ برنامه (فرمول)</t>
+        </is>
+      </c>
+      <c r="T4" s="88" t="inlineStr">
+        <is>
+          <t>آفست (پیش‌فرض 0)</t>
+        </is>
+      </c>
+      <c r="U4" s="89" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="5" ht="54" customHeight="1">
@@ -1219,6 +1309,15 @@
         <f>IF(OR(L5="",L5="در انتظار"),"",IF(Q5="",TODAY(),Q5))</f>
         <v/>
       </c>
+      <c r="R5" s="86">
+        <f>"خروجی با خط پیش‌فرض کارخانه: "&amp;TEXT($U$2*$U$3/3000+$U$4,"0")&amp;" (بدون رکورد در فلش، همین خط کار می‌کند)"</f>
+        <v/>
+      </c>
+      <c r="T5" s="90" t="inlineStr">
+        <is>
+          <t>پیش‌بینی برای حالت پایدار است؛ چشمک و زمان‌بندی را با چشم و کرنومتر چک کن و با برد مقایسه کن.</t>
+        </is>
+      </c>
     </row>
     <row r="6" ht="67.5" customHeight="1">
       <c r="A6" s="52" t="inlineStr">
@@ -1303,6 +1402,11 @@
         <f>IF(OR(L6="",L6="در انتظار"),"",IF(Q6="",TODAY(),Q6))</f>
         <v/>
       </c>
+      <c r="R6" s="91" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
     </row>
     <row r="7" ht="54" customHeight="1">
       <c r="A7" s="52" t="inlineStr">
@@ -1386,6 +1490,11 @@
         <f>IF(OR(L7="",L7="در انتظار"),"",IF(Q7="",TODAY(),Q7))</f>
         <v/>
       </c>
+      <c r="R7" s="91" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
     </row>
     <row r="8" ht="54" customHeight="1">
       <c r="A8" s="52" t="inlineStr">
@@ -1470,6 +1579,11 @@
         <f>IF(OR(L8="",L8="در انتظار"),"",IF(Q8="",TODAY(),Q8))</f>
         <v/>
       </c>
+      <c r="R8" s="91" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
     </row>
     <row r="9" ht="54" customHeight="1">
       <c r="A9" s="52" t="inlineStr">
@@ -1553,6 +1667,11 @@
       <c r="Q9" s="62">
         <f>IF(OR(L9="",L9="در انتظار"),"",IF(Q9="",TODAY(),Q9))</f>
         <v/>
+      </c>
+      <c r="R9" s="91" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
     </row>
     <row r="10" ht="54" customHeight="1">
@@ -1638,6 +1757,11 @@
         <f>IF(OR(L10="",L10="در انتظار"),"",IF(Q10="",TODAY(),Q10))</f>
         <v/>
       </c>
+      <c r="R10" s="91" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
     </row>
     <row r="11" ht="54" customHeight="1">
       <c r="A11" s="52" t="inlineStr">
@@ -1722,6 +1846,11 @@
         <f>IF(OR(L11="",L11="در انتظار"),"",IF(Q11="",TODAY(),Q11))</f>
         <v/>
       </c>
+      <c r="R11" s="91" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
     </row>
     <row r="12" ht="54" customHeight="1">
       <c r="A12" s="52" t="inlineStr">
@@ -1808,6 +1937,11 @@
         <f>IF(OR(L12="",L12="در انتظار"),"",IF(Q12="",TODAY(),Q12))</f>
         <v/>
       </c>
+      <c r="R12" s="91" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
     </row>
     <row r="13" ht="40.5" customHeight="1">
       <c r="A13" s="52" t="inlineStr">
@@ -1883,6 +2017,11 @@
       <c r="Q13" s="62">
         <f>IF(OR(L13="",L13="در انتظار"),"",IF(Q13="",TODAY(),Q13))</f>
         <v/>
+      </c>
+      <c r="R13" s="91" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
     </row>
     <row r="14">
@@ -2647,6 +2786,10 @@
     </row>
   </sheetData>
   <autoFilter ref="A4:Q60"/>
+  <mergeCells count="2">
+    <mergeCell ref="T1:U1"/>
+    <mergeCell ref="T5:U5"/>
+  </mergeCells>
   <dataValidations count="2">
     <dataValidation sqref="C5:C13" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>='فهرست‌ها'!$B$9:$B$11</formula1>
@@ -4938,7 +5081,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C7"/>
+  <dimension ref="A1:C6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -4952,7 +5095,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3" ht="24" customHeight="1">
       <c r="A3" s="11" t="inlineStr">
         <is>
@@ -5001,7 +5143,6 @@
         </is>
       </c>
     </row>
-    <row r="7"/>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:C1"/>

--- a/Firmware/Modules/CalLut/CalLut_Validation.xlsx
+++ b/Firmware/Modules/CalLut/CalLut_Validation.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="راهنما" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="برنامه تست" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="تست‌های آزمایشگاهی" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="مراجع سناریو" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="ثبت ایراد" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="تأیید نهایی" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="فهرست‌ها" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="تست‌های برنامه‌نویسی" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="ماشین حالت" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="راهنما" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="برنامه تست" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="تست‌های آزمایشگاهی" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="مراجع سناریو" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ثبت ایراد" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="تأیید نهایی" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="فهرست‌ها" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="تست‌های برنامه‌نویسی" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ماشین حالت" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'برنامه تست'!$A$4:$Q$60</definedName>
